--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -9133,48 +9133,72 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B142" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C142" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D142" s="1" t="inlineStr"/>
-      <c r="E142" s="1" t="inlineStr"/>
-      <c r="F142" s="1" t="inlineStr"/>
-      <c r="G142" s="1" t="inlineStr"/>
-      <c r="H142" s="1" t="inlineStr"/>
-      <c r="I142" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J142" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="K142" s="1" t="inlineStr"/>
-      <c r="L142" s="1" t="inlineStr"/>
-      <c r="M142" s="1" t="inlineStr"/>
-      <c r="N142" s="1" t="inlineStr"/>
-      <c r="O142" s="1" t="inlineStr"/>
-      <c r="P142" s="1" t="inlineStr"/>
-      <c r="Q142" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R142" s="1" t="inlineStr">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Maksymovych</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Via della Portella, 31</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>06/5576474</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>www.maksymovychristorante.it</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>maksymovych.ristorante</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>maksymovych_ristorante</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (maksymovych.ristorante) | IG: trovato (maksymovych_ristorante)</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
@@ -9183,32 +9207,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Maksymovych</t>
+          <t>Mamma Angelina</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Via della Portella, 31</t>
+          <t>Viale Arrigo Boito, 65</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>06/5576474</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>www.maksymovychristorante.it</t>
+          <t>06/8608928</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>maksymovych.ristorante</t>
+          <t>Mamma-Angelina-163636110315582</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>maksymovych_ristorante</t>
+          <t>Mamma-Angelina</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -9233,7 +9252,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -9243,7 +9262,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (maksymovych.ristorante) | IG: trovato (maksymovych_ristorante)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (Mamma-Angelina-163636110315582) | IG: trovato (Mamma-Angelina)</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -9255,27 +9274,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Mamma Angelina</t>
+          <t>Mamma Orso</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Viale Arrigo Boito, 65</t>
+          <t>Via Arezzo, 17</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>06/8608928</t>
+          <t>06/97277922</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mamma-Angelina-163636110315582</t>
+          <t>mammaorsoroma</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mamma-Angelina</t>
+          <t>ristorantemammaorso</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -9300,7 +9319,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
+          <t>{'lunedì': {'opens': '19', 'closes': '23:30'}, 'martedì': {'opens': '19', 'close</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -9310,7 +9329,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (Mamma-Angelina-163636110315582) | IG: trovato (Mamma-Angelina)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (mammaorsoroma) | IG: trovato (ristorantemammaorso)</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -9322,37 +9341,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mamma Orso</t>
+          <t>Mangiafuoco</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Via Arezzo, 17</t>
+          <t>Via Cicerone, 40</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>06/97277922</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>mammaorsoroma</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>ristorantemammaorso</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/9411904</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9367,17 +9366,12 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '19', 'closes': '23:30'}, 'martedì': {'opens': '19', 'close</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15, 00', 'break': '15–19:30'}, '</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (mammaorsoroma) | IG: trovato (ristorantemammaorso)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -9389,17 +9383,42 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Mangiafuoco</t>
+          <t>Mazzo</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Via Cicerone, 40</t>
+          <t>Via degli Equi, 62</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>06/9411904</t>
+          <t>06/69420455</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>www.mazzoroma.it</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>MAZZO.ROMA</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>mazzo_roma</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9414,12 +9433,17 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15, 00', 'break': '15–19:30'}, '</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (MAZZO.ROMA) | IG: trovato (mazzo_roma)</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -9429,48 +9453,72 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="inlineStr">
-        <is>
-          <t>Mario L'Ostricaro</t>
-        </is>
-      </c>
-      <c r="B147" s="1" t="inlineStr">
-        <is>
-          <t>Via Appia, km 102</t>
-        </is>
-      </c>
-      <c r="C147" s="1" t="inlineStr">
-        <is>
-          <t>0773/702461</t>
-        </is>
-      </c>
-      <c r="D147" s="1" t="inlineStr"/>
-      <c r="E147" s="1" t="inlineStr"/>
-      <c r="F147" s="1" t="inlineStr"/>
-      <c r="G147" s="1" t="inlineStr"/>
-      <c r="H147" s="1" t="inlineStr"/>
-      <c r="I147" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J147" s="1" t="inlineStr">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Menabó Vino e Cucina</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Via delle Palme, 44/D-E</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>06/86937299</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>www.menabovinoecucina.it</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>menabovinoecucina</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>menabo_vino_e_cucina</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K147" s="1" t="inlineStr"/>
-      <c r="L147" s="1" t="inlineStr"/>
-      <c r="M147" s="1" t="inlineStr"/>
-      <c r="N147" s="1" t="inlineStr"/>
-      <c r="O147" s="1" t="inlineStr"/>
-      <c r="P147" s="1" t="inlineStr"/>
-      <c r="Q147" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R147" s="1" t="inlineStr">
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '00'}, '</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (menabovinoecucina) | IG: trovato (menabo_vino_e_cucina)</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
@@ -9479,32 +9527,32 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Mazzo</t>
+          <t>Michele Chinappi</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Via degli Equi, 62</t>
+          <t>Via Abate Tosti, 101</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>06/69420455</t>
+          <t>0771/279917</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>www.mazzoroma.it</t>
+          <t>www.michelechinappi.it</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>MAZZO.ROMA</t>
+          <t>RistoranteMicheleChinappi</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>mazzo_roma</t>
+          <t>istorantemichelechinappi</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9527,11 +9575,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
-        </is>
-      </c>
       <c r="O148" t="inlineStr">
         <is>
           <t>Si</t>
@@ -9539,7 +9582,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (MAZZO.ROMA) | IG: trovato (mazzo_roma)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (RistoranteMicheleChinappi) | IG: trovato (istorantemichelechinappi)</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -9551,32 +9594,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Menabó Vino e Cucina</t>
+          <t>Mile</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Via delle Palme, 44/D-E</t>
+          <t>Via Pesaro, 8</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>06/86937299</t>
+          <t>327/5878046</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>www.menabovinoecucina.it</t>
+          <t>mile-ristorante-roma.eatbu.com</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>menabovinoecucina</t>
+          <t>mileristorante</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>menabo_vino_e_cucina</t>
+          <t>mile_pigneto</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -9601,7 +9644,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '00'}, '</t>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '23'}, 'martedì': {'opens': '19:30', 'cl</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -9611,7 +9654,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (menabovinoecucina) | IG: trovato (menabo_vino_e_cucina)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (mileristorante) | IG: trovato (mile_pigneto)</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -9623,32 +9666,32 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Michele Chinappi</t>
+          <t>Molo 21</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Via Abate Tosti, 101</t>
+          <t>Lungomare Guglielmo Marconi, 21</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0771/279917</t>
+          <t>0766/1894210</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>www.michelechinappi.it</t>
+          <t>www.molo21.com</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RistoranteMicheleChinappi</t>
+          <t>moloventuno</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>istorantemichelechinappi</t>
+          <t>_molo21</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -9671,6 +9714,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10:30', 'closes': '17'}, 'martedì': {'opens': '10:30', 'cl</t>
+        </is>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>Si</t>
@@ -9678,7 +9726,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (RistoranteMicheleChinappi) | IG: trovato (istorantemichelechinappi)</t>
+          <t>Rating Google: 3.9 ( rec.) | TF: non trovato | FB: trovato (moloventuno) | IG: trovato (_molo21)</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
@@ -9690,42 +9738,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Mile</t>
+          <t>Molo 29</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Via Pesaro, 8</t>
+          <t>Via Mario Musco, 29/31</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>327/5878046</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>mile-ristorante-roma.eatbu.com</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>mileristorante</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>mile_pigneto</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/59600651</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9740,17 +9763,12 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '19:30', 'closes': '23'}, 'martedì': {'opens': '19:30', 'cl</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (mileristorante) | IG: trovato (mile_pigneto)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
@@ -9762,42 +9780,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Molo 21</t>
+          <t>Mr. Meat Kitchen and Grill</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lungomare Guglielmo Marconi, 21</t>
+          <t>Via di Salone, 248</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0766/1894210</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>www.molo21.com</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>moloventuno</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>_molo21</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>345/1764800</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9812,17 +9805,12 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '10:30', 'closes': '17'}, 'martedì': {'opens': '10:30', 'cl</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '12', 'closes': '15'}, 'martedì': {'opens': '12', 'closes':</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>Rating Google: 3.9 ( rec.) | TF: non trovato | FB: trovato (moloventuno) | IG: trovato (_molo21)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
@@ -9834,17 +9822,37 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Molo 29</t>
+          <t>Mudejar Spiriti e Cucina</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Via Mario Musco, 29/31</t>
+          <t>Corso San Leone, 3/A</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>06/59600651</t>
+          <t>338/6839418</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>mudejarspiritiecucina</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>mudejar_spiriti_e_cucina</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9859,12 +9867,17 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
+          <t>{'lunedì': {'opens': '11:30, 18', 'closes': '15:30, 23:30', 'break': '15:30–18'}</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 3.6 ( rec.) | TF: non trovato | FB: trovato (mudejarspiritiecucina) | IG: trovato (mudejar_spiriti_e_cucina)</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -9876,17 +9889,27 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Mr. Meat Kitchen and Grill</t>
+          <t>Nena Mercato&amp;Cucina</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Via di Salone, 248</t>
+          <t>Via dei Sabelli, 193</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>345/1764800</t>
+          <t>06/83434951</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>nena.mercatocucina</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9901,12 +9924,17 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12', 'closes': '15'}, 'martedì': {'opens': '12', 'closes':</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '00'}, '</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (nena.mercatocucina)</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -9918,27 +9946,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Mudejar Spiriti e Cucina</t>
+          <t>NuAN</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Corso San Leone, 3/A</t>
+          <t>Via Siria, 3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>338/6839418</t>
+          <t>06/69401880</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>www.nuancucina.icalu.com</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>mudejarspiritiecucina</t>
+          <t>nuancucina</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>mudejar_spiriti_e_cucina</t>
+          <t>nuancucina</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9963,7 +9996,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '11:30, 18', 'closes': '15:30, 23:30', 'break': '15:30–18'}</t>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -9973,7 +10006,7 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Rating Google: 3.6 ( rec.) | TF: non trovato | FB: trovato (mudejarspiritiecucina) | IG: trovato (mudejar_spiriti_e_cucina)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (nuancucina) | IG: trovato (nuancucina)</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -9985,25 +10018,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nena Mercato&amp;Cucina</t>
+          <t>Osteria “Il Bersagliere”</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Via dei Sabelli, 193</t>
+          <t>Via Casilina, km 25,000</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>06/83434951</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>nena.mercatocucina</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
+          <t>320/6851104</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>colonna.roma.fuoriporta</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
@@ -10020,7 +10053,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '00'}, '</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12, 19:30', 'closes': '15,</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -10030,7 +10063,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (nena.mercatocucina)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (colonna.roma.fuoriporta) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -10042,32 +10075,32 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NuAN</t>
+          <t>Osteria Anna</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Via Siria, 3</t>
+          <t>S.R. 630 Cassino Formia km. 15</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>06/69401880</t>
+          <t>0776/952596</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>www.nuancucina.icalu.com</t>
+          <t>www.osteriaanna.com</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>nuancucina</t>
+          <t>osteriaanna</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>nuancucina</t>
+          <t>osteria_anna</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10085,16 +10118,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
-        </is>
-      </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>Si</t>
@@ -10102,7 +10125,7 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (nuancucina) | IG: trovato (nuancucina)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (osteriaanna) | IG: trovato (osteria_anna)</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -10114,22 +10137,32 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Osteria “Il Bersagliere”</t>
+          <t>Osteria del Borgo</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Via Casilina, km 25,000</t>
+          <t>Via Borgo di Sopra, 21/23</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>320/6851104</t>
+          <t>06/30430023</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>www.osteriadelborgocesano.com</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>colonna.roma.fuoriporta</t>
+          <t>osteria.delborgo.50</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>osteriadelborgocesano</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10137,21 +10170,16 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12, 19:30', 'closes': '15,</t>
-        </is>
-      </c>
       <c r="O158" t="inlineStr">
         <is>
           <t>Si</t>
@@ -10159,7 +10187,7 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (colonna.roma.fuoriporta) | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (osteria.delborgo.50) | IG: non trovato (osteriadelborgocesano)</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -10171,32 +10199,32 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Osteria Anna</t>
+          <t>Osteria del Tempo Perso</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>S.R. 630 Cassino Formia km. 15</t>
+          <t>Piazza San Rocco, 13</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0776/952596</t>
+          <t>0776/638039</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>www.osteriaanna.com</t>
+          <t>www.osteriadeltempoperso.info</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>osteriaanna</t>
+          <t>ostempoperso</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>osteria_anna</t>
+          <t>osteria_del_tempoperso</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -10221,7 +10249,7 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (osteriaanna) | IG: trovato (osteria_anna)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ostempoperso) | IG: non trovato (osteria_del_tempoperso)</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -10233,32 +10261,32 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Osteria del Borgo</t>
+          <t>Osteria di Maccarese</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Via Borgo di Sopra, 21/23</t>
+          <t>Via dei Pastori, 26-A/28</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>06/30430023</t>
+          <t>06/30328324</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>www.osteriadelborgocesano.com</t>
+          <t>www.osteria-di-maccarese.eatbu.com</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>osteria.delborgo.50</t>
+          <t>osteriadimaccarese</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>osteriadelborgocesano</t>
+          <t>osteriadimaccarese</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -10276,6 +10304,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr">
         <is>
           <t>Si</t>
@@ -10283,7 +10321,7 @@
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (osteria.delborgo.50) | IG: non trovato (osteriadelborgocesano)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (osteriadimaccarese) | IG: non trovato (osteriadimaccarese)</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -10295,32 +10333,32 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Osteria del Tempo Perso</t>
+          <t>Osteria La Briciola</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Piazza San Rocco, 13</t>
+          <t>Via Scuole Rurali, 1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0776/638039</t>
+          <t>0774/418421</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>www.osteriadeltempoperso.info</t>
+          <t>www.osterialabriciola.it</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ostempoperso</t>
+          <t>osteria.labriciola</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>osteria_del_tempoperso</t>
+          <t>osterialabriciola</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -10345,7 +10383,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ostempoperso) | IG: non trovato (osteria_del_tempoperso)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (osteria.labriciola) | IG: non trovato (osterialabriciola)</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -10357,42 +10395,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Osteria di Maccarese</t>
+          <t>Osteria La Massaia</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Via dei Pastori, 26-A/28</t>
+          <t>Via della Seta, 1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>06/30328324</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>www.osteria-di-maccarese.eatbu.com</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>osteriadimaccarese</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>osteriadimaccarese</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/52205140</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10407,17 +10420,12 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–1</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15, 23:30', 'break': '15–19:30'}</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (osteriadimaccarese) | IG: non trovato (osteriadimaccarese)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -10429,42 +10437,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Osteria La Briciola</t>
+          <t>Osteria Santa Lucia</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Via Scuole Rurali, 1</t>
+          <t>Corso della Repubblica, 26</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0774/418421</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>www.osterialabriciola.it</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>osteria.labriciola</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>osterialabriciola</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>0775/211863</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10472,14 +10455,19 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12, 19', 'closes': '15, 23', 'break': '15–19'}, 'martedì':</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (osteria.labriciola) | IG: non trovato (osterialabriciola)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -10491,17 +10479,42 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Osteria La Massaia</t>
+          <t>Pastorie</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Via della Seta, 1</t>
+          <t>Via Pesaro, 40</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>06/52205140</t>
+          <t>393/9558235</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>www.pastorie.it</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>pastorie</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>ristorantepastorieroma</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10516,12 +10529,17 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15, 23:30', 'break': '15–19:30'}</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '23'}, '</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (pastorie) | IG: non trovato (ristorantepastorieroma)</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -10533,17 +10551,42 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Osteria Santa Lucia</t>
+          <t>Popina Trattoria</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Corso della Repubblica, 26</t>
+          <t>Via Giovanni Verga, 42</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0775/211863</t>
+          <t>06/72499997</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>www.trattoriapopina.it</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>trattoriapopina</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>trattoriapopina</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10558,12 +10601,17 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12, 19', 'closes': '15, 23', 'break': '15–19'}, 'martedì':</t>
+          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15, 22:30', 'break': '15–19:30'}</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (trattoriapopina) | IG: non trovato (trattoriapopina)</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -10575,32 +10623,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Pastorie</t>
+          <t>Porto Quadro</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Via Pesaro, 40</t>
+          <t>Piazza Ippolito Nievo, 13/14</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>393/9558235</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>www.pastorie.it</t>
+          <t>340/8640569</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>pastorie</t>
+          <t>PortoQuadroristorante</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ristorantepastorieroma</t>
+          <t>portoquadro_ristorante</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10625,7 +10668,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '23'}, '</t>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '22:30'}, 'martedì': {'opens': '19:30',</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -10635,7 +10678,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (pastorie) | IG: non trovato (ristorantepastorieroma)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (PortoQuadroristorante) | IG: non trovato (portoquadro_ristorante)</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -10647,32 +10690,32 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Popina Trattoria</t>
+          <t>Prato di Sopra</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Via Giovanni Verga, 42</t>
+          <t>Via Principe Amedeo, 7</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>06/72499997</t>
+          <t>06/94315464</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>www.trattoriapopina.it</t>
+          <t>www.pratodisopra.it</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>trattoriapopina</t>
+          <t>profile.php?id=100045448885045</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>trattoriapopina</t>
+          <t>pratodisopra</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10697,7 +10740,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12:30, 19:30', 'closes': '15, 22:30', 'break': '15–19:30'}</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '00'}, '</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -10707,7 +10750,7 @@
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (trattoriapopina) | IG: non trovato (trattoriapopina)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100045448885045) | IG: non trovato (pratodisopra)</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -10719,37 +10762,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Porto Quadro</t>
+          <t>Ristorante Belvedere dal 1933</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Piazza Ippolito Nievo, 13/14</t>
+          <t>Via Regina Margherita, 29</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>340/8640569</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>PortoQuadroristorante</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>portoquadro_ristorante</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/9419004</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10767,14 +10790,9 @@
           <t>{'lunedì': {'opens': '19:30', 'closes': '22:30'}, 'martedì': {'opens': '19:30',</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (PortoQuadroristorante) | IG: non trovato (portoquadro_ristorante)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -10786,32 +10804,32 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Prato di Sopra</t>
+          <t>Ristorante degli Angeli</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Via Principe Amedeo, 7</t>
+          <t>Località Madonna degli Angeli</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>06/94315464</t>
+          <t>0744/91377</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>www.pratodisopra.it</t>
+          <t>www.ristorantedegliangeli.it</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>profile.php?id=100045448885045</t>
+          <t>angelimagliano</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>pratodisopra</t>
+          <t>gli_angeli_gourmet</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10836,7 +10854,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19:30', 'closes': '00'}, '</t>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '23'}, 'martedì': {'opens': '19:30', 'cl</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -10846,7 +10864,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100045448885045) | IG: non trovato (pratodisopra)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (angelimagliano) | IG: non trovato (gli_angeli_gourmet)</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -10858,17 +10876,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ristorante Belvedere dal 1933</t>
+          <t>Santuccio ai Colli</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Via Regina Margherita, 29</t>
+          <t>Via Santi Sebastiano e Rocco, 95</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>06/9419004</t>
+          <t>0773/888573</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10883,12 +10901,12 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '19:30', 'closes': '22:30'}, 'martedì': {'opens': '19:30',</t>
+          <t>{'lunedì': {'opens': '13, 20', 'closes': '14:30, 22:30', 'break': '14:30–20'}, '</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -10900,32 +10918,32 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ristorante degli Angeli</t>
+          <t>Scottadito</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Località Madonna degli Angeli</t>
+          <t>Via Veglia, 14</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0744/91377</t>
+          <t>06/97162153</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>www.ristorantedegliangeli.it</t>
+          <t>www.scottaditoristorante.it</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>angelimagliano</t>
+          <t>Scottaditotalenti</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>gli_angeli_gourmet</t>
+          <t>scottadito_ristorante</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10948,11 +10966,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '19:30', 'closes': '23'}, 'martedì': {'opens': '19:30', 'cl</t>
-        </is>
-      </c>
       <c r="O171" t="inlineStr">
         <is>
           <t>Si</t>
@@ -10960,7 +10973,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (angelimagliano) | IG: non trovato (gli_angeli_gourmet)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Scottaditotalenti) | IG: non trovato (scottadito_ristorante)</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -10972,17 +10985,42 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Santuccio ai Colli</t>
+          <t>Sora Maria e Arcangelo</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Via Santi Sebastiano e Rocco, 95</t>
+          <t>Via Roma, 45</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0773/888573</t>
+          <t>06/9564043</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>www.soramariaearcangelo.com</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>SoraMariaArcangelo</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>soramariaarcangelo</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10997,12 +11035,17 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '13, 20', 'closes': '14:30, 22:30', 'break': '14:30–20'}, '</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30', 'closes': '14:30'}</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (SoraMariaArcangelo) | IG: non trovato (soramariaarcangelo)</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -11012,155 +11055,139 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="inlineStr">
-        <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
-        </is>
-      </c>
-      <c r="B173" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Erbe, 16</t>
-        </is>
-      </c>
-      <c r="C173" s="1" t="inlineStr">
-        <is>
-          <t>348/7277746</t>
-        </is>
-      </c>
-      <c r="D173" s="1" t="inlineStr"/>
-      <c r="E173" s="1" t="inlineStr"/>
-      <c r="F173" s="1" t="inlineStr"/>
-      <c r="G173" s="1" t="inlineStr"/>
-      <c r="H173" s="1" t="inlineStr"/>
-      <c r="I173" s="1" t="inlineStr">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Tram Tram</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Via dei Reti, 44/46</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>06/490416</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>www.tramtram.it</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>TramTramOsteria</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>fabiolissimasultram</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (TramTramOsteria) | IG: non trovato (fabiolissimasultram)</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>Bless</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t>Via dell’Indipendenza, 208</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>0771/030188</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="inlineStr"/>
+      <c r="E174" s="1" t="inlineStr"/>
+      <c r="F174" s="1" t="inlineStr"/>
+      <c r="G174" s="1" t="inlineStr"/>
+      <c r="H174" s="1" t="inlineStr"/>
+      <c r="I174" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J173" s="1" t="inlineStr"/>
-      <c r="K173" s="1" t="inlineStr"/>
-      <c r="L173" s="1" t="inlineStr"/>
-      <c r="M173" s="1" t="inlineStr"/>
-      <c r="N173" s="1" t="inlineStr"/>
-      <c r="O173" s="1" t="inlineStr"/>
-      <c r="P173" s="1" t="inlineStr"/>
-      <c r="Q173" s="1" t="inlineStr">
+      <c r="J174" s="1" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="K174" s="1" t="inlineStr"/>
+      <c r="L174" s="1" t="inlineStr"/>
+      <c r="M174" s="1" t="inlineStr"/>
+      <c r="N174" s="1" t="inlineStr"/>
+      <c r="O174" s="1" t="inlineStr"/>
+      <c r="P174" s="1" t="inlineStr"/>
+      <c r="Q174" s="1" t="inlineStr">
         <is>
           <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
-      <c r="R173" s="1" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Scottadito</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Via Veglia, 14</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>06/97162153</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>www.scottaditoristorante.it</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Scottaditotalenti</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>scottadito_ristorante</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Scottaditotalenti) | IG: non trovato (scottadito_ristorante)</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
+      <c r="R174" s="1" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sora Maria e Arcangelo</t>
+          <t>Mario L'Ostricaro</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Via Roma, 45</t>
+          <t>Via Appia, km 102</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>06/9564043</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>www.soramariaearcangelo.com</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>SoraMariaArcangelo</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>soramariaarcangelo</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>0773/702461</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11175,1542 +11202,1571 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30', 'closes': '14:30'}</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
+          <t>{'giovedì': {'opens': '09', 'closes': '23'}, 'venerdì': {'opens': '09', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>Piazza delle Erbe, 16</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>348/7277746</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr"/>
+      <c r="E176" s="1" t="inlineStr"/>
+      <c r="F176" s="1" t="inlineStr"/>
+      <c r="G176" s="1" t="inlineStr"/>
+      <c r="H176" s="1" t="inlineStr"/>
+      <c r="I176" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J176" s="1" t="inlineStr"/>
+      <c r="K176" s="1" t="inlineStr"/>
+      <c r="L176" s="1" t="inlineStr"/>
+      <c r="M176" s="1" t="inlineStr"/>
+      <c r="N176" s="1" t="inlineStr"/>
+      <c r="O176" s="1" t="inlineStr"/>
+      <c r="P176" s="1" t="inlineStr"/>
+      <c r="Q176" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R176" s="1" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Tratto</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Viale Dell’Aeronautica 67/69</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>06/5921244</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15:30, 23', 'break': '15:30–19:</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Trattoria del Pesce</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Via Folco Portinari, 27</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>06/95945393</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>www.trattoriadelpesce.it</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Trattoria-del-pesce-128785123888261</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>trattoria-del-pesce</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '14:30, 23', 'break': '14:30–19:</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (SoraMariaArcangelo) | IG: non trovato (soramariaarcangelo)</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Tram Tram</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Via dei Reti, 44/46</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>06/490416</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>www.tramtram.it</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>TramTramOsteria</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>fabiolissimasultram</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (Trattoria-del-pesce-128785123888261) | IG: trovato (trattoria-del-pesce)</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Trattoria della Fortuna</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Via Salaria, 57</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>06/9004098</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>www.trattoriadellafortuna.it</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>TrattoriaDellaFortuna</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>trattoriadellafortuna</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (TrattoriaDellaFortuna) | IG: trovato (trattoriadellafortuna)</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Trattoria Enoteca Assunta</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Via Pontina Km 74,000</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>0773/241940</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>trattoriaenotecaassunta</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>trattoriaenotecaassunta</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19:30', 'closes': '</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr">
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19', 'closes': '23:30'}, 'venerdì': {'opens': '19', 'clos</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (TramTramOsteria) | IG: non trovato (fabiolissimasultram)</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="inlineStr">
-        <is>
-          <t>Tratto</t>
-        </is>
-      </c>
-      <c r="B177" s="1" t="inlineStr">
-        <is>
-          <t>Viale Dell’Aeronautica 67/69</t>
-        </is>
-      </c>
-      <c r="C177" s="1" t="inlineStr">
-        <is>
-          <t>06/5921244</t>
-        </is>
-      </c>
-      <c r="D177" s="1" t="inlineStr"/>
-      <c r="E177" s="1" t="inlineStr"/>
-      <c r="F177" s="1" t="inlineStr"/>
-      <c r="G177" s="1" t="inlineStr"/>
-      <c r="H177" s="1" t="inlineStr"/>
-      <c r="I177" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J177" s="1" t="inlineStr"/>
-      <c r="K177" s="1" t="inlineStr"/>
-      <c r="L177" s="1" t="inlineStr"/>
-      <c r="M177" s="1" t="inlineStr"/>
-      <c r="N177" s="1" t="inlineStr"/>
-      <c r="O177" s="1" t="inlineStr"/>
-      <c r="P177" s="1" t="inlineStr"/>
-      <c r="Q177" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R177" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria del Pesce</t>
-        </is>
-      </c>
-      <c r="B178" s="1" t="inlineStr">
-        <is>
-          <t>Via Folco Portinari, 27</t>
-        </is>
-      </c>
-      <c r="C178" s="1" t="inlineStr">
-        <is>
-          <t>06/95945393</t>
-        </is>
-      </c>
-      <c r="D178" s="1" t="inlineStr">
-        <is>
-          <t>www.trattoriadelpesce.it</t>
-        </is>
-      </c>
-      <c r="E178" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria-del-pesce-128785123888261</t>
-        </is>
-      </c>
-      <c r="F178" s="1" t="inlineStr">
-        <is>
-          <t>trattoria-del-pesce</t>
-        </is>
-      </c>
-      <c r="G178" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H178" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I178" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J178" s="1" t="inlineStr"/>
-      <c r="K178" s="1" t="inlineStr"/>
-      <c r="L178" s="1" t="inlineStr"/>
-      <c r="M178" s="1" t="inlineStr"/>
-      <c r="N178" s="1" t="inlineStr"/>
-      <c r="O178" s="1" t="inlineStr"/>
-      <c r="P178" s="1" t="inlineStr"/>
-      <c r="Q178" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R178" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria della Fortuna</t>
-        </is>
-      </c>
-      <c r="B179" s="1" t="inlineStr">
-        <is>
-          <t>Via Salaria, 57</t>
-        </is>
-      </c>
-      <c r="C179" s="1" t="inlineStr">
-        <is>
-          <t>06/9004098</t>
-        </is>
-      </c>
-      <c r="D179" s="1" t="inlineStr">
-        <is>
-          <t>www.trattoriadellafortuna.it</t>
-        </is>
-      </c>
-      <c r="E179" s="1" t="inlineStr">
-        <is>
-          <t>TrattoriaDellaFortuna</t>
-        </is>
-      </c>
-      <c r="F179" s="1" t="inlineStr">
-        <is>
-          <t>trattoriadellafortuna</t>
-        </is>
-      </c>
-      <c r="G179" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H179" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I179" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J179" s="1" t="inlineStr"/>
-      <c r="K179" s="1" t="inlineStr"/>
-      <c r="L179" s="1" t="inlineStr"/>
-      <c r="M179" s="1" t="inlineStr"/>
-      <c r="N179" s="1" t="inlineStr"/>
-      <c r="O179" s="1" t="inlineStr"/>
-      <c r="P179" s="1" t="inlineStr"/>
-      <c r="Q179" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R179" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria Enoteca Assunta</t>
-        </is>
-      </c>
-      <c r="B180" s="1" t="inlineStr">
-        <is>
-          <t>Via Pontina Km 74,000</t>
-        </is>
-      </c>
-      <c r="C180" s="1" t="inlineStr">
-        <is>
-          <t>0773/241940</t>
-        </is>
-      </c>
-      <c r="D180" s="1" t="inlineStr"/>
-      <c r="E180" s="1" t="inlineStr">
-        <is>
-          <t>trattoriaenotecaassunta</t>
-        </is>
-      </c>
-      <c r="F180" s="1" t="inlineStr">
-        <is>
-          <t>trattoriaenotecaassunta</t>
-        </is>
-      </c>
-      <c r="G180" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H180" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I180" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J180" s="1" t="inlineStr"/>
-      <c r="K180" s="1" t="inlineStr"/>
-      <c r="L180" s="1" t="inlineStr"/>
-      <c r="M180" s="1" t="inlineStr"/>
-      <c r="N180" s="1" t="inlineStr"/>
-      <c r="O180" s="1" t="inlineStr"/>
-      <c r="P180" s="1" t="inlineStr"/>
-      <c r="Q180" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R180" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (trattoriaenotecaassunta) | IG: trovato (trattoriaenotecaassunta)</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="inlineStr">
+      <c r="A181" t="inlineStr">
         <is>
           <t>Trattoria Monti</t>
         </is>
       </c>
-      <c r="B181" s="1" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Via San Vito, 13/A</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>06/4466573</t>
         </is>
       </c>
-      <c r="D181" s="1" t="inlineStr"/>
-      <c r="E181" s="1" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>Trattoria-Monti</t>
         </is>
       </c>
-      <c r="F181" s="1" t="inlineStr"/>
-      <c r="G181" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H181" s="1" t="inlineStr"/>
-      <c r="I181" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J181" s="1" t="inlineStr"/>
-      <c r="K181" s="1" t="inlineStr"/>
-      <c r="L181" s="1" t="inlineStr"/>
-      <c r="M181" s="1" t="inlineStr"/>
-      <c r="N181" s="1" t="inlineStr"/>
-      <c r="O181" s="1" t="inlineStr"/>
-      <c r="P181" s="1" t="inlineStr"/>
-      <c r="Q181" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R181" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '13, 20', 'closes': '14:45, 22:45', 'break': '14:45–20'},</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (Trattoria-Monti) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="inlineStr">
+      <c r="A182" t="inlineStr">
         <is>
           <t>Vineria Cesare dal 1963</t>
         </is>
       </c>
-      <c r="B182" s="1" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Via San Francesco Nuovo, 1</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>0773/703921</t>
         </is>
       </c>
-      <c r="D182" s="1" t="inlineStr"/>
-      <c r="E182" s="1" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>VineriaCesare1963</t>
         </is>
       </c>
-      <c r="F182" s="1" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>vineria_cesare</t>
         </is>
       </c>
-      <c r="G182" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H182" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I182" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J182" s="1" t="inlineStr"/>
-      <c r="K182" s="1" t="inlineStr"/>
-      <c r="L182" s="1" t="inlineStr"/>
-      <c r="M182" s="1" t="inlineStr"/>
-      <c r="N182" s="1" t="inlineStr"/>
-      <c r="O182" s="1" t="inlineStr"/>
-      <c r="P182" s="1" t="inlineStr"/>
-      <c r="Q182" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R182" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '19', 'closes'</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (VineriaCesare1963) | IG: trovato (vineria_cesare)</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="inlineStr">
+      <c r="A183" t="inlineStr">
         <is>
           <t>Zero Miglia</t>
         </is>
       </c>
-      <c r="B183" s="1" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Piazza Giuseppe Mazzini, 45</t>
         </is>
       </c>
-      <c r="C183" s="1" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>06/9803030</t>
         </is>
       </c>
-      <c r="D183" s="1" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>www.ristorantezeromiglia.it</t>
         </is>
       </c>
-      <c r="E183" s="1" t="inlineStr">
+      <c r="E183" t="inlineStr">
         <is>
           <t>ristorantezeromiglia</t>
         </is>
       </c>
-      <c r="F183" s="1" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>ristorantezeromiglia</t>
         </is>
       </c>
-      <c r="G183" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H183" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I183" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J183" s="1" t="inlineStr"/>
-      <c r="K183" s="1" t="inlineStr"/>
-      <c r="L183" s="1" t="inlineStr"/>
-      <c r="M183" s="1" t="inlineStr"/>
-      <c r="N183" s="1" t="inlineStr"/>
-      <c r="O183" s="1" t="inlineStr"/>
-      <c r="P183" s="1" t="inlineStr"/>
-      <c r="Q183" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R183" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ristorantezeromiglia) | IG: trovato (ristorantezeromiglia)</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="inlineStr">
+      <c r="A184" t="inlineStr">
         <is>
           <t>La Barrique</t>
         </is>
       </c>
-      <c r="B184" s="1" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Via del Boschetto, 41</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>06/47825953</t>
         </is>
       </c>
-      <c r="D184" s="1" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>www.labarriquemonti.it</t>
         </is>
       </c>
-      <c r="E184" s="1" t="inlineStr">
+      <c r="E184" t="inlineStr">
         <is>
           <t>la.barrique.94</t>
         </is>
       </c>
-      <c r="F184" s="1" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>labarriquemonti</t>
         </is>
       </c>
-      <c r="G184" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H184" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I184" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J184" s="1" t="inlineStr"/>
-      <c r="K184" s="1" t="inlineStr"/>
-      <c r="L184" s="1" t="inlineStr"/>
-      <c r="M184" s="1" t="inlineStr"/>
-      <c r="N184" s="1" t="inlineStr"/>
-      <c r="O184" s="1" t="inlineStr"/>
-      <c r="P184" s="1" t="inlineStr"/>
-      <c r="Q184" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R184" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (la.barrique.94) | IG: trovato (labarriquemonti)</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="inlineStr">
+      <c r="A185" t="inlineStr">
         <is>
           <t>Latteria</t>
         </is>
       </c>
-      <c r="B185" s="1" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>Vicolo della Scala, 1</t>
         </is>
       </c>
-      <c r="C185" s="1" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>06/58332008</t>
         </is>
       </c>
-      <c r="D185" s="1" t="inlineStr"/>
-      <c r="E185" s="1" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>latteriatrastevere</t>
         </is>
       </c>
-      <c r="F185" s="1" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>latteria_trastevere</t>
         </is>
       </c>
-      <c r="G185" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H185" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I185" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J185" s="1" t="inlineStr"/>
-      <c r="K185" s="1" t="inlineStr"/>
-      <c r="L185" s="1" t="inlineStr"/>
-      <c r="M185" s="1" t="inlineStr"/>
-      <c r="N185" s="1" t="inlineStr"/>
-      <c r="O185" s="1" t="inlineStr"/>
-      <c r="P185" s="1" t="inlineStr"/>
-      <c r="Q185" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R185" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '00'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: trovato (latteriatrastevere) | IG: trovato (latteria_trastevere)</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="inlineStr">
+      <c r="A186" t="inlineStr">
         <is>
           <t>Roscioli</t>
         </is>
       </c>
-      <c r="B186" s="1" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>Via dei Giubbonari, 21/22</t>
         </is>
       </c>
-      <c r="C186" s="1" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>06/6875287</t>
         </is>
       </c>
-      <c r="D186" s="1" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>www.salumeriaroscioli.com</t>
         </is>
       </c>
-      <c r="E186" s="1" t="inlineStr">
+      <c r="E186" t="inlineStr">
         <is>
           <t>RoscioliRistoranteSalumeria</t>
         </is>
       </c>
-      <c r="F186" s="1" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>roscioliroma</t>
         </is>
       </c>
-      <c r="G186" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H186" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I186" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J186" s="1" t="inlineStr"/>
-      <c r="K186" s="1" t="inlineStr"/>
-      <c r="L186" s="1" t="inlineStr"/>
-      <c r="M186" s="1" t="inlineStr"/>
-      <c r="N186" s="1" t="inlineStr"/>
-      <c r="O186" s="1" t="inlineStr"/>
-      <c r="P186" s="1" t="inlineStr"/>
-      <c r="Q186" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R186" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (RoscioliRistoranteSalumeria) | IG: trovato (roscioliroma)</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="inlineStr">
+      <c r="A187" t="inlineStr">
         <is>
           <t>Santo Bevitore</t>
         </is>
       </c>
-      <c r="B187" s="1" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Via Guglielmo Marconi, 8</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>329/2911575</t>
         </is>
       </c>
-      <c r="D187" s="1" t="inlineStr"/>
-      <c r="E187" s="1" t="inlineStr"/>
-      <c r="F187" s="1" t="inlineStr"/>
-      <c r="G187" s="1" t="inlineStr"/>
-      <c r="H187" s="1" t="inlineStr"/>
-      <c r="I187" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J187" s="1" t="inlineStr"/>
-      <c r="K187" s="1" t="inlineStr"/>
-      <c r="L187" s="1" t="inlineStr"/>
-      <c r="M187" s="1" t="inlineStr"/>
-      <c r="N187" s="1" t="inlineStr"/>
-      <c r="O187" s="1" t="inlineStr"/>
-      <c r="P187" s="1" t="inlineStr"/>
-      <c r="Q187" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R187" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="inlineStr">
+      <c r="A188" t="inlineStr">
         <is>
           <t>Da Cesare</t>
         </is>
       </c>
-      <c r="B188" s="1" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>Via del Casaletto, 45</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>06/536015</t>
         </is>
       </c>
-      <c r="D188" s="1" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>www.trattoriadacesare.it</t>
         </is>
       </c>
-      <c r="E188" s="1" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>trattoriadacesare</t>
         </is>
       </c>
-      <c r="F188" s="1" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>trattoriadacesare</t>
         </is>
       </c>
-      <c r="G188" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H188" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I188" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J188" s="1" t="inlineStr"/>
-      <c r="K188" s="1" t="inlineStr"/>
-      <c r="L188" s="1" t="inlineStr"/>
-      <c r="M188" s="1" t="inlineStr"/>
-      <c r="N188" s="1" t="inlineStr"/>
-      <c r="O188" s="1" t="inlineStr"/>
-      <c r="P188" s="1" t="inlineStr"/>
-      <c r="Q188" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R188" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (trattoriadacesare) | IG: trovato (trattoriadacesare)</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="inlineStr">
+      <c r="A189" t="inlineStr">
         <is>
           <t>Da Danilo</t>
         </is>
       </c>
-      <c r="B189" s="1" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>Via Petrarca, 13</t>
         </is>
       </c>
-      <c r="C189" s="1" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>06/77200111</t>
         </is>
       </c>
-      <c r="D189" s="1" t="inlineStr"/>
-      <c r="E189" s="1" t="inlineStr"/>
-      <c r="F189" s="1" t="inlineStr"/>
-      <c r="G189" s="1" t="inlineStr"/>
-      <c r="H189" s="1" t="inlineStr"/>
-      <c r="I189" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J189" s="1" t="inlineStr"/>
-      <c r="K189" s="1" t="inlineStr"/>
-      <c r="L189" s="1" t="inlineStr"/>
-      <c r="M189" s="1" t="inlineStr"/>
-      <c r="N189" s="1" t="inlineStr"/>
-      <c r="O189" s="1" t="inlineStr"/>
-      <c r="P189" s="1" t="inlineStr"/>
-      <c r="Q189" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R189" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '13, 20', 'closes': '15, 23', 'break': '15–20'}, 'venerdì'</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="inlineStr">
+      <c r="A190" t="inlineStr">
         <is>
           <t>Da Enzo al 29</t>
         </is>
       </c>
-      <c r="B190" s="1" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Via dei Vascellari, 29</t>
         </is>
       </c>
-      <c r="C190" s="1" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>06/5812260</t>
         </is>
       </c>
-      <c r="D190" s="1" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>www.daenzoal29.com</t>
         </is>
       </c>
-      <c r="E190" s="1" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>daenzoal29</t>
         </is>
       </c>
-      <c r="F190" s="1" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>daenzoal29</t>
         </is>
       </c>
-      <c r="G190" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H190" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I190" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J190" s="1" t="inlineStr"/>
-      <c r="K190" s="1" t="inlineStr"/>
-      <c r="L190" s="1" t="inlineStr"/>
-      <c r="M190" s="1" t="inlineStr"/>
-      <c r="N190" s="1" t="inlineStr"/>
-      <c r="O190" s="1" t="inlineStr"/>
-      <c r="P190" s="1" t="inlineStr"/>
-      <c r="Q190" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R190" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12, 18:30', 'closes': '15, 22:30', 'break': '15–18:30'},</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (daenzoal29) | IG: trovato (daenzoal29)</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="inlineStr">
+      <c r="A191" t="inlineStr">
         <is>
           <t>Felice</t>
         </is>
       </c>
-      <c r="B191" s="1" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>Via Mastro Giorgio, 29</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>06/5746800</t>
         </is>
       </c>
-      <c r="D191" s="1" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>www.feliceatestaccio.it</t>
         </is>
       </c>
-      <c r="E191" s="1" t="inlineStr">
+      <c r="E191" t="inlineStr">
         <is>
           <t>FeliceatestaccioRM</t>
         </is>
       </c>
-      <c r="F191" s="1" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>feliceatestaccio</t>
         </is>
       </c>
-      <c r="G191" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H191" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I191" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J191" s="1" t="inlineStr"/>
-      <c r="K191" s="1" t="inlineStr"/>
-      <c r="L191" s="1" t="inlineStr"/>
-      <c r="M191" s="1" t="inlineStr"/>
-      <c r="N191" s="1" t="inlineStr"/>
-      <c r="O191" s="1" t="inlineStr"/>
-      <c r="P191" s="1" t="inlineStr"/>
-      <c r="Q191" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R191" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19', 'closes': '15:30, 23:30', 'break': '15:30–19'</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (FeliceatestaccioRM) | IG: trovato (feliceatestaccio)</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="inlineStr">
+      <c r="A192" t="inlineStr">
         <is>
           <t>Flavio al Velavevodetto</t>
         </is>
       </c>
-      <c r="B192" s="1" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>Piazza dei Quiriti, 4/5</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>06/36000009</t>
         </is>
       </c>
-      <c r="D192" s="1" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t>www.ristorantevelavevodetto.it</t>
         </is>
       </c>
-      <c r="E192" s="1" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>velavevodetto</t>
         </is>
       </c>
-      <c r="F192" s="1" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t>velavevodetto</t>
         </is>
       </c>
-      <c r="G192" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H192" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I192" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J192" s="1" t="inlineStr"/>
-      <c r="K192" s="1" t="inlineStr"/>
-      <c r="L192" s="1" t="inlineStr"/>
-      <c r="M192" s="1" t="inlineStr"/>
-      <c r="N192" s="1" t="inlineStr"/>
-      <c r="O192" s="1" t="inlineStr"/>
-      <c r="P192" s="1" t="inlineStr"/>
-      <c r="Q192" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R192" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (velavevodetto) | IG: trovato (velavevodetto)</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="inlineStr">
+      <c r="A193" t="inlineStr">
         <is>
           <t>Hosteria Grappolo d'Oro</t>
         </is>
       </c>
-      <c r="B193" s="1" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>Piazza della Cancelleria, 80</t>
         </is>
       </c>
-      <c r="C193" s="1" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>06/6897080</t>
         </is>
       </c>
-      <c r="D193" s="1" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>www.hosteriagrappolodoro.it</t>
         </is>
       </c>
-      <c r="E193" s="1" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t>HosteriaGrappoloDOro</t>
         </is>
       </c>
-      <c r="F193" s="1" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>Grappolo_d_Oro-Rome_Lazio</t>
         </is>
       </c>
-      <c r="G193" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H193" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I193" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J193" s="1" t="inlineStr"/>
-      <c r="K193" s="1" t="inlineStr"/>
-      <c r="L193" s="1" t="inlineStr"/>
-      <c r="M193" s="1" t="inlineStr"/>
-      <c r="N193" s="1" t="inlineStr"/>
-      <c r="O193" s="1" t="inlineStr"/>
-      <c r="P193" s="1" t="inlineStr"/>
-      <c r="Q193" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R193" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (HosteriaGrappoloDOro) | IG: trovato (Grappolo_d_Oro-Rome_Lazio)</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="inlineStr">
+      <c r="A194" t="inlineStr">
         <is>
           <t>Il Vecchio Mulino</t>
         </is>
       </c>
-      <c r="B194" s="1" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>Via G. Marconi, 25/A</t>
         </is>
       </c>
-      <c r="C194" s="1" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>0761/780505</t>
         </is>
       </c>
-      <c r="D194" s="1" t="inlineStr"/>
-      <c r="E194" s="1" t="inlineStr"/>
-      <c r="F194" s="1" t="inlineStr"/>
-      <c r="G194" s="1" t="inlineStr"/>
-      <c r="H194" s="1" t="inlineStr"/>
-      <c r="I194" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J194" s="1" t="inlineStr"/>
-      <c r="K194" s="1" t="inlineStr"/>
-      <c r="L194" s="1" t="inlineStr"/>
-      <c r="M194" s="1" t="inlineStr"/>
-      <c r="N194" s="1" t="inlineStr"/>
-      <c r="O194" s="1" t="inlineStr"/>
-      <c r="P194" s="1" t="inlineStr"/>
-      <c r="Q194" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R194" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19', 'closes': '15:15, 23', 'break': '15:15–19'},</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="inlineStr">
+      <c r="A195" t="inlineStr">
         <is>
           <t>Iotto</t>
         </is>
       </c>
-      <c r="B195" s="1" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>Corso Vittorio Emanuele, 96</t>
         </is>
       </c>
-      <c r="C195" s="1" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>06/9041746</t>
         </is>
       </c>
-      <c r="D195" s="1" t="inlineStr"/>
-      <c r="E195" s="1" t="inlineStr">
+      <c r="E195" t="inlineStr">
         <is>
           <t>OsteriaIotto</t>
         </is>
       </c>
-      <c r="F195" s="1" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>osteria.iotto</t>
         </is>
       </c>
-      <c r="G195" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H195" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I195" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J195" s="1" t="inlineStr"/>
-      <c r="K195" s="1" t="inlineStr"/>
-      <c r="L195" s="1" t="inlineStr"/>
-      <c r="M195" s="1" t="inlineStr"/>
-      <c r="N195" s="1" t="inlineStr"/>
-      <c r="O195" s="1" t="inlineStr"/>
-      <c r="P195" s="1" t="inlineStr"/>
-      <c r="Q195" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R195" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '14:30, 21:30', 'break': '14:30–</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (OsteriaIotto) | IG: trovato (osteria.iotto)</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="inlineStr">
+      <c r="A196" t="inlineStr">
         <is>
           <t>La Briciola di Adriana</t>
         </is>
       </c>
-      <c r="B196" s="1" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>Via Domenichino, 14</t>
         </is>
       </c>
-      <c r="C196" s="1" t="inlineStr">
+      <c r="C196" t="inlineStr">
         <is>
           <t>06/9459338</t>
         </is>
       </c>
-      <c r="D196" s="1" t="inlineStr"/>
-      <c r="E196" s="1" t="inlineStr"/>
-      <c r="F196" s="1" t="inlineStr"/>
-      <c r="G196" s="1" t="inlineStr"/>
-      <c r="H196" s="1" t="inlineStr"/>
-      <c r="I196" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J196" s="1" t="inlineStr"/>
-      <c r="K196" s="1" t="inlineStr"/>
-      <c r="L196" s="1" t="inlineStr"/>
-      <c r="M196" s="1" t="inlineStr"/>
-      <c r="N196" s="1" t="inlineStr"/>
-      <c r="O196" s="1" t="inlineStr"/>
-      <c r="P196" s="1" t="inlineStr"/>
-      <c r="Q196" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R196" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '16, 23', 'break': '16–19:30'},</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="inlineStr">
+      <c r="A197" t="inlineStr">
         <is>
           <t>La Tavernaccia</t>
         </is>
       </c>
-      <c r="B197" s="1" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>Via Giovanni di Castel Bolognese, 63</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>06/5812792</t>
         </is>
       </c>
-      <c r="D197" s="1" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>www.latavernaccia.com</t>
         </is>
       </c>
-      <c r="E197" s="1" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>info.tavernaccia.roma</t>
         </is>
       </c>
-      <c r="F197" s="1" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>latavernacciaroma</t>
         </is>
       </c>
-      <c r="G197" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H197" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I197" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J197" s="1" t="inlineStr"/>
-      <c r="K197" s="1" t="inlineStr"/>
-      <c r="L197" s="1" t="inlineStr"/>
-      <c r="M197" s="1" t="inlineStr"/>
-      <c r="N197" s="1" t="inlineStr"/>
-      <c r="O197" s="1" t="inlineStr"/>
-      <c r="P197" s="1" t="inlineStr"/>
-      <c r="Q197" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R197" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': 'Chiuso'}, 'venerdì': {'opens': '13, 19:30', 'closes': '15</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (info.tavernaccia.roma) | IG: trovato (latavernacciaroma)</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="inlineStr">
+      <c r="A198" t="inlineStr">
         <is>
           <t>Mangiadischi la moderna trattoria</t>
         </is>
       </c>
-      <c r="B198" s="1" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>Via Val di Sangro, 35</t>
         </is>
       </c>
-      <c r="C198" s="1" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>348/0081620</t>
         </is>
       </c>
-      <c r="D198" s="1" t="inlineStr"/>
-      <c r="E198" s="1" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>mangiadischilamodernatrattoria</t>
         </is>
       </c>
-      <c r="F198" s="1" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>mangiadischi_roma</t>
         </is>
       </c>
-      <c r="G198" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H198" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I198" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J198" s="1" t="inlineStr"/>
-      <c r="K198" s="1" t="inlineStr"/>
-      <c r="L198" s="1" t="inlineStr"/>
-      <c r="M198" s="1" t="inlineStr"/>
-      <c r="N198" s="1" t="inlineStr"/>
-      <c r="O198" s="1" t="inlineStr"/>
-      <c r="P198" s="1" t="inlineStr"/>
-      <c r="Q198" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R198" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (mangiadischilamodernatrattoria) | IG: trovato (mangiadischi_roma)</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="inlineStr">
+      <c r="A199" t="inlineStr">
         <is>
           <t>N'Antro</t>
         </is>
       </c>
-      <c r="B199" s="1" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>Largo Appio Claudio, 350</t>
         </is>
       </c>
-      <c r="C199" s="1" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>333/3900984</t>
         </is>
       </c>
-      <c r="D199" s="1" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>www.nantrobistrot.it</t>
         </is>
       </c>
-      <c r="E199" s="1" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>profile.php?id=61551934953405</t>
         </is>
       </c>
-      <c r="F199" s="1" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>nantrocalicietaglieri</t>
         </is>
       </c>
-      <c r="G199" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H199" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I199" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J199" s="1" t="inlineStr"/>
-      <c r="K199" s="1" t="inlineStr"/>
-      <c r="L199" s="1" t="inlineStr"/>
-      <c r="M199" s="1" t="inlineStr"/>
-      <c r="N199" s="1" t="inlineStr"/>
-      <c r="O199" s="1" t="inlineStr"/>
-      <c r="P199" s="1" t="inlineStr"/>
-      <c r="Q199" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R199" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12, 18:30', 'closes': '15, 23:30', 'break': '15–18:30'},</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=61551934953405) | IG: trovato (nantrocalicietaglieri)</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="inlineStr">
+      <c r="A200" t="inlineStr">
         <is>
           <t>NU' Trattoria Italiana dal 1960</t>
         </is>
       </c>
-      <c r="B200" s="1" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>Via Prenestina, 27</t>
         </is>
       </c>
-      <c r="C200" s="1" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>0775/56372</t>
         </is>
       </c>
-      <c r="D200" s="1" t="inlineStr"/>
-      <c r="E200" s="1" t="inlineStr"/>
-      <c r="F200" s="1" t="inlineStr"/>
-      <c r="G200" s="1" t="inlineStr"/>
-      <c r="H200" s="1" t="inlineStr"/>
-      <c r="I200" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J200" s="1" t="inlineStr"/>
-      <c r="K200" s="1" t="inlineStr"/>
-      <c r="L200" s="1" t="inlineStr"/>
-      <c r="M200" s="1" t="inlineStr"/>
-      <c r="N200" s="1" t="inlineStr"/>
-      <c r="O200" s="1" t="inlineStr"/>
-      <c r="P200" s="1" t="inlineStr"/>
-      <c r="Q200" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R200" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '19', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="inlineStr">
+      <c r="A201" t="inlineStr">
         <is>
           <t>Osteria del Velodromo Vecchio</t>
         </is>
       </c>
-      <c r="B201" s="1" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>Via Genzano, 139</t>
         </is>
       </c>
-      <c r="C201" s="1" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>06/7886793</t>
         </is>
       </c>
-      <c r="D201" s="1" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>www.osteriadelvelodromovecchio.it</t>
         </is>
       </c>
-      <c r="E201" s="1" t="inlineStr">
+      <c r="E201" t="inlineStr">
         <is>
           <t>osteriadelvelodromovecchio</t>
         </is>
       </c>
-      <c r="F201" s="1" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>osteria_del_velodromo_vecchio</t>
         </is>
       </c>
-      <c r="G201" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H201" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I201" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J201" s="1" t="inlineStr"/>
-      <c r="K201" s="1" t="inlineStr"/>
-      <c r="L201" s="1" t="inlineStr"/>
-      <c r="M201" s="1" t="inlineStr"/>
-      <c r="N201" s="1" t="inlineStr"/>
-      <c r="O201" s="1" t="inlineStr"/>
-      <c r="P201" s="1" t="inlineStr"/>
-      <c r="Q201" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R201" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (osteriadelvelodromovecchio) | IG: trovato (osteria_del_velodromo_vecchio)</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -12740,7 +12796,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J202" s="1" t="inlineStr"/>
+      <c r="J202" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K202" s="1" t="inlineStr"/>
       <c r="L202" s="1" t="inlineStr"/>
       <c r="M202" s="1" t="inlineStr"/>
@@ -12749,132 +12809,136 @@
       <c r="P202" s="1" t="inlineStr"/>
       <c r="Q202" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R202" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="inlineStr">
+      <c r="A203" t="inlineStr">
         <is>
           <t>Osteria Fratelli Mori</t>
         </is>
       </c>
-      <c r="B203" s="1" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>Via dei Conciatori, 10</t>
         </is>
       </c>
-      <c r="C203" s="1" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>331/3234399</t>
         </is>
       </c>
-      <c r="D203" s="1" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>www.osteriafratellimori.it</t>
         </is>
       </c>
-      <c r="E203" s="1" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>OsteriaFratelliMori</t>
         </is>
       </c>
-      <c r="F203" s="1" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>osteriafratellimori</t>
         </is>
       </c>
-      <c r="G203" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H203" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I203" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J203" s="1" t="inlineStr"/>
-      <c r="K203" s="1" t="inlineStr"/>
-      <c r="L203" s="1" t="inlineStr"/>
-      <c r="M203" s="1" t="inlineStr"/>
-      <c r="N203" s="1" t="inlineStr"/>
-      <c r="O203" s="1" t="inlineStr"/>
-      <c r="P203" s="1" t="inlineStr"/>
-      <c r="Q203" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R203" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (OsteriaFratelliMori) | IG: trovato (osteriafratellimori)</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="inlineStr">
+      <c r="A204" t="inlineStr">
         <is>
           <t>Piatto Romano</t>
         </is>
       </c>
-      <c r="B204" s="1" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>Via Giovanni Battista Bodoni, 62</t>
         </is>
       </c>
-      <c r="C204" s="1" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>06/64014447</t>
         </is>
       </c>
-      <c r="D204" s="1" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>www.piattoromano.com</t>
         </is>
       </c>
-      <c r="E204" s="1" t="inlineStr"/>
-      <c r="F204" s="1" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>piatto_romano</t>
         </is>
       </c>
-      <c r="G204" s="1" t="inlineStr"/>
-      <c r="H204" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I204" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J204" s="1" t="inlineStr"/>
-      <c r="K204" s="1" t="inlineStr"/>
-      <c r="L204" s="1" t="inlineStr"/>
-      <c r="M204" s="1" t="inlineStr"/>
-      <c r="N204" s="1" t="inlineStr"/>
-      <c r="O204" s="1" t="inlineStr"/>
-      <c r="P204" s="1" t="inlineStr"/>
-      <c r="Q204" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R204" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (piatto_romano)</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -12904,7 +12968,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J205" s="1" t="inlineStr"/>
+      <c r="J205" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K205" s="1" t="inlineStr"/>
       <c r="L205" s="1" t="inlineStr"/>
       <c r="M205" s="1" t="inlineStr"/>
@@ -12913,140 +12981,146 @@
       <c r="P205" s="1" t="inlineStr"/>
       <c r="Q205" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="inlineStr">
+      <c r="A206" t="inlineStr">
         <is>
           <t>Proloco Trastevere</t>
         </is>
       </c>
-      <c r="B206" s="1" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>Via Goffredo Mameli, 23</t>
         </is>
       </c>
-      <c r="C206" s="1" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>06/45596137</t>
         </is>
       </c>
-      <c r="D206" s="1" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>www.prolocotrastevere.it</t>
         </is>
       </c>
-      <c r="E206" s="1" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t>prolocotrastevere</t>
         </is>
       </c>
-      <c r="F206" s="1" t="inlineStr">
+      <c r="F206" t="inlineStr">
         <is>
           <t>prolocotrastevere</t>
         </is>
       </c>
-      <c r="G206" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H206" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I206" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J206" s="1" t="inlineStr"/>
-      <c r="K206" s="1" t="inlineStr"/>
-      <c r="L206" s="1" t="inlineStr"/>
-      <c r="M206" s="1" t="inlineStr"/>
-      <c r="N206" s="1" t="inlineStr"/>
-      <c r="O206" s="1" t="inlineStr"/>
-      <c r="P206" s="1" t="inlineStr"/>
-      <c r="Q206" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R206" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (prolocotrastevere) | IG: trovato (prolocotrastevere)</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="inlineStr">
+      <c r="A207" t="inlineStr">
         <is>
           <t>Santo Palato</t>
         </is>
       </c>
-      <c r="B207" s="1" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Via Gallia, 28</t>
         </is>
       </c>
-      <c r="C207" s="1" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>06/77207354</t>
         </is>
       </c>
-      <c r="D207" s="1" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>www.santopalatoroma.it</t>
         </is>
       </c>
-      <c r="E207" s="1" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>santopalatoroma</t>
         </is>
       </c>
-      <c r="F207" s="1" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>santopalatoroma</t>
         </is>
       </c>
-      <c r="G207" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H207" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I207" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J207" s="1" t="inlineStr"/>
-      <c r="K207" s="1" t="inlineStr"/>
-      <c r="L207" s="1" t="inlineStr"/>
-      <c r="M207" s="1" t="inlineStr"/>
-      <c r="N207" s="1" t="inlineStr"/>
-      <c r="O207" s="1" t="inlineStr"/>
-      <c r="P207" s="1" t="inlineStr"/>
-      <c r="Q207" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R207" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (santopalatoroma) | IG: trovato (santopalatoroma)</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -11127,48 +11127,42 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B174" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C174" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D174" s="1" t="inlineStr"/>
-      <c r="E174" s="1" t="inlineStr"/>
-      <c r="F174" s="1" t="inlineStr"/>
-      <c r="G174" s="1" t="inlineStr"/>
-      <c r="H174" s="1" t="inlineStr"/>
-      <c r="I174" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J174" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="K174" s="1" t="inlineStr"/>
-      <c r="L174" s="1" t="inlineStr"/>
-      <c r="M174" s="1" t="inlineStr"/>
-      <c r="N174" s="1" t="inlineStr"/>
-      <c r="O174" s="1" t="inlineStr"/>
-      <c r="P174" s="1" t="inlineStr"/>
-      <c r="Q174" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R174" s="1" t="inlineStr">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Mario L'Ostricaro</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Via Appia, km 102</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>0773/702461</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '09', 'closes': '23'}, 'venerdì': {'opens': '09', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -11177,17 +11171,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mario L'Ostricaro</t>
+          <t>Tratto</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Via Appia, km 102</t>
+          <t>Viale Dell’Aeronautica 67/69</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0773/702461</t>
+          <t>06/5921244</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11202,12 +11196,12 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '09', 'closes': '23'}, 'venerdì': {'opens': '09', 'closes'</t>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15:30, 23', 'break': '15:30–19:</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -11217,44 +11211,72 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="inlineStr">
-        <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
-        </is>
-      </c>
-      <c r="B176" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Erbe, 16</t>
-        </is>
-      </c>
-      <c r="C176" s="1" t="inlineStr">
-        <is>
-          <t>348/7277746</t>
-        </is>
-      </c>
-      <c r="D176" s="1" t="inlineStr"/>
-      <c r="E176" s="1" t="inlineStr"/>
-      <c r="F176" s="1" t="inlineStr"/>
-      <c r="G176" s="1" t="inlineStr"/>
-      <c r="H176" s="1" t="inlineStr"/>
-      <c r="I176" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J176" s="1" t="inlineStr"/>
-      <c r="K176" s="1" t="inlineStr"/>
-      <c r="L176" s="1" t="inlineStr"/>
-      <c r="M176" s="1" t="inlineStr"/>
-      <c r="N176" s="1" t="inlineStr"/>
-      <c r="O176" s="1" t="inlineStr"/>
-      <c r="P176" s="1" t="inlineStr"/>
-      <c r="Q176" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R176" s="1" t="inlineStr">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Trattoria del Pesce</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Via Folco Portinari, 27</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>06/95945393</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>www.trattoriadelpesce.it</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Trattoria-del-pesce-128785123888261</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>trattoria-del-pesce</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '14:30, 23', 'break': '14:30–19:</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (Trattoria-del-pesce-128785123888261) | IG: trovato (trattoria-del-pesce)</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -11263,17 +11285,42 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Tratto</t>
+          <t>Trattoria della Fortuna</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Viale Dell’Aeronautica 67/69</t>
+          <t>Via Salaria, 57</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>06/5921244</t>
+          <t>06/9004098</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>www.trattoriadellafortuna.it</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>TrattoriaDellaFortuna</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>trattoriadellafortuna</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11281,19 +11328,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15:30, 23', 'break': '15:30–19:</t>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (TrattoriaDellaFortuna) | IG: trovato (trattoriadellafortuna)</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -11305,32 +11347,27 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Trattoria del Pesce</t>
+          <t>Trattoria Enoteca Assunta</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Via Folco Portinari, 27</t>
+          <t>Via Pontina Km 74,000</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>06/95945393</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>www.trattoriadelpesce.it</t>
+          <t>0773/241940</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Trattoria-del-pesce-128785123888261</t>
+          <t>trattoriaenotecaassunta</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>trattoria-del-pesce</t>
+          <t>trattoriaenotecaassunta</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -11355,7 +11392,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '14:30, 23', 'break': '14:30–19:</t>
+          <t>{'giovedì': {'opens': '19', 'closes': '23:30'}, 'venerdì': {'opens': '19', 'clos</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -11365,7 +11402,7 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (Trattoria-del-pesce-128785123888261) | IG: trovato (trattoria-del-pesce)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (trattoriaenotecaassunta) | IG: trovato (trattoriaenotecaassunta)</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -11377,32 +11414,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Trattoria della Fortuna</t>
+          <t>Trattoria Monti</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Via Salaria, 57</t>
+          <t>Via San Vito, 13/A</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>06/9004098</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>www.trattoriadellafortuna.it</t>
+          <t>06/4466573</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>TrattoriaDellaFortuna</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>trattoriadellafortuna</t>
+          <t>Trattoria-Monti</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -11410,16 +11437,21 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I179" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '13, 20', 'closes': '14:45, 22:45', 'break': '14:45–20'},</t>
+        </is>
+      </c>
       <c r="O179" t="inlineStr">
         <is>
           <t>Si</t>
@@ -11427,7 +11459,7 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (TrattoriaDellaFortuna) | IG: trovato (trattoriadellafortuna)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (Trattoria-Monti) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -11439,27 +11471,27 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Trattoria Enoteca Assunta</t>
+          <t>Vineria Cesare dal 1963</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Via Pontina Km 74,000</t>
+          <t>Via San Francesco Nuovo, 1</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0773/241940</t>
+          <t>0773/703921</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>trattoriaenotecaassunta</t>
+          <t>VineriaCesare1963</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>trattoriaenotecaassunta</t>
+          <t>vineria_cesare</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -11484,7 +11516,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '19', 'closes': '23:30'}, 'venerdì': {'opens': '19', 'clos</t>
+          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '19', 'closes'</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -11494,7 +11526,7 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (trattoriaenotecaassunta) | IG: trovato (trattoriaenotecaassunta)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (VineriaCesare1963) | IG: trovato (vineria_cesare)</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -11506,22 +11538,32 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Trattoria Monti</t>
+          <t>Zero Miglia</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Via San Vito, 13/A</t>
+          <t>Piazza Giuseppe Mazzini, 45</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>06/4466573</t>
+          <t>06/9803030</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>www.ristorantezeromiglia.it</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Trattoria-Monti</t>
+          <t>ristorantezeromiglia</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ristorantezeromiglia</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -11529,21 +11571,16 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I181" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '13, 20', 'closes': '14:45, 22:45', 'break': '14:45–20'},</t>
-        </is>
-      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>Si</t>
@@ -11551,7 +11588,7 @@
       </c>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (Trattoria-Monti) | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ristorantezeromiglia) | IG: trovato (ristorantezeromiglia)</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -11563,27 +11600,32 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Vineria Cesare dal 1963</t>
+          <t>La Barrique</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Via San Francesco Nuovo, 1</t>
+          <t>Via del Boschetto, 41</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0773/703921</t>
+          <t>06/47825953</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>www.labarriquemonti.it</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>VineriaCesare1963</t>
+          <t>la.barrique.94</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>vineria_cesare</t>
+          <t>labarriquemonti</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -11601,16 +11643,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '19', 'closes'</t>
-        </is>
-      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>Si</t>
@@ -11618,7 +11650,7 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (VineriaCesare1963) | IG: trovato (vineria_cesare)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (la.barrique.94) | IG: trovato (labarriquemonti)</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -11630,32 +11662,27 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Zero Miglia</t>
+          <t>Latteria</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Piazza Giuseppe Mazzini, 45</t>
+          <t>Vicolo della Scala, 1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>06/9803030</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>www.ristorantezeromiglia.it</t>
+          <t>06/58332008</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>ristorantezeromiglia</t>
+          <t>latteriatrastevere</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ristorantezeromiglia</t>
+          <t>latteria_trastevere</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -11673,6 +11700,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '00'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>Si</t>
@@ -11680,7 +11717,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ristorantezeromiglia) | IG: trovato (ristorantezeromiglia)</t>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: trovato (latteriatrastevere) | IG: trovato (latteria_trastevere)</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -11692,32 +11729,32 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>La Barrique</t>
+          <t>Roscioli</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Via del Boschetto, 41</t>
+          <t>Via dei Giubbonari, 21/22</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>06/47825953</t>
+          <t>06/6875287</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>www.labarriquemonti.it</t>
+          <t>www.salumeriaroscioli.com</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>la.barrique.94</t>
+          <t>RoscioliRistoranteSalumeria</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>labarriquemonti</t>
+          <t>roscioliroma</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11735,6 +11772,11 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>Si</t>
@@ -11742,7 +11784,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (la.barrique.94) | IG: trovato (labarriquemonti)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (RoscioliRistoranteSalumeria) | IG: trovato (roscioliroma)</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -11754,37 +11796,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Latteria</t>
+          <t>Santo Bevitore</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Vicolo della Scala, 1</t>
+          <t>Via Guglielmo Marconi, 8</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>06/58332008</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>latteriatrastevere</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>latteria_trastevere</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>329/2911575</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11797,19 +11819,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '18', 'closes': '00'}, 'venerdì': {'opens': '18', 'closes'</t>
-        </is>
-      </c>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: trovato (latteriatrastevere) | IG: trovato (latteria_trastevere)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -11821,32 +11833,32 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Roscioli</t>
+          <t>Da Cesare</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Via dei Giubbonari, 21/22</t>
+          <t>Via del Casaletto, 45</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>06/6875287</t>
+          <t>06/536015</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>www.salumeriaroscioli.com</t>
+          <t>www.trattoriadacesare.it</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>RoscioliRistoranteSalumeria</t>
+          <t>trattoriadacesare</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>roscioliroma</t>
+          <t>trattoriadacesare</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -11864,11 +11876,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
       <c r="O186" t="inlineStr">
         <is>
           <t>Si</t>
@@ -11876,7 +11883,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (RoscioliRistoranteSalumeria) | IG: trovato (roscioliroma)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (trattoriadacesare) | IG: trovato (trattoriadacesare)</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -11888,17 +11895,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Santo Bevitore</t>
+          <t>Da Danilo</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Via Guglielmo Marconi, 8</t>
+          <t>Via Petrarca, 13</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>329/2911575</t>
+          <t>06/77200111</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11911,9 +11918,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '13, 20', 'closes': '15, 23', 'break': '15–20'}, 'venerdì'</t>
+        </is>
+      </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -11925,32 +11937,32 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Da Cesare</t>
+          <t>Da Enzo al 29</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Via del Casaletto, 45</t>
+          <t>Via dei Vascellari, 29</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>06/536015</t>
+          <t>06/5812260</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>www.trattoriadacesare.it</t>
+          <t>www.daenzoal29.com</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>trattoriadacesare</t>
+          <t>daenzoal29</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>trattoriadacesare</t>
+          <t>daenzoal29</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11968,6 +11980,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12, 18:30', 'closes': '15, 22:30', 'break': '15–18:30'},</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>Si</t>
@@ -11975,7 +11997,7 @@
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (trattoriadacesare) | IG: trovato (trattoriadacesare)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (daenzoal29) | IG: trovato (daenzoal29)</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -11987,17 +12009,42 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Da Danilo</t>
+          <t>Felice</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Via Petrarca, 13</t>
+          <t>Via Mastro Giorgio, 29</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>06/77200111</t>
+          <t>06/5746800</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>www.feliceatestaccio.it</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>FeliceatestaccioRM</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>feliceatestaccio</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12012,12 +12059,17 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '13, 20', 'closes': '15, 23', 'break': '15–20'}, 'venerdì'</t>
+          <t>{'giovedì': {'opens': '12:30, 19', 'closes': '15:30, 23:30', 'break': '15:30–19'</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (FeliceatestaccioRM) | IG: trovato (feliceatestaccio)</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -12029,32 +12081,32 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Da Enzo al 29</t>
+          <t>Flavio al Velavevodetto</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Via dei Vascellari, 29</t>
+          <t>Piazza dei Quiriti, 4/5</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>06/5812260</t>
+          <t>06/36000009</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>www.daenzoal29.com</t>
+          <t>www.ristorantevelavevodetto.it</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>daenzoal29</t>
+          <t>velavevodetto</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>daenzoal29</t>
+          <t>velavevodetto</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -12079,7 +12131,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12, 18:30', 'closes': '15, 22:30', 'break': '15–18:30'},</t>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -12089,7 +12141,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (daenzoal29) | IG: trovato (daenzoal29)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (velavevodetto) | IG: trovato (velavevodetto)</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -12101,32 +12153,32 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Felice</t>
+          <t>Hosteria Grappolo d'Oro</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Via Mastro Giorgio, 29</t>
+          <t>Piazza della Cancelleria, 80</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>06/5746800</t>
+          <t>06/6897080</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>www.feliceatestaccio.it</t>
+          <t>www.hosteriagrappolodoro.it</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FeliceatestaccioRM</t>
+          <t>HosteriaGrappoloDOro</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>feliceatestaccio</t>
+          <t>Grappolo_d_Oro-Rome_Lazio</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -12144,16 +12196,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12:30, 19', 'closes': '15:30, 23:30', 'break': '15:30–19'</t>
-        </is>
-      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>Si</t>
@@ -12161,7 +12203,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (FeliceatestaccioRM) | IG: trovato (feliceatestaccio)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (HosteriaGrappoloDOro) | IG: trovato (Grappolo_d_Oro-Rome_Lazio)</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -12173,42 +12215,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Flavio al Velavevodetto</t>
+          <t>Il Vecchio Mulino</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Piazza dei Quiriti, 4/5</t>
+          <t>Via G. Marconi, 25/A</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>06/36000009</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>www.ristorantevelavevodetto.it</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>velavevodetto</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>velavevodetto</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>0761/780505</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12223,17 +12240,12 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
-        </is>
-      </c>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'giovedì': {'opens': '12:30, 19', 'closes': '15:15, 23', 'break': '15:15–19'},</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (velavevodetto) | IG: trovato (velavevodetto)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -12245,32 +12257,27 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Hosteria Grappolo d'Oro</t>
+          <t>Iotto</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Piazza della Cancelleria, 80</t>
+          <t>Corso Vittorio Emanuele, 96</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>06/6897080</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>www.hosteriagrappolodoro.it</t>
+          <t>06/9041746</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>HosteriaGrappoloDOro</t>
+          <t>OsteriaIotto</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Grappolo_d_Oro-Rome_Lazio</t>
+          <t>osteria.iotto</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -12288,6 +12295,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '14:30, 21:30', 'break': '14:30–</t>
+        </is>
+      </c>
       <c r="O193" t="inlineStr">
         <is>
           <t>Si</t>
@@ -12295,7 +12312,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (HosteriaGrappoloDOro) | IG: trovato (Grappolo_d_Oro-Rome_Lazio)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (OsteriaIotto) | IG: trovato (osteria.iotto)</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -12307,17 +12324,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Il Vecchio Mulino</t>
+          <t>La Briciola di Adriana</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Via G. Marconi, 25/A</t>
+          <t>Via Domenichino, 14</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>0761/780505</t>
+          <t>06/9459338</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12332,12 +12349,12 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12:30, 19', 'closes': '15:15, 23', 'break': '15:15–19'},</t>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '16, 23', 'break': '16–19:30'},</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -12349,27 +12366,32 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Iotto</t>
+          <t>La Tavernaccia</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Corso Vittorio Emanuele, 96</t>
+          <t>Via Giovanni di Castel Bolognese, 63</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>06/9041746</t>
+          <t>06/5812792</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>www.latavernaccia.com</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>OsteriaIotto</t>
+          <t>info.tavernaccia.roma</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>osteria.iotto</t>
+          <t>latavernacciaroma</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -12394,7 +12416,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '14:30, 21:30', 'break': '14:30–</t>
+          <t>{'giovedì': {'opens': 'Chiuso'}, 'venerdì': {'opens': '13, 19:30', 'closes': '15</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -12404,7 +12426,7 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (OsteriaIotto) | IG: trovato (osteria.iotto)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (info.tavernaccia.roma) | IG: trovato (latavernacciaroma)</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -12416,17 +12438,37 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>La Briciola di Adriana</t>
+          <t>Mangiadischi la moderna trattoria</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Via Domenichino, 14</t>
+          <t>Via Val di Sangro, 35</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>06/9459338</t>
+          <t>348/0081620</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>mangiadischilamodernatrattoria</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>mangiadischi_roma</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12434,19 +12476,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '16, 23', 'break': '16–19:30'},</t>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (mangiadischilamodernatrattoria) | IG: trovato (mangiadischi_roma)</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -12458,32 +12495,32 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>La Tavernaccia</t>
+          <t>N'Antro</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Via Giovanni di Castel Bolognese, 63</t>
+          <t>Largo Appio Claudio, 350</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>06/5812792</t>
+          <t>333/3900984</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>www.latavernaccia.com</t>
+          <t>www.nantrobistrot.it</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>info.tavernaccia.roma</t>
+          <t>profile.php?id=61551934953405</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>latavernacciaroma</t>
+          <t>nantrocalicietaglieri</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -12508,7 +12545,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': 'Chiuso'}, 'venerdì': {'opens': '13, 19:30', 'closes': '15</t>
+          <t>{'giovedì': {'opens': '12, 18:30', 'closes': '15, 23:30', 'break': '15–18:30'},</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -12518,7 +12555,7 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (info.tavernaccia.roma) | IG: trovato (latavernacciaroma)</t>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=61551934953405) | IG: trovato (nantrocalicietaglieri)</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -12530,37 +12567,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Mangiadischi la moderna trattoria</t>
+          <t>NU' Trattoria Italiana dal 1960</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Via Val di Sangro, 35</t>
+          <t>Via Prenestina, 27</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>348/0081620</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>mangiadischilamodernatrattoria</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>mangiadischi_roma</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>0775/56372</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12568,14 +12585,19 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '19', 'closes'</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (mangiadischilamodernatrattoria) | IG: trovato (mangiadischi_roma)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -12587,32 +12609,32 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>N'Antro</t>
+          <t>Osteria del Velodromo Vecchio</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Largo Appio Claudio, 350</t>
+          <t>Via Genzano, 139</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>333/3900984</t>
+          <t>06/7886793</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>www.nantrobistrot.it</t>
+          <t>www.osteriadelvelodromovecchio.it</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>profile.php?id=61551934953405</t>
+          <t>osteriadelvelodromovecchio</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>nantrocalicietaglieri</t>
+          <t>osteria_del_velodromo_vecchio</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -12637,7 +12659,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12, 18:30', 'closes': '15, 23:30', 'break': '15–18:30'},</t>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -12647,7 +12669,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=61551934953405) | IG: trovato (nantrocalicietaglieri)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (osteriadelvelodromovecchio) | IG: trovato (osteria_del_velodromo_vecchio)</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -12659,17 +12681,42 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>NU' Trattoria Italiana dal 1960</t>
+          <t>Osteria Fratelli Mori</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Via Prenestina, 27</t>
+          <t>Via dei Conciatori, 10</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0775/56372</t>
+          <t>331/3234399</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>www.osteriafratellimori.it</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>OsteriaFratelliMori</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>osteriafratellimori</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12682,14 +12729,14 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '19', 'closes'</t>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>TF: non trovato | FB: trovato (OsteriaFratelliMori) | IG: trovato (osteriafratellimori)</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -12701,37 +12748,27 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Osteria del Velodromo Vecchio</t>
+          <t>Piatto Romano</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Via Genzano, 139</t>
+          <t>Via Giovanni Battista Bodoni, 62</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>06/7886793</t>
+          <t>06/64014447</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>www.osteriadelvelodromovecchio.it</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>osteriadelvelodromovecchio</t>
+          <t>www.piattoromano.com</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>osteria_del_velodromo_vecchio</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>piatto_romano</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12749,11 +12786,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
-        </is>
-      </c>
       <c r="O201" t="inlineStr">
         <is>
           <t>Si</t>
@@ -12761,7 +12793,7 @@
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (osteriadelvelodromovecchio) | IG: trovato (osteria_del_velodromo_vecchio)</t>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (piatto_romano)</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -12771,48 +12803,67 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="inlineStr">
-        <is>
-          <t>Osteria del Vicolo Fatato</t>
-        </is>
-      </c>
-      <c r="B202" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Forno Fatato, 11</t>
-        </is>
-      </c>
-      <c r="C202" s="1" t="inlineStr">
-        <is>
-          <t>0775/503035</t>
-        </is>
-      </c>
-      <c r="D202" s="1" t="inlineStr"/>
-      <c r="E202" s="1" t="inlineStr"/>
-      <c r="F202" s="1" t="inlineStr"/>
-      <c r="G202" s="1" t="inlineStr"/>
-      <c r="H202" s="1" t="inlineStr"/>
-      <c r="I202" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J202" s="1" t="inlineStr">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Proloco Trastevere</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Via Goffredo Mameli, 23</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>06/45596137</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>www.prolocotrastevere.it</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>prolocotrastevere</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>prolocotrastevere</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K202" s="1" t="inlineStr"/>
-      <c r="L202" s="1" t="inlineStr"/>
-      <c r="M202" s="1" t="inlineStr"/>
-      <c r="N202" s="1" t="inlineStr"/>
-      <c r="O202" s="1" t="inlineStr"/>
-      <c r="P202" s="1" t="inlineStr"/>
-      <c r="Q202" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R202" s="1" t="inlineStr">
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (prolocotrastevere) | IG: trovato (prolocotrastevere)</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
@@ -12821,32 +12872,32 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Osteria Fratelli Mori</t>
+          <t>Santo Palato</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Via dei Conciatori, 10</t>
+          <t>Via Gallia, 28</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>331/3234399</t>
+          <t>06/77207354</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>www.osteriafratellimori.it</t>
+          <t>www.santopalatoroma.it</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>OsteriaFratelliMori</t>
+          <t>santopalatoroma</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>osteriafratellimori</t>
+          <t>santopalatoroma</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -12876,7 +12927,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (OsteriaFratelliMori) | IG: trovato (osteriafratellimori)</t>
+          <t>TF: non trovato | FB: trovato (santopalatoroma) | IG: trovato (santopalatoroma)</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -12886,76 +12937,67 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Piatto Romano</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Via Giovanni Battista Bodoni, 62</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>06/64014447</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>www.piattoromano.com</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>piatto_romano</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>Bless</t>
+        </is>
+      </c>
+      <c r="B204" s="1" t="inlineStr">
+        <is>
+          <t>Via dell’Indipendenza, 208</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="inlineStr">
+        <is>
+          <t>0771/030188</t>
+        </is>
+      </c>
+      <c r="D204" s="1" t="inlineStr"/>
+      <c r="E204" s="1" t="inlineStr"/>
+      <c r="F204" s="1" t="inlineStr"/>
+      <c r="G204" s="1" t="inlineStr"/>
+      <c r="H204" s="1" t="inlineStr"/>
+      <c r="I204" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J204" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (piatto_romano)</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K204" s="1" t="inlineStr"/>
+      <c r="L204" s="1" t="inlineStr"/>
+      <c r="M204" s="1" t="inlineStr"/>
+      <c r="N204" s="1" t="inlineStr"/>
+      <c r="O204" s="1" t="inlineStr"/>
+      <c r="P204" s="1" t="inlineStr"/>
+      <c r="Q204" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R204" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>Poldo e Gianna</t>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
         </is>
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>Vicolo Rosini, 6</t>
+          <t>Piazza delle Erbe, 16</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>06/6893499</t>
+          <t>348/7277746</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr"/>
@@ -12986,141 +13028,103 @@
       </c>
       <c r="R205" s="1" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Proloco Trastevere</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Via Goffredo Mameli, 23</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>06/45596137</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>www.prolocotrastevere.it</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>prolocotrastevere</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>prolocotrastevere</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>Osteria del Vicolo Fatato</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>Vicolo Forno Fatato, 11</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>0775/503035</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="inlineStr"/>
+      <c r="E206" s="1" t="inlineStr"/>
+      <c r="F206" s="1" t="inlineStr"/>
+      <c r="G206" s="1" t="inlineStr"/>
+      <c r="H206" s="1" t="inlineStr"/>
+      <c r="I206" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J206" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O206" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (prolocotrastevere) | IG: trovato (prolocotrastevere)</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K206" s="1" t="inlineStr"/>
+      <c r="L206" s="1" t="inlineStr"/>
+      <c r="M206" s="1" t="inlineStr"/>
+      <c r="N206" s="1" t="inlineStr"/>
+      <c r="O206" s="1" t="inlineStr"/>
+      <c r="P206" s="1" t="inlineStr"/>
+      <c r="Q206" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R206" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Santo Palato</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Via Gallia, 28</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>06/77207354</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>www.santopalatoroma.it</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>santopalatoroma</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>santopalatoroma</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>Poldo e Gianna</t>
+        </is>
+      </c>
+      <c r="B207" s="1" t="inlineStr">
+        <is>
+          <t>Vicolo Rosini, 6</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="inlineStr">
+        <is>
+          <t>06/6893499</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="inlineStr"/>
+      <c r="E207" s="1" t="inlineStr"/>
+      <c r="F207" s="1" t="inlineStr"/>
+      <c r="G207" s="1" t="inlineStr"/>
+      <c r="H207" s="1" t="inlineStr"/>
+      <c r="I207" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J207" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (santopalatoroma) | IG: trovato (santopalatoroma)</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
+      <c r="K207" s="1" t="inlineStr"/>
+      <c r="L207" s="1" t="inlineStr"/>
+      <c r="M207" s="1" t="inlineStr"/>
+      <c r="N207" s="1" t="inlineStr"/>
+      <c r="O207" s="1" t="inlineStr"/>
+      <c r="P207" s="1" t="inlineStr"/>
+      <c r="Q207" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R207" s="1" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13154,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J208" s="1" t="inlineStr"/>
+      <c r="J208" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K208" s="1" t="inlineStr"/>
       <c r="L208" s="1" t="inlineStr"/>
       <c r="M208" s="1" t="inlineStr"/>
@@ -13159,576 +13167,600 @@
       <c r="P208" s="1" t="inlineStr"/>
       <c r="Q208" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R208" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="inlineStr">
+      <c r="A209" t="inlineStr">
         <is>
           <t>Trattoria del Cimino dal 1895</t>
         </is>
       </c>
-      <c r="B209" s="1" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>Via Filippo Nicolai, 44</t>
         </is>
       </c>
-      <c r="C209" s="1" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>0761/646173</t>
         </is>
       </c>
-      <c r="D209" s="1" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>www.trattoriadelciminodal1895.it</t>
         </is>
       </c>
-      <c r="E209" s="1" t="inlineStr">
+      <c r="E209" t="inlineStr">
         <is>
           <t>TattoriadelCiminodal1895</t>
         </is>
       </c>
-      <c r="F209" s="1" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>trattoriadelcimino</t>
         </is>
       </c>
-      <c r="G209" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H209" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I209" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J209" s="1" t="inlineStr"/>
-      <c r="K209" s="1" t="inlineStr"/>
-      <c r="L209" s="1" t="inlineStr"/>
-      <c r="M209" s="1" t="inlineStr"/>
-      <c r="N209" s="1" t="inlineStr"/>
-      <c r="O209" s="1" t="inlineStr"/>
-      <c r="P209" s="1" t="inlineStr"/>
-      <c r="Q209" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R209" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (TattoriadelCiminodal1895) | IG: non trovato (trattoriadelcimino)</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="inlineStr">
+      <c r="A210" t="inlineStr">
         <is>
           <t>Trecca - cucina di mercato</t>
         </is>
       </c>
-      <c r="B210" s="1" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>Via Alessandro Severo, 222</t>
         </is>
       </c>
-      <c r="C210" s="1" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>06/88650867</t>
         </is>
       </c>
-      <c r="D210" s="1" t="inlineStr"/>
-      <c r="E210" s="1" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>treccacucinadimercato</t>
         </is>
       </c>
-      <c r="F210" s="1" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>trecca_roma</t>
         </is>
       </c>
-      <c r="G210" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H210" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I210" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J210" s="1" t="inlineStr"/>
-      <c r="K210" s="1" t="inlineStr"/>
-      <c r="L210" s="1" t="inlineStr"/>
-      <c r="M210" s="1" t="inlineStr"/>
-      <c r="N210" s="1" t="inlineStr"/>
-      <c r="O210" s="1" t="inlineStr"/>
-      <c r="P210" s="1" t="inlineStr"/>
-      <c r="Q210" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R210" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (treccacucinadimercato) | IG: non trovato (trecca_roma)</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="inlineStr">
+      <c r="A211" t="inlineStr">
         <is>
           <t>Aiki Pub</t>
         </is>
       </c>
-      <c r="B211" s="1" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>Via Gaetano Rappini, 23</t>
         </is>
       </c>
-      <c r="C211" s="1" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>378/3064424</t>
         </is>
       </c>
-      <c r="D211" s="1" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>www.aiki.it</t>
         </is>
       </c>
-      <c r="E211" s="1" t="inlineStr">
+      <c r="E211" t="inlineStr">
         <is>
           <t>aikipub</t>
         </is>
       </c>
-      <c r="F211" s="1" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>aiki.pub</t>
         </is>
       </c>
-      <c r="G211" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H211" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I211" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J211" s="1" t="inlineStr"/>
-      <c r="K211" s="1" t="inlineStr"/>
-      <c r="L211" s="1" t="inlineStr"/>
-      <c r="M211" s="1" t="inlineStr"/>
-      <c r="N211" s="1" t="inlineStr"/>
-      <c r="O211" s="1" t="inlineStr"/>
-      <c r="P211" s="1" t="inlineStr"/>
-      <c r="Q211" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R211" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (aikipub) | IG: non trovato (aiki.pub)</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="inlineStr">
+      <c r="A212" t="inlineStr">
         <is>
           <t>Casaloca</t>
         </is>
       </c>
-      <c r="B212" s="1" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>Corso di Francia, 207</t>
         </is>
       </c>
-      <c r="C212" s="1" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>06/40069361</t>
         </is>
       </c>
-      <c r="D212" s="1" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>www.casalocaroma.com</t>
         </is>
       </c>
-      <c r="E212" s="1" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>CasaLocaRoma</t>
         </is>
       </c>
-      <c r="F212" s="1" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>casalocaroma</t>
         </is>
       </c>
-      <c r="G212" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H212" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I212" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J212" s="1" t="inlineStr"/>
-      <c r="K212" s="1" t="inlineStr"/>
-      <c r="L212" s="1" t="inlineStr"/>
-      <c r="M212" s="1" t="inlineStr"/>
-      <c r="N212" s="1" t="inlineStr"/>
-      <c r="O212" s="1" t="inlineStr"/>
-      <c r="P212" s="1" t="inlineStr"/>
-      <c r="Q212" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R212" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (CasaLocaRoma) | IG: non trovato (casalocaroma)</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="inlineStr">
+      <c r="A213" t="inlineStr">
         <is>
           <t>Dar Basha</t>
         </is>
       </c>
-      <c r="B213" s="1" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Via Aurora, 10</t>
         </is>
       </c>
-      <c r="C213" s="1" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>06/94377684 - 375/8207355</t>
         </is>
       </c>
-      <c r="D213" s="1" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>www.darbasha.it</t>
         </is>
       </c>
-      <c r="E213" s="1" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>profile.php?id=61570232620829</t>
         </is>
       </c>
-      <c r="F213" s="1" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>darbasharistorante</t>
         </is>
       </c>
-      <c r="G213" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H213" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I213" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J213" s="1" t="inlineStr"/>
-      <c r="K213" s="1" t="inlineStr"/>
-      <c r="L213" s="1" t="inlineStr"/>
-      <c r="M213" s="1" t="inlineStr"/>
-      <c r="N213" s="1" t="inlineStr"/>
-      <c r="O213" s="1" t="inlineStr"/>
-      <c r="P213" s="1" t="inlineStr"/>
-      <c r="Q213" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R213" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=61570232620829) | IG: non trovato (darbasharistorante)</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="inlineStr">
+      <c r="A214" t="inlineStr">
         <is>
           <t>Galbi</t>
         </is>
       </c>
-      <c r="B214" s="1" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>Via Cremera, 21</t>
         </is>
       </c>
-      <c r="C214" s="1" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>06/8842132</t>
         </is>
       </c>
-      <c r="D214" s="1" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>www.galbiroma.it</t>
         </is>
       </c>
-      <c r="E214" s="1" t="inlineStr">
+      <c r="E214" t="inlineStr">
         <is>
           <t>galbiroma</t>
         </is>
       </c>
-      <c r="F214" s="1" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>galbiroma</t>
         </is>
       </c>
-      <c r="G214" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H214" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I214" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J214" s="1" t="inlineStr"/>
-      <c r="K214" s="1" t="inlineStr"/>
-      <c r="L214" s="1" t="inlineStr"/>
-      <c r="M214" s="1" t="inlineStr"/>
-      <c r="N214" s="1" t="inlineStr"/>
-      <c r="O214" s="1" t="inlineStr"/>
-      <c r="P214" s="1" t="inlineStr"/>
-      <c r="Q214" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R214" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (galbiroma) | IG: non trovato (galbiroma)</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="inlineStr">
+      <c r="A215" t="inlineStr">
         <is>
           <t>Green T.</t>
         </is>
       </c>
-      <c r="B215" s="1" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>Via di Pie' di Marmo, 28</t>
         </is>
       </c>
-      <c r="C215" s="1" t="inlineStr">
+      <c r="C215" t="inlineStr">
         <is>
           <t>06/6798628</t>
         </is>
       </c>
-      <c r="D215" s="1" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>www.green-tea.it</t>
         </is>
       </c>
-      <c r="E215" s="1" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>greenT.ufficiale</t>
         </is>
       </c>
-      <c r="F215" s="1" t="inlineStr"/>
-      <c r="G215" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H215" s="1" t="inlineStr"/>
-      <c r="I215" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J215" s="1" t="inlineStr"/>
-      <c r="K215" s="1" t="inlineStr"/>
-      <c r="L215" s="1" t="inlineStr"/>
-      <c r="M215" s="1" t="inlineStr"/>
-      <c r="N215" s="1" t="inlineStr"/>
-      <c r="O215" s="1" t="inlineStr"/>
-      <c r="P215" s="1" t="inlineStr"/>
-      <c r="Q215" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R215" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (greenT.ufficiale) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="inlineStr">
+      <c r="A216" t="inlineStr">
         <is>
           <t>Hasekura</t>
         </is>
       </c>
-      <c r="B216" s="1" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>Via dei Serpenti, 27</t>
         </is>
       </c>
-      <c r="C216" s="1" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>06/483648</t>
         </is>
       </c>
-      <c r="D216" s="1" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>www.hasekura.it</t>
         </is>
       </c>
-      <c r="E216" s="1" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t>RistoranteHasekura</t>
         </is>
       </c>
-      <c r="F216" s="1" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>hasekuraroma</t>
         </is>
       </c>
-      <c r="G216" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H216" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I216" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J216" s="1" t="inlineStr"/>
-      <c r="K216" s="1" t="inlineStr"/>
-      <c r="L216" s="1" t="inlineStr"/>
-      <c r="M216" s="1" t="inlineStr"/>
-      <c r="N216" s="1" t="inlineStr"/>
-      <c r="O216" s="1" t="inlineStr"/>
-      <c r="P216" s="1" t="inlineStr"/>
-      <c r="Q216" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R216" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (RistoranteHasekura) | IG: non trovato (hasekuraroma)</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="inlineStr">
+      <c r="A217" t="inlineStr">
         <is>
           <t>Hiromi La Maison</t>
         </is>
       </c>
-      <c r="B217" s="1" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>Via Reggio Emilia, 24</t>
         </is>
       </c>
-      <c r="C217" s="1" t="inlineStr">
+      <c r="C217" t="inlineStr">
         <is>
           <t>06/88936084</t>
         </is>
       </c>
-      <c r="D217" s="1" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>www.hiromimaison.it</t>
         </is>
       </c>
-      <c r="E217" s="1" t="inlineStr">
+      <c r="E217" t="inlineStr">
         <is>
           <t>profile.php?id=100095623623513</t>
         </is>
       </c>
-      <c r="F217" s="1" t="inlineStr">
+      <c r="F217" t="inlineStr">
         <is>
           <t>hiromimaison</t>
         </is>
       </c>
-      <c r="G217" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H217" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I217" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J217" s="1" t="inlineStr"/>
-      <c r="K217" s="1" t="inlineStr"/>
-      <c r="L217" s="1" t="inlineStr"/>
-      <c r="M217" s="1" t="inlineStr"/>
-      <c r="N217" s="1" t="inlineStr"/>
-      <c r="O217" s="1" t="inlineStr"/>
-      <c r="P217" s="1" t="inlineStr"/>
-      <c r="Q217" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R217" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=100095623623513) | IG: non trovato (hiromimaison)</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13790,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J218" s="1" t="inlineStr"/>
+      <c r="J218" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K218" s="1" t="inlineStr"/>
       <c r="L218" s="1" t="inlineStr"/>
       <c r="M218" s="1" t="inlineStr"/>
@@ -13767,332 +13803,347 @@
       <c r="P218" s="1" t="inlineStr"/>
       <c r="Q218" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R218" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="inlineStr">
+      <c r="A219" t="inlineStr">
         <is>
           <t>Kohaku</t>
         </is>
       </c>
-      <c r="B219" s="1" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Via Marche, 66</t>
         </is>
       </c>
-      <c r="C219" s="1" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>06/45665202</t>
         </is>
       </c>
-      <c r="D219" s="1" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>www.kohakurome.com</t>
         </is>
       </c>
-      <c r="E219" s="1" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>kohakurome</t>
         </is>
       </c>
-      <c r="F219" s="1" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>kohakurome</t>
         </is>
       </c>
-      <c r="G219" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H219" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I219" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J219" s="1" t="inlineStr"/>
-      <c r="K219" s="1" t="inlineStr"/>
-      <c r="L219" s="1" t="inlineStr"/>
-      <c r="M219" s="1" t="inlineStr"/>
-      <c r="N219" s="1" t="inlineStr"/>
-      <c r="O219" s="1" t="inlineStr"/>
-      <c r="P219" s="1" t="inlineStr"/>
-      <c r="Q219" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R219" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (kohakurome) | IG: non trovato (kohakurome)</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="inlineStr">
+      <c r="A220" t="inlineStr">
         <is>
           <t>La Punta Expendio de Agave</t>
         </is>
       </c>
-      <c r="B220" s="1" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>Via di Santa Cecilia, 8</t>
         </is>
       </c>
-      <c r="C220" s="1" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>06/5816665</t>
         </is>
       </c>
-      <c r="D220" s="1" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>www.lapuntaexpendiodeagave.com</t>
         </is>
       </c>
-      <c r="E220" s="1" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>expendiodeagave</t>
         </is>
       </c>
-      <c r="F220" s="1" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>expendiodeagave</t>
         </is>
       </c>
-      <c r="G220" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H220" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I220" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J220" s="1" t="inlineStr"/>
-      <c r="K220" s="1" t="inlineStr"/>
-      <c r="L220" s="1" t="inlineStr"/>
-      <c r="M220" s="1" t="inlineStr"/>
-      <c r="N220" s="1" t="inlineStr"/>
-      <c r="O220" s="1" t="inlineStr"/>
-      <c r="P220" s="1" t="inlineStr"/>
-      <c r="Q220" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R220" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (expendiodeagave) | IG: non trovato (expendiodeagave)</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="inlineStr">
+      <c r="A221" t="inlineStr">
         <is>
           <t>La Renardière</t>
         </is>
       </c>
-      <c r="B221" s="1" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>Viale Aventino, 31</t>
         </is>
       </c>
-      <c r="C221" s="1" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>06/87785445</t>
         </is>
       </c>
-      <c r="D221" s="1" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>larenardiereroma.eatbu.com</t>
         </is>
       </c>
-      <c r="E221" s="1" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>LaRenardière</t>
         </is>
       </c>
-      <c r="F221" s="1" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>larenardiereaventino</t>
         </is>
       </c>
-      <c r="G221" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H221" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I221" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J221" s="1" t="inlineStr"/>
-      <c r="K221" s="1" t="inlineStr"/>
-      <c r="L221" s="1" t="inlineStr"/>
-      <c r="M221" s="1" t="inlineStr"/>
-      <c r="N221" s="1" t="inlineStr"/>
-      <c r="O221" s="1" t="inlineStr"/>
-      <c r="P221" s="1" t="inlineStr"/>
-      <c r="Q221" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R221" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (LaRenardière) | IG: non trovato (larenardiereaventino)</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="inlineStr">
+      <c r="A222" t="inlineStr">
         <is>
           <t>Lin</t>
         </is>
       </c>
-      <c r="B222" s="1" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>Via Basento, 70/76</t>
         </is>
       </c>
-      <c r="C222" s="1" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>06/8546270</t>
         </is>
       </c>
-      <c r="D222" s="1" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>www.ristorante-lin.it</t>
         </is>
       </c>
-      <c r="E222" s="1" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>ristorantelin</t>
         </is>
       </c>
-      <c r="F222" s="1" t="inlineStr">
+      <c r="F222" t="inlineStr">
         <is>
           <t>ristorante.lin</t>
         </is>
       </c>
-      <c r="G222" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H222" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I222" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J222" s="1" t="inlineStr"/>
-      <c r="K222" s="1" t="inlineStr"/>
-      <c r="L222" s="1" t="inlineStr"/>
-      <c r="M222" s="1" t="inlineStr"/>
-      <c r="N222" s="1" t="inlineStr"/>
-      <c r="O222" s="1" t="inlineStr"/>
-      <c r="P222" s="1" t="inlineStr"/>
-      <c r="Q222" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R222" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ristorantelin) | IG: non trovato (ristorante.lin)</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="inlineStr">
+      <c r="A223" t="inlineStr">
         <is>
           <t>Mama-ya Ramen</t>
         </is>
       </c>
-      <c r="B223" s="1" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>Via Ostiense, 166/A</t>
         </is>
       </c>
-      <c r="C223" s="1" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>393/8123386</t>
         </is>
       </c>
-      <c r="D223" s="1" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>www.mamayaramen.it</t>
         </is>
       </c>
-      <c r="E223" s="1" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>mamayaramen</t>
         </is>
       </c>
-      <c r="F223" s="1" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>mamayaramen</t>
         </is>
       </c>
-      <c r="G223" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H223" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I223" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J223" s="1" t="inlineStr"/>
-      <c r="K223" s="1" t="inlineStr"/>
-      <c r="L223" s="1" t="inlineStr"/>
-      <c r="M223" s="1" t="inlineStr"/>
-      <c r="N223" s="1" t="inlineStr"/>
-      <c r="O223" s="1" t="inlineStr"/>
-      <c r="P223" s="1" t="inlineStr"/>
-      <c r="Q223" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R223" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (mamayaramen) | IG: non trovato (mamayaramen)</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14181,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J224" s="1" t="inlineStr"/>
+      <c r="J224" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K224" s="1" t="inlineStr"/>
       <c r="L224" s="1" t="inlineStr"/>
       <c r="M224" s="1" t="inlineStr"/>
@@ -14139,140 +14194,146 @@
       <c r="P224" s="1" t="inlineStr"/>
       <c r="Q224" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: non trovato (mi_ristorante)</t>
         </is>
       </c>
       <c r="R224" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="inlineStr">
+      <c r="A225" t="inlineStr">
         <is>
           <t>Mifang</t>
         </is>
       </c>
-      <c r="B225" s="1" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>Via Firenze, 30</t>
         </is>
       </c>
-      <c r="C225" s="1" t="inlineStr">
+      <c r="C225" t="inlineStr">
         <is>
           <t>06/87759632</t>
         </is>
       </c>
-      <c r="D225" s="1" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>www.mifang.it</t>
         </is>
       </c>
-      <c r="E225" s="1" t="inlineStr">
+      <c r="E225" t="inlineStr">
         <is>
           <t>MifangRoma</t>
         </is>
       </c>
-      <c r="F225" s="1" t="inlineStr">
+      <c r="F225" t="inlineStr">
         <is>
           <t>mifang_roma</t>
         </is>
       </c>
-      <c r="G225" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H225" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I225" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J225" s="1" t="inlineStr"/>
-      <c r="K225" s="1" t="inlineStr"/>
-      <c r="L225" s="1" t="inlineStr"/>
-      <c r="M225" s="1" t="inlineStr"/>
-      <c r="N225" s="1" t="inlineStr"/>
-      <c r="O225" s="1" t="inlineStr"/>
-      <c r="P225" s="1" t="inlineStr"/>
-      <c r="Q225" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R225" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (MifangRoma) | IG: non trovato (mifang_roma)</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="inlineStr">
+      <c r="A226" t="inlineStr">
         <is>
           <t>Mikachan</t>
         </is>
       </c>
-      <c r="B226" s="1" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>Via Torcegno, 39</t>
         </is>
       </c>
-      <c r="C226" s="1" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>338/1737246</t>
         </is>
       </c>
-      <c r="D226" s="1" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>www.mikachan.it</t>
         </is>
       </c>
-      <c r="E226" s="1" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>mikag72</t>
         </is>
       </c>
-      <c r="F226" s="1" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>mikachan_ristorante_giapponese</t>
         </is>
       </c>
-      <c r="G226" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H226" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I226" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J226" s="1" t="inlineStr"/>
-      <c r="K226" s="1" t="inlineStr"/>
-      <c r="L226" s="1" t="inlineStr"/>
-      <c r="M226" s="1" t="inlineStr"/>
-      <c r="N226" s="1" t="inlineStr"/>
-      <c r="O226" s="1" t="inlineStr"/>
-      <c r="P226" s="1" t="inlineStr"/>
-      <c r="Q226" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R226" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (mikag72) | IG: non trovato (mikachan_ristorante_giapponese)</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -14302,7 +14363,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J227" s="1" t="inlineStr"/>
+      <c r="J227" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K227" s="1" t="inlineStr"/>
       <c r="L227" s="1" t="inlineStr"/>
       <c r="M227" s="1" t="inlineStr"/>
@@ -14311,12 +14376,12 @@
       <c r="P227" s="1" t="inlineStr"/>
       <c r="Q227" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -14346,7 +14411,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J228" s="1" t="inlineStr"/>
+      <c r="J228" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K228" s="1" t="inlineStr"/>
       <c r="L228" s="1" t="inlineStr"/>
       <c r="M228" s="1" t="inlineStr"/>
@@ -14355,456 +14424,476 @@
       <c r="P228" s="1" t="inlineStr"/>
       <c r="Q228" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="inlineStr">
+      <c r="A229" t="inlineStr">
         <is>
           <t>Oolong</t>
         </is>
       </c>
-      <c r="B229" s="1" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>Piazza di San Paolo alla Regola, 40</t>
         </is>
       </c>
-      <c r="C229" s="1" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>06/21707385</t>
         </is>
       </c>
-      <c r="D229" s="1" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>www.oolong.it</t>
         </is>
       </c>
-      <c r="E229" s="1" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>Oolong-Roma-100070383215025</t>
         </is>
       </c>
-      <c r="F229" s="1" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>oolong_roma</t>
         </is>
       </c>
-      <c r="G229" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H229" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I229" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J229" s="1" t="inlineStr"/>
-      <c r="K229" s="1" t="inlineStr"/>
-      <c r="L229" s="1" t="inlineStr"/>
-      <c r="M229" s="1" t="inlineStr"/>
-      <c r="N229" s="1" t="inlineStr"/>
-      <c r="O229" s="1" t="inlineStr"/>
-      <c r="P229" s="1" t="inlineStr"/>
-      <c r="Q229" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R229" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Oolong-Roma-100070383215025) | IG: non trovato (oolong_roma)</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="inlineStr">
+      <c r="A230" t="inlineStr">
         <is>
           <t>Sakana Sushi</t>
         </is>
       </c>
-      <c r="B230" s="1" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>Via del Gazometro, 54</t>
         </is>
       </c>
-      <c r="C230" s="1" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>06/5744958</t>
         </is>
       </c>
-      <c r="D230" s="1" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>www.sakana.it</t>
         </is>
       </c>
-      <c r="E230" s="1" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>profile.php?id=100063643475130</t>
         </is>
       </c>
-      <c r="F230" s="1" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>sakanasushiroma</t>
         </is>
       </c>
-      <c r="G230" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H230" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I230" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J230" s="1" t="inlineStr"/>
-      <c r="K230" s="1" t="inlineStr"/>
-      <c r="L230" s="1" t="inlineStr"/>
-      <c r="M230" s="1" t="inlineStr"/>
-      <c r="N230" s="1" t="inlineStr"/>
-      <c r="O230" s="1" t="inlineStr"/>
-      <c r="P230" s="1" t="inlineStr"/>
-      <c r="Q230" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R230" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=100063643475130) | IG: non trovato (sakanasushiroma)</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="inlineStr">
+      <c r="A231" t="inlineStr">
         <is>
           <t>Sinosteria</t>
         </is>
       </c>
-      <c r="B231" s="1" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>Viale Guglielmo Marconi, 586</t>
         </is>
       </c>
-      <c r="C231" s="1" t="inlineStr">
+      <c r="C231" t="inlineStr">
         <is>
           <t>324/6399916</t>
         </is>
       </c>
-      <c r="D231" s="1" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>www.sinosteria.it</t>
         </is>
       </c>
-      <c r="E231" s="1" t="inlineStr">
+      <c r="E231" t="inlineStr">
         <is>
           <t>sinosteria</t>
         </is>
       </c>
-      <c r="F231" s="1" t="inlineStr">
+      <c r="F231" t="inlineStr">
         <is>
           <t>sinosteria</t>
         </is>
       </c>
-      <c r="G231" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H231" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I231" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J231" s="1" t="inlineStr"/>
-      <c r="K231" s="1" t="inlineStr"/>
-      <c r="L231" s="1" t="inlineStr"/>
-      <c r="M231" s="1" t="inlineStr"/>
-      <c r="N231" s="1" t="inlineStr"/>
-      <c r="O231" s="1" t="inlineStr"/>
-      <c r="P231" s="1" t="inlineStr"/>
-      <c r="Q231" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R231" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (sinosteria) | IG: non trovato (sinosteria)</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="inlineStr">
+      <c r="A232" t="inlineStr">
         <is>
           <t>Song</t>
         </is>
       </c>
-      <c r="B232" s="1" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>Via Valadier, 14</t>
         </is>
       </c>
-      <c r="C232" s="1" t="inlineStr">
+      <c r="C232" t="inlineStr">
         <is>
           <t>06/3215804</t>
         </is>
       </c>
-      <c r="D232" s="1" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>www.songdimsum.it</t>
         </is>
       </c>
-      <c r="E232" s="1" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>songdimsum</t>
         </is>
       </c>
-      <c r="F232" s="1" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>song_dimsum</t>
         </is>
       </c>
-      <c r="G232" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H232" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I232" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J232" s="1" t="inlineStr"/>
-      <c r="K232" s="1" t="inlineStr"/>
-      <c r="L232" s="1" t="inlineStr"/>
-      <c r="M232" s="1" t="inlineStr"/>
-      <c r="N232" s="1" t="inlineStr"/>
-      <c r="O232" s="1" t="inlineStr"/>
-      <c r="P232" s="1" t="inlineStr"/>
-      <c r="Q232" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R232" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (songdimsum) | IG: non trovato (song_dimsum)</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="inlineStr">
+      <c r="A233" t="inlineStr">
         <is>
           <t>Sushisen</t>
         </is>
       </c>
-      <c r="B233" s="1" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>Via Giuseppe Giulietti, 21/A</t>
         </is>
       </c>
-      <c r="C233" s="1" t="inlineStr">
+      <c r="C233" t="inlineStr">
         <is>
           <t>06/5756945</t>
         </is>
       </c>
-      <c r="D233" s="1" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>www.sushisen.it</t>
         </is>
       </c>
-      <c r="E233" s="1" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>RistoranteSushisen</t>
         </is>
       </c>
-      <c r="F233" s="1" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>sushisen_roma</t>
         </is>
       </c>
-      <c r="G233" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H233" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I233" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J233" s="1" t="inlineStr"/>
-      <c r="K233" s="1" t="inlineStr"/>
-      <c r="L233" s="1" t="inlineStr"/>
-      <c r="M233" s="1" t="inlineStr"/>
-      <c r="N233" s="1" t="inlineStr"/>
-      <c r="O233" s="1" t="inlineStr"/>
-      <c r="P233" s="1" t="inlineStr"/>
-      <c r="Q233" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R233" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (RistoranteSushisen) | IG: non trovato (sushisen_roma)</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="inlineStr">
+      <c r="A234" t="inlineStr">
         <is>
           <t>Umami - trattoria giapponese</t>
         </is>
       </c>
-      <c r="B234" s="1" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>Via Mario Menghini, 99</t>
         </is>
       </c>
-      <c r="C234" s="1" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>06/89138094</t>
         </is>
       </c>
-      <c r="D234" s="1" t="inlineStr"/>
-      <c r="E234" s="1" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>umami.roma</t>
         </is>
       </c>
-      <c r="F234" s="1" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>umami_roma</t>
         </is>
       </c>
-      <c r="G234" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H234" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I234" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J234" s="1" t="inlineStr"/>
-      <c r="K234" s="1" t="inlineStr"/>
-      <c r="L234" s="1" t="inlineStr"/>
-      <c r="M234" s="1" t="inlineStr"/>
-      <c r="N234" s="1" t="inlineStr"/>
-      <c r="O234" s="1" t="inlineStr"/>
-      <c r="P234" s="1" t="inlineStr"/>
-      <c r="Q234" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R234" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (umami.roma) | IG: non trovato (umami_roma)</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="inlineStr">
+      <c r="A235" t="inlineStr">
         <is>
           <t>Waraku</t>
         </is>
       </c>
-      <c r="B235" s="1" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>Via Prenestina, 321/A</t>
         </is>
       </c>
-      <c r="C235" s="1" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>06/21702358</t>
         </is>
       </c>
-      <c r="D235" s="1" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>www.warakuroma.webs.com</t>
         </is>
       </c>
-      <c r="E235" s="1" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>warakuramen</t>
         </is>
       </c>
-      <c r="F235" s="1" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>Waraku</t>
         </is>
       </c>
-      <c r="G235" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H235" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I235" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J235" s="1" t="inlineStr"/>
-      <c r="K235" s="1" t="inlineStr"/>
-      <c r="L235" s="1" t="inlineStr"/>
-      <c r="M235" s="1" t="inlineStr"/>
-      <c r="N235" s="1" t="inlineStr"/>
-      <c r="O235" s="1" t="inlineStr"/>
-      <c r="P235" s="1" t="inlineStr"/>
-      <c r="Q235" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R235" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (warakuramen) | IG: non trovato (Waraku)</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -14834,7 +14923,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J236" s="1" t="inlineStr"/>
+      <c r="J236" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K236" s="1" t="inlineStr"/>
       <c r="L236" s="1" t="inlineStr"/>
       <c r="M236" s="1" t="inlineStr"/>
@@ -14843,12 +14936,12 @@
       <c r="P236" s="1" t="inlineStr"/>
       <c r="Q236" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>
@@ -14878,7 +14971,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J237" s="1" t="inlineStr"/>
+      <c r="J237" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K237" s="1" t="inlineStr"/>
       <c r="L237" s="1" t="inlineStr"/>
       <c r="M237" s="1" t="inlineStr"/>
@@ -14887,12 +14984,12 @@
       <c r="P237" s="1" t="inlineStr"/>
       <c r="Q237" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -12937,240 +12937,330 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B204" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C204" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D204" s="1" t="inlineStr"/>
-      <c r="E204" s="1" t="inlineStr"/>
-      <c r="F204" s="1" t="inlineStr"/>
-      <c r="G204" s="1" t="inlineStr"/>
-      <c r="H204" s="1" t="inlineStr"/>
-      <c r="I204" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J204" s="1" t="inlineStr">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Trattoria del Cimino dal 1895</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Via Filippo Nicolai, 44</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>0761/646173</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>www.trattoriadelciminodal1895.it</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>TattoriadelCiminodal1895</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>trattoriadelcimino</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K204" s="1" t="inlineStr"/>
-      <c r="L204" s="1" t="inlineStr"/>
-      <c r="M204" s="1" t="inlineStr"/>
-      <c r="N204" s="1" t="inlineStr"/>
-      <c r="O204" s="1" t="inlineStr"/>
-      <c r="P204" s="1" t="inlineStr"/>
-      <c r="Q204" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R204" s="1" t="inlineStr">
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (TattoriadelCiminodal1895) | IG: non trovato (trattoriadelcimino)</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="inlineStr">
-        <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
-        </is>
-      </c>
-      <c r="B205" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Erbe, 16</t>
-        </is>
-      </c>
-      <c r="C205" s="1" t="inlineStr">
-        <is>
-          <t>348/7277746</t>
-        </is>
-      </c>
-      <c r="D205" s="1" t="inlineStr"/>
-      <c r="E205" s="1" t="inlineStr"/>
-      <c r="F205" s="1" t="inlineStr"/>
-      <c r="G205" s="1" t="inlineStr"/>
-      <c r="H205" s="1" t="inlineStr"/>
-      <c r="I205" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J205" s="1" t="inlineStr">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Trecca - cucina di mercato</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Via Alessandro Severo, 222</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>06/88650867</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>treccacucinadimercato</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>trecca_roma</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K205" s="1" t="inlineStr"/>
-      <c r="L205" s="1" t="inlineStr"/>
-      <c r="M205" s="1" t="inlineStr"/>
-      <c r="N205" s="1" t="inlineStr"/>
-      <c r="O205" s="1" t="inlineStr"/>
-      <c r="P205" s="1" t="inlineStr"/>
-      <c r="Q205" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R205" s="1" t="inlineStr">
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (treccacucinadimercato) | IG: non trovato (trecca_roma)</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="inlineStr">
-        <is>
-          <t>Osteria del Vicolo Fatato</t>
-        </is>
-      </c>
-      <c r="B206" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Forno Fatato, 11</t>
-        </is>
-      </c>
-      <c r="C206" s="1" t="inlineStr">
-        <is>
-          <t>0775/503035</t>
-        </is>
-      </c>
-      <c r="D206" s="1" t="inlineStr"/>
-      <c r="E206" s="1" t="inlineStr"/>
-      <c r="F206" s="1" t="inlineStr"/>
-      <c r="G206" s="1" t="inlineStr"/>
-      <c r="H206" s="1" t="inlineStr"/>
-      <c r="I206" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J206" s="1" t="inlineStr">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Aiki Pub</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Via Gaetano Rappini, 23</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>378/3064424</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>www.aiki.it</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>aikipub</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>aiki.pub</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K206" s="1" t="inlineStr"/>
-      <c r="L206" s="1" t="inlineStr"/>
-      <c r="M206" s="1" t="inlineStr"/>
-      <c r="N206" s="1" t="inlineStr"/>
-      <c r="O206" s="1" t="inlineStr"/>
-      <c r="P206" s="1" t="inlineStr"/>
-      <c r="Q206" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R206" s="1" t="inlineStr">
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (aikipub) | IG: non trovato (aiki.pub)</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="inlineStr">
-        <is>
-          <t>Poldo e Gianna</t>
-        </is>
-      </c>
-      <c r="B207" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Rosini, 6</t>
-        </is>
-      </c>
-      <c r="C207" s="1" t="inlineStr">
-        <is>
-          <t>06/6893499</t>
-        </is>
-      </c>
-      <c r="D207" s="1" t="inlineStr"/>
-      <c r="E207" s="1" t="inlineStr"/>
-      <c r="F207" s="1" t="inlineStr"/>
-      <c r="G207" s="1" t="inlineStr"/>
-      <c r="H207" s="1" t="inlineStr"/>
-      <c r="I207" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J207" s="1" t="inlineStr">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Casaloca</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Corso di Francia, 207</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>06/40069361</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>www.casalocaroma.com</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>CasaLocaRoma</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>casalocaroma</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K207" s="1" t="inlineStr"/>
-      <c r="L207" s="1" t="inlineStr"/>
-      <c r="M207" s="1" t="inlineStr"/>
-      <c r="N207" s="1" t="inlineStr"/>
-      <c r="O207" s="1" t="inlineStr"/>
-      <c r="P207" s="1" t="inlineStr"/>
-      <c r="Q207" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R207" s="1" t="inlineStr">
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (CasaLocaRoma) | IG: non trovato (casalocaroma)</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria A Casa Di Rita</t>
-        </is>
-      </c>
-      <c r="B208" s="1" t="inlineStr">
-        <is>
-          <t>Via delle Ciliegie, 145</t>
-        </is>
-      </c>
-      <c r="C208" s="1" t="inlineStr">
-        <is>
-          <t>338/9860960</t>
-        </is>
-      </c>
-      <c r="D208" s="1" t="inlineStr"/>
-      <c r="E208" s="1" t="inlineStr"/>
-      <c r="F208" s="1" t="inlineStr"/>
-      <c r="G208" s="1" t="inlineStr"/>
-      <c r="H208" s="1" t="inlineStr"/>
-      <c r="I208" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J208" s="1" t="inlineStr">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Dar Basha</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Via Aurora, 10</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>06/94377684 - 375/8207355</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>www.darbasha.it</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>profile.php?id=61570232620829</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>darbasharistorante</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K208" s="1" t="inlineStr"/>
-      <c r="L208" s="1" t="inlineStr"/>
-      <c r="M208" s="1" t="inlineStr"/>
-      <c r="N208" s="1" t="inlineStr"/>
-      <c r="O208" s="1" t="inlineStr"/>
-      <c r="P208" s="1" t="inlineStr"/>
-      <c r="Q208" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R208" s="1" t="inlineStr">
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=61570232620829) | IG: non trovato (darbasharistorante)</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
@@ -13179,32 +13269,32 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Trattoria del Cimino dal 1895</t>
+          <t>Galbi</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Via Filippo Nicolai, 44</t>
+          <t>Via Cremera, 21</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>0761/646173</t>
+          <t>06/8842132</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>www.trattoriadelciminodal1895.it</t>
+          <t>www.galbiroma.it</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>TattoriadelCiminodal1895</t>
+          <t>galbiroma</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>trattoriadelcimino</t>
+          <t>galbiroma</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -13234,7 +13324,7 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (TattoriadelCiminodal1895) | IG: non trovato (trattoriadelcimino)</t>
+          <t>TF: non trovato | FB: trovato (galbiroma) | IG: non trovato (galbiroma)</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -13246,27 +13336,27 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Trecca - cucina di mercato</t>
+          <t>Green T.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Via Alessandro Severo, 222</t>
+          <t>Via di Pie' di Marmo, 28</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>06/88650867</t>
+          <t>06/6798628</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>www.green-tea.it</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>treccacucinadimercato</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>trecca_roma</t>
+          <t>greenT.ufficiale</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -13274,11 +13364,6 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I210" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -13296,7 +13381,7 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (treccacucinadimercato) | IG: non trovato (trecca_roma)</t>
+          <t>TF: non trovato | FB: trovato (greenT.ufficiale) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -13308,32 +13393,32 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Aiki Pub</t>
+          <t>Hasekura</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Via Gaetano Rappini, 23</t>
+          <t>Via dei Serpenti, 27</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>378/3064424</t>
+          <t>06/483648</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>www.aiki.it</t>
+          <t>www.hasekura.it</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>aikipub</t>
+          <t>RistoranteHasekura</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>aiki.pub</t>
+          <t>hasekuraroma</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -13363,7 +13448,7 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (aikipub) | IG: non trovato (aiki.pub)</t>
+          <t>TF: non trovato | FB: trovato (RistoranteHasekura) | IG: non trovato (hasekuraroma)</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -13375,32 +13460,32 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Casaloca</t>
+          <t>Hiromi La Maison</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Corso di Francia, 207</t>
+          <t>Via Reggio Emilia, 24</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>06/40069361</t>
+          <t>06/88936084</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>www.casalocaroma.com</t>
+          <t>www.hiromimaison.it</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>CasaLocaRoma</t>
+          <t>profile.php?id=100095623623513</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>casalocaroma</t>
+          <t>hiromimaison</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -13430,7 +13515,7 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (CasaLocaRoma) | IG: non trovato (casalocaroma)</t>
+          <t>TF: non trovato | FB: trovato (profile.php?id=100095623623513) | IG: non trovato (hiromimaison)</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -13442,32 +13527,32 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Dar Basha</t>
+          <t>Kohaku</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Via Aurora, 10</t>
+          <t>Via Marche, 66</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>06/94377684 - 375/8207355</t>
+          <t>06/45665202</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>www.darbasha.it</t>
+          <t>www.kohakurome.com</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>profile.php?id=61570232620829</t>
+          <t>kohakurome</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>darbasharistorante</t>
+          <t>kohakurome</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -13497,7 +13582,7 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (profile.php?id=61570232620829) | IG: non trovato (darbasharistorante)</t>
+          <t>TF: non trovato | FB: trovato (kohakurome) | IG: non trovato (kohakurome)</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
@@ -13509,32 +13594,32 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Galbi</t>
+          <t>La Punta Expendio de Agave</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Via Cremera, 21</t>
+          <t>Via di Santa Cecilia, 8</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>06/8842132</t>
+          <t>06/5816665</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>www.galbiroma.it</t>
+          <t>www.lapuntaexpendiodeagave.com</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>galbiroma</t>
+          <t>expendiodeagave</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>galbiroma</t>
+          <t>expendiodeagave</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -13564,7 +13649,7 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (galbiroma) | IG: non trovato (galbiroma)</t>
+          <t>TF: non trovato | FB: trovato (expendiodeagave) | IG: non trovato (expendiodeagave)</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
@@ -13576,27 +13661,32 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Green T.</t>
+          <t>La Renardière</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Via di Pie' di Marmo, 28</t>
+          <t>Viale Aventino, 31</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>06/6798628</t>
+          <t>06/87785445</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>www.green-tea.it</t>
+          <t>larenardiereroma.eatbu.com</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>greenT.ufficiale</t>
+          <t>LaRenardière</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>larenardiereaventino</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -13604,6 +13694,11 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I215" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -13621,7 +13716,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (greenT.ufficiale) | IG: nessun handle</t>
+          <t>TF: non trovato | FB: trovato (LaRenardière) | IG: non trovato (larenardiereaventino)</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -13633,32 +13728,32 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Hasekura</t>
+          <t>Lin</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Via dei Serpenti, 27</t>
+          <t>Via Basento, 70/76</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>06/483648</t>
+          <t>06/8546270</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>www.hasekura.it</t>
+          <t>www.ristorante-lin.it</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>RistoranteHasekura</t>
+          <t>ristorantelin</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>hasekuraroma</t>
+          <t>ristorante.lin</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -13688,7 +13783,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (RistoranteHasekura) | IG: non trovato (hasekuraroma)</t>
+          <t>TF: non trovato | FB: trovato (ristorantelin) | IG: non trovato (ristorante.lin)</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -13700,32 +13795,32 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Hiromi La Maison</t>
+          <t>Mama-ya Ramen</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Via Reggio Emilia, 24</t>
+          <t>Via Ostiense, 166/A</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>06/88936084</t>
+          <t>393/8123386</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>www.hiromimaison.it</t>
+          <t>www.mamayaramen.it</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>profile.php?id=100095623623513</t>
+          <t>mamayaramen</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>hiromimaison</t>
+          <t>mamayaramen</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -13755,7 +13850,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (profile.php?id=100095623623513) | IG: non trovato (hiromimaison)</t>
+          <t>TF: non trovato | FB: trovato (mamayaramen) | IG: non trovato (mamayaramen)</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -13765,48 +13860,67 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="inlineStr">
-        <is>
-          <t>Ie Koji Japanese Izakaya</t>
-        </is>
-      </c>
-      <c r="B218" s="1" t="inlineStr">
-        <is>
-          <t>Via Marcantonio Bragadin, 13</t>
-        </is>
-      </c>
-      <c r="C218" s="1" t="inlineStr">
-        <is>
-          <t>348/4302368 - 06/69459860</t>
-        </is>
-      </c>
-      <c r="D218" s="1" t="inlineStr"/>
-      <c r="E218" s="1" t="inlineStr"/>
-      <c r="F218" s="1" t="inlineStr"/>
-      <c r="G218" s="1" t="inlineStr"/>
-      <c r="H218" s="1" t="inlineStr"/>
-      <c r="I218" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J218" s="1" t="inlineStr">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Mifang</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Via Firenze, 30</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>06/87759632</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>www.mifang.it</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>MifangRoma</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>mifang_roma</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K218" s="1" t="inlineStr"/>
-      <c r="L218" s="1" t="inlineStr"/>
-      <c r="M218" s="1" t="inlineStr"/>
-      <c r="N218" s="1" t="inlineStr"/>
-      <c r="O218" s="1" t="inlineStr"/>
-      <c r="P218" s="1" t="inlineStr"/>
-      <c r="Q218" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R218" s="1" t="inlineStr">
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (MifangRoma) | IG: non trovato (mifang_roma)</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
@@ -13815,32 +13929,32 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Kohaku</t>
+          <t>Mikachan</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Via Marche, 66</t>
+          <t>Via Torcegno, 39</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>06/45665202</t>
+          <t>338/1737246</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>www.kohakurome.com</t>
+          <t>www.mikachan.it</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>kohakurome</t>
+          <t>mikag72</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>kohakurome</t>
+          <t>mikachan_ristorante_giapponese</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -13870,7 +13984,7 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (kohakurome) | IG: non trovato (kohakurome)</t>
+          <t>TF: non trovato | FB: trovato (mikag72) | IG: non trovato (mikachan_ristorante_giapponese)</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
@@ -13882,32 +13996,32 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>La Punta Expendio de Agave</t>
+          <t>Oolong</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Via di Santa Cecilia, 8</t>
+          <t>Piazza di San Paolo alla Regola, 40</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>06/5816665</t>
+          <t>06/21707385</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>www.lapuntaexpendiodeagave.com</t>
+          <t>www.oolong.it</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>expendiodeagave</t>
+          <t>Oolong-Roma-100070383215025</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>expendiodeagave</t>
+          <t>oolong_roma</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -13937,7 +14051,7 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (expendiodeagave) | IG: non trovato (expendiodeagave)</t>
+          <t>TF: non trovato | FB: trovato (Oolong-Roma-100070383215025) | IG: non trovato (oolong_roma)</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -13949,32 +14063,32 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>La Renardière</t>
+          <t>Sakana Sushi</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Viale Aventino, 31</t>
+          <t>Via del Gazometro, 54</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>06/87785445</t>
+          <t>06/5744958</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>larenardiereroma.eatbu.com</t>
+          <t>www.sakana.it</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>LaRenardière</t>
+          <t>profile.php?id=100063643475130</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>larenardiereaventino</t>
+          <t>sakanasushiroma</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -14004,7 +14118,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (LaRenardière) | IG: non trovato (larenardiereaventino)</t>
+          <t>TF: non trovato | FB: trovato (profile.php?id=100063643475130) | IG: non trovato (sakanasushiroma)</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -14016,32 +14130,32 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Lin</t>
+          <t>Sinosteria</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Via Basento, 70/76</t>
+          <t>Viale Guglielmo Marconi, 586</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>06/8546270</t>
+          <t>324/6399916</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>www.ristorante-lin.it</t>
+          <t>www.sinosteria.it</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>ristorantelin</t>
+          <t>sinosteria</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>ristorante.lin</t>
+          <t>sinosteria</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -14071,7 +14185,7 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (ristorantelin) | IG: non trovato (ristorante.lin)</t>
+          <t>TF: non trovato | FB: trovato (sinosteria) | IG: non trovato (sinosteria)</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -14083,32 +14197,32 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Mama-ya Ramen</t>
+          <t>Song</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Via Ostiense, 166/A</t>
+          <t>Via Valadier, 14</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>393/8123386</t>
+          <t>06/3215804</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>www.mamayaramen.it</t>
+          <t>www.songdimsum.it</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>mamayaramen</t>
+          <t>songdimsum</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>mamayaramen</t>
+          <t>song_dimsum</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -14138,7 +14252,7 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (mamayaramen) | IG: non trovato (mamayaramen)</t>
+          <t>TF: non trovato | FB: trovato (songdimsum) | IG: non trovato (song_dimsum)</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -14148,56 +14262,67 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="inlineStr">
-        <is>
-          <t>Mi Cucina Cinese Contemporanea</t>
-        </is>
-      </c>
-      <c r="B224" s="1" t="inlineStr">
-        <is>
-          <t>Via Giovanni Botero, 31/33</t>
-        </is>
-      </c>
-      <c r="C224" s="1" t="inlineStr">
-        <is>
-          <t>06/89346223</t>
-        </is>
-      </c>
-      <c r="D224" s="1" t="inlineStr"/>
-      <c r="E224" s="1" t="inlineStr"/>
-      <c r="F224" s="1" t="inlineStr">
-        <is>
-          <t>mi_ristorante</t>
-        </is>
-      </c>
-      <c r="G224" s="1" t="inlineStr"/>
-      <c r="H224" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I224" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J224" s="1" t="inlineStr">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sushisen</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Via Giuseppe Giulietti, 21/A</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>06/5756945</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>www.sushisen.it</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>RistoranteSushisen</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>sushisen_roma</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K224" s="1" t="inlineStr"/>
-      <c r="L224" s="1" t="inlineStr"/>
-      <c r="M224" s="1" t="inlineStr"/>
-      <c r="N224" s="1" t="inlineStr"/>
-      <c r="O224" s="1" t="inlineStr"/>
-      <c r="P224" s="1" t="inlineStr"/>
-      <c r="Q224" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: non trovato (mi_ristorante)</t>
-        </is>
-      </c>
-      <c r="R224" s="1" t="inlineStr">
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (RistoranteSushisen) | IG: non trovato (sushisen_roma)</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
         <is>
           <t>25/05/2026</t>
         </is>
@@ -14206,32 +14331,27 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Mifang</t>
+          <t>Umami - trattoria giapponese</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Via Firenze, 30</t>
+          <t>Via Mario Menghini, 99</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>06/87759632</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>www.mifang.it</t>
+          <t>06/89138094</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>MifangRoma</t>
+          <t>umami.roma</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>mifang_roma</t>
+          <t>umami_roma</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -14261,7 +14381,7 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (MifangRoma) | IG: non trovato (mifang_roma)</t>
+          <t>TF: non trovato | FB: trovato (umami.roma) | IG: non trovato (umami_roma)</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -14273,32 +14393,32 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Mikachan</t>
+          <t>Waraku</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Via Torcegno, 39</t>
+          <t>Via Prenestina, 321/A</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>338/1737246</t>
+          <t>06/21702358</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>www.mikachan.it</t>
+          <t>www.warakuroma.webs.com</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>mikag72</t>
+          <t>warakuramen</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>mikachan_ristorante_giapponese</t>
+          <t>Waraku</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -14328,7 +14448,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (mikag72) | IG: non trovato (mikachan_ristorante_giapponese)</t>
+          <t>TF: non trovato | FB: trovato (warakuramen) | IG: non trovato (Waraku)</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -14340,17 +14460,17 @@
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>Mrgda Ristorante</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>Via Prenestina, 182</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>329/933355</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D227" s="1" t="inlineStr"/>
@@ -14381,24 +14501,24 @@
       </c>
       <c r="R227" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>Nomisan</t>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
         </is>
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>Viale Gianluigi Bonelli, 237</t>
+          <t>Piazza delle Erbe, 16</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>342/8036080</t>
+          <t>348/7277746</t>
         </is>
       </c>
       <c r="D228" s="1" t="inlineStr"/>
@@ -14429,312 +14549,221 @@
       </c>
       <c r="R228" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Oolong</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Piazza di San Paolo alla Regola, 40</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>06/21707385</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>www.oolong.it</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Oolong-Roma-100070383215025</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>oolong_roma</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J229" t="inlineStr">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>Osteria del Vicolo Fatato</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="inlineStr">
+        <is>
+          <t>Vicolo Forno Fatato, 11</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>0775/503035</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="inlineStr"/>
+      <c r="E229" s="1" t="inlineStr"/>
+      <c r="F229" s="1" t="inlineStr"/>
+      <c r="G229" s="1" t="inlineStr"/>
+      <c r="H229" s="1" t="inlineStr"/>
+      <c r="I229" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J229" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Oolong-Roma-100070383215025) | IG: non trovato (oolong_roma)</t>
-        </is>
-      </c>
-      <c r="R229" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
+      <c r="K229" s="1" t="inlineStr"/>
+      <c r="L229" s="1" t="inlineStr"/>
+      <c r="M229" s="1" t="inlineStr"/>
+      <c r="N229" s="1" t="inlineStr"/>
+      <c r="O229" s="1" t="inlineStr"/>
+      <c r="P229" s="1" t="inlineStr"/>
+      <c r="Q229" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R229" s="1" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Sakana Sushi</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Via del Gazometro, 54</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>06/5744958</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>www.sakana.it</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>profile.php?id=100063643475130</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>sakanasushiroma</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>Poldo e Gianna</t>
+        </is>
+      </c>
+      <c r="B230" s="1" t="inlineStr">
+        <is>
+          <t>Vicolo Rosini, 6</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>06/6893499</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="inlineStr"/>
+      <c r="E230" s="1" t="inlineStr"/>
+      <c r="F230" s="1" t="inlineStr"/>
+      <c r="G230" s="1" t="inlineStr"/>
+      <c r="H230" s="1" t="inlineStr"/>
+      <c r="I230" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J230" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (profile.php?id=100063643475130) | IG: non trovato (sakanasushiroma)</t>
-        </is>
-      </c>
-      <c r="R230" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
+      <c r="K230" s="1" t="inlineStr"/>
+      <c r="L230" s="1" t="inlineStr"/>
+      <c r="M230" s="1" t="inlineStr"/>
+      <c r="N230" s="1" t="inlineStr"/>
+      <c r="O230" s="1" t="inlineStr"/>
+      <c r="P230" s="1" t="inlineStr"/>
+      <c r="Q230" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R230" s="1" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Sinosteria</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Viale Guglielmo Marconi, 586</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>324/6399916</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>www.sinosteria.it</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>sinosteria</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>sinosteria</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>Trattoria A Casa Di Rita</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t>Via delle Ciliegie, 145</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>338/9860960</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr"/>
+      <c r="E231" s="1" t="inlineStr"/>
+      <c r="F231" s="1" t="inlineStr"/>
+      <c r="G231" s="1" t="inlineStr"/>
+      <c r="H231" s="1" t="inlineStr"/>
+      <c r="I231" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J231" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (sinosteria) | IG: non trovato (sinosteria)</t>
-        </is>
-      </c>
-      <c r="R231" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
+      <c r="K231" s="1" t="inlineStr"/>
+      <c r="L231" s="1" t="inlineStr"/>
+      <c r="M231" s="1" t="inlineStr"/>
+      <c r="N231" s="1" t="inlineStr"/>
+      <c r="O231" s="1" t="inlineStr"/>
+      <c r="P231" s="1" t="inlineStr"/>
+      <c r="Q231" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R231" s="1" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Song</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Via Valadier, 14</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>06/3215804</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>www.songdimsum.it</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>songdimsum</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>song_dimsum</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>Ie Koji Japanese Izakaya</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="inlineStr">
+        <is>
+          <t>Via Marcantonio Bragadin, 13</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>348/4302368 - 06/69459860</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="inlineStr"/>
+      <c r="E232" s="1" t="inlineStr"/>
+      <c r="F232" s="1" t="inlineStr"/>
+      <c r="G232" s="1" t="inlineStr"/>
+      <c r="H232" s="1" t="inlineStr"/>
+      <c r="I232" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J232" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (songdimsum) | IG: non trovato (song_dimsum)</t>
-        </is>
-      </c>
-      <c r="R232" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
+      <c r="K232" s="1" t="inlineStr"/>
+      <c r="L232" s="1" t="inlineStr"/>
+      <c r="M232" s="1" t="inlineStr"/>
+      <c r="N232" s="1" t="inlineStr"/>
+      <c r="O232" s="1" t="inlineStr"/>
+      <c r="P232" s="1" t="inlineStr"/>
+      <c r="Q232" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R232" s="1" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Sushisen</t>
+          <t>Mi Cucina Cinese Contemporanea</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Via Giuseppe Giulietti, 21/A</t>
+          <t>Via Giovanni Botero, 31/33</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>06/5756945</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>www.sushisen.it</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>RistoranteSushisen</t>
+          <t>06/89346223</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>sushisen_roma</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>mi_ristorante</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14759,141 +14788,108 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (RistoranteSushisen) | IG: non trovato (sushisen_roma)</t>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (mi_ristorante)</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Umami - trattoria giapponese</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Via Mario Menghini, 99</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>06/89138094</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>umami.roma</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>umami_roma</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>Mrgda Ristorante</t>
+        </is>
+      </c>
+      <c r="B234" s="1" t="inlineStr">
+        <is>
+          <t>Via Prenestina, 182</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="inlineStr">
+        <is>
+          <t>329/933355</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="inlineStr"/>
+      <c r="E234" s="1" t="inlineStr"/>
+      <c r="F234" s="1" t="inlineStr"/>
+      <c r="G234" s="1" t="inlineStr"/>
+      <c r="H234" s="1" t="inlineStr"/>
+      <c r="I234" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J234" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (umami.roma) | IG: non trovato (umami_roma)</t>
-        </is>
-      </c>
-      <c r="R234" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
+      <c r="K234" s="1" t="inlineStr"/>
+      <c r="L234" s="1" t="inlineStr"/>
+      <c r="M234" s="1" t="inlineStr"/>
+      <c r="N234" s="1" t="inlineStr"/>
+      <c r="O234" s="1" t="inlineStr"/>
+      <c r="P234" s="1" t="inlineStr"/>
+      <c r="Q234" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R234" s="1" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Waraku</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 321/A</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>06/21702358</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>www.warakuroma.webs.com</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>warakuramen</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>Waraku</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>Nomisan</t>
+        </is>
+      </c>
+      <c r="B235" s="1" t="inlineStr">
+        <is>
+          <t>Viale Gianluigi Bonelli, 237</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>342/8036080</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr"/>
+      <c r="E235" s="1" t="inlineStr"/>
+      <c r="F235" s="1" t="inlineStr"/>
+      <c r="G235" s="1" t="inlineStr"/>
+      <c r="H235" s="1" t="inlineStr"/>
+      <c r="I235" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J235" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (warakuramen) | IG: non trovato (Waraku)</t>
-        </is>
-      </c>
-      <c r="R235" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
+      <c r="K235" s="1" t="inlineStr"/>
+      <c r="L235" s="1" t="inlineStr"/>
+      <c r="M235" s="1" t="inlineStr"/>
+      <c r="N235" s="1" t="inlineStr"/>
+      <c r="O235" s="1" t="inlineStr"/>
+      <c r="P235" s="1" t="inlineStr"/>
+      <c r="Q235" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R235" s="1" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14937,7 @@
       </c>
       <c r="R236" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -14989,327 +14985,342 @@
       </c>
       <c r="R237" s="1" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="inlineStr">
+      <c r="A238" t="inlineStr">
         <is>
           <t>Avenida Calò</t>
         </is>
       </c>
-      <c r="B238" s="1" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>Viale Pinturicchio, 38/42</t>
         </is>
       </c>
-      <c r="C238" s="1" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>06/89238209</t>
         </is>
       </c>
-      <c r="D238" s="1" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>avenidacalo.it</t>
         </is>
       </c>
-      <c r="E238" s="1" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>avenidacalo</t>
         </is>
       </c>
-      <c r="F238" s="1" t="inlineStr">
+      <c r="F238" t="inlineStr">
         <is>
           <t>avenidacalo</t>
         </is>
       </c>
-      <c r="G238" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H238" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I238" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J238" s="1" t="inlineStr"/>
-      <c r="K238" s="1" t="inlineStr"/>
-      <c r="L238" s="1" t="inlineStr"/>
-      <c r="M238" s="1" t="inlineStr"/>
-      <c r="N238" s="1" t="inlineStr"/>
-      <c r="O238" s="1" t="inlineStr"/>
-      <c r="P238" s="1" t="inlineStr"/>
-      <c r="Q238" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R238" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (avenidacalo) | IG: trovato (avenidacalo)</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="inlineStr">
+      <c r="A239" t="inlineStr">
         <is>
           <t>Baccio e i Gradini</t>
         </is>
       </c>
-      <c r="B239" s="1" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>Viale della Piramide Cestia, 25</t>
         </is>
       </c>
-      <c r="C239" s="1" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>351/8823737</t>
         </is>
       </c>
-      <c r="D239" s="1" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>www.baccioeigradini.it</t>
         </is>
       </c>
-      <c r="E239" s="1" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>baccioeigradini</t>
         </is>
       </c>
-      <c r="F239" s="1" t="inlineStr">
+      <c r="F239" t="inlineStr">
         <is>
           <t>baccioeigradini</t>
         </is>
       </c>
-      <c r="G239" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H239" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I239" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J239" s="1" t="inlineStr"/>
-      <c r="K239" s="1" t="inlineStr"/>
-      <c r="L239" s="1" t="inlineStr"/>
-      <c r="M239" s="1" t="inlineStr"/>
-      <c r="N239" s="1" t="inlineStr"/>
-      <c r="O239" s="1" t="inlineStr"/>
-      <c r="P239" s="1" t="inlineStr"/>
-      <c r="Q239" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R239" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (baccioeigradini) | IG: trovato (baccioeigradini)</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="inlineStr">
+      <c r="A240" t="inlineStr">
         <is>
           <t>Berberè</t>
         </is>
       </c>
-      <c r="B240" s="1" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>Via Mantova, 5</t>
         </is>
       </c>
-      <c r="C240" s="1" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>06/45654390</t>
         </is>
       </c>
-      <c r="D240" s="1" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>www.berbere.it</t>
         </is>
       </c>
-      <c r="E240" s="1" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>berbereroma</t>
         </is>
       </c>
-      <c r="F240" s="1" t="inlineStr">
+      <c r="F240" t="inlineStr">
         <is>
           <t>berbereroma</t>
         </is>
       </c>
-      <c r="G240" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H240" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I240" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J240" s="1" t="inlineStr"/>
-      <c r="K240" s="1" t="inlineStr"/>
-      <c r="L240" s="1" t="inlineStr"/>
-      <c r="M240" s="1" t="inlineStr"/>
-      <c r="N240" s="1" t="inlineStr"/>
-      <c r="O240" s="1" t="inlineStr"/>
-      <c r="P240" s="1" t="inlineStr"/>
-      <c r="Q240" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R240" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (berbereroma) | IG: trovato (berbereroma)</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="inlineStr">
+      <c r="A241" t="inlineStr">
         <is>
           <t>Brucio - La Contemporanea</t>
         </is>
       </c>
-      <c r="B241" s="1" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>Via degli Stradivari, 1</t>
         </is>
       </c>
-      <c r="C241" s="1" t="inlineStr">
+      <c r="C241" t="inlineStr">
         <is>
           <t>06/83082083</t>
         </is>
       </c>
-      <c r="D241" s="1" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>www.bruciolacontemporanea.it</t>
         </is>
       </c>
-      <c r="E241" s="1" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>bruciolacontemporanea</t>
         </is>
       </c>
-      <c r="F241" s="1" t="inlineStr">
+      <c r="F241" t="inlineStr">
         <is>
           <t>brucio_lacontemporanea</t>
         </is>
       </c>
-      <c r="G241" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H241" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I241" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J241" s="1" t="inlineStr"/>
-      <c r="K241" s="1" t="inlineStr"/>
-      <c r="L241" s="1" t="inlineStr"/>
-      <c r="M241" s="1" t="inlineStr"/>
-      <c r="N241" s="1" t="inlineStr"/>
-      <c r="O241" s="1" t="inlineStr"/>
-      <c r="P241" s="1" t="inlineStr"/>
-      <c r="Q241" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R241" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (bruciolacontemporanea) | IG: trovato (brucio_lacontemporanea)</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="inlineStr">
+      <c r="A242" t="inlineStr">
         <is>
           <t>Brucio - La Romana</t>
         </is>
       </c>
-      <c r="B242" s="1" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>Piazza delle Coppelle, 8</t>
         </is>
       </c>
-      <c r="C242" s="1" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>06/89024862</t>
         </is>
       </c>
-      <c r="D242" s="1" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>www.brucioroma.it</t>
         </is>
       </c>
-      <c r="E242" s="1" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>brucioroma</t>
         </is>
       </c>
-      <c r="F242" s="1" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>brucio_roma</t>
         </is>
       </c>
-      <c r="G242" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H242" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I242" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J242" s="1" t="inlineStr"/>
-      <c r="K242" s="1" t="inlineStr"/>
-      <c r="L242" s="1" t="inlineStr"/>
-      <c r="M242" s="1" t="inlineStr"/>
-      <c r="N242" s="1" t="inlineStr"/>
-      <c r="O242" s="1" t="inlineStr"/>
-      <c r="P242" s="1" t="inlineStr"/>
-      <c r="Q242" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R242" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (brucioroma) | IG: trovato (brucio_roma)</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15350,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J243" s="1" t="inlineStr"/>
+      <c r="J243" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K243" s="1" t="inlineStr"/>
       <c r="L243" s="1" t="inlineStr"/>
       <c r="M243" s="1" t="inlineStr"/>
@@ -15348,76 +15363,79 @@
       <c r="P243" s="1" t="inlineStr"/>
       <c r="Q243" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R243" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="inlineStr">
+      <c r="A244" t="inlineStr">
         <is>
           <t>Crunch!</t>
         </is>
       </c>
-      <c r="B244" s="1" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>Via Francesco D'Ovidio, 27</t>
         </is>
       </c>
-      <c r="C244" s="1" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>06/87609540</t>
         </is>
       </c>
-      <c r="D244" s="1" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>www.crunchroma.it</t>
         </is>
       </c>
-      <c r="E244" s="1" t="inlineStr">
+      <c r="E244" t="inlineStr">
         <is>
           <t>crunchroma</t>
         </is>
       </c>
-      <c r="F244" s="1" t="inlineStr">
+      <c r="F244" t="inlineStr">
         <is>
           <t>crunch_roma</t>
         </is>
       </c>
-      <c r="G244" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H244" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I244" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J244" s="1" t="inlineStr"/>
-      <c r="K244" s="1" t="inlineStr"/>
-      <c r="L244" s="1" t="inlineStr"/>
-      <c r="M244" s="1" t="inlineStr"/>
-      <c r="N244" s="1" t="inlineStr"/>
-      <c r="O244" s="1" t="inlineStr"/>
-      <c r="P244" s="1" t="inlineStr"/>
-      <c r="Q244" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R244" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (crunchroma) | IG: trovato (crunch_roma)</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15465,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J245" s="1" t="inlineStr"/>
+      <c r="J245" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K245" s="1" t="inlineStr"/>
       <c r="L245" s="1" t="inlineStr"/>
       <c r="M245" s="1" t="inlineStr"/>
@@ -15456,76 +15478,79 @@
       <c r="P245" s="1" t="inlineStr"/>
       <c r="Q245" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="inlineStr">
+      <c r="A246" t="inlineStr">
         <is>
           <t>Dazio Roma</t>
         </is>
       </c>
-      <c r="B246" s="1" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>Via Nomentana, 1206</t>
         </is>
       </c>
-      <c r="C246" s="1" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>06/83525515</t>
         </is>
       </c>
-      <c r="D246" s="1" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>www.dazioroma.it</t>
         </is>
       </c>
-      <c r="E246" s="1" t="inlineStr">
+      <c r="E246" t="inlineStr">
         <is>
           <t>DazioRoma</t>
         </is>
       </c>
-      <c r="F246" s="1" t="inlineStr">
+      <c r="F246" t="inlineStr">
         <is>
           <t>dazio_roma</t>
         </is>
       </c>
-      <c r="G246" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H246" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I246" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J246" s="1" t="inlineStr"/>
-      <c r="K246" s="1" t="inlineStr"/>
-      <c r="L246" s="1" t="inlineStr"/>
-      <c r="M246" s="1" t="inlineStr"/>
-      <c r="N246" s="1" t="inlineStr"/>
-      <c r="O246" s="1" t="inlineStr"/>
-      <c r="P246" s="1" t="inlineStr"/>
-      <c r="Q246" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R246" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (DazioRoma) | IG: trovato (dazio_roma)</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15580,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J247" s="1" t="inlineStr"/>
+      <c r="J247" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K247" s="1" t="inlineStr"/>
       <c r="L247" s="1" t="inlineStr"/>
       <c r="M247" s="1" t="inlineStr"/>
@@ -15564,264 +15593,275 @@
       <c r="P247" s="1" t="inlineStr"/>
       <c r="Q247" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R247" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="inlineStr">
+      <c r="A248" t="inlineStr">
         <is>
           <t>Extremis</t>
         </is>
       </c>
-      <c r="B248" s="1" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>Via del Casale Rocchi, 20/22</t>
         </is>
       </c>
-      <c r="C248" s="1" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>06/87809051</t>
         </is>
       </c>
-      <c r="D248" s="1" t="inlineStr"/>
-      <c r="E248" s="1" t="inlineStr">
+      <c r="E248" t="inlineStr">
         <is>
           <t>extremisrome</t>
         </is>
       </c>
-      <c r="F248" s="1" t="inlineStr">
+      <c r="F248" t="inlineStr">
         <is>
           <t>extremis_rome</t>
         </is>
       </c>
-      <c r="G248" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H248" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I248" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J248" s="1" t="inlineStr"/>
-      <c r="K248" s="1" t="inlineStr"/>
-      <c r="L248" s="1" t="inlineStr"/>
-      <c r="M248" s="1" t="inlineStr"/>
-      <c r="N248" s="1" t="inlineStr"/>
-      <c r="O248" s="1" t="inlineStr"/>
-      <c r="P248" s="1" t="inlineStr"/>
-      <c r="Q248" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R248" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (extremisrome) | IG: trovato (extremis_rome)</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="inlineStr">
+      <c r="A249" t="inlineStr">
         <is>
           <t>Farinè la pizza</t>
         </is>
       </c>
-      <c r="B249" s="1" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>Via degli Aurunci, 6/8</t>
         </is>
       </c>
-      <c r="C249" s="1" t="inlineStr">
+      <c r="C249" t="inlineStr">
         <is>
           <t>06/4451162</t>
         </is>
       </c>
-      <c r="D249" s="1" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>www.farinelapizza.it</t>
         </is>
       </c>
-      <c r="E249" s="1" t="inlineStr">
+      <c r="E249" t="inlineStr">
         <is>
           <t>farinelapizza</t>
         </is>
       </c>
-      <c r="F249" s="1" t="inlineStr">
+      <c r="F249" t="inlineStr">
         <is>
           <t>farine_la_pizza</t>
         </is>
       </c>
-      <c r="G249" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H249" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I249" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J249" s="1" t="inlineStr"/>
-      <c r="K249" s="1" t="inlineStr"/>
-      <c r="L249" s="1" t="inlineStr"/>
-      <c r="M249" s="1" t="inlineStr"/>
-      <c r="N249" s="1" t="inlineStr"/>
-      <c r="O249" s="1" t="inlineStr"/>
-      <c r="P249" s="1" t="inlineStr"/>
-      <c r="Q249" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R249" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (farinelapizza) | IG: trovato (farine_la_pizza)</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="inlineStr">
+      <c r="A250" t="inlineStr">
         <is>
           <t>Fermentum</t>
         </is>
       </c>
-      <c r="B250" s="1" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>Via Lemonia, 214</t>
         </is>
       </c>
-      <c r="C250" s="1" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>06/88939709</t>
         </is>
       </c>
-      <c r="D250" s="1" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>www.fermentum.it</t>
         </is>
       </c>
-      <c r="E250" s="1" t="inlineStr">
+      <c r="E250" t="inlineStr">
         <is>
           <t>Fermentum</t>
         </is>
       </c>
-      <c r="F250" s="1" t="inlineStr">
+      <c r="F250" t="inlineStr">
         <is>
           <t>fermentum_roma</t>
         </is>
       </c>
-      <c r="G250" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H250" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I250" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J250" s="1" t="inlineStr"/>
-      <c r="K250" s="1" t="inlineStr"/>
-      <c r="L250" s="1" t="inlineStr"/>
-      <c r="M250" s="1" t="inlineStr"/>
-      <c r="N250" s="1" t="inlineStr"/>
-      <c r="O250" s="1" t="inlineStr"/>
-      <c r="P250" s="1" t="inlineStr"/>
-      <c r="Q250" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R250" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Fermentum) | IG: trovato (fermentum_roma)</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="inlineStr">
+      <c r="A251" t="inlineStr">
         <is>
           <t>GianPà</t>
         </is>
       </c>
-      <c r="B251" s="1" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>Via Appia Nuova, 37</t>
         </is>
       </c>
-      <c r="C251" s="1" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>379/1290077</t>
         </is>
       </c>
-      <c r="D251" s="1" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t>www.pizzeriagianpa.it</t>
         </is>
       </c>
-      <c r="E251" s="1" t="inlineStr">
+      <c r="E251" t="inlineStr">
         <is>
           <t>pizzeriagianpa</t>
         </is>
       </c>
-      <c r="F251" s="1" t="inlineStr">
+      <c r="F251" t="inlineStr">
         <is>
           <t>gianpapizzeria</t>
         </is>
       </c>
-      <c r="G251" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H251" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I251" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J251" s="1" t="inlineStr"/>
-      <c r="K251" s="1" t="inlineStr"/>
-      <c r="L251" s="1" t="inlineStr"/>
-      <c r="M251" s="1" t="inlineStr"/>
-      <c r="N251" s="1" t="inlineStr"/>
-      <c r="O251" s="1" t="inlineStr"/>
-      <c r="P251" s="1" t="inlineStr"/>
-      <c r="Q251" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R251" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (pizzeriagianpa) | IG: trovato (gianpapizzeria)</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
@@ -15851,7 +15891,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J252" s="1" t="inlineStr"/>
+      <c r="J252" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K252" s="1" t="inlineStr"/>
       <c r="L252" s="1" t="inlineStr"/>
       <c r="M252" s="1" t="inlineStr"/>
@@ -15860,516 +15904,538 @@
       <c r="P252" s="1" t="inlineStr"/>
       <c r="Q252" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="inlineStr">
+      <c r="A253" t="inlineStr">
         <is>
           <t>I Quintili</t>
         </is>
       </c>
-      <c r="B253" s="1" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>Via Eurialo, 7/C</t>
         </is>
       </c>
-      <c r="C253" s="1" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t>06/80077157</t>
         </is>
       </c>
-      <c r="D253" s="1" t="inlineStr"/>
-      <c r="E253" s="1" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>iquintiliFurioCamillo</t>
         </is>
       </c>
-      <c r="F253" s="1" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t>iquintiliroma</t>
         </is>
       </c>
-      <c r="G253" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H253" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I253" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J253" s="1" t="inlineStr"/>
-      <c r="K253" s="1" t="inlineStr"/>
-      <c r="L253" s="1" t="inlineStr"/>
-      <c r="M253" s="1" t="inlineStr"/>
-      <c r="N253" s="1" t="inlineStr"/>
-      <c r="O253" s="1" t="inlineStr"/>
-      <c r="P253" s="1" t="inlineStr"/>
-      <c r="Q253" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R253" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (iquintiliFurioCamillo) | IG: trovato (iquintiliroma)</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="inlineStr">
+      <c r="A254" t="inlineStr">
         <is>
           <t>Il Maratoneta</t>
         </is>
       </c>
-      <c r="B254" s="1" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>Via dei Volsci, 99</t>
         </is>
       </c>
-      <c r="C254" s="1" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t>06/42990845</t>
         </is>
       </c>
-      <c r="D254" s="1" t="inlineStr"/>
-      <c r="E254" s="1" t="inlineStr">
+      <c r="E254" t="inlineStr">
         <is>
           <t>profile.php?id=61560324418289</t>
         </is>
       </c>
-      <c r="F254" s="1" t="inlineStr">
+      <c r="F254" t="inlineStr">
         <is>
           <t>ilmaratoneta_roma</t>
         </is>
       </c>
-      <c r="G254" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H254" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I254" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J254" s="1" t="inlineStr"/>
-      <c r="K254" s="1" t="inlineStr"/>
-      <c r="L254" s="1" t="inlineStr"/>
-      <c r="M254" s="1" t="inlineStr"/>
-      <c r="N254" s="1" t="inlineStr"/>
-      <c r="O254" s="1" t="inlineStr"/>
-      <c r="P254" s="1" t="inlineStr"/>
-      <c r="Q254" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R254" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=61560324418289) | IG: trovato (ilmaratoneta_roma)</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="inlineStr">
+      <c r="A255" t="inlineStr">
         <is>
           <t>InFucina</t>
         </is>
       </c>
-      <c r="B255" s="1" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>Via dei Salentini, 6/12</t>
         </is>
       </c>
-      <c r="C255" s="1" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>06/88791819</t>
         </is>
       </c>
-      <c r="D255" s="1" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>www.infucina.it</t>
         </is>
       </c>
-      <c r="E255" s="1" t="inlineStr">
+      <c r="E255" t="inlineStr">
         <is>
           <t>infucina</t>
         </is>
       </c>
-      <c r="F255" s="1" t="inlineStr">
+      <c r="F255" t="inlineStr">
         <is>
           <t>infucina_edoardopapa</t>
         </is>
       </c>
-      <c r="G255" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H255" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I255" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J255" s="1" t="inlineStr"/>
-      <c r="K255" s="1" t="inlineStr"/>
-      <c r="L255" s="1" t="inlineStr"/>
-      <c r="M255" s="1" t="inlineStr"/>
-      <c r="N255" s="1" t="inlineStr"/>
-      <c r="O255" s="1" t="inlineStr"/>
-      <c r="P255" s="1" t="inlineStr"/>
-      <c r="Q255" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R255" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (infucina) | IG: trovato (infucina_edoardopapa)</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="inlineStr">
+      <c r="A256" t="inlineStr">
         <is>
           <t>La Gatta Mangiona</t>
         </is>
       </c>
-      <c r="B256" s="1" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>Via Federico Ozanam, 30/32</t>
         </is>
       </c>
-      <c r="C256" s="1" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>06/5346702</t>
         </is>
       </c>
-      <c r="D256" s="1" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>www.lagattamangiona.com</t>
         </is>
       </c>
-      <c r="E256" s="1" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>GattaMangionaRoma</t>
         </is>
       </c>
-      <c r="F256" s="1" t="inlineStr">
+      <c r="F256" t="inlineStr">
         <is>
           <t>lagattamangiona</t>
         </is>
       </c>
-      <c r="G256" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H256" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I256" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J256" s="1" t="inlineStr"/>
-      <c r="K256" s="1" t="inlineStr"/>
-      <c r="L256" s="1" t="inlineStr"/>
-      <c r="M256" s="1" t="inlineStr"/>
-      <c r="N256" s="1" t="inlineStr"/>
-      <c r="O256" s="1" t="inlineStr"/>
-      <c r="P256" s="1" t="inlineStr"/>
-      <c r="Q256" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R256" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (GattaMangionaRoma) | IG: trovato (lagattamangiona)</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="inlineStr">
+      <c r="A257" t="inlineStr">
         <is>
           <t>L'Elementare</t>
         </is>
       </c>
-      <c r="B257" s="1" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>Via Benedetta, 23</t>
         </is>
       </c>
-      <c r="C257" s="1" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>06/5894016</t>
         </is>
       </c>
-      <c r="D257" s="1" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>www.pizzerialelementare.it</t>
         </is>
       </c>
-      <c r="E257" s="1" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>elementaretrastevere</t>
         </is>
       </c>
-      <c r="F257" s="1" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>elementaretrastevere</t>
         </is>
       </c>
-      <c r="G257" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H257" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I257" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J257" s="1" t="inlineStr"/>
-      <c r="K257" s="1" t="inlineStr"/>
-      <c r="L257" s="1" t="inlineStr"/>
-      <c r="M257" s="1" t="inlineStr"/>
-      <c r="N257" s="1" t="inlineStr"/>
-      <c r="O257" s="1" t="inlineStr"/>
-      <c r="P257" s="1" t="inlineStr"/>
-      <c r="Q257" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R257" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (elementaretrastevere) | IG: trovato (elementaretrastevere)</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="inlineStr">
+      <c r="A258" t="inlineStr">
         <is>
           <t>Magnifica</t>
         </is>
       </c>
-      <c r="B258" s="1" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>Via Ugo de Carolis, 72/D</t>
         </is>
       </c>
-      <c r="C258" s="1" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>06/35452285</t>
         </is>
       </c>
-      <c r="D258" s="1" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>www.pizzeriamagnifica.com</t>
         </is>
       </c>
-      <c r="E258" s="1" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>PizzeriaMagnifica</t>
         </is>
       </c>
-      <c r="F258" s="1" t="inlineStr">
+      <c r="F258" t="inlineStr">
         <is>
           <t>pizzeria_magnifica</t>
         </is>
       </c>
-      <c r="G258" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H258" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I258" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J258" s="1" t="inlineStr"/>
-      <c r="K258" s="1" t="inlineStr"/>
-      <c r="L258" s="1" t="inlineStr"/>
-      <c r="M258" s="1" t="inlineStr"/>
-      <c r="N258" s="1" t="inlineStr"/>
-      <c r="O258" s="1" t="inlineStr"/>
-      <c r="P258" s="1" t="inlineStr"/>
-      <c r="Q258" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R258" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (PizzeriaMagnifica) | IG: trovato (pizzeria_magnifica)</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="inlineStr">
+      <c r="A259" t="inlineStr">
         <is>
           <t>Mater</t>
         </is>
       </c>
-      <c r="B259" s="1" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Via Pier Paolo Pasolini, snc</t>
         </is>
       </c>
-      <c r="C259" s="1" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>0765/ 480785 - 331/1650624</t>
         </is>
       </c>
-      <c r="D259" s="1" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>www.mater.bio</t>
         </is>
       </c>
-      <c r="E259" s="1" t="inlineStr">
+      <c r="E259" t="inlineStr">
         <is>
           <t>pizzamater</t>
         </is>
       </c>
-      <c r="F259" s="1" t="inlineStr">
+      <c r="F259" t="inlineStr">
         <is>
           <t>pizzamater</t>
         </is>
       </c>
-      <c r="G259" s="1" t="inlineStr">
+      <c r="G259" t="inlineStr">
         <is>
           <t>17/03/2026</t>
         </is>
       </c>
-      <c r="H259" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I259" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J259" s="1" t="inlineStr"/>
-      <c r="K259" s="1" t="inlineStr"/>
-      <c r="L259" s="1" t="inlineStr"/>
-      <c r="M259" s="1" t="inlineStr"/>
-      <c r="N259" s="1" t="inlineStr"/>
-      <c r="O259" s="1" t="inlineStr"/>
-      <c r="P259" s="1" t="inlineStr"/>
-      <c r="Q259" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R259" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (pizzamater) | IG: trovato (pizzamater)</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="inlineStr">
+      <c r="A260" t="inlineStr">
         <is>
           <t>MIA - pizzeria creativa</t>
         </is>
       </c>
-      <c r="B260" s="1" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>Via Collatina, 126/D</t>
         </is>
       </c>
-      <c r="C260" s="1" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>06/2590699</t>
         </is>
       </c>
-      <c r="D260" s="1" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>www.miapizzeriacreativa.it</t>
         </is>
       </c>
-      <c r="E260" s="1" t="inlineStr">
+      <c r="E260" t="inlineStr">
         <is>
           <t>mia.pizzeria.creativa</t>
         </is>
       </c>
-      <c r="F260" s="1" t="inlineStr">
+      <c r="F260" t="inlineStr">
         <is>
           <t>mia.pizzeria.creativa</t>
         </is>
       </c>
-      <c r="G260" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H260" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I260" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J260" s="1" t="inlineStr"/>
-      <c r="K260" s="1" t="inlineStr"/>
-      <c r="L260" s="1" t="inlineStr"/>
-      <c r="M260" s="1" t="inlineStr"/>
-      <c r="N260" s="1" t="inlineStr"/>
-      <c r="O260" s="1" t="inlineStr"/>
-      <c r="P260" s="1" t="inlineStr"/>
-      <c r="Q260" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R260" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (mia.pizzeria.creativa) | IG: trovato (mia.pizzeria.creativa)</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -14458,288 +14458,387 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B227" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C227" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D227" s="1" t="inlineStr"/>
-      <c r="E227" s="1" t="inlineStr"/>
-      <c r="F227" s="1" t="inlineStr"/>
-      <c r="G227" s="1" t="inlineStr"/>
-      <c r="H227" s="1" t="inlineStr"/>
-      <c r="I227" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J227" s="1" t="inlineStr">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Mi Cucina Cinese Contemporanea</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Via Giovanni Botero, 31/33</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>06/89346223</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>mi_ristorante</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K227" s="1" t="inlineStr"/>
-      <c r="L227" s="1" t="inlineStr"/>
-      <c r="M227" s="1" t="inlineStr"/>
-      <c r="N227" s="1" t="inlineStr"/>
-      <c r="O227" s="1" t="inlineStr"/>
-      <c r="P227" s="1" t="inlineStr"/>
-      <c r="Q227" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R227" s="1" t="inlineStr">
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (mi_ristorante)</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="inlineStr">
-        <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
-        </is>
-      </c>
-      <c r="B228" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Erbe, 16</t>
-        </is>
-      </c>
-      <c r="C228" s="1" t="inlineStr">
-        <is>
-          <t>348/7277746</t>
-        </is>
-      </c>
-      <c r="D228" s="1" t="inlineStr"/>
-      <c r="E228" s="1" t="inlineStr"/>
-      <c r="F228" s="1" t="inlineStr"/>
-      <c r="G228" s="1" t="inlineStr"/>
-      <c r="H228" s="1" t="inlineStr"/>
-      <c r="I228" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J228" s="1" t="inlineStr">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Avenida Calò</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Viale Pinturicchio, 38/42</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>06/89238209</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>avenidacalo.it</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>avenidacalo</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>avenidacalo</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K228" s="1" t="inlineStr"/>
-      <c r="L228" s="1" t="inlineStr"/>
-      <c r="M228" s="1" t="inlineStr"/>
-      <c r="N228" s="1" t="inlineStr"/>
-      <c r="O228" s="1" t="inlineStr"/>
-      <c r="P228" s="1" t="inlineStr"/>
-      <c r="Q228" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R228" s="1" t="inlineStr">
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (avenidacalo) | IG: trovato (avenidacalo)</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="inlineStr">
-        <is>
-          <t>Osteria del Vicolo Fatato</t>
-        </is>
-      </c>
-      <c r="B229" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Forno Fatato, 11</t>
-        </is>
-      </c>
-      <c r="C229" s="1" t="inlineStr">
-        <is>
-          <t>0775/503035</t>
-        </is>
-      </c>
-      <c r="D229" s="1" t="inlineStr"/>
-      <c r="E229" s="1" t="inlineStr"/>
-      <c r="F229" s="1" t="inlineStr"/>
-      <c r="G229" s="1" t="inlineStr"/>
-      <c r="H229" s="1" t="inlineStr"/>
-      <c r="I229" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J229" s="1" t="inlineStr">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Baccio e i Gradini</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Viale della Piramide Cestia, 25</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>351/8823737</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>www.baccioeigradini.it</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>baccioeigradini</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>baccioeigradini</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K229" s="1" t="inlineStr"/>
-      <c r="L229" s="1" t="inlineStr"/>
-      <c r="M229" s="1" t="inlineStr"/>
-      <c r="N229" s="1" t="inlineStr"/>
-      <c r="O229" s="1" t="inlineStr"/>
-      <c r="P229" s="1" t="inlineStr"/>
-      <c r="Q229" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R229" s="1" t="inlineStr">
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (baccioeigradini) | IG: trovato (baccioeigradini)</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="inlineStr">
-        <is>
-          <t>Poldo e Gianna</t>
-        </is>
-      </c>
-      <c r="B230" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Rosini, 6</t>
-        </is>
-      </c>
-      <c r="C230" s="1" t="inlineStr">
-        <is>
-          <t>06/6893499</t>
-        </is>
-      </c>
-      <c r="D230" s="1" t="inlineStr"/>
-      <c r="E230" s="1" t="inlineStr"/>
-      <c r="F230" s="1" t="inlineStr"/>
-      <c r="G230" s="1" t="inlineStr"/>
-      <c r="H230" s="1" t="inlineStr"/>
-      <c r="I230" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J230" s="1" t="inlineStr">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Berberè</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Via Mantova, 5</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>06/45654390</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>www.berbere.it</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>berbereroma</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>berbereroma</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K230" s="1" t="inlineStr"/>
-      <c r="L230" s="1" t="inlineStr"/>
-      <c r="M230" s="1" t="inlineStr"/>
-      <c r="N230" s="1" t="inlineStr"/>
-      <c r="O230" s="1" t="inlineStr"/>
-      <c r="P230" s="1" t="inlineStr"/>
-      <c r="Q230" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R230" s="1" t="inlineStr">
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (berbereroma) | IG: trovato (berbereroma)</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria A Casa Di Rita</t>
-        </is>
-      </c>
-      <c r="B231" s="1" t="inlineStr">
-        <is>
-          <t>Via delle Ciliegie, 145</t>
-        </is>
-      </c>
-      <c r="C231" s="1" t="inlineStr">
-        <is>
-          <t>338/9860960</t>
-        </is>
-      </c>
-      <c r="D231" s="1" t="inlineStr"/>
-      <c r="E231" s="1" t="inlineStr"/>
-      <c r="F231" s="1" t="inlineStr"/>
-      <c r="G231" s="1" t="inlineStr"/>
-      <c r="H231" s="1" t="inlineStr"/>
-      <c r="I231" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J231" s="1" t="inlineStr">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Brucio - La Contemporanea</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Via degli Stradivari, 1</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>06/83082083</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>www.bruciolacontemporanea.it</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>bruciolacontemporanea</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>brucio_lacontemporanea</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K231" s="1" t="inlineStr"/>
-      <c r="L231" s="1" t="inlineStr"/>
-      <c r="M231" s="1" t="inlineStr"/>
-      <c r="N231" s="1" t="inlineStr"/>
-      <c r="O231" s="1" t="inlineStr"/>
-      <c r="P231" s="1" t="inlineStr"/>
-      <c r="Q231" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R231" s="1" t="inlineStr">
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (bruciolacontemporanea) | IG: trovato (brucio_lacontemporanea)</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="inlineStr">
-        <is>
-          <t>Ie Koji Japanese Izakaya</t>
-        </is>
-      </c>
-      <c r="B232" s="1" t="inlineStr">
-        <is>
-          <t>Via Marcantonio Bragadin, 13</t>
-        </is>
-      </c>
-      <c r="C232" s="1" t="inlineStr">
-        <is>
-          <t>348/4302368 - 06/69459860</t>
-        </is>
-      </c>
-      <c r="D232" s="1" t="inlineStr"/>
-      <c r="E232" s="1" t="inlineStr"/>
-      <c r="F232" s="1" t="inlineStr"/>
-      <c r="G232" s="1" t="inlineStr"/>
-      <c r="H232" s="1" t="inlineStr"/>
-      <c r="I232" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J232" s="1" t="inlineStr">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Brucio - La Romana</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Piazza delle Coppelle, 8</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>06/89024862</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>www.brucioroma.it</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>brucioroma</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>brucio_roma</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K232" s="1" t="inlineStr"/>
-      <c r="L232" s="1" t="inlineStr"/>
-      <c r="M232" s="1" t="inlineStr"/>
-      <c r="N232" s="1" t="inlineStr"/>
-      <c r="O232" s="1" t="inlineStr"/>
-      <c r="P232" s="1" t="inlineStr"/>
-      <c r="Q232" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R232" s="1" t="inlineStr">
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (brucioroma) | IG: trovato (brucio_roma)</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
@@ -14748,22 +14847,37 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Mi Cucina Cinese Contemporanea</t>
+          <t>Crunch!</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Via Giovanni Botero, 31/33</t>
+          <t>Via Francesco D'Ovidio, 27</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>06/89346223</t>
+          <t>06/87609540</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>www.crunchroma.it</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>crunchroma</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>mi_ristorante</t>
+          <t>crunch_roma</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14788,7 +14902,7 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (mi_ristorante)</t>
+          <t>TF: non trovato | FB: trovato (crunchroma) | IG: trovato (crunch_roma)</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -14798,192 +14912,263 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B234" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C234" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D234" s="1" t="inlineStr"/>
-      <c r="E234" s="1" t="inlineStr"/>
-      <c r="F234" s="1" t="inlineStr"/>
-      <c r="G234" s="1" t="inlineStr"/>
-      <c r="H234" s="1" t="inlineStr"/>
-      <c r="I234" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J234" s="1" t="inlineStr">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Dazio Roma</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Via Nomentana, 1206</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>06/83525515</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>www.dazioroma.it</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>DazioRoma</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>dazio_roma</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K234" s="1" t="inlineStr"/>
-      <c r="L234" s="1" t="inlineStr"/>
-      <c r="M234" s="1" t="inlineStr"/>
-      <c r="N234" s="1" t="inlineStr"/>
-      <c r="O234" s="1" t="inlineStr"/>
-      <c r="P234" s="1" t="inlineStr"/>
-      <c r="Q234" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R234" s="1" t="inlineStr">
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (DazioRoma) | IG: trovato (dazio_roma)</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="inlineStr">
-        <is>
-          <t>Nomisan</t>
-        </is>
-      </c>
-      <c r="B235" s="1" t="inlineStr">
-        <is>
-          <t>Viale Gianluigi Bonelli, 237</t>
-        </is>
-      </c>
-      <c r="C235" s="1" t="inlineStr">
-        <is>
-          <t>342/8036080</t>
-        </is>
-      </c>
-      <c r="D235" s="1" t="inlineStr"/>
-      <c r="E235" s="1" t="inlineStr"/>
-      <c r="F235" s="1" t="inlineStr"/>
-      <c r="G235" s="1" t="inlineStr"/>
-      <c r="H235" s="1" t="inlineStr"/>
-      <c r="I235" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J235" s="1" t="inlineStr">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Extremis</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Via del Casale Rocchi, 20/22</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>06/87809051</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>extremisrome</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>extremis_rome</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K235" s="1" t="inlineStr"/>
-      <c r="L235" s="1" t="inlineStr"/>
-      <c r="M235" s="1" t="inlineStr"/>
-      <c r="N235" s="1" t="inlineStr"/>
-      <c r="O235" s="1" t="inlineStr"/>
-      <c r="P235" s="1" t="inlineStr"/>
-      <c r="Q235" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R235" s="1" t="inlineStr">
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (extremisrome) | IG: trovato (extremis_rome)</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="inlineStr">
-        <is>
-          <t>Al Setaccio</t>
-        </is>
-      </c>
-      <c r="B236" s="1" t="inlineStr">
-        <is>
-          <t>Via di Mezzocammino, 193</t>
-        </is>
-      </c>
-      <c r="C236" s="1" t="inlineStr">
-        <is>
-          <t>06/52372056</t>
-        </is>
-      </c>
-      <c r="D236" s="1" t="inlineStr"/>
-      <c r="E236" s="1" t="inlineStr"/>
-      <c r="F236" s="1" t="inlineStr"/>
-      <c r="G236" s="1" t="inlineStr"/>
-      <c r="H236" s="1" t="inlineStr"/>
-      <c r="I236" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J236" s="1" t="inlineStr">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Farinè la pizza</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Via degli Aurunci, 6/8</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>06/4451162</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>www.farinelapizza.it</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>farinelapizza</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>farine_la_pizza</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K236" s="1" t="inlineStr"/>
-      <c r="L236" s="1" t="inlineStr"/>
-      <c r="M236" s="1" t="inlineStr"/>
-      <c r="N236" s="1" t="inlineStr"/>
-      <c r="O236" s="1" t="inlineStr"/>
-      <c r="P236" s="1" t="inlineStr"/>
-      <c r="Q236" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R236" s="1" t="inlineStr">
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (farinelapizza) | IG: trovato (farine_la_pizza)</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="inlineStr">
-        <is>
-          <t>Angelo Pezzella</t>
-        </is>
-      </c>
-      <c r="B237" s="1" t="inlineStr">
-        <is>
-          <t>Via Appia Nuova, 1095</t>
-        </is>
-      </c>
-      <c r="C237" s="1" t="inlineStr">
-        <is>
-          <t>06/7188560</t>
-        </is>
-      </c>
-      <c r="D237" s="1" t="inlineStr"/>
-      <c r="E237" s="1" t="inlineStr"/>
-      <c r="F237" s="1" t="inlineStr"/>
-      <c r="G237" s="1" t="inlineStr"/>
-      <c r="H237" s="1" t="inlineStr"/>
-      <c r="I237" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J237" s="1" t="inlineStr">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Fermentum</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Via Lemonia, 214</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>06/88939709</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>www.fermentum.it</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Fermentum</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>fermentum_roma</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K237" s="1" t="inlineStr"/>
-      <c r="L237" s="1" t="inlineStr"/>
-      <c r="M237" s="1" t="inlineStr"/>
-      <c r="N237" s="1" t="inlineStr"/>
-      <c r="O237" s="1" t="inlineStr"/>
-      <c r="P237" s="1" t="inlineStr"/>
-      <c r="Q237" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R237" s="1" t="inlineStr">
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Fermentum) | IG: trovato (fermentum_roma)</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
@@ -14992,32 +15177,32 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Avenida Calò</t>
+          <t>GianPà</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Viale Pinturicchio, 38/42</t>
+          <t>Via Appia Nuova, 37</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>06/89238209</t>
+          <t>379/1290077</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>avenidacalo.it</t>
+          <t>www.pizzeriagianpa.it</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>avenidacalo</t>
+          <t>pizzeriagianpa</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>avenidacalo</t>
+          <t>gianpapizzeria</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -15047,7 +15232,7 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (avenidacalo) | IG: trovato (avenidacalo)</t>
+          <t>TF: non trovato | FB: trovato (pizzeriagianpa) | IG: trovato (gianpapizzeria)</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -15059,32 +15244,27 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Baccio e i Gradini</t>
+          <t>I Quintili</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Viale della Piramide Cestia, 25</t>
+          <t>Via Eurialo, 7/C</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>351/8823737</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>www.baccioeigradini.it</t>
+          <t>06/80077157</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>baccioeigradini</t>
+          <t>iquintiliFurioCamillo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>baccioeigradini</t>
+          <t>iquintiliroma</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -15114,7 +15294,7 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (baccioeigradini) | IG: trovato (baccioeigradini)</t>
+          <t>TF: non trovato | FB: trovato (iquintiliFurioCamillo) | IG: trovato (iquintiliroma)</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -15126,32 +15306,27 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Berberè</t>
+          <t>Il Maratoneta</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Via Mantova, 5</t>
+          <t>Via dei Volsci, 99</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>06/45654390</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>www.berbere.it</t>
+          <t>06/42990845</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>berbereroma</t>
+          <t>profile.php?id=61560324418289</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>berbereroma</t>
+          <t>ilmaratoneta_roma</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -15181,7 +15356,7 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (berbereroma) | IG: trovato (berbereroma)</t>
+          <t>TF: non trovato | FB: trovato (profile.php?id=61560324418289) | IG: trovato (ilmaratoneta_roma)</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -15193,32 +15368,32 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Brucio - La Contemporanea</t>
+          <t>InFucina</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Via degli Stradivari, 1</t>
+          <t>Via dei Salentini, 6/12</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>06/83082083</t>
+          <t>06/88791819</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>www.bruciolacontemporanea.it</t>
+          <t>www.infucina.it</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>bruciolacontemporanea</t>
+          <t>infucina</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>brucio_lacontemporanea</t>
+          <t>infucina_edoardopapa</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -15248,7 +15423,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (bruciolacontemporanea) | IG: trovato (brucio_lacontemporanea)</t>
+          <t>TF: non trovato | FB: trovato (infucina) | IG: trovato (infucina_edoardopapa)</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -15260,32 +15435,32 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Brucio - La Romana</t>
+          <t>La Gatta Mangiona</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Piazza delle Coppelle, 8</t>
+          <t>Via Federico Ozanam, 30/32</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>06/89024862</t>
+          <t>06/5346702</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>www.brucioroma.it</t>
+          <t>www.lagattamangiona.com</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>brucioroma</t>
+          <t>GattaMangionaRoma</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>brucio_roma</t>
+          <t>lagattamangiona</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -15315,7 +15490,7 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (brucioroma) | IG: trovato (brucio_roma)</t>
+          <t>TF: non trovato | FB: trovato (GattaMangionaRoma) | IG: trovato (lagattamangiona)</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
@@ -15325,48 +15500,67 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="inlineStr">
-        <is>
-          <t>Clementina</t>
-        </is>
-      </c>
-      <c r="B243" s="1" t="inlineStr">
-        <is>
-          <t>Via della Torre Clementina, 158</t>
-        </is>
-      </c>
-      <c r="C243" s="1" t="inlineStr">
-        <is>
-          <t>328/8181651</t>
-        </is>
-      </c>
-      <c r="D243" s="1" t="inlineStr"/>
-      <c r="E243" s="1" t="inlineStr"/>
-      <c r="F243" s="1" t="inlineStr"/>
-      <c r="G243" s="1" t="inlineStr"/>
-      <c r="H243" s="1" t="inlineStr"/>
-      <c r="I243" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J243" s="1" t="inlineStr">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>L'Elementare</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Via Benedetta, 23</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>06/5894016</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>www.pizzerialelementare.it</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>elementaretrastevere</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>elementaretrastevere</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K243" s="1" t="inlineStr"/>
-      <c r="L243" s="1" t="inlineStr"/>
-      <c r="M243" s="1" t="inlineStr"/>
-      <c r="N243" s="1" t="inlineStr"/>
-      <c r="O243" s="1" t="inlineStr"/>
-      <c r="P243" s="1" t="inlineStr"/>
-      <c r="Q243" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R243" s="1" t="inlineStr">
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (elementaretrastevere) | IG: trovato (elementaretrastevere)</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
@@ -15375,32 +15569,32 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Crunch!</t>
+          <t>Magnifica</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Via Francesco D'Ovidio, 27</t>
+          <t>Via Ugo de Carolis, 72/D</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>06/87609540</t>
+          <t>06/35452285</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>www.crunchroma.it</t>
+          <t>www.pizzeriamagnifica.com</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>crunchroma</t>
+          <t>PizzeriaMagnifica</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>crunch_roma</t>
+          <t>pizzeria_magnifica</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -15430,7 +15624,7 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (crunchroma) | IG: trovato (crunch_roma)</t>
+          <t>TF: non trovato | FB: trovato (PizzeriaMagnifica) | IG: trovato (pizzeria_magnifica)</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -15440,48 +15634,67 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="inlineStr">
-        <is>
-          <t>Da Antonio</t>
-        </is>
-      </c>
-      <c r="B245" s="1" t="inlineStr">
-        <is>
-          <t>Via Mario Lizzani, 21</t>
-        </is>
-      </c>
-      <c r="C245" s="1" t="inlineStr">
-        <is>
-          <t>391/7475549</t>
-        </is>
-      </c>
-      <c r="D245" s="1" t="inlineStr"/>
-      <c r="E245" s="1" t="inlineStr"/>
-      <c r="F245" s="1" t="inlineStr"/>
-      <c r="G245" s="1" t="inlineStr"/>
-      <c r="H245" s="1" t="inlineStr"/>
-      <c r="I245" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J245" s="1" t="inlineStr">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Mater</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Via Pier Paolo Pasolini, snc</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>0765/ 480785 - 331/1650624</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>www.mater.bio</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>pizzamater</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>pizzamater</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K245" s="1" t="inlineStr"/>
-      <c r="L245" s="1" t="inlineStr"/>
-      <c r="M245" s="1" t="inlineStr"/>
-      <c r="N245" s="1" t="inlineStr"/>
-      <c r="O245" s="1" t="inlineStr"/>
-      <c r="P245" s="1" t="inlineStr"/>
-      <c r="Q245" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R245" s="1" t="inlineStr">
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (pizzamater) | IG: trovato (pizzamater)</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
@@ -15490,32 +15703,32 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Dazio Roma</t>
+          <t>MIA - pizzeria creativa</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Via Nomentana, 1206</t>
+          <t>Via Collatina, 126/D</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>06/83525515</t>
+          <t>06/2590699</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>www.dazioroma.it</t>
+          <t>www.miapizzeriacreativa.it</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>DazioRoma</t>
+          <t>mia.pizzeria.creativa</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>dazio_roma</t>
+          <t>mia.pizzeria.creativa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -15545,7 +15758,7 @@
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (DazioRoma) | IG: trovato (dazio_roma)</t>
+          <t>TF: non trovato | FB: trovato (mia.pizzeria.creativa) | IG: trovato (mia.pizzeria.creativa)</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
@@ -15557,17 +15770,17 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>Diego Vitagliano</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>Via Chiana, 80</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t>06/72276443</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr"/>
@@ -15598,287 +15811,216 @@
       </c>
       <c r="R247" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Extremis</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Via del Casale Rocchi, 20/22</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>06/87809051</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>extremisrome</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>extremis_rome</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="inlineStr">
+        <is>
+          <t>Piazza delle Erbe, 16</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>348/7277746</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="inlineStr"/>
+      <c r="E248" s="1" t="inlineStr"/>
+      <c r="F248" s="1" t="inlineStr"/>
+      <c r="G248" s="1" t="inlineStr"/>
+      <c r="H248" s="1" t="inlineStr"/>
+      <c r="I248" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J248" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O248" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q248" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (extremisrome) | IG: trovato (extremis_rome)</t>
-        </is>
-      </c>
-      <c r="R248" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
+      <c r="K248" s="1" t="inlineStr"/>
+      <c r="L248" s="1" t="inlineStr"/>
+      <c r="M248" s="1" t="inlineStr"/>
+      <c r="N248" s="1" t="inlineStr"/>
+      <c r="O248" s="1" t="inlineStr"/>
+      <c r="P248" s="1" t="inlineStr"/>
+      <c r="Q248" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R248" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Farinè la pizza</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Via degli Aurunci, 6/8</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>06/4451162</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>www.farinelapizza.it</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>farinelapizza</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>farine_la_pizza</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>Osteria del Vicolo Fatato</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="inlineStr">
+        <is>
+          <t>Vicolo Forno Fatato, 11</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>0775/503035</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr"/>
+      <c r="E249" s="1" t="inlineStr"/>
+      <c r="F249" s="1" t="inlineStr"/>
+      <c r="G249" s="1" t="inlineStr"/>
+      <c r="H249" s="1" t="inlineStr"/>
+      <c r="I249" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J249" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q249" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (farinelapizza) | IG: trovato (farine_la_pizza)</t>
-        </is>
-      </c>
-      <c r="R249" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
+      <c r="K249" s="1" t="inlineStr"/>
+      <c r="L249" s="1" t="inlineStr"/>
+      <c r="M249" s="1" t="inlineStr"/>
+      <c r="N249" s="1" t="inlineStr"/>
+      <c r="O249" s="1" t="inlineStr"/>
+      <c r="P249" s="1" t="inlineStr"/>
+      <c r="Q249" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R249" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Fermentum</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Via Lemonia, 214</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>06/88939709</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>www.fermentum.it</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Fermentum</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>fermentum_roma</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>Poldo e Gianna</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t>Vicolo Rosini, 6</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>06/6893499</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="inlineStr"/>
+      <c r="E250" s="1" t="inlineStr"/>
+      <c r="F250" s="1" t="inlineStr"/>
+      <c r="G250" s="1" t="inlineStr"/>
+      <c r="H250" s="1" t="inlineStr"/>
+      <c r="I250" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J250" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Fermentum) | IG: trovato (fermentum_roma)</t>
-        </is>
-      </c>
-      <c r="R250" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
+      <c r="K250" s="1" t="inlineStr"/>
+      <c r="L250" s="1" t="inlineStr"/>
+      <c r="M250" s="1" t="inlineStr"/>
+      <c r="N250" s="1" t="inlineStr"/>
+      <c r="O250" s="1" t="inlineStr"/>
+      <c r="P250" s="1" t="inlineStr"/>
+      <c r="Q250" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R250" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>GianPà</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Via Appia Nuova, 37</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>379/1290077</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>www.pizzeriagianpa.it</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>pizzeriagianpa</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>gianpapizzeria</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>Trattoria A Casa Di Rita</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="inlineStr">
+        <is>
+          <t>Via delle Ciliegie, 145</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>338/9860960</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="inlineStr"/>
+      <c r="E251" s="1" t="inlineStr"/>
+      <c r="F251" s="1" t="inlineStr"/>
+      <c r="G251" s="1" t="inlineStr"/>
+      <c r="H251" s="1" t="inlineStr"/>
+      <c r="I251" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J251" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q251" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (pizzeriagianpa) | IG: trovato (gianpapizzeria)</t>
-        </is>
-      </c>
-      <c r="R251" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
+      <c r="K251" s="1" t="inlineStr"/>
+      <c r="L251" s="1" t="inlineStr"/>
+      <c r="M251" s="1" t="inlineStr"/>
+      <c r="N251" s="1" t="inlineStr"/>
+      <c r="O251" s="1" t="inlineStr"/>
+      <c r="P251" s="1" t="inlineStr"/>
+      <c r="Q251" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R251" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>GioMà</t>
+          <t>Ie Koji Japanese Izakaya</t>
         </is>
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t>Via Calpurnio Fiamma, 40/44</t>
+          <t>Via Marcantonio Bragadin, 13</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t>06/7674717</t>
+          <t>348/4302368 - 06/69459860</t>
         </is>
       </c>
       <c r="D252" s="1" t="inlineStr"/>
@@ -15909,597 +16051,458 @@
       </c>
       <c r="R252" s="1" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>I Quintili</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Via Eurialo, 7/C</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>06/80077157</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>iquintiliFurioCamillo</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>iquintiliroma</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>Mrgda Ristorante</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="inlineStr">
+        <is>
+          <t>Via Prenestina, 182</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>329/933355</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="inlineStr"/>
+      <c r="E253" s="1" t="inlineStr"/>
+      <c r="F253" s="1" t="inlineStr"/>
+      <c r="G253" s="1" t="inlineStr"/>
+      <c r="H253" s="1" t="inlineStr"/>
+      <c r="I253" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J253" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O253" t="inlineStr">
+      <c r="K253" s="1" t="inlineStr"/>
+      <c r="L253" s="1" t="inlineStr"/>
+      <c r="M253" s="1" t="inlineStr"/>
+      <c r="N253" s="1" t="inlineStr"/>
+      <c r="O253" s="1" t="inlineStr"/>
+      <c r="P253" s="1" t="inlineStr"/>
+      <c r="Q253" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R253" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>Nomisan</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="inlineStr">
+        <is>
+          <t>Viale Gianluigi Bonelli, 237</t>
+        </is>
+      </c>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t>342/8036080</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="inlineStr"/>
+      <c r="E254" s="1" t="inlineStr"/>
+      <c r="F254" s="1" t="inlineStr"/>
+      <c r="G254" s="1" t="inlineStr"/>
+      <c r="H254" s="1" t="inlineStr"/>
+      <c r="I254" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J254" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K254" s="1" t="inlineStr"/>
+      <c r="L254" s="1" t="inlineStr"/>
+      <c r="M254" s="1" t="inlineStr"/>
+      <c r="N254" s="1" t="inlineStr"/>
+      <c r="O254" s="1" t="inlineStr"/>
+      <c r="P254" s="1" t="inlineStr"/>
+      <c r="Q254" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R254" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>Al Setaccio</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="inlineStr">
+        <is>
+          <t>Via di Mezzocammino, 193</t>
+        </is>
+      </c>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>06/52372056</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="inlineStr"/>
+      <c r="E255" s="1" t="inlineStr"/>
+      <c r="F255" s="1" t="inlineStr"/>
+      <c r="G255" s="1" t="inlineStr"/>
+      <c r="H255" s="1" t="inlineStr"/>
+      <c r="I255" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J255" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K255" s="1" t="inlineStr"/>
+      <c r="L255" s="1" t="inlineStr"/>
+      <c r="M255" s="1" t="inlineStr"/>
+      <c r="N255" s="1" t="inlineStr"/>
+      <c r="O255" s="1" t="inlineStr"/>
+      <c r="P255" s="1" t="inlineStr"/>
+      <c r="Q255" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R255" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>Angelo Pezzella</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="inlineStr">
+        <is>
+          <t>Via Appia Nuova, 1095</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="inlineStr">
+        <is>
+          <t>06/7188560</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="inlineStr"/>
+      <c r="E256" s="1" t="inlineStr"/>
+      <c r="F256" s="1" t="inlineStr"/>
+      <c r="G256" s="1" t="inlineStr"/>
+      <c r="H256" s="1" t="inlineStr"/>
+      <c r="I256" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J256" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K256" s="1" t="inlineStr"/>
+      <c r="L256" s="1" t="inlineStr"/>
+      <c r="M256" s="1" t="inlineStr"/>
+      <c r="N256" s="1" t="inlineStr"/>
+      <c r="O256" s="1" t="inlineStr"/>
+      <c r="P256" s="1" t="inlineStr"/>
+      <c r="Q256" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R256" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>Clementina</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="inlineStr">
+        <is>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr"/>
+      <c r="E257" s="1" t="inlineStr"/>
+      <c r="F257" s="1" t="inlineStr"/>
+      <c r="G257" s="1" t="inlineStr"/>
+      <c r="H257" s="1" t="inlineStr"/>
+      <c r="I257" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J257" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K257" s="1" t="inlineStr"/>
+      <c r="L257" s="1" t="inlineStr"/>
+      <c r="M257" s="1" t="inlineStr"/>
+      <c r="N257" s="1" t="inlineStr"/>
+      <c r="O257" s="1" t="inlineStr"/>
+      <c r="P257" s="1" t="inlineStr"/>
+      <c r="Q257" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R257" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>Da Antonio</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="inlineStr">
+        <is>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="inlineStr"/>
+      <c r="E258" s="1" t="inlineStr"/>
+      <c r="F258" s="1" t="inlineStr"/>
+      <c r="G258" s="1" t="inlineStr"/>
+      <c r="H258" s="1" t="inlineStr"/>
+      <c r="I258" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J258" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K258" s="1" t="inlineStr"/>
+      <c r="L258" s="1" t="inlineStr"/>
+      <c r="M258" s="1" t="inlineStr"/>
+      <c r="N258" s="1" t="inlineStr"/>
+      <c r="O258" s="1" t="inlineStr"/>
+      <c r="P258" s="1" t="inlineStr"/>
+      <c r="Q258" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R258" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>Diego Vitagliano</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="inlineStr">
+        <is>
+          <t>Via Chiana, 80</t>
+        </is>
+      </c>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>06/72276443</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr"/>
+      <c r="E259" s="1" t="inlineStr"/>
+      <c r="F259" s="1" t="inlineStr"/>
+      <c r="G259" s="1" t="inlineStr"/>
+      <c r="H259" s="1" t="inlineStr"/>
+      <c r="I259" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J259" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K259" s="1" t="inlineStr"/>
+      <c r="L259" s="1" t="inlineStr"/>
+      <c r="M259" s="1" t="inlineStr"/>
+      <c r="N259" s="1" t="inlineStr"/>
+      <c r="O259" s="1" t="inlineStr"/>
+      <c r="P259" s="1" t="inlineStr"/>
+      <c r="Q259" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R259" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>GioMà</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="inlineStr">
+        <is>
+          <t>Via Calpurnio Fiamma, 40/44</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="inlineStr">
+        <is>
+          <t>06/7674717</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="inlineStr"/>
+      <c r="E260" s="1" t="inlineStr"/>
+      <c r="F260" s="1" t="inlineStr"/>
+      <c r="G260" s="1" t="inlineStr"/>
+      <c r="H260" s="1" t="inlineStr"/>
+      <c r="I260" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J260" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K260" s="1" t="inlineStr"/>
+      <c r="L260" s="1" t="inlineStr"/>
+      <c r="M260" s="1" t="inlineStr"/>
+      <c r="N260" s="1" t="inlineStr"/>
+      <c r="O260" s="1" t="inlineStr"/>
+      <c r="P260" s="1" t="inlineStr"/>
+      <c r="Q260" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R260" s="1" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Piccolo Buco</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Via del Lavatore, 91</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>06/69380163</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>www.pizzeriapiccolobuco.it</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>PiccoloBuco</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>piccolobucoroma</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q253" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (iquintiliFurioCamillo) | IG: trovato (iquintiliroma)</t>
-        </is>
-      </c>
-      <c r="R253" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Il Maratoneta</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Via dei Volsci, 99</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>06/42990845</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>profile.php?id=61560324418289</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>ilmaratoneta_roma</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (profile.php?id=61560324418289) | IG: trovato (ilmaratoneta_roma)</t>
-        </is>
-      </c>
-      <c r="R254" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>InFucina</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Via dei Salentini, 6/12</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>06/88791819</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>www.infucina.it</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>infucina</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>infucina_edoardopapa</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (infucina) | IG: trovato (infucina_edoardopapa)</t>
-        </is>
-      </c>
-      <c r="R255" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>La Gatta Mangiona</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Via Federico Ozanam, 30/32</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>06/5346702</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>www.lagattamangiona.com</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>GattaMangionaRoma</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>lagattamangiona</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (GattaMangionaRoma) | IG: trovato (lagattamangiona)</t>
-        </is>
-      </c>
-      <c r="R256" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>L'Elementare</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Via Benedetta, 23</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>06/5894016</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>www.pizzerialelementare.it</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>elementaretrastevere</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>elementaretrastevere</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q257" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (elementaretrastevere) | IG: trovato (elementaretrastevere)</t>
-        </is>
-      </c>
-      <c r="R257" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Magnifica</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Via Ugo de Carolis, 72/D</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>06/35452285</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>www.pizzeriamagnifica.com</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>PizzeriaMagnifica</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>pizzeria_magnifica</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O258" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q258" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (PizzeriaMagnifica) | IG: trovato (pizzeria_magnifica)</t>
-        </is>
-      </c>
-      <c r="R258" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Mater</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Via Pier Paolo Pasolini, snc</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>0765/ 480785 - 331/1650624</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>www.mater.bio</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>pizzamater</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>pizzamater</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>17/03/2026</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O259" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (pizzamater) | IG: trovato (pizzamater)</t>
-        </is>
-      </c>
-      <c r="R259" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>MIA - pizzeria creativa</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Via Collatina, 126/D</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>06/2590699</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>www.miapizzeriacreativa.it</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>mia.pizzeria.creativa</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>mia.pizzeria.creativa</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O260" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q260" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (mia.pizzeria.creativa) | IG: trovato (mia.pizzeria.creativa)</t>
-        </is>
-      </c>
-      <c r="R260" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="1" t="inlineStr">
-        <is>
-          <t>Piccolo Buco</t>
-        </is>
-      </c>
-      <c r="B261" s="1" t="inlineStr">
-        <is>
-          <t>Via del Lavatore, 91</t>
-        </is>
-      </c>
-      <c r="C261" s="1" t="inlineStr">
-        <is>
-          <t>06/69380163</t>
-        </is>
-      </c>
-      <c r="D261" s="1" t="inlineStr">
-        <is>
-          <t>www.pizzeriapiccolobuco.it</t>
-        </is>
-      </c>
-      <c r="E261" s="1" t="inlineStr">
-        <is>
-          <t>PiccoloBuco</t>
-        </is>
-      </c>
-      <c r="F261" s="1" t="inlineStr">
-        <is>
-          <t>piccolobucoroma</t>
-        </is>
-      </c>
-      <c r="G261" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H261" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I261" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J261" s="1" t="inlineStr"/>
-      <c r="K261" s="1" t="inlineStr"/>
-      <c r="L261" s="1" t="inlineStr"/>
-      <c r="M261" s="1" t="inlineStr"/>
-      <c r="N261" s="1" t="inlineStr"/>
-      <c r="O261" s="1" t="inlineStr"/>
-      <c r="P261" s="1" t="inlineStr"/>
-      <c r="Q261" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R261" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (PiccoloBuco) | IG: trovato (piccolobucoroma)</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -16529,7 +16532,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J262" s="1" t="inlineStr"/>
+      <c r="J262" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K262" s="1" t="inlineStr"/>
       <c r="L262" s="1" t="inlineStr"/>
       <c r="M262" s="1" t="inlineStr"/>
@@ -16538,12 +16545,12 @@
       <c r="P262" s="1" t="inlineStr"/>
       <c r="Q262" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R262" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -16573,7 +16580,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J263" s="1" t="inlineStr"/>
+      <c r="J263" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K263" s="1" t="inlineStr"/>
       <c r="L263" s="1" t="inlineStr"/>
       <c r="M263" s="1" t="inlineStr"/>
@@ -16582,12 +16593,12 @@
       <c r="P263" s="1" t="inlineStr"/>
       <c r="Q263" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R263" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
@@ -16617,7 +16628,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J264" s="1" t="inlineStr"/>
+      <c r="J264" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K264" s="1" t="inlineStr"/>
       <c r="L264" s="1" t="inlineStr"/>
       <c r="M264" s="1" t="inlineStr"/>
@@ -16626,1012 +16641,1054 @@
       <c r="P264" s="1" t="inlineStr"/>
       <c r="Q264" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="inlineStr">
+      <c r="A265" t="inlineStr">
         <is>
           <t>Spiazzo</t>
         </is>
       </c>
-      <c r="B265" s="1" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>Via Antonio Pacinotti, 83</t>
         </is>
       </c>
-      <c r="C265" s="1" t="inlineStr">
+      <c r="C265" t="inlineStr">
         <is>
           <t>065562738</t>
         </is>
       </c>
-      <c r="D265" s="1" t="inlineStr">
+      <c r="D265" t="inlineStr">
         <is>
           <t>www.pizzeriaspiazzo.it</t>
         </is>
       </c>
-      <c r="E265" s="1" t="inlineStr">
+      <c r="E265" t="inlineStr">
         <is>
           <t>PizzeriaSpiazzo</t>
         </is>
       </c>
-      <c r="F265" s="1" t="inlineStr">
+      <c r="F265" t="inlineStr">
         <is>
           <t>spiazzoroma</t>
         </is>
       </c>
-      <c r="G265" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H265" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I265" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J265" s="1" t="inlineStr"/>
-      <c r="K265" s="1" t="inlineStr"/>
-      <c r="L265" s="1" t="inlineStr"/>
-      <c r="M265" s="1" t="inlineStr"/>
-      <c r="N265" s="1" t="inlineStr"/>
-      <c r="O265" s="1" t="inlineStr"/>
-      <c r="P265" s="1" t="inlineStr"/>
-      <c r="Q265" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R265" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (PizzeriaSpiazzo) | IG: trovato (spiazzoroma)</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="inlineStr">
+      <c r="A266" t="inlineStr">
         <is>
           <t>Svario-Pizza Bar</t>
         </is>
       </c>
-      <c r="B266" s="1" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>Via Val Senio, 18</t>
         </is>
       </c>
-      <c r="C266" s="1" t="inlineStr">
+      <c r="C266" t="inlineStr">
         <is>
           <t>329/9299705</t>
         </is>
       </c>
-      <c r="D266" s="1" t="inlineStr">
+      <c r="D266" t="inlineStr">
         <is>
           <t>www.svario.it</t>
         </is>
       </c>
-      <c r="E266" s="1" t="inlineStr">
+      <c r="E266" t="inlineStr">
         <is>
           <t>svariopizzabar</t>
         </is>
       </c>
-      <c r="F266" s="1" t="inlineStr">
+      <c r="F266" t="inlineStr">
         <is>
           <t>svario_pizzabar</t>
         </is>
       </c>
-      <c r="G266" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H266" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I266" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J266" s="1" t="inlineStr"/>
-      <c r="K266" s="1" t="inlineStr"/>
-      <c r="L266" s="1" t="inlineStr"/>
-      <c r="M266" s="1" t="inlineStr"/>
-      <c r="N266" s="1" t="inlineStr"/>
-      <c r="O266" s="1" t="inlineStr"/>
-      <c r="P266" s="1" t="inlineStr"/>
-      <c r="Q266" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R266" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (svariopizzabar) | IG: trovato (svario_pizzabar)</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="inlineStr">
+      <c r="A267" t="inlineStr">
         <is>
           <t>TAC - Thin And Crunchy</t>
         </is>
       </c>
-      <c r="B267" s="1" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>Via Fiume delle Perle, 136/138</t>
         </is>
       </c>
-      <c r="C267" s="1" t="inlineStr">
+      <c r="C267" t="inlineStr">
         <is>
           <t>06/45652738</t>
         </is>
       </c>
-      <c r="D267" s="1" t="inlineStr">
+      <c r="D267" t="inlineStr">
         <is>
           <t>www.seupizza.com</t>
         </is>
       </c>
-      <c r="E267" s="1" t="inlineStr">
+      <c r="E267" t="inlineStr">
         <is>
           <t>TACThinAndCrunchy</t>
         </is>
       </c>
-      <c r="F267" s="1" t="inlineStr">
+      <c r="F267" t="inlineStr">
         <is>
           <t>tacthinandcrunchy</t>
         </is>
       </c>
-      <c r="G267" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H267" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I267" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J267" s="1" t="inlineStr"/>
-      <c r="K267" s="1" t="inlineStr"/>
-      <c r="L267" s="1" t="inlineStr"/>
-      <c r="M267" s="1" t="inlineStr"/>
-      <c r="N267" s="1" t="inlineStr"/>
-      <c r="O267" s="1" t="inlineStr"/>
-      <c r="P267" s="1" t="inlineStr"/>
-      <c r="Q267" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R267" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (TACThinAndCrunchy) | IG: trovato (tacthinandcrunchy)</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="inlineStr">
+      <c r="A268" t="inlineStr">
         <is>
           <t>Tonda</t>
         </is>
       </c>
-      <c r="B268" s="1" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>Via Valle Corteno, 31</t>
         </is>
       </c>
-      <c r="C268" s="1" t="inlineStr">
+      <c r="C268" t="inlineStr">
         <is>
           <t>06/8180960</t>
         </is>
       </c>
-      <c r="D268" s="1" t="inlineStr"/>
-      <c r="E268" s="1" t="inlineStr">
+      <c r="E268" t="inlineStr">
         <is>
           <t>pizzeriatonda</t>
         </is>
       </c>
-      <c r="F268" s="1" t="inlineStr">
+      <c r="F268" t="inlineStr">
         <is>
           <t>tondapizzeria</t>
         </is>
       </c>
-      <c r="G268" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H268" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I268" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J268" s="1" t="inlineStr"/>
-      <c r="K268" s="1" t="inlineStr"/>
-      <c r="L268" s="1" t="inlineStr"/>
-      <c r="M268" s="1" t="inlineStr"/>
-      <c r="N268" s="1" t="inlineStr"/>
-      <c r="O268" s="1" t="inlineStr"/>
-      <c r="P268" s="1" t="inlineStr"/>
-      <c r="Q268" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R268" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (pizzeriatonda) | IG: trovato (tondapizzeria)</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="inlineStr">
+      <c r="A269" t="inlineStr">
         <is>
           <t>Artigiano del Caffè</t>
         </is>
       </c>
-      <c r="B269" s="1" t="inlineStr">
+      <c r="B269" t="inlineStr">
         <is>
           <t>Via Famagosta, 14</t>
         </is>
       </c>
-      <c r="C269" s="1" t="inlineStr">
+      <c r="C269" t="inlineStr">
         <is>
           <t>329/7467044</t>
         </is>
       </c>
-      <c r="D269" s="1" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>www.artigianodelcafferoma.it</t>
         </is>
       </c>
-      <c r="E269" s="1" t="inlineStr">
+      <c r="E269" t="inlineStr">
         <is>
           <t>ArtigianodelCaffeRome</t>
         </is>
       </c>
-      <c r="F269" s="1" t="inlineStr">
+      <c r="F269" t="inlineStr">
         <is>
           <t>artigianodelcaffe</t>
         </is>
       </c>
-      <c r="G269" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H269" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I269" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J269" s="1" t="inlineStr"/>
-      <c r="K269" s="1" t="inlineStr"/>
-      <c r="L269" s="1" t="inlineStr"/>
-      <c r="M269" s="1" t="inlineStr"/>
-      <c r="N269" s="1" t="inlineStr"/>
-      <c r="O269" s="1" t="inlineStr"/>
-      <c r="P269" s="1" t="inlineStr"/>
-      <c r="Q269" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R269" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ArtigianodelCaffeRome) | IG: trovato (artigianodelcaffe)</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="inlineStr">
+      <c r="A270" t="inlineStr">
         <is>
           <t>Bap</t>
         </is>
       </c>
-      <c r="B270" s="1" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>Via Raffaele Cadorna, 5</t>
         </is>
       </c>
-      <c r="C270" s="1" t="inlineStr">
+      <c r="C270" t="inlineStr">
         <is>
           <t>06/2428174</t>
         </is>
       </c>
-      <c r="D270" s="1" t="inlineStr">
+      <c r="D270" t="inlineStr">
         <is>
           <t>www.baproma.com</t>
         </is>
       </c>
-      <c r="E270" s="1" t="inlineStr">
+      <c r="E270" t="inlineStr">
         <is>
           <t>profile.php?id=61559578166509</t>
         </is>
       </c>
-      <c r="F270" s="1" t="inlineStr">
+      <c r="F270" t="inlineStr">
         <is>
           <t>bap__roma</t>
         </is>
       </c>
-      <c r="G270" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H270" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I270" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J270" s="1" t="inlineStr"/>
-      <c r="K270" s="1" t="inlineStr"/>
-      <c r="L270" s="1" t="inlineStr"/>
-      <c r="M270" s="1" t="inlineStr"/>
-      <c r="N270" s="1" t="inlineStr"/>
-      <c r="O270" s="1" t="inlineStr"/>
-      <c r="P270" s="1" t="inlineStr"/>
-      <c r="Q270" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R270" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=61559578166509) | IG: trovato (bap__roma)</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="inlineStr">
+      <c r="A271" t="inlineStr">
         <is>
           <t>Barnum Café</t>
         </is>
       </c>
-      <c r="B271" s="1" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>Via del Pellegrino, 87</t>
         </is>
       </c>
-      <c r="C271" s="1" t="inlineStr">
+      <c r="C271" t="inlineStr">
         <is>
           <t>06/64760483</t>
         </is>
       </c>
-      <c r="D271" s="1" t="inlineStr">
+      <c r="D271" t="inlineStr">
         <is>
           <t>www.barnumroma.com</t>
         </is>
       </c>
-      <c r="E271" s="1" t="inlineStr">
+      <c r="E271" t="inlineStr">
         <is>
           <t>barnumroma</t>
         </is>
       </c>
-      <c r="F271" s="1" t="inlineStr">
+      <c r="F271" t="inlineStr">
         <is>
           <t>barnumroma</t>
         </is>
       </c>
-      <c r="G271" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H271" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I271" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J271" s="1" t="inlineStr"/>
-      <c r="K271" s="1" t="inlineStr"/>
-      <c r="L271" s="1" t="inlineStr"/>
-      <c r="M271" s="1" t="inlineStr"/>
-      <c r="N271" s="1" t="inlineStr"/>
-      <c r="O271" s="1" t="inlineStr"/>
-      <c r="P271" s="1" t="inlineStr"/>
-      <c r="Q271" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R271" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (barnumroma) | IG: trovato (barnumroma)</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="inlineStr">
+      <c r="A272" t="inlineStr">
         <is>
           <t>Cafè Merenda</t>
         </is>
       </c>
-      <c r="B272" s="1" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>Via del Gazometro, 5/A</t>
         </is>
       </c>
-      <c r="C272" s="1" t="inlineStr">
+      <c r="C272" t="inlineStr">
         <is>
           <t>06/45479738</t>
         </is>
       </c>
-      <c r="D272" s="1" t="inlineStr">
+      <c r="D272" t="inlineStr">
         <is>
           <t>www.cafemerenda.it</t>
         </is>
       </c>
-      <c r="E272" s="1" t="inlineStr">
+      <c r="E272" t="inlineStr">
         <is>
           <t>cafemerenda</t>
         </is>
       </c>
-      <c r="F272" s="1" t="inlineStr">
+      <c r="F272" t="inlineStr">
         <is>
           <t>cafemerenda_roma</t>
         </is>
       </c>
-      <c r="G272" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H272" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I272" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J272" s="1" t="inlineStr"/>
-      <c r="K272" s="1" t="inlineStr"/>
-      <c r="L272" s="1" t="inlineStr"/>
-      <c r="M272" s="1" t="inlineStr"/>
-      <c r="N272" s="1" t="inlineStr"/>
-      <c r="O272" s="1" t="inlineStr"/>
-      <c r="P272" s="1" t="inlineStr"/>
-      <c r="Q272" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R272" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (cafemerenda) | IG: trovato (cafemerenda_roma)</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="inlineStr">
+      <c r="A273" t="inlineStr">
         <is>
           <t>Caffè Conti</t>
         </is>
       </c>
-      <c r="B273" s="1" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>Via Tuscolana, 1677</t>
         </is>
       </c>
-      <c r="C273" s="1" t="inlineStr">
+      <c r="C273" t="inlineStr">
         <is>
           <t>351/9711876</t>
         </is>
       </c>
-      <c r="D273" s="1" t="inlineStr">
+      <c r="D273" t="inlineStr">
         <is>
           <t>www.caffeconti.it</t>
         </is>
       </c>
-      <c r="E273" s="1" t="inlineStr">
+      <c r="E273" t="inlineStr">
         <is>
           <t>caffetteriaconti</t>
         </is>
       </c>
-      <c r="F273" s="1" t="inlineStr">
+      <c r="F273" t="inlineStr">
         <is>
           <t>caffe_conti</t>
         </is>
       </c>
-      <c r="G273" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H273" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I273" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J273" s="1" t="inlineStr"/>
-      <c r="K273" s="1" t="inlineStr"/>
-      <c r="L273" s="1" t="inlineStr"/>
-      <c r="M273" s="1" t="inlineStr"/>
-      <c r="N273" s="1" t="inlineStr"/>
-      <c r="O273" s="1" t="inlineStr"/>
-      <c r="P273" s="1" t="inlineStr"/>
-      <c r="Q273" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R273" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (caffetteriaconti) | IG: trovato (caffe_conti)</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="inlineStr">
+      <c r="A274" t="inlineStr">
         <is>
           <t>Casa Manfredi Teatro</t>
         </is>
       </c>
-      <c r="B274" s="1" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>Via dei Conciatori, 5/A</t>
         </is>
       </c>
-      <c r="C274" s="1" t="inlineStr">
+      <c r="C274" t="inlineStr">
         <is>
           <t>06/97605892</t>
         </is>
       </c>
-      <c r="D274" s="1" t="inlineStr">
+      <c r="D274" t="inlineStr">
         <is>
           <t>www.casamanfredi.it</t>
         </is>
       </c>
-      <c r="E274" s="1" t="inlineStr">
+      <c r="E274" t="inlineStr">
         <is>
           <t>casamanfrediaventino</t>
         </is>
       </c>
-      <c r="F274" s="1" t="inlineStr">
+      <c r="F274" t="inlineStr">
         <is>
           <t>casamanfredi</t>
         </is>
       </c>
-      <c r="G274" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H274" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I274" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J274" s="1" t="inlineStr"/>
-      <c r="K274" s="1" t="inlineStr"/>
-      <c r="L274" s="1" t="inlineStr"/>
-      <c r="M274" s="1" t="inlineStr"/>
-      <c r="N274" s="1" t="inlineStr"/>
-      <c r="O274" s="1" t="inlineStr"/>
-      <c r="P274" s="1" t="inlineStr"/>
-      <c r="Q274" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R274" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (casamanfrediaventino) | IG: trovato (casamanfredi)</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="inlineStr">
+      <c r="A275" t="inlineStr">
         <is>
           <t>Casa Matti</t>
         </is>
       </c>
-      <c r="B275" s="1" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>Via Sabotino, 49/51</t>
         </is>
       </c>
-      <c r="C275" s="1" t="inlineStr">
+      <c r="C275" t="inlineStr">
         <is>
           <t>06/93563371</t>
         </is>
       </c>
-      <c r="D275" s="1" t="inlineStr"/>
-      <c r="E275" s="1" t="inlineStr"/>
-      <c r="F275" s="1" t="inlineStr">
+      <c r="F275" t="inlineStr">
         <is>
           <t>casa_matti_rm</t>
         </is>
       </c>
-      <c r="G275" s="1" t="inlineStr"/>
-      <c r="H275" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I275" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J275" s="1" t="inlineStr"/>
-      <c r="K275" s="1" t="inlineStr"/>
-      <c r="L275" s="1" t="inlineStr"/>
-      <c r="M275" s="1" t="inlineStr"/>
-      <c r="N275" s="1" t="inlineStr"/>
-      <c r="O275" s="1" t="inlineStr"/>
-      <c r="P275" s="1" t="inlineStr"/>
-      <c r="Q275" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R275" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (casa_matti_rm)</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="inlineStr">
+      <c r="A276" t="inlineStr">
         <is>
           <t>Cristalli di Zucchero</t>
         </is>
       </c>
-      <c r="B276" s="1" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>Via di Val Tellina, 114</t>
         </is>
       </c>
-      <c r="C276" s="1" t="inlineStr">
+      <c r="C276" t="inlineStr">
         <is>
           <t>06/58230323</t>
         </is>
       </c>
-      <c r="D276" s="1" t="inlineStr"/>
-      <c r="E276" s="1" t="inlineStr">
+      <c r="E276" t="inlineStr">
         <is>
           <t>CristalliDiZuccheroRoma</t>
         </is>
       </c>
-      <c r="F276" s="1" t="inlineStr">
+      <c r="F276" t="inlineStr">
         <is>
           <t>cristalli.di.zucchero</t>
         </is>
       </c>
-      <c r="G276" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H276" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I276" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J276" s="1" t="inlineStr"/>
-      <c r="K276" s="1" t="inlineStr"/>
-      <c r="L276" s="1" t="inlineStr"/>
-      <c r="M276" s="1" t="inlineStr"/>
-      <c r="N276" s="1" t="inlineStr"/>
-      <c r="O276" s="1" t="inlineStr"/>
-      <c r="P276" s="1" t="inlineStr"/>
-      <c r="Q276" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R276" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (CristalliDiZuccheroRoma) | IG: trovato (cristalli.di.zucchero)</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="inlineStr">
+      <c r="A277" t="inlineStr">
         <is>
           <t>D'Antoni dal 1974</t>
         </is>
       </c>
-      <c r="B277" s="1" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>Via Dino Penazzato, 83/H</t>
         </is>
       </c>
-      <c r="C277" s="1" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>06/2593441</t>
         </is>
       </c>
-      <c r="D277" s="1" t="inlineStr">
+      <c r="D277" t="inlineStr">
         <is>
           <t>www.dantoni1974.it</t>
         </is>
       </c>
-      <c r="E277" s="1" t="inlineStr">
+      <c r="E277" t="inlineStr">
         <is>
           <t>dantoni1974</t>
         </is>
       </c>
-      <c r="F277" s="1" t="inlineStr">
+      <c r="F277" t="inlineStr">
         <is>
           <t>dantoni1974</t>
         </is>
       </c>
-      <c r="G277" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H277" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I277" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J277" s="1" t="inlineStr"/>
-      <c r="K277" s="1" t="inlineStr"/>
-      <c r="L277" s="1" t="inlineStr"/>
-      <c r="M277" s="1" t="inlineStr"/>
-      <c r="N277" s="1" t="inlineStr"/>
-      <c r="O277" s="1" t="inlineStr"/>
-      <c r="P277" s="1" t="inlineStr"/>
-      <c r="Q277" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R277" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (dantoni1974) | IG: trovato (dantoni1974)</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="inlineStr">
+      <c r="A278" t="inlineStr">
         <is>
           <t>Faro - Caffè Specialty</t>
         </is>
       </c>
-      <c r="B278" s="1" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>Via Piave, 55</t>
         </is>
       </c>
-      <c r="C278" s="1" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>06/42815714</t>
         </is>
       </c>
-      <c r="D278" s="1" t="inlineStr">
+      <c r="D278" t="inlineStr">
         <is>
           <t>www.farorome.com</t>
         </is>
       </c>
-      <c r="E278" s="1" t="inlineStr">
+      <c r="E278" t="inlineStr">
         <is>
           <t>farorome</t>
         </is>
       </c>
-      <c r="F278" s="1" t="inlineStr">
+      <c r="F278" t="inlineStr">
         <is>
           <t>farorome</t>
         </is>
       </c>
-      <c r="G278" s="1" t="inlineStr">
+      <c r="G278" t="inlineStr">
         <is>
           <t>24/02/2026</t>
         </is>
       </c>
-      <c r="H278" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I278" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J278" s="1" t="inlineStr"/>
-      <c r="K278" s="1" t="inlineStr"/>
-      <c r="L278" s="1" t="inlineStr"/>
-      <c r="M278" s="1" t="inlineStr"/>
-      <c r="N278" s="1" t="inlineStr"/>
-      <c r="O278" s="1" t="inlineStr"/>
-      <c r="P278" s="1" t="inlineStr"/>
-      <c r="Q278" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R278" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (farorome) | IG: trovato (farorome)</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="inlineStr">
+      <c r="A279" t="inlineStr">
         <is>
           <t>Fax Factory</t>
         </is>
       </c>
-      <c r="B279" s="1" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>Via Antonio Raimondi, 87</t>
         </is>
       </c>
-      <c r="C279" s="1" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>06/69301043</t>
         </is>
       </c>
-      <c r="D279" s="1" t="inlineStr">
+      <c r="D279" t="inlineStr">
         <is>
           <t>www.faxfactory.it</t>
         </is>
       </c>
-      <c r="E279" s="1" t="inlineStr">
+      <c r="E279" t="inlineStr">
         <is>
           <t>FAXFactory</t>
         </is>
       </c>
-      <c r="F279" s="1" t="inlineStr">
+      <c r="F279" t="inlineStr">
         <is>
           <t>faxfactory</t>
         </is>
       </c>
-      <c r="G279" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H279" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I279" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J279" s="1" t="inlineStr"/>
-      <c r="K279" s="1" t="inlineStr"/>
-      <c r="L279" s="1" t="inlineStr"/>
-      <c r="M279" s="1" t="inlineStr"/>
-      <c r="N279" s="1" t="inlineStr"/>
-      <c r="O279" s="1" t="inlineStr"/>
-      <c r="P279" s="1" t="inlineStr"/>
-      <c r="Q279" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R279" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (FAXFactory) | IG: trovato (faxfactory)</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="inlineStr">
+      <c r="A280" t="inlineStr">
         <is>
           <t>Federico Prodon Pâtisserie</t>
         </is>
       </c>
-      <c r="B280" s="1" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>Via Giovanni Schiaparelli, 21</t>
         </is>
       </c>
-      <c r="C280" s="1" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>06/89325263</t>
         </is>
       </c>
-      <c r="D280" s="1" t="inlineStr"/>
-      <c r="E280" s="1" t="inlineStr">
+      <c r="E280" t="inlineStr">
         <is>
           <t>prodonpatisserie</t>
         </is>
       </c>
-      <c r="F280" s="1" t="inlineStr">
+      <c r="F280" t="inlineStr">
         <is>
           <t>federicoprodon</t>
         </is>
       </c>
-      <c r="G280" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H280" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I280" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J280" s="1" t="inlineStr"/>
-      <c r="K280" s="1" t="inlineStr"/>
-      <c r="L280" s="1" t="inlineStr"/>
-      <c r="M280" s="1" t="inlineStr"/>
-      <c r="N280" s="1" t="inlineStr"/>
-      <c r="O280" s="1" t="inlineStr"/>
-      <c r="P280" s="1" t="inlineStr"/>
-      <c r="Q280" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R280" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (prodonpatisserie) | IG: trovato (federicoprodon)</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -15768,672 +15768,913 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B247" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C247" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D247" s="1" t="inlineStr"/>
-      <c r="E247" s="1" t="inlineStr"/>
-      <c r="F247" s="1" t="inlineStr"/>
-      <c r="G247" s="1" t="inlineStr"/>
-      <c r="H247" s="1" t="inlineStr"/>
-      <c r="I247" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J247" s="1" t="inlineStr">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Piccolo Buco</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Via del Lavatore, 91</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>06/69380163</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>www.pizzeriapiccolobuco.it</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>PiccoloBuco</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>piccolobucoroma</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K247" s="1" t="inlineStr"/>
-      <c r="L247" s="1" t="inlineStr"/>
-      <c r="M247" s="1" t="inlineStr"/>
-      <c r="N247" s="1" t="inlineStr"/>
-      <c r="O247" s="1" t="inlineStr"/>
-      <c r="P247" s="1" t="inlineStr"/>
-      <c r="Q247" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R247" s="1" t="inlineStr">
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (PiccoloBuco) | IG: trovato (piccolobucoroma)</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="inlineStr">
-        <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
-        </is>
-      </c>
-      <c r="B248" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Erbe, 16</t>
-        </is>
-      </c>
-      <c r="C248" s="1" t="inlineStr">
-        <is>
-          <t>348/7277746</t>
-        </is>
-      </c>
-      <c r="D248" s="1" t="inlineStr"/>
-      <c r="E248" s="1" t="inlineStr"/>
-      <c r="F248" s="1" t="inlineStr"/>
-      <c r="G248" s="1" t="inlineStr"/>
-      <c r="H248" s="1" t="inlineStr"/>
-      <c r="I248" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J248" s="1" t="inlineStr">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Spiazzo</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Via Antonio Pacinotti, 83</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>065562738</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>www.pizzeriaspiazzo.it</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>PizzeriaSpiazzo</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>spiazzoroma</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K248" s="1" t="inlineStr"/>
-      <c r="L248" s="1" t="inlineStr"/>
-      <c r="M248" s="1" t="inlineStr"/>
-      <c r="N248" s="1" t="inlineStr"/>
-      <c r="O248" s="1" t="inlineStr"/>
-      <c r="P248" s="1" t="inlineStr"/>
-      <c r="Q248" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R248" s="1" t="inlineStr">
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (PizzeriaSpiazzo) | IG: trovato (spiazzoroma)</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="inlineStr">
-        <is>
-          <t>Osteria del Vicolo Fatato</t>
-        </is>
-      </c>
-      <c r="B249" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Forno Fatato, 11</t>
-        </is>
-      </c>
-      <c r="C249" s="1" t="inlineStr">
-        <is>
-          <t>0775/503035</t>
-        </is>
-      </c>
-      <c r="D249" s="1" t="inlineStr"/>
-      <c r="E249" s="1" t="inlineStr"/>
-      <c r="F249" s="1" t="inlineStr"/>
-      <c r="G249" s="1" t="inlineStr"/>
-      <c r="H249" s="1" t="inlineStr"/>
-      <c r="I249" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J249" s="1" t="inlineStr">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Svario-Pizza Bar</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Via Val Senio, 18</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>329/9299705</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>www.svario.it</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>svariopizzabar</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>svario_pizzabar</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K249" s="1" t="inlineStr"/>
-      <c r="L249" s="1" t="inlineStr"/>
-      <c r="M249" s="1" t="inlineStr"/>
-      <c r="N249" s="1" t="inlineStr"/>
-      <c r="O249" s="1" t="inlineStr"/>
-      <c r="P249" s="1" t="inlineStr"/>
-      <c r="Q249" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R249" s="1" t="inlineStr">
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (svariopizzabar) | IG: trovato (svario_pizzabar)</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="inlineStr">
-        <is>
-          <t>Poldo e Gianna</t>
-        </is>
-      </c>
-      <c r="B250" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Rosini, 6</t>
-        </is>
-      </c>
-      <c r="C250" s="1" t="inlineStr">
-        <is>
-          <t>06/6893499</t>
-        </is>
-      </c>
-      <c r="D250" s="1" t="inlineStr"/>
-      <c r="E250" s="1" t="inlineStr"/>
-      <c r="F250" s="1" t="inlineStr"/>
-      <c r="G250" s="1" t="inlineStr"/>
-      <c r="H250" s="1" t="inlineStr"/>
-      <c r="I250" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J250" s="1" t="inlineStr">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>TAC - Thin And Crunchy</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Via Fiume delle Perle, 136/138</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>06/45652738</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>www.seupizza.com</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>TACThinAndCrunchy</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>tacthinandcrunchy</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K250" s="1" t="inlineStr"/>
-      <c r="L250" s="1" t="inlineStr"/>
-      <c r="M250" s="1" t="inlineStr"/>
-      <c r="N250" s="1" t="inlineStr"/>
-      <c r="O250" s="1" t="inlineStr"/>
-      <c r="P250" s="1" t="inlineStr"/>
-      <c r="Q250" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R250" s="1" t="inlineStr">
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (TACThinAndCrunchy) | IG: trovato (tacthinandcrunchy)</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria A Casa Di Rita</t>
-        </is>
-      </c>
-      <c r="B251" s="1" t="inlineStr">
-        <is>
-          <t>Via delle Ciliegie, 145</t>
-        </is>
-      </c>
-      <c r="C251" s="1" t="inlineStr">
-        <is>
-          <t>338/9860960</t>
-        </is>
-      </c>
-      <c r="D251" s="1" t="inlineStr"/>
-      <c r="E251" s="1" t="inlineStr"/>
-      <c r="F251" s="1" t="inlineStr"/>
-      <c r="G251" s="1" t="inlineStr"/>
-      <c r="H251" s="1" t="inlineStr"/>
-      <c r="I251" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J251" s="1" t="inlineStr">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Tonda</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Via Valle Corteno, 31</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>06/8180960</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>pizzeriatonda</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>tondapizzeria</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K251" s="1" t="inlineStr"/>
-      <c r="L251" s="1" t="inlineStr"/>
-      <c r="M251" s="1" t="inlineStr"/>
-      <c r="N251" s="1" t="inlineStr"/>
-      <c r="O251" s="1" t="inlineStr"/>
-      <c r="P251" s="1" t="inlineStr"/>
-      <c r="Q251" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R251" s="1" t="inlineStr">
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (pizzeriatonda) | IG: trovato (tondapizzeria)</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="inlineStr">
-        <is>
-          <t>Ie Koji Japanese Izakaya</t>
-        </is>
-      </c>
-      <c r="B252" s="1" t="inlineStr">
-        <is>
-          <t>Via Marcantonio Bragadin, 13</t>
-        </is>
-      </c>
-      <c r="C252" s="1" t="inlineStr">
-        <is>
-          <t>348/4302368 - 06/69459860</t>
-        </is>
-      </c>
-      <c r="D252" s="1" t="inlineStr"/>
-      <c r="E252" s="1" t="inlineStr"/>
-      <c r="F252" s="1" t="inlineStr"/>
-      <c r="G252" s="1" t="inlineStr"/>
-      <c r="H252" s="1" t="inlineStr"/>
-      <c r="I252" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J252" s="1" t="inlineStr">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Artigiano del Caffè</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Via Famagosta, 14</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>329/7467044</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>www.artigianodelcafferoma.it</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>ArtigianodelCaffeRome</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>artigianodelcaffe</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K252" s="1" t="inlineStr"/>
-      <c r="L252" s="1" t="inlineStr"/>
-      <c r="M252" s="1" t="inlineStr"/>
-      <c r="N252" s="1" t="inlineStr"/>
-      <c r="O252" s="1" t="inlineStr"/>
-      <c r="P252" s="1" t="inlineStr"/>
-      <c r="Q252" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R252" s="1" t="inlineStr">
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ArtigianodelCaffeRome) | IG: trovato (artigianodelcaffe)</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B253" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C253" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D253" s="1" t="inlineStr"/>
-      <c r="E253" s="1" t="inlineStr"/>
-      <c r="F253" s="1" t="inlineStr"/>
-      <c r="G253" s="1" t="inlineStr"/>
-      <c r="H253" s="1" t="inlineStr"/>
-      <c r="I253" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J253" s="1" t="inlineStr">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Bap</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Via Raffaele Cadorna, 5</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>06/2428174</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>www.baproma.com</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>profile.php?id=61559578166509</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>bap__roma</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K253" s="1" t="inlineStr"/>
-      <c r="L253" s="1" t="inlineStr"/>
-      <c r="M253" s="1" t="inlineStr"/>
-      <c r="N253" s="1" t="inlineStr"/>
-      <c r="O253" s="1" t="inlineStr"/>
-      <c r="P253" s="1" t="inlineStr"/>
-      <c r="Q253" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R253" s="1" t="inlineStr">
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=61559578166509) | IG: trovato (bap__roma)</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="inlineStr">
-        <is>
-          <t>Nomisan</t>
-        </is>
-      </c>
-      <c r="B254" s="1" t="inlineStr">
-        <is>
-          <t>Viale Gianluigi Bonelli, 237</t>
-        </is>
-      </c>
-      <c r="C254" s="1" t="inlineStr">
-        <is>
-          <t>342/8036080</t>
-        </is>
-      </c>
-      <c r="D254" s="1" t="inlineStr"/>
-      <c r="E254" s="1" t="inlineStr"/>
-      <c r="F254" s="1" t="inlineStr"/>
-      <c r="G254" s="1" t="inlineStr"/>
-      <c r="H254" s="1" t="inlineStr"/>
-      <c r="I254" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J254" s="1" t="inlineStr">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Barnum Café</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Via del Pellegrino, 87</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>06/64760483</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>www.barnumroma.com</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>barnumroma</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>barnumroma</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K254" s="1" t="inlineStr"/>
-      <c r="L254" s="1" t="inlineStr"/>
-      <c r="M254" s="1" t="inlineStr"/>
-      <c r="N254" s="1" t="inlineStr"/>
-      <c r="O254" s="1" t="inlineStr"/>
-      <c r="P254" s="1" t="inlineStr"/>
-      <c r="Q254" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R254" s="1" t="inlineStr">
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (barnumroma) | IG: trovato (barnumroma)</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="inlineStr">
-        <is>
-          <t>Al Setaccio</t>
-        </is>
-      </c>
-      <c r="B255" s="1" t="inlineStr">
-        <is>
-          <t>Via di Mezzocammino, 193</t>
-        </is>
-      </c>
-      <c r="C255" s="1" t="inlineStr">
-        <is>
-          <t>06/52372056</t>
-        </is>
-      </c>
-      <c r="D255" s="1" t="inlineStr"/>
-      <c r="E255" s="1" t="inlineStr"/>
-      <c r="F255" s="1" t="inlineStr"/>
-      <c r="G255" s="1" t="inlineStr"/>
-      <c r="H255" s="1" t="inlineStr"/>
-      <c r="I255" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J255" s="1" t="inlineStr">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Cafè Merenda</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Via del Gazometro, 5/A</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>06/45479738</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>www.cafemerenda.it</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>cafemerenda</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>cafemerenda_roma</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K255" s="1" t="inlineStr"/>
-      <c r="L255" s="1" t="inlineStr"/>
-      <c r="M255" s="1" t="inlineStr"/>
-      <c r="N255" s="1" t="inlineStr"/>
-      <c r="O255" s="1" t="inlineStr"/>
-      <c r="P255" s="1" t="inlineStr"/>
-      <c r="Q255" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R255" s="1" t="inlineStr">
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (cafemerenda) | IG: trovato (cafemerenda_roma)</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="inlineStr">
-        <is>
-          <t>Angelo Pezzella</t>
-        </is>
-      </c>
-      <c r="B256" s="1" t="inlineStr">
-        <is>
-          <t>Via Appia Nuova, 1095</t>
-        </is>
-      </c>
-      <c r="C256" s="1" t="inlineStr">
-        <is>
-          <t>06/7188560</t>
-        </is>
-      </c>
-      <c r="D256" s="1" t="inlineStr"/>
-      <c r="E256" s="1" t="inlineStr"/>
-      <c r="F256" s="1" t="inlineStr"/>
-      <c r="G256" s="1" t="inlineStr"/>
-      <c r="H256" s="1" t="inlineStr"/>
-      <c r="I256" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J256" s="1" t="inlineStr">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Caffè Conti</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Via Tuscolana, 1677</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>351/9711876</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>www.caffeconti.it</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>caffetteriaconti</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>caffe_conti</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K256" s="1" t="inlineStr"/>
-      <c r="L256" s="1" t="inlineStr"/>
-      <c r="M256" s="1" t="inlineStr"/>
-      <c r="N256" s="1" t="inlineStr"/>
-      <c r="O256" s="1" t="inlineStr"/>
-      <c r="P256" s="1" t="inlineStr"/>
-      <c r="Q256" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R256" s="1" t="inlineStr">
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (caffetteriaconti) | IG: trovato (caffe_conti)</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="inlineStr">
-        <is>
-          <t>Clementina</t>
-        </is>
-      </c>
-      <c r="B257" s="1" t="inlineStr">
-        <is>
-          <t>Via della Torre Clementina, 158</t>
-        </is>
-      </c>
-      <c r="C257" s="1" t="inlineStr">
-        <is>
-          <t>328/8181651</t>
-        </is>
-      </c>
-      <c r="D257" s="1" t="inlineStr"/>
-      <c r="E257" s="1" t="inlineStr"/>
-      <c r="F257" s="1" t="inlineStr"/>
-      <c r="G257" s="1" t="inlineStr"/>
-      <c r="H257" s="1" t="inlineStr"/>
-      <c r="I257" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J257" s="1" t="inlineStr">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Casa Manfredi Teatro</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Via dei Conciatori, 5/A</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>06/97605892</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>www.casamanfredi.it</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>casamanfrediaventino</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>casamanfredi</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K257" s="1" t="inlineStr"/>
-      <c r="L257" s="1" t="inlineStr"/>
-      <c r="M257" s="1" t="inlineStr"/>
-      <c r="N257" s="1" t="inlineStr"/>
-      <c r="O257" s="1" t="inlineStr"/>
-      <c r="P257" s="1" t="inlineStr"/>
-      <c r="Q257" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R257" s="1" t="inlineStr">
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (casamanfrediaventino) | IG: trovato (casamanfredi)</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="inlineStr">
-        <is>
-          <t>Da Antonio</t>
-        </is>
-      </c>
-      <c r="B258" s="1" t="inlineStr">
-        <is>
-          <t>Via Mario Lizzani, 21</t>
-        </is>
-      </c>
-      <c r="C258" s="1" t="inlineStr">
-        <is>
-          <t>391/7475549</t>
-        </is>
-      </c>
-      <c r="D258" s="1" t="inlineStr"/>
-      <c r="E258" s="1" t="inlineStr"/>
-      <c r="F258" s="1" t="inlineStr"/>
-      <c r="G258" s="1" t="inlineStr"/>
-      <c r="H258" s="1" t="inlineStr"/>
-      <c r="I258" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J258" s="1" t="inlineStr">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Casa Matti</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Via Sabotino, 49/51</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>06/93563371</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>casa_matti_rm</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K258" s="1" t="inlineStr"/>
-      <c r="L258" s="1" t="inlineStr"/>
-      <c r="M258" s="1" t="inlineStr"/>
-      <c r="N258" s="1" t="inlineStr"/>
-      <c r="O258" s="1" t="inlineStr"/>
-      <c r="P258" s="1" t="inlineStr"/>
-      <c r="Q258" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R258" s="1" t="inlineStr">
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (casa_matti_rm)</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="inlineStr">
-        <is>
-          <t>Diego Vitagliano</t>
-        </is>
-      </c>
-      <c r="B259" s="1" t="inlineStr">
-        <is>
-          <t>Via Chiana, 80</t>
-        </is>
-      </c>
-      <c r="C259" s="1" t="inlineStr">
-        <is>
-          <t>06/72276443</t>
-        </is>
-      </c>
-      <c r="D259" s="1" t="inlineStr"/>
-      <c r="E259" s="1" t="inlineStr"/>
-      <c r="F259" s="1" t="inlineStr"/>
-      <c r="G259" s="1" t="inlineStr"/>
-      <c r="H259" s="1" t="inlineStr"/>
-      <c r="I259" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J259" s="1" t="inlineStr">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Cristalli di Zucchero</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Via di Val Tellina, 114</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>06/58230323</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>CristalliDiZuccheroRoma</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>cristalli.di.zucchero</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K259" s="1" t="inlineStr"/>
-      <c r="L259" s="1" t="inlineStr"/>
-      <c r="M259" s="1" t="inlineStr"/>
-      <c r="N259" s="1" t="inlineStr"/>
-      <c r="O259" s="1" t="inlineStr"/>
-      <c r="P259" s="1" t="inlineStr"/>
-      <c r="Q259" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R259" s="1" t="inlineStr">
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (CristalliDiZuccheroRoma) | IG: trovato (cristalli.di.zucchero)</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="inlineStr">
-        <is>
-          <t>GioMà</t>
-        </is>
-      </c>
-      <c r="B260" s="1" t="inlineStr">
-        <is>
-          <t>Via Calpurnio Fiamma, 40/44</t>
-        </is>
-      </c>
-      <c r="C260" s="1" t="inlineStr">
-        <is>
-          <t>06/7674717</t>
-        </is>
-      </c>
-      <c r="D260" s="1" t="inlineStr"/>
-      <c r="E260" s="1" t="inlineStr"/>
-      <c r="F260" s="1" t="inlineStr"/>
-      <c r="G260" s="1" t="inlineStr"/>
-      <c r="H260" s="1" t="inlineStr"/>
-      <c r="I260" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J260" s="1" t="inlineStr">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>D'Antoni dal 1974</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Via Dino Penazzato, 83/H</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>06/2593441</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>www.dantoni1974.it</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>dantoni1974</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>dantoni1974</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K260" s="1" t="inlineStr"/>
-      <c r="L260" s="1" t="inlineStr"/>
-      <c r="M260" s="1" t="inlineStr"/>
-      <c r="N260" s="1" t="inlineStr"/>
-      <c r="O260" s="1" t="inlineStr"/>
-      <c r="P260" s="1" t="inlineStr"/>
-      <c r="Q260" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R260" s="1" t="inlineStr">
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (dantoni1974) | IG: trovato (dantoni1974)</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
@@ -16442,37 +16683,37 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Piccolo Buco</t>
+          <t>Faro - Caffè Specialty</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Via del Lavatore, 91</t>
+          <t>Via Piave, 55</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>06/69380163</t>
+          <t>06/42815714</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>www.pizzeriapiccolobuco.it</t>
+          <t>www.farorome.com</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>PiccoloBuco</t>
+          <t>farorome</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>piccolobucoroma</t>
+          <t>farorome</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16497,7 +16738,7 @@
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (PiccoloBuco) | IG: trovato (piccolobucoroma)</t>
+          <t>TF: non trovato | FB: trovato (farorome) | IG: trovato (farorome)</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -16507,96 +16748,129 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="inlineStr">
-        <is>
-          <t>Pupillo Pura Pizza</t>
-        </is>
-      </c>
-      <c r="B262" s="1" t="inlineStr">
-        <is>
-          <t>Via Giacomo Matteotti, 29</t>
-        </is>
-      </c>
-      <c r="C262" s="1" t="inlineStr">
-        <is>
-          <t>339/4143148</t>
-        </is>
-      </c>
-      <c r="D262" s="1" t="inlineStr"/>
-      <c r="E262" s="1" t="inlineStr"/>
-      <c r="F262" s="1" t="inlineStr"/>
-      <c r="G262" s="1" t="inlineStr"/>
-      <c r="H262" s="1" t="inlineStr"/>
-      <c r="I262" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J262" s="1" t="inlineStr">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Fax Factory</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Via Antonio Raimondi, 87</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>06/69301043</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>www.faxfactory.it</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>FAXFactory</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>faxfactory</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K262" s="1" t="inlineStr"/>
-      <c r="L262" s="1" t="inlineStr"/>
-      <c r="M262" s="1" t="inlineStr"/>
-      <c r="N262" s="1" t="inlineStr"/>
-      <c r="O262" s="1" t="inlineStr"/>
-      <c r="P262" s="1" t="inlineStr"/>
-      <c r="Q262" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R262" s="1" t="inlineStr">
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (FAXFactory) | IG: trovato (faxfactory)</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="inlineStr">
-        <is>
-          <t>Santa Romana</t>
-        </is>
-      </c>
-      <c r="B263" s="1" t="inlineStr">
-        <is>
-          <t>Piazza Certaldo, 12</t>
-        </is>
-      </c>
-      <c r="C263" s="1" t="inlineStr">
-        <is>
-          <t>06/69317674</t>
-        </is>
-      </c>
-      <c r="D263" s="1" t="inlineStr"/>
-      <c r="E263" s="1" t="inlineStr"/>
-      <c r="F263" s="1" t="inlineStr"/>
-      <c r="G263" s="1" t="inlineStr"/>
-      <c r="H263" s="1" t="inlineStr"/>
-      <c r="I263" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J263" s="1" t="inlineStr">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Federico Prodon Pâtisserie</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Via Giovanni Schiaparelli, 21</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>06/89325263</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>prodonpatisserie</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>federicoprodon</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K263" s="1" t="inlineStr"/>
-      <c r="L263" s="1" t="inlineStr"/>
-      <c r="M263" s="1" t="inlineStr"/>
-      <c r="N263" s="1" t="inlineStr"/>
-      <c r="O263" s="1" t="inlineStr"/>
-      <c r="P263" s="1" t="inlineStr"/>
-      <c r="Q263" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R263" s="1" t="inlineStr">
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (prodonpatisserie) | IG: trovato (federicoprodon)</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
@@ -16605,17 +16879,17 @@
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>Seu Pizza Illuminati</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>Via Angelo Bargoni, 10/18</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t>06/5883384</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D264" s="1" t="inlineStr"/>
@@ -16646,1105 +16920,832 @@
       </c>
       <c r="R264" s="1" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>Spiazzo</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Via Antonio Pacinotti, 83</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>065562738</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>www.pizzeriaspiazzo.it</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>PizzeriaSpiazzo</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>spiazzoroma</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="inlineStr">
+        <is>
+          <t>Piazza delle Erbe, 16</t>
+        </is>
+      </c>
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>348/7277746</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr"/>
+      <c r="E265" s="1" t="inlineStr"/>
+      <c r="F265" s="1" t="inlineStr"/>
+      <c r="G265" s="1" t="inlineStr"/>
+      <c r="H265" s="1" t="inlineStr"/>
+      <c r="I265" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J265" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O265" t="inlineStr">
+      <c r="K265" s="1" t="inlineStr"/>
+      <c r="L265" s="1" t="inlineStr"/>
+      <c r="M265" s="1" t="inlineStr"/>
+      <c r="N265" s="1" t="inlineStr"/>
+      <c r="O265" s="1" t="inlineStr"/>
+      <c r="P265" s="1" t="inlineStr"/>
+      <c r="Q265" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R265" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>Osteria del Vicolo Fatato</t>
+        </is>
+      </c>
+      <c r="B266" s="1" t="inlineStr">
+        <is>
+          <t>Vicolo Forno Fatato, 11</t>
+        </is>
+      </c>
+      <c r="C266" s="1" t="inlineStr">
+        <is>
+          <t>0775/503035</t>
+        </is>
+      </c>
+      <c r="D266" s="1" t="inlineStr"/>
+      <c r="E266" s="1" t="inlineStr"/>
+      <c r="F266" s="1" t="inlineStr"/>
+      <c r="G266" s="1" t="inlineStr"/>
+      <c r="H266" s="1" t="inlineStr"/>
+      <c r="I266" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J266" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K266" s="1" t="inlineStr"/>
+      <c r="L266" s="1" t="inlineStr"/>
+      <c r="M266" s="1" t="inlineStr"/>
+      <c r="N266" s="1" t="inlineStr"/>
+      <c r="O266" s="1" t="inlineStr"/>
+      <c r="P266" s="1" t="inlineStr"/>
+      <c r="Q266" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R266" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>Poldo e Gianna</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="inlineStr">
+        <is>
+          <t>Vicolo Rosini, 6</t>
+        </is>
+      </c>
+      <c r="C267" s="1" t="inlineStr">
+        <is>
+          <t>06/6893499</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr"/>
+      <c r="E267" s="1" t="inlineStr"/>
+      <c r="F267" s="1" t="inlineStr"/>
+      <c r="G267" s="1" t="inlineStr"/>
+      <c r="H267" s="1" t="inlineStr"/>
+      <c r="I267" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J267" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K267" s="1" t="inlineStr"/>
+      <c r="L267" s="1" t="inlineStr"/>
+      <c r="M267" s="1" t="inlineStr"/>
+      <c r="N267" s="1" t="inlineStr"/>
+      <c r="O267" s="1" t="inlineStr"/>
+      <c r="P267" s="1" t="inlineStr"/>
+      <c r="Q267" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R267" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>Trattoria A Casa Di Rita</t>
+        </is>
+      </c>
+      <c r="B268" s="1" t="inlineStr">
+        <is>
+          <t>Via delle Ciliegie, 145</t>
+        </is>
+      </c>
+      <c r="C268" s="1" t="inlineStr">
+        <is>
+          <t>338/9860960</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="inlineStr"/>
+      <c r="E268" s="1" t="inlineStr"/>
+      <c r="F268" s="1" t="inlineStr"/>
+      <c r="G268" s="1" t="inlineStr"/>
+      <c r="H268" s="1" t="inlineStr"/>
+      <c r="I268" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J268" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K268" s="1" t="inlineStr"/>
+      <c r="L268" s="1" t="inlineStr"/>
+      <c r="M268" s="1" t="inlineStr"/>
+      <c r="N268" s="1" t="inlineStr"/>
+      <c r="O268" s="1" t="inlineStr"/>
+      <c r="P268" s="1" t="inlineStr"/>
+      <c r="Q268" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R268" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>Ie Koji Japanese Izakaya</t>
+        </is>
+      </c>
+      <c r="B269" s="1" t="inlineStr">
+        <is>
+          <t>Via Marcantonio Bragadin, 13</t>
+        </is>
+      </c>
+      <c r="C269" s="1" t="inlineStr">
+        <is>
+          <t>348/4302368 - 06/69459860</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="inlineStr"/>
+      <c r="E269" s="1" t="inlineStr"/>
+      <c r="F269" s="1" t="inlineStr"/>
+      <c r="G269" s="1" t="inlineStr"/>
+      <c r="H269" s="1" t="inlineStr"/>
+      <c r="I269" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J269" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K269" s="1" t="inlineStr"/>
+      <c r="L269" s="1" t="inlineStr"/>
+      <c r="M269" s="1" t="inlineStr"/>
+      <c r="N269" s="1" t="inlineStr"/>
+      <c r="O269" s="1" t="inlineStr"/>
+      <c r="P269" s="1" t="inlineStr"/>
+      <c r="Q269" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R269" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>Mrgda Ristorante</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="inlineStr">
+        <is>
+          <t>Via Prenestina, 182</t>
+        </is>
+      </c>
+      <c r="C270" s="1" t="inlineStr">
+        <is>
+          <t>329/933355</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="inlineStr"/>
+      <c r="E270" s="1" t="inlineStr"/>
+      <c r="F270" s="1" t="inlineStr"/>
+      <c r="G270" s="1" t="inlineStr"/>
+      <c r="H270" s="1" t="inlineStr"/>
+      <c r="I270" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J270" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K270" s="1" t="inlineStr"/>
+      <c r="L270" s="1" t="inlineStr"/>
+      <c r="M270" s="1" t="inlineStr"/>
+      <c r="N270" s="1" t="inlineStr"/>
+      <c r="O270" s="1" t="inlineStr"/>
+      <c r="P270" s="1" t="inlineStr"/>
+      <c r="Q270" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R270" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>Nomisan</t>
+        </is>
+      </c>
+      <c r="B271" s="1" t="inlineStr">
+        <is>
+          <t>Viale Gianluigi Bonelli, 237</t>
+        </is>
+      </c>
+      <c r="C271" s="1" t="inlineStr">
+        <is>
+          <t>342/8036080</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="inlineStr"/>
+      <c r="E271" s="1" t="inlineStr"/>
+      <c r="F271" s="1" t="inlineStr"/>
+      <c r="G271" s="1" t="inlineStr"/>
+      <c r="H271" s="1" t="inlineStr"/>
+      <c r="I271" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J271" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K271" s="1" t="inlineStr"/>
+      <c r="L271" s="1" t="inlineStr"/>
+      <c r="M271" s="1" t="inlineStr"/>
+      <c r="N271" s="1" t="inlineStr"/>
+      <c r="O271" s="1" t="inlineStr"/>
+      <c r="P271" s="1" t="inlineStr"/>
+      <c r="Q271" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R271" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>Al Setaccio</t>
+        </is>
+      </c>
+      <c r="B272" s="1" t="inlineStr">
+        <is>
+          <t>Via di Mezzocammino, 193</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="inlineStr">
+        <is>
+          <t>06/52372056</t>
+        </is>
+      </c>
+      <c r="D272" s="1" t="inlineStr"/>
+      <c r="E272" s="1" t="inlineStr"/>
+      <c r="F272" s="1" t="inlineStr"/>
+      <c r="G272" s="1" t="inlineStr"/>
+      <c r="H272" s="1" t="inlineStr"/>
+      <c r="I272" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J272" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K272" s="1" t="inlineStr"/>
+      <c r="L272" s="1" t="inlineStr"/>
+      <c r="M272" s="1" t="inlineStr"/>
+      <c r="N272" s="1" t="inlineStr"/>
+      <c r="O272" s="1" t="inlineStr"/>
+      <c r="P272" s="1" t="inlineStr"/>
+      <c r="Q272" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R272" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>Angelo Pezzella</t>
+        </is>
+      </c>
+      <c r="B273" s="1" t="inlineStr">
+        <is>
+          <t>Via Appia Nuova, 1095</t>
+        </is>
+      </c>
+      <c r="C273" s="1" t="inlineStr">
+        <is>
+          <t>06/7188560</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="inlineStr"/>
+      <c r="E273" s="1" t="inlineStr"/>
+      <c r="F273" s="1" t="inlineStr"/>
+      <c r="G273" s="1" t="inlineStr"/>
+      <c r="H273" s="1" t="inlineStr"/>
+      <c r="I273" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J273" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K273" s="1" t="inlineStr"/>
+      <c r="L273" s="1" t="inlineStr"/>
+      <c r="M273" s="1" t="inlineStr"/>
+      <c r="N273" s="1" t="inlineStr"/>
+      <c r="O273" s="1" t="inlineStr"/>
+      <c r="P273" s="1" t="inlineStr"/>
+      <c r="Q273" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R273" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>Clementina</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="inlineStr">
+        <is>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C274" s="1" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr"/>
+      <c r="E274" s="1" t="inlineStr"/>
+      <c r="F274" s="1" t="inlineStr"/>
+      <c r="G274" s="1" t="inlineStr"/>
+      <c r="H274" s="1" t="inlineStr"/>
+      <c r="I274" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J274" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K274" s="1" t="inlineStr"/>
+      <c r="L274" s="1" t="inlineStr"/>
+      <c r="M274" s="1" t="inlineStr"/>
+      <c r="N274" s="1" t="inlineStr"/>
+      <c r="O274" s="1" t="inlineStr"/>
+      <c r="P274" s="1" t="inlineStr"/>
+      <c r="Q274" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R274" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>Da Antonio</t>
+        </is>
+      </c>
+      <c r="B275" s="1" t="inlineStr">
+        <is>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C275" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="inlineStr"/>
+      <c r="E275" s="1" t="inlineStr"/>
+      <c r="F275" s="1" t="inlineStr"/>
+      <c r="G275" s="1" t="inlineStr"/>
+      <c r="H275" s="1" t="inlineStr"/>
+      <c r="I275" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J275" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K275" s="1" t="inlineStr"/>
+      <c r="L275" s="1" t="inlineStr"/>
+      <c r="M275" s="1" t="inlineStr"/>
+      <c r="N275" s="1" t="inlineStr"/>
+      <c r="O275" s="1" t="inlineStr"/>
+      <c r="P275" s="1" t="inlineStr"/>
+      <c r="Q275" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R275" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>Diego Vitagliano</t>
+        </is>
+      </c>
+      <c r="B276" s="1" t="inlineStr">
+        <is>
+          <t>Via Chiana, 80</t>
+        </is>
+      </c>
+      <c r="C276" s="1" t="inlineStr">
+        <is>
+          <t>06/72276443</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="inlineStr"/>
+      <c r="E276" s="1" t="inlineStr"/>
+      <c r="F276" s="1" t="inlineStr"/>
+      <c r="G276" s="1" t="inlineStr"/>
+      <c r="H276" s="1" t="inlineStr"/>
+      <c r="I276" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J276" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K276" s="1" t="inlineStr"/>
+      <c r="L276" s="1" t="inlineStr"/>
+      <c r="M276" s="1" t="inlineStr"/>
+      <c r="N276" s="1" t="inlineStr"/>
+      <c r="O276" s="1" t="inlineStr"/>
+      <c r="P276" s="1" t="inlineStr"/>
+      <c r="Q276" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R276" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>GioMà</t>
+        </is>
+      </c>
+      <c r="B277" s="1" t="inlineStr">
+        <is>
+          <t>Via Calpurnio Fiamma, 40/44</t>
+        </is>
+      </c>
+      <c r="C277" s="1" t="inlineStr">
+        <is>
+          <t>06/7674717</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="inlineStr"/>
+      <c r="E277" s="1" t="inlineStr"/>
+      <c r="F277" s="1" t="inlineStr"/>
+      <c r="G277" s="1" t="inlineStr"/>
+      <c r="H277" s="1" t="inlineStr"/>
+      <c r="I277" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J277" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K277" s="1" t="inlineStr"/>
+      <c r="L277" s="1" t="inlineStr"/>
+      <c r="M277" s="1" t="inlineStr"/>
+      <c r="N277" s="1" t="inlineStr"/>
+      <c r="O277" s="1" t="inlineStr"/>
+      <c r="P277" s="1" t="inlineStr"/>
+      <c r="Q277" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R277" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>Pupillo Pura Pizza</t>
+        </is>
+      </c>
+      <c r="B278" s="1" t="inlineStr">
+        <is>
+          <t>Via Giacomo Matteotti, 29</t>
+        </is>
+      </c>
+      <c r="C278" s="1" t="inlineStr">
+        <is>
+          <t>339/4143148</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="inlineStr"/>
+      <c r="E278" s="1" t="inlineStr"/>
+      <c r="F278" s="1" t="inlineStr"/>
+      <c r="G278" s="1" t="inlineStr"/>
+      <c r="H278" s="1" t="inlineStr"/>
+      <c r="I278" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J278" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K278" s="1" t="inlineStr"/>
+      <c r="L278" s="1" t="inlineStr"/>
+      <c r="M278" s="1" t="inlineStr"/>
+      <c r="N278" s="1" t="inlineStr"/>
+      <c r="O278" s="1" t="inlineStr"/>
+      <c r="P278" s="1" t="inlineStr"/>
+      <c r="Q278" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R278" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>Santa Romana</t>
+        </is>
+      </c>
+      <c r="B279" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Certaldo, 12</t>
+        </is>
+      </c>
+      <c r="C279" s="1" t="inlineStr">
+        <is>
+          <t>06/69317674</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="inlineStr"/>
+      <c r="E279" s="1" t="inlineStr"/>
+      <c r="F279" s="1" t="inlineStr"/>
+      <c r="G279" s="1" t="inlineStr"/>
+      <c r="H279" s="1" t="inlineStr"/>
+      <c r="I279" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J279" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K279" s="1" t="inlineStr"/>
+      <c r="L279" s="1" t="inlineStr"/>
+      <c r="M279" s="1" t="inlineStr"/>
+      <c r="N279" s="1" t="inlineStr"/>
+      <c r="O279" s="1" t="inlineStr"/>
+      <c r="P279" s="1" t="inlineStr"/>
+      <c r="Q279" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R279" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>Seu Pizza Illuminati</t>
+        </is>
+      </c>
+      <c r="B280" s="1" t="inlineStr">
+        <is>
+          <t>Via Angelo Bargoni, 10/18</t>
+        </is>
+      </c>
+      <c r="C280" s="1" t="inlineStr">
+        <is>
+          <t>06/5883384</t>
+        </is>
+      </c>
+      <c r="D280" s="1" t="inlineStr"/>
+      <c r="E280" s="1" t="inlineStr"/>
+      <c r="F280" s="1" t="inlineStr"/>
+      <c r="G280" s="1" t="inlineStr"/>
+      <c r="H280" s="1" t="inlineStr"/>
+      <c r="I280" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J280" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K280" s="1" t="inlineStr"/>
+      <c r="L280" s="1" t="inlineStr"/>
+      <c r="M280" s="1" t="inlineStr"/>
+      <c r="N280" s="1" t="inlineStr"/>
+      <c r="O280" s="1" t="inlineStr"/>
+      <c r="P280" s="1" t="inlineStr"/>
+      <c r="Q280" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R280" s="1" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Forno Conti &amp; Co.</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Via Giusti, 18</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>06/2757595</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>www.fornoconti.co</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>fornoconti.roma</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q265" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (PizzeriaSpiazzo) | IG: trovato (spiazzoroma)</t>
-        </is>
-      </c>
-      <c r="R265" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>Svario-Pizza Bar</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Via Val Senio, 18</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>329/9299705</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>www.svario.it</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>svariopizzabar</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>svario_pizzabar</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O266" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (svariopizzabar) | IG: trovato (svario_pizzabar)</t>
-        </is>
-      </c>
-      <c r="R266" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>TAC - Thin And Crunchy</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Via Fiume delle Perle, 136/138</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>06/45652738</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>www.seupizza.com</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>TACThinAndCrunchy</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>tacthinandcrunchy</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O267" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q267" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (TACThinAndCrunchy) | IG: trovato (tacthinandcrunchy)</t>
-        </is>
-      </c>
-      <c r="R267" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Tonda</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Via Valle Corteno, 31</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>06/8180960</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>pizzeriatonda</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>tondapizzeria</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O268" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q268" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (pizzeriatonda) | IG: trovato (tondapizzeria)</t>
-        </is>
-      </c>
-      <c r="R268" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Artigiano del Caffè</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Via Famagosta, 14</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>329/7467044</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>www.artigianodelcafferoma.it</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>ArtigianodelCaffeRome</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>artigianodelcaffe</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O269" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q269" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (ArtigianodelCaffeRome) | IG: trovato (artigianodelcaffe)</t>
-        </is>
-      </c>
-      <c r="R269" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>Bap</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Via Raffaele Cadorna, 5</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>06/2428174</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>www.baproma.com</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>profile.php?id=61559578166509</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>bap__roma</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O270" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q270" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (profile.php?id=61559578166509) | IG: trovato (bap__roma)</t>
-        </is>
-      </c>
-      <c r="R270" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Barnum Café</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Via del Pellegrino, 87</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>06/64760483</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>www.barnumroma.com</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>barnumroma</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>barnumroma</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O271" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q271" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (barnumroma) | IG: trovato (barnumroma)</t>
-        </is>
-      </c>
-      <c r="R271" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>Cafè Merenda</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Via del Gazometro, 5/A</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>06/45479738</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>www.cafemerenda.it</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>cafemerenda</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>cafemerenda_roma</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O272" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (cafemerenda) | IG: trovato (cafemerenda_roma)</t>
-        </is>
-      </c>
-      <c r="R272" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>Caffè Conti</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Via Tuscolana, 1677</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>351/9711876</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>www.caffeconti.it</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>caffetteriaconti</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>caffe_conti</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O273" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (caffetteriaconti) | IG: trovato (caffe_conti)</t>
-        </is>
-      </c>
-      <c r="R273" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Casa Manfredi Teatro</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Via dei Conciatori, 5/A</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>06/97605892</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>www.casamanfredi.it</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>casamanfrediaventino</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>casamanfredi</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O274" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (casamanfrediaventino) | IG: trovato (casamanfredi)</t>
-        </is>
-      </c>
-      <c r="R274" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Casa Matti</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Via Sabotino, 49/51</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>06/93563371</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>casa_matti_rm</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O275" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q275" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (casa_matti_rm)</t>
-        </is>
-      </c>
-      <c r="R275" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Cristalli di Zucchero</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Via di Val Tellina, 114</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>06/58230323</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>CristalliDiZuccheroRoma</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>cristalli.di.zucchero</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O276" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q276" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (CristalliDiZuccheroRoma) | IG: trovato (cristalli.di.zucchero)</t>
-        </is>
-      </c>
-      <c r="R276" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>D'Antoni dal 1974</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Via Dino Penazzato, 83/H</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>06/2593441</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>www.dantoni1974.it</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>dantoni1974</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>dantoni1974</t>
-        </is>
-      </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O277" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q277" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (dantoni1974) | IG: trovato (dantoni1974)</t>
-        </is>
-      </c>
-      <c r="R277" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>Faro - Caffè Specialty</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Via Piave, 55</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>06/42815714</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>www.farorome.com</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>farorome</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>farorome</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>24/02/2026</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O278" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q278" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (farorome) | IG: trovato (farorome)</t>
-        </is>
-      </c>
-      <c r="R278" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>Fax Factory</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Via Antonio Raimondi, 87</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>06/69301043</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>www.faxfactory.it</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>FAXFactory</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>faxfactory</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O279" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q279" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (FAXFactory) | IG: trovato (faxfactory)</t>
-        </is>
-      </c>
-      <c r="R279" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>Federico Prodon Pâtisserie</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Via Giovanni Schiaparelli, 21</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>06/89325263</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>prodonpatisserie</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>federicoprodon</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O280" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q280" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (prodonpatisserie) | IG: trovato (federicoprodon)</t>
-        </is>
-      </c>
-      <c r="R280" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="1" t="inlineStr">
-        <is>
-          <t>Forno Conti &amp; Co.</t>
-        </is>
-      </c>
-      <c r="B281" s="1" t="inlineStr">
-        <is>
-          <t>Via Giusti, 18</t>
-        </is>
-      </c>
-      <c r="C281" s="1" t="inlineStr">
-        <is>
-          <t>06/2757595</t>
-        </is>
-      </c>
-      <c r="D281" s="1" t="inlineStr">
-        <is>
-          <t>www.fornoconti.co</t>
-        </is>
-      </c>
-      <c r="E281" s="1" t="inlineStr"/>
-      <c r="F281" s="1" t="inlineStr">
-        <is>
-          <t>fornoconti.roma</t>
-        </is>
-      </c>
-      <c r="G281" s="1" t="inlineStr"/>
-      <c r="H281" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I281" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J281" s="1" t="inlineStr"/>
-      <c r="K281" s="1" t="inlineStr"/>
-      <c r="L281" s="1" t="inlineStr"/>
-      <c r="M281" s="1" t="inlineStr"/>
-      <c r="N281" s="1" t="inlineStr"/>
-      <c r="O281" s="1" t="inlineStr"/>
-      <c r="P281" s="1" t="inlineStr"/>
-      <c r="Q281" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R281" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (fornoconti.roma)</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -17774,7 +17775,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J282" s="1" t="inlineStr"/>
+      <c r="J282" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K282" s="1" t="inlineStr"/>
       <c r="L282" s="1" t="inlineStr"/>
       <c r="M282" s="1" t="inlineStr"/>
@@ -17783,128 +17788,131 @@
       <c r="P282" s="1" t="inlineStr"/>
       <c r="Q282" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="inlineStr">
+      <c r="A283" t="inlineStr">
         <is>
           <t>Gastromario</t>
         </is>
       </c>
-      <c r="B283" s="1" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>Via Voghera, 10</t>
         </is>
       </c>
-      <c r="C283" s="1" t="inlineStr">
+      <c r="C283" t="inlineStr">
         <is>
           <t>06/79782584</t>
         </is>
       </c>
-      <c r="D283" s="1" t="inlineStr"/>
-      <c r="E283" s="1" t="inlineStr">
+      <c r="E283" t="inlineStr">
         <is>
           <t>Gastromario</t>
         </is>
       </c>
-      <c r="F283" s="1" t="inlineStr">
+      <c r="F283" t="inlineStr">
         <is>
           <t>gastromario.it</t>
         </is>
       </c>
-      <c r="G283" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H283" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I283" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J283" s="1" t="inlineStr"/>
-      <c r="K283" s="1" t="inlineStr"/>
-      <c r="L283" s="1" t="inlineStr"/>
-      <c r="M283" s="1" t="inlineStr"/>
-      <c r="N283" s="1" t="inlineStr"/>
-      <c r="O283" s="1" t="inlineStr"/>
-      <c r="P283" s="1" t="inlineStr"/>
-      <c r="Q283" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R283" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Gastromario) | IG: trovato (gastromario.it)</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="inlineStr">
+      <c r="A284" t="inlineStr">
         <is>
           <t>Grani, farine e caffè</t>
         </is>
       </c>
-      <c r="B284" s="1" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>Viale dei Quattro Venti, 152/C</t>
         </is>
       </c>
-      <c r="C284" s="1" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>3476145569</t>
         </is>
       </c>
-      <c r="D284" s="1" t="inlineStr">
+      <c r="D284" t="inlineStr">
         <is>
           <t>www.granifarinecaffe.it</t>
         </is>
       </c>
-      <c r="E284" s="1" t="inlineStr"/>
-      <c r="F284" s="1" t="inlineStr">
+      <c r="F284" t="inlineStr">
         <is>
           <t>grani_farine_e_caffe</t>
         </is>
       </c>
-      <c r="G284" s="1" t="inlineStr"/>
-      <c r="H284" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I284" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J284" s="1" t="inlineStr"/>
-      <c r="K284" s="1" t="inlineStr"/>
-      <c r="L284" s="1" t="inlineStr"/>
-      <c r="M284" s="1" t="inlineStr"/>
-      <c r="N284" s="1" t="inlineStr"/>
-      <c r="O284" s="1" t="inlineStr"/>
-      <c r="P284" s="1" t="inlineStr"/>
-      <c r="Q284" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R284" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (grani_farine_e_caffe)</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17942,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J285" s="1" t="inlineStr"/>
+      <c r="J285" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K285" s="1" t="inlineStr"/>
       <c r="L285" s="1" t="inlineStr"/>
       <c r="M285" s="1" t="inlineStr"/>
@@ -17943,12 +17955,12 @@
       <c r="P285" s="1" t="inlineStr"/>
       <c r="Q285" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17990,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J286" s="1" t="inlineStr"/>
+      <c r="J286" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K286" s="1" t="inlineStr"/>
       <c r="L286" s="1" t="inlineStr"/>
       <c r="M286" s="1" t="inlineStr"/>
@@ -17987,628 +18003,652 @@
       <c r="P286" s="1" t="inlineStr"/>
       <c r="Q286" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="inlineStr">
+      <c r="A287" t="inlineStr">
         <is>
           <t>Le Levain Café</t>
         </is>
       </c>
-      <c r="B287" s="1" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>Via Piave, 8</t>
         </is>
       </c>
-      <c r="C287" s="1" t="inlineStr">
+      <c r="C287" t="inlineStr">
         <is>
           <t>376/2067672</t>
         </is>
       </c>
-      <c r="D287" s="1" t="inlineStr">
+      <c r="D287" t="inlineStr">
         <is>
           <t>www.lelevainroma.it</t>
         </is>
       </c>
-      <c r="E287" s="1" t="inlineStr">
+      <c r="E287" t="inlineStr">
         <is>
           <t>LeLevainRoma</t>
         </is>
       </c>
-      <c r="F287" s="1" t="inlineStr">
+      <c r="F287" t="inlineStr">
         <is>
           <t>lelevainroma</t>
         </is>
       </c>
-      <c r="G287" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H287" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I287" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J287" s="1" t="inlineStr"/>
-      <c r="K287" s="1" t="inlineStr"/>
-      <c r="L287" s="1" t="inlineStr"/>
-      <c r="M287" s="1" t="inlineStr"/>
-      <c r="N287" s="1" t="inlineStr"/>
-      <c r="O287" s="1" t="inlineStr"/>
-      <c r="P287" s="1" t="inlineStr"/>
-      <c r="Q287" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R287" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (LeLevainRoma) | IG: trovato (lelevainroma)</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="inlineStr">
+      <c r="A288" t="inlineStr">
         <is>
           <t>Lievito Francesco Arnesano</t>
         </is>
       </c>
-      <c r="B288" s="1" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>Via Simone Martini, 6/8</t>
         </is>
       </c>
-      <c r="C288" s="1" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>06/69363592</t>
         </is>
       </c>
-      <c r="D288" s="1" t="inlineStr"/>
-      <c r="E288" s="1" t="inlineStr">
+      <c r="E288" t="inlineStr">
         <is>
           <t>lievitofrancescoarnesano</t>
         </is>
       </c>
-      <c r="F288" s="1" t="inlineStr">
+      <c r="F288" t="inlineStr">
         <is>
           <t>lievitopizzapane</t>
         </is>
       </c>
-      <c r="G288" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H288" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I288" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J288" s="1" t="inlineStr"/>
-      <c r="K288" s="1" t="inlineStr"/>
-      <c r="L288" s="1" t="inlineStr"/>
-      <c r="M288" s="1" t="inlineStr"/>
-      <c r="N288" s="1" t="inlineStr"/>
-      <c r="O288" s="1" t="inlineStr"/>
-      <c r="P288" s="1" t="inlineStr"/>
-      <c r="Q288" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R288" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (lievitofrancescoarnesano) | IG: trovato (lievitopizzapane)</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="inlineStr">
+      <c r="A289" t="inlineStr">
         <is>
           <t>Love</t>
         </is>
       </c>
-      <c r="B289" s="1" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>Via Tunisi, 51</t>
         </is>
       </c>
-      <c r="C289" s="1" t="inlineStr">
+      <c r="C289" t="inlineStr">
         <is>
           <t>06/96525119</t>
         </is>
       </c>
-      <c r="D289" s="1" t="inlineStr">
+      <c r="D289" t="inlineStr">
         <is>
           <t>www.love4caffeine.com</t>
         </is>
       </c>
-      <c r="E289" s="1" t="inlineStr">
+      <c r="E289" t="inlineStr">
         <is>
           <t>Love-Specialty-Croissants</t>
         </is>
       </c>
-      <c r="F289" s="1" t="inlineStr">
+      <c r="F289" t="inlineStr">
         <is>
           <t>love.roma_</t>
         </is>
       </c>
-      <c r="G289" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H289" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I289" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J289" s="1" t="inlineStr"/>
-      <c r="K289" s="1" t="inlineStr"/>
-      <c r="L289" s="1" t="inlineStr"/>
-      <c r="M289" s="1" t="inlineStr"/>
-      <c r="N289" s="1" t="inlineStr"/>
-      <c r="O289" s="1" t="inlineStr"/>
-      <c r="P289" s="1" t="inlineStr"/>
-      <c r="Q289" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R289" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Love-Specialty-Croissants) | IG: trovato (love.roma_)</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="inlineStr">
+      <c r="A290" t="inlineStr">
         <is>
           <t>Marzapane Café &amp; Bakery</t>
         </is>
       </c>
-      <c r="B290" s="1" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>Via Flaminia, 64</t>
         </is>
       </c>
-      <c r="C290" s="1" t="inlineStr">
+      <c r="C290" t="inlineStr">
         <is>
           <t>06/64781692</t>
         </is>
       </c>
-      <c r="D290" s="1" t="inlineStr">
+      <c r="D290" t="inlineStr">
         <is>
           <t>www.marzapaneroma.com</t>
         </is>
       </c>
-      <c r="E290" s="1" t="inlineStr">
+      <c r="E290" t="inlineStr">
         <is>
           <t>marzapaneroma</t>
         </is>
       </c>
-      <c r="F290" s="1" t="inlineStr">
+      <c r="F290" t="inlineStr">
         <is>
           <t>marzapaneroma</t>
         </is>
       </c>
-      <c r="G290" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H290" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I290" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J290" s="1" t="inlineStr"/>
-      <c r="K290" s="1" t="inlineStr"/>
-      <c r="L290" s="1" t="inlineStr"/>
-      <c r="M290" s="1" t="inlineStr"/>
-      <c r="N290" s="1" t="inlineStr"/>
-      <c r="O290" s="1" t="inlineStr"/>
-      <c r="P290" s="1" t="inlineStr"/>
-      <c r="Q290" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R290" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (marzapaneroma) | IG: trovato (marzapaneroma)</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="inlineStr">
+      <c r="A291" t="inlineStr">
         <is>
           <t>Otaleg!</t>
         </is>
       </c>
-      <c r="B291" s="1" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>Viale dei Quattro Venti, 70</t>
         </is>
       </c>
-      <c r="C291" s="1" t="inlineStr">
+      <c r="C291" t="inlineStr">
         <is>
           <t>338/6515450</t>
         </is>
       </c>
-      <c r="D291" s="1" t="inlineStr">
+      <c r="D291" t="inlineStr">
         <is>
           <t>www.otaleg.com</t>
         </is>
       </c>
-      <c r="E291" s="1" t="inlineStr"/>
-      <c r="F291" s="1" t="inlineStr">
+      <c r="F291" t="inlineStr">
         <is>
           <t>otaleg.radicioni</t>
         </is>
       </c>
-      <c r="G291" s="1" t="inlineStr"/>
-      <c r="H291" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I291" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J291" s="1" t="inlineStr"/>
-      <c r="K291" s="1" t="inlineStr"/>
-      <c r="L291" s="1" t="inlineStr"/>
-      <c r="M291" s="1" t="inlineStr"/>
-      <c r="N291" s="1" t="inlineStr"/>
-      <c r="O291" s="1" t="inlineStr"/>
-      <c r="P291" s="1" t="inlineStr"/>
-      <c r="Q291" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R291" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (otaleg.radicioni)</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="inlineStr">
+      <c r="A292" t="inlineStr">
         <is>
           <t>Pasticceria Barberini</t>
         </is>
       </c>
-      <c r="B292" s="1" t="inlineStr">
+      <c r="B292" t="inlineStr">
         <is>
           <t>Via Marmorata, 41</t>
         </is>
       </c>
-      <c r="C292" s="1" t="inlineStr">
+      <c r="C292" t="inlineStr">
         <is>
           <t>06/57250431</t>
         </is>
       </c>
-      <c r="D292" s="1" t="inlineStr">
+      <c r="D292" t="inlineStr">
         <is>
           <t>www.pasticceriabarberini.it</t>
         </is>
       </c>
-      <c r="E292" s="1" t="inlineStr">
+      <c r="E292" t="inlineStr">
         <is>
           <t>pasticceriabarberini</t>
         </is>
       </c>
-      <c r="F292" s="1" t="inlineStr">
+      <c r="F292" t="inlineStr">
         <is>
           <t>pasticceria_barberini</t>
         </is>
       </c>
-      <c r="G292" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H292" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I292" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J292" s="1" t="inlineStr"/>
-      <c r="K292" s="1" t="inlineStr"/>
-      <c r="L292" s="1" t="inlineStr"/>
-      <c r="M292" s="1" t="inlineStr"/>
-      <c r="N292" s="1" t="inlineStr"/>
-      <c r="O292" s="1" t="inlineStr"/>
-      <c r="P292" s="1" t="inlineStr"/>
-      <c r="Q292" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R292" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (pasticceriabarberini) | IG: trovato (pasticceria_barberini)</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="inlineStr">
+      <c r="A293" t="inlineStr">
         <is>
           <t>Pasticceria Walter Musco</t>
         </is>
       </c>
-      <c r="B293" s="1" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>Largo Benedetto Bompiani, 8/10</t>
         </is>
       </c>
-      <c r="C293" s="1" t="inlineStr">
+      <c r="C293" t="inlineStr">
         <is>
           <t>06/5124103</t>
         </is>
       </c>
-      <c r="D293" s="1" t="inlineStr">
+      <c r="D293" t="inlineStr">
         <is>
           <t>www.pasticceriawaltermusco.it</t>
         </is>
       </c>
-      <c r="E293" s="1" t="inlineStr">
+      <c r="E293" t="inlineStr">
         <is>
           <t>pasticceriawaltermuscobompiani</t>
         </is>
       </c>
-      <c r="F293" s="1" t="inlineStr">
+      <c r="F293" t="inlineStr">
         <is>
           <t>pasticceriawaltermuscobompiani</t>
         </is>
       </c>
-      <c r="G293" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H293" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I293" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J293" s="1" t="inlineStr"/>
-      <c r="K293" s="1" t="inlineStr"/>
-      <c r="L293" s="1" t="inlineStr"/>
-      <c r="M293" s="1" t="inlineStr"/>
-      <c r="N293" s="1" t="inlineStr"/>
-      <c r="O293" s="1" t="inlineStr"/>
-      <c r="P293" s="1" t="inlineStr"/>
-      <c r="Q293" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R293" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (pasticceriawaltermuscobompiani) | IG: trovato (pasticceriawaltermuscobompiani)</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="inlineStr">
+      <c r="A294" t="inlineStr">
         <is>
           <t>Pontisso</t>
         </is>
       </c>
-      <c r="B294" s="1" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>Via Antonio Cantore, 3</t>
         </is>
       </c>
-      <c r="C294" s="1" t="inlineStr">
+      <c r="C294" t="inlineStr">
         <is>
           <t>06/86214524</t>
         </is>
       </c>
-      <c r="D294" s="1" t="inlineStr"/>
-      <c r="E294" s="1" t="inlineStr"/>
-      <c r="F294" s="1" t="inlineStr">
+      <c r="F294" t="inlineStr">
         <is>
           <t>pontissobar</t>
         </is>
       </c>
-      <c r="G294" s="1" t="inlineStr"/>
-      <c r="H294" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I294" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J294" s="1" t="inlineStr"/>
-      <c r="K294" s="1" t="inlineStr"/>
-      <c r="L294" s="1" t="inlineStr"/>
-      <c r="M294" s="1" t="inlineStr"/>
-      <c r="N294" s="1" t="inlineStr"/>
-      <c r="O294" s="1" t="inlineStr"/>
-      <c r="P294" s="1" t="inlineStr"/>
-      <c r="Q294" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R294" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (pontissobar)</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="inlineStr">
+      <c r="A295" t="inlineStr">
         <is>
           <t>Roscioli Caffè</t>
         </is>
       </c>
-      <c r="B295" s="1" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>Piazza Benedetto Cairoli, 16</t>
         </is>
       </c>
-      <c r="C295" s="1" t="inlineStr">
+      <c r="C295" t="inlineStr">
         <is>
           <t>06/89165330</t>
         </is>
       </c>
-      <c r="D295" s="1" t="inlineStr">
+      <c r="D295" t="inlineStr">
         <is>
           <t>www.rosciolicaffe.com</t>
         </is>
       </c>
-      <c r="E295" s="1" t="inlineStr">
+      <c r="E295" t="inlineStr">
         <is>
           <t>Rosciolicaffe</t>
         </is>
       </c>
-      <c r="F295" s="1" t="inlineStr">
+      <c r="F295" t="inlineStr">
         <is>
           <t>Rosciolicaffe</t>
         </is>
       </c>
-      <c r="G295" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H295" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I295" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J295" s="1" t="inlineStr"/>
-      <c r="K295" s="1" t="inlineStr"/>
-      <c r="L295" s="1" t="inlineStr"/>
-      <c r="M295" s="1" t="inlineStr"/>
-      <c r="N295" s="1" t="inlineStr"/>
-      <c r="O295" s="1" t="inlineStr"/>
-      <c r="P295" s="1" t="inlineStr"/>
-      <c r="Q295" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R295" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Rosciolicaffe) | IG: trovato (Rosciolicaffe)</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="inlineStr">
+      <c r="A296" t="inlineStr">
         <is>
           <t>Santi Sebastiano e Valentino</t>
         </is>
       </c>
-      <c r="B296" s="1" t="inlineStr">
+      <c r="B296" t="inlineStr">
         <is>
           <t>Via Tirso, 107</t>
         </is>
       </c>
-      <c r="C296" s="1" t="inlineStr">
+      <c r="C296" t="inlineStr">
         <is>
           <t>06/87568048</t>
         </is>
       </c>
-      <c r="D296" s="1" t="inlineStr">
+      <c r="D296" t="inlineStr">
         <is>
           <t>www.santisebastianoevalentino.it</t>
         </is>
       </c>
-      <c r="E296" s="1" t="inlineStr">
+      <c r="E296" t="inlineStr">
         <is>
           <t>santisebastianoevalentino</t>
         </is>
       </c>
-      <c r="F296" s="1" t="inlineStr">
+      <c r="F296" t="inlineStr">
         <is>
           <t>santisebastianoevalentino</t>
         </is>
       </c>
-      <c r="G296" s="1" t="inlineStr">
+      <c r="G296" t="inlineStr">
         <is>
           <t>23/02/2026</t>
         </is>
       </c>
-      <c r="H296" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I296" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J296" s="1" t="inlineStr"/>
-      <c r="K296" s="1" t="inlineStr"/>
-      <c r="L296" s="1" t="inlineStr"/>
-      <c r="M296" s="1" t="inlineStr"/>
-      <c r="N296" s="1" t="inlineStr"/>
-      <c r="O296" s="1" t="inlineStr"/>
-      <c r="P296" s="1" t="inlineStr"/>
-      <c r="Q296" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R296" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (santisebastianoevalentino) | IG: trovato (santisebastianoevalentino)</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18674,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J297" s="1" t="inlineStr"/>
+      <c r="J297" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K297" s="1" t="inlineStr"/>
       <c r="L297" s="1" t="inlineStr"/>
       <c r="M297" s="1" t="inlineStr"/>
@@ -18643,12 +18687,12 @@
       <c r="P297" s="1" t="inlineStr"/>
       <c r="Q297" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -16877,624 +16877,816 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B264" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C264" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D264" s="1" t="inlineStr"/>
-      <c r="E264" s="1" t="inlineStr"/>
-      <c r="F264" s="1" t="inlineStr"/>
-      <c r="G264" s="1" t="inlineStr"/>
-      <c r="H264" s="1" t="inlineStr"/>
-      <c r="I264" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J264" s="1" t="inlineStr">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Forno Conti &amp; Co.</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Via Giusti, 18</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>06/2757595</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>www.fornoconti.co</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>fornoconti.roma</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K264" s="1" t="inlineStr"/>
-      <c r="L264" s="1" t="inlineStr"/>
-      <c r="M264" s="1" t="inlineStr"/>
-      <c r="N264" s="1" t="inlineStr"/>
-      <c r="O264" s="1" t="inlineStr"/>
-      <c r="P264" s="1" t="inlineStr"/>
-      <c r="Q264" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R264" s="1" t="inlineStr">
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (fornoconti.roma)</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="inlineStr">
-        <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
-        </is>
-      </c>
-      <c r="B265" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Erbe, 16</t>
-        </is>
-      </c>
-      <c r="C265" s="1" t="inlineStr">
-        <is>
-          <t>348/7277746</t>
-        </is>
-      </c>
-      <c r="D265" s="1" t="inlineStr"/>
-      <c r="E265" s="1" t="inlineStr"/>
-      <c r="F265" s="1" t="inlineStr"/>
-      <c r="G265" s="1" t="inlineStr"/>
-      <c r="H265" s="1" t="inlineStr"/>
-      <c r="I265" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J265" s="1" t="inlineStr">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Gastromario</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Via Voghera, 10</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>06/79782584</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Gastromario</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>gastromario.it</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K265" s="1" t="inlineStr"/>
-      <c r="L265" s="1" t="inlineStr"/>
-      <c r="M265" s="1" t="inlineStr"/>
-      <c r="N265" s="1" t="inlineStr"/>
-      <c r="O265" s="1" t="inlineStr"/>
-      <c r="P265" s="1" t="inlineStr"/>
-      <c r="Q265" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R265" s="1" t="inlineStr">
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Gastromario) | IG: trovato (gastromario.it)</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="inlineStr">
-        <is>
-          <t>Osteria del Vicolo Fatato</t>
-        </is>
-      </c>
-      <c r="B266" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Forno Fatato, 11</t>
-        </is>
-      </c>
-      <c r="C266" s="1" t="inlineStr">
-        <is>
-          <t>0775/503035</t>
-        </is>
-      </c>
-      <c r="D266" s="1" t="inlineStr"/>
-      <c r="E266" s="1" t="inlineStr"/>
-      <c r="F266" s="1" t="inlineStr"/>
-      <c r="G266" s="1" t="inlineStr"/>
-      <c r="H266" s="1" t="inlineStr"/>
-      <c r="I266" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J266" s="1" t="inlineStr">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Grani, farine e caffè</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Viale dei Quattro Venti, 152/C</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>3476145569</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>www.granifarinecaffe.it</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>grani_farine_e_caffe</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K266" s="1" t="inlineStr"/>
-      <c r="L266" s="1" t="inlineStr"/>
-      <c r="M266" s="1" t="inlineStr"/>
-      <c r="N266" s="1" t="inlineStr"/>
-      <c r="O266" s="1" t="inlineStr"/>
-      <c r="P266" s="1" t="inlineStr"/>
-      <c r="Q266" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R266" s="1" t="inlineStr">
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (grani_farine_e_caffe)</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="inlineStr">
-        <is>
-          <t>Poldo e Gianna</t>
-        </is>
-      </c>
-      <c r="B267" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Rosini, 6</t>
-        </is>
-      </c>
-      <c r="C267" s="1" t="inlineStr">
-        <is>
-          <t>06/6893499</t>
-        </is>
-      </c>
-      <c r="D267" s="1" t="inlineStr"/>
-      <c r="E267" s="1" t="inlineStr"/>
-      <c r="F267" s="1" t="inlineStr"/>
-      <c r="G267" s="1" t="inlineStr"/>
-      <c r="H267" s="1" t="inlineStr"/>
-      <c r="I267" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J267" s="1" t="inlineStr">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Le Levain Café</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Via Piave, 8</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>376/2067672</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>www.lelevainroma.it</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>LeLevainRoma</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>lelevainroma</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K267" s="1" t="inlineStr"/>
-      <c r="L267" s="1" t="inlineStr"/>
-      <c r="M267" s="1" t="inlineStr"/>
-      <c r="N267" s="1" t="inlineStr"/>
-      <c r="O267" s="1" t="inlineStr"/>
-      <c r="P267" s="1" t="inlineStr"/>
-      <c r="Q267" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R267" s="1" t="inlineStr">
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (LeLevainRoma) | IG: trovato (lelevainroma)</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria A Casa Di Rita</t>
-        </is>
-      </c>
-      <c r="B268" s="1" t="inlineStr">
-        <is>
-          <t>Via delle Ciliegie, 145</t>
-        </is>
-      </c>
-      <c r="C268" s="1" t="inlineStr">
-        <is>
-          <t>338/9860960</t>
-        </is>
-      </c>
-      <c r="D268" s="1" t="inlineStr"/>
-      <c r="E268" s="1" t="inlineStr"/>
-      <c r="F268" s="1" t="inlineStr"/>
-      <c r="G268" s="1" t="inlineStr"/>
-      <c r="H268" s="1" t="inlineStr"/>
-      <c r="I268" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J268" s="1" t="inlineStr">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Lievito Francesco Arnesano</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Via Simone Martini, 6/8</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>06/69363592</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>lievitofrancescoarnesano</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>lievitopizzapane</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K268" s="1" t="inlineStr"/>
-      <c r="L268" s="1" t="inlineStr"/>
-      <c r="M268" s="1" t="inlineStr"/>
-      <c r="N268" s="1" t="inlineStr"/>
-      <c r="O268" s="1" t="inlineStr"/>
-      <c r="P268" s="1" t="inlineStr"/>
-      <c r="Q268" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R268" s="1" t="inlineStr">
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (lievitofrancescoarnesano) | IG: trovato (lievitopizzapane)</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="inlineStr">
-        <is>
-          <t>Ie Koji Japanese Izakaya</t>
-        </is>
-      </c>
-      <c r="B269" s="1" t="inlineStr">
-        <is>
-          <t>Via Marcantonio Bragadin, 13</t>
-        </is>
-      </c>
-      <c r="C269" s="1" t="inlineStr">
-        <is>
-          <t>348/4302368 - 06/69459860</t>
-        </is>
-      </c>
-      <c r="D269" s="1" t="inlineStr"/>
-      <c r="E269" s="1" t="inlineStr"/>
-      <c r="F269" s="1" t="inlineStr"/>
-      <c r="G269" s="1" t="inlineStr"/>
-      <c r="H269" s="1" t="inlineStr"/>
-      <c r="I269" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J269" s="1" t="inlineStr">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Via Tunisi, 51</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>06/96525119</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>www.love4caffeine.com</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Love-Specialty-Croissants</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>love.roma_</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K269" s="1" t="inlineStr"/>
-      <c r="L269" s="1" t="inlineStr"/>
-      <c r="M269" s="1" t="inlineStr"/>
-      <c r="N269" s="1" t="inlineStr"/>
-      <c r="O269" s="1" t="inlineStr"/>
-      <c r="P269" s="1" t="inlineStr"/>
-      <c r="Q269" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R269" s="1" t="inlineStr">
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Love-Specialty-Croissants) | IG: trovato (love.roma_)</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B270" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C270" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D270" s="1" t="inlineStr"/>
-      <c r="E270" s="1" t="inlineStr"/>
-      <c r="F270" s="1" t="inlineStr"/>
-      <c r="G270" s="1" t="inlineStr"/>
-      <c r="H270" s="1" t="inlineStr"/>
-      <c r="I270" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J270" s="1" t="inlineStr">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Marzapane Café &amp; Bakery</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Via Flaminia, 64</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>06/64781692</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>www.marzapaneroma.com</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>marzapaneroma</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>marzapaneroma</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K270" s="1" t="inlineStr"/>
-      <c r="L270" s="1" t="inlineStr"/>
-      <c r="M270" s="1" t="inlineStr"/>
-      <c r="N270" s="1" t="inlineStr"/>
-      <c r="O270" s="1" t="inlineStr"/>
-      <c r="P270" s="1" t="inlineStr"/>
-      <c r="Q270" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R270" s="1" t="inlineStr">
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (marzapaneroma) | IG: trovato (marzapaneroma)</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="inlineStr">
-        <is>
-          <t>Nomisan</t>
-        </is>
-      </c>
-      <c r="B271" s="1" t="inlineStr">
-        <is>
-          <t>Viale Gianluigi Bonelli, 237</t>
-        </is>
-      </c>
-      <c r="C271" s="1" t="inlineStr">
-        <is>
-          <t>342/8036080</t>
-        </is>
-      </c>
-      <c r="D271" s="1" t="inlineStr"/>
-      <c r="E271" s="1" t="inlineStr"/>
-      <c r="F271" s="1" t="inlineStr"/>
-      <c r="G271" s="1" t="inlineStr"/>
-      <c r="H271" s="1" t="inlineStr"/>
-      <c r="I271" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J271" s="1" t="inlineStr">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Otaleg!</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Viale dei Quattro Venti, 70</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>338/6515450</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>www.otaleg.com</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>otaleg.radicioni</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K271" s="1" t="inlineStr"/>
-      <c r="L271" s="1" t="inlineStr"/>
-      <c r="M271" s="1" t="inlineStr"/>
-      <c r="N271" s="1" t="inlineStr"/>
-      <c r="O271" s="1" t="inlineStr"/>
-      <c r="P271" s="1" t="inlineStr"/>
-      <c r="Q271" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R271" s="1" t="inlineStr">
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (otaleg.radicioni)</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="inlineStr">
-        <is>
-          <t>Al Setaccio</t>
-        </is>
-      </c>
-      <c r="B272" s="1" t="inlineStr">
-        <is>
-          <t>Via di Mezzocammino, 193</t>
-        </is>
-      </c>
-      <c r="C272" s="1" t="inlineStr">
-        <is>
-          <t>06/52372056</t>
-        </is>
-      </c>
-      <c r="D272" s="1" t="inlineStr"/>
-      <c r="E272" s="1" t="inlineStr"/>
-      <c r="F272" s="1" t="inlineStr"/>
-      <c r="G272" s="1" t="inlineStr"/>
-      <c r="H272" s="1" t="inlineStr"/>
-      <c r="I272" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J272" s="1" t="inlineStr">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Pasticceria Barberini</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Via Marmorata, 41</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>06/57250431</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>www.pasticceriabarberini.it</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>pasticceriabarberini</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>pasticceria_barberini</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K272" s="1" t="inlineStr"/>
-      <c r="L272" s="1" t="inlineStr"/>
-      <c r="M272" s="1" t="inlineStr"/>
-      <c r="N272" s="1" t="inlineStr"/>
-      <c r="O272" s="1" t="inlineStr"/>
-      <c r="P272" s="1" t="inlineStr"/>
-      <c r="Q272" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R272" s="1" t="inlineStr">
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (pasticceriabarberini) | IG: trovato (pasticceria_barberini)</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="inlineStr">
-        <is>
-          <t>Angelo Pezzella</t>
-        </is>
-      </c>
-      <c r="B273" s="1" t="inlineStr">
-        <is>
-          <t>Via Appia Nuova, 1095</t>
-        </is>
-      </c>
-      <c r="C273" s="1" t="inlineStr">
-        <is>
-          <t>06/7188560</t>
-        </is>
-      </c>
-      <c r="D273" s="1" t="inlineStr"/>
-      <c r="E273" s="1" t="inlineStr"/>
-      <c r="F273" s="1" t="inlineStr"/>
-      <c r="G273" s="1" t="inlineStr"/>
-      <c r="H273" s="1" t="inlineStr"/>
-      <c r="I273" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J273" s="1" t="inlineStr">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Pasticceria Walter Musco</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Largo Benedetto Bompiani, 8/10</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>06/5124103</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>www.pasticceriawaltermusco.it</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>pasticceriawaltermuscobompiani</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>pasticceriawaltermuscobompiani</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K273" s="1" t="inlineStr"/>
-      <c r="L273" s="1" t="inlineStr"/>
-      <c r="M273" s="1" t="inlineStr"/>
-      <c r="N273" s="1" t="inlineStr"/>
-      <c r="O273" s="1" t="inlineStr"/>
-      <c r="P273" s="1" t="inlineStr"/>
-      <c r="Q273" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R273" s="1" t="inlineStr">
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (pasticceriawaltermuscobompiani) | IG: trovato (pasticceriawaltermuscobompiani)</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="inlineStr">
-        <is>
-          <t>Clementina</t>
-        </is>
-      </c>
-      <c r="B274" s="1" t="inlineStr">
-        <is>
-          <t>Via della Torre Clementina, 158</t>
-        </is>
-      </c>
-      <c r="C274" s="1" t="inlineStr">
-        <is>
-          <t>328/8181651</t>
-        </is>
-      </c>
-      <c r="D274" s="1" t="inlineStr"/>
-      <c r="E274" s="1" t="inlineStr"/>
-      <c r="F274" s="1" t="inlineStr"/>
-      <c r="G274" s="1" t="inlineStr"/>
-      <c r="H274" s="1" t="inlineStr"/>
-      <c r="I274" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J274" s="1" t="inlineStr">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Pontisso</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Via Antonio Cantore, 3</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>06/86214524</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>pontissobar</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K274" s="1" t="inlineStr"/>
-      <c r="L274" s="1" t="inlineStr"/>
-      <c r="M274" s="1" t="inlineStr"/>
-      <c r="N274" s="1" t="inlineStr"/>
-      <c r="O274" s="1" t="inlineStr"/>
-      <c r="P274" s="1" t="inlineStr"/>
-      <c r="Q274" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R274" s="1" t="inlineStr">
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (pontissobar)</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="inlineStr">
-        <is>
-          <t>Da Antonio</t>
-        </is>
-      </c>
-      <c r="B275" s="1" t="inlineStr">
-        <is>
-          <t>Via Mario Lizzani, 21</t>
-        </is>
-      </c>
-      <c r="C275" s="1" t="inlineStr">
-        <is>
-          <t>391/7475549</t>
-        </is>
-      </c>
-      <c r="D275" s="1" t="inlineStr"/>
-      <c r="E275" s="1" t="inlineStr"/>
-      <c r="F275" s="1" t="inlineStr"/>
-      <c r="G275" s="1" t="inlineStr"/>
-      <c r="H275" s="1" t="inlineStr"/>
-      <c r="I275" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J275" s="1" t="inlineStr">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Roscioli Caffè</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Piazza Benedetto Cairoli, 16</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>06/89165330</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>www.rosciolicaffe.com</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Rosciolicaffe</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Rosciolicaffe</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K275" s="1" t="inlineStr"/>
-      <c r="L275" s="1" t="inlineStr"/>
-      <c r="M275" s="1" t="inlineStr"/>
-      <c r="N275" s="1" t="inlineStr"/>
-      <c r="O275" s="1" t="inlineStr"/>
-      <c r="P275" s="1" t="inlineStr"/>
-      <c r="Q275" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R275" s="1" t="inlineStr">
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Rosciolicaffe) | IG: trovato (Rosciolicaffe)</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="inlineStr">
-        <is>
-          <t>Diego Vitagliano</t>
-        </is>
-      </c>
-      <c r="B276" s="1" t="inlineStr">
-        <is>
-          <t>Via Chiana, 80</t>
-        </is>
-      </c>
-      <c r="C276" s="1" t="inlineStr">
-        <is>
-          <t>06/72276443</t>
-        </is>
-      </c>
-      <c r="D276" s="1" t="inlineStr"/>
-      <c r="E276" s="1" t="inlineStr"/>
-      <c r="F276" s="1" t="inlineStr"/>
-      <c r="G276" s="1" t="inlineStr"/>
-      <c r="H276" s="1" t="inlineStr"/>
-      <c r="I276" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J276" s="1" t="inlineStr">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Santi Sebastiano e Valentino</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Via Tirso, 107</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>06/87568048</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>www.santisebastianoevalentino.it</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>santisebastianoevalentino</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>santisebastianoevalentino</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>23/02/2026</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K276" s="1" t="inlineStr"/>
-      <c r="L276" s="1" t="inlineStr"/>
-      <c r="M276" s="1" t="inlineStr"/>
-      <c r="N276" s="1" t="inlineStr"/>
-      <c r="O276" s="1" t="inlineStr"/>
-      <c r="P276" s="1" t="inlineStr"/>
-      <c r="Q276" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R276" s="1" t="inlineStr">
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (santisebastianoevalentino) | IG: trovato (santisebastianoevalentino)</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
@@ -17503,17 +17695,17 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>GioMà</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>Via Calpurnio Fiamma, 40/44</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t>06/7674717</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr"/>
@@ -17544,24 +17736,24 @@
       </c>
       <c r="R277" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>Pupillo Pura Pizza</t>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
         </is>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>Via Giacomo Matteotti, 29</t>
+          <t>Piazza delle Erbe, 16</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>339/4143148</t>
+          <t>348/7277746</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr"/>
@@ -17592,24 +17784,24 @@
       </c>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>Santa Romana</t>
+          <t>Osteria del Vicolo Fatato</t>
         </is>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Piazza Certaldo, 12</t>
+          <t>Vicolo Forno Fatato, 11</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>06/69317674</t>
+          <t>0775/503035</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr"/>
@@ -17640,24 +17832,24 @@
       </c>
       <c r="R279" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>Seu Pizza Illuminati</t>
+          <t>Poldo e Gianna</t>
         </is>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>Via Angelo Bargoni, 10/18</t>
+          <t>Vicolo Rosini, 6</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>06/5883384</t>
+          <t>06/6893499</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr"/>
@@ -17688,81 +17880,72 @@
       </c>
       <c r="R280" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>Forno Conti &amp; Co.</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Via Giusti, 18</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>06/2757595</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>www.fornoconti.co</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>fornoconti.roma</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>Trattoria A Casa Di Rita</t>
+        </is>
+      </c>
+      <c r="B281" s="1" t="inlineStr">
+        <is>
+          <t>Via delle Ciliegie, 145</t>
+        </is>
+      </c>
+      <c r="C281" s="1" t="inlineStr">
+        <is>
+          <t>338/9860960</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="inlineStr"/>
+      <c r="E281" s="1" t="inlineStr"/>
+      <c r="F281" s="1" t="inlineStr"/>
+      <c r="G281" s="1" t="inlineStr"/>
+      <c r="H281" s="1" t="inlineStr"/>
+      <c r="I281" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J281" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O281" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q281" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (fornoconti.roma)</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K281" s="1" t="inlineStr"/>
+      <c r="L281" s="1" t="inlineStr"/>
+      <c r="M281" s="1" t="inlineStr"/>
+      <c r="N281" s="1" t="inlineStr"/>
+      <c r="O281" s="1" t="inlineStr"/>
+      <c r="P281" s="1" t="inlineStr"/>
+      <c r="Q281" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R281" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>Forno Ritorno</t>
+          <t>Ie Koji Japanese Izakaya</t>
         </is>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>Via Amerigo Vespucci, 20</t>
+          <t>Via Marcantonio Bragadin, 13</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t>392/7768427</t>
+          <t>348/4302368 - 06/69459860</t>
         </is>
       </c>
       <c r="D282" s="1" t="inlineStr"/>
@@ -17793,143 +17976,120 @@
       </c>
       <c r="R282" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>Gastromario</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Via Voghera, 10</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>06/79782584</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>Gastromario</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>gastromario.it</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>Mrgda Ristorante</t>
+        </is>
+      </c>
+      <c r="B283" s="1" t="inlineStr">
+        <is>
+          <t>Via Prenestina, 182</t>
+        </is>
+      </c>
+      <c r="C283" s="1" t="inlineStr">
+        <is>
+          <t>329/933355</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="inlineStr"/>
+      <c r="E283" s="1" t="inlineStr"/>
+      <c r="F283" s="1" t="inlineStr"/>
+      <c r="G283" s="1" t="inlineStr"/>
+      <c r="H283" s="1" t="inlineStr"/>
+      <c r="I283" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J283" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Gastromario) | IG: trovato (gastromario.it)</t>
-        </is>
-      </c>
-      <c r="R283" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K283" s="1" t="inlineStr"/>
+      <c r="L283" s="1" t="inlineStr"/>
+      <c r="M283" s="1" t="inlineStr"/>
+      <c r="N283" s="1" t="inlineStr"/>
+      <c r="O283" s="1" t="inlineStr"/>
+      <c r="P283" s="1" t="inlineStr"/>
+      <c r="Q283" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R283" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Grani, farine e caffè</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Viale dei Quattro Venti, 152/C</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>3476145569</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>www.granifarinecaffe.it</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>grani_farine_e_caffe</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>Nomisan</t>
+        </is>
+      </c>
+      <c r="B284" s="1" t="inlineStr">
+        <is>
+          <t>Viale Gianluigi Bonelli, 237</t>
+        </is>
+      </c>
+      <c r="C284" s="1" t="inlineStr">
+        <is>
+          <t>342/8036080</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="inlineStr"/>
+      <c r="E284" s="1" t="inlineStr"/>
+      <c r="F284" s="1" t="inlineStr"/>
+      <c r="G284" s="1" t="inlineStr"/>
+      <c r="H284" s="1" t="inlineStr"/>
+      <c r="I284" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J284" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O284" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (grani_farine_e_caffe)</t>
-        </is>
-      </c>
-      <c r="R284" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K284" s="1" t="inlineStr"/>
+      <c r="L284" s="1" t="inlineStr"/>
+      <c r="M284" s="1" t="inlineStr"/>
+      <c r="N284" s="1" t="inlineStr"/>
+      <c r="O284" s="1" t="inlineStr"/>
+      <c r="P284" s="1" t="inlineStr"/>
+      <c r="Q284" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R284" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>Il tuo fornaio</t>
+          <t>Al Setaccio</t>
         </is>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>Via Francesco Sapori, 35</t>
+          <t>Via di Mezzocammino, 193</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>06/5017873</t>
+          <t>06/52372056</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr"/>
@@ -17960,24 +18120,24 @@
       </c>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>Krapfen Paglia</t>
+          <t>Angelo Pezzella</t>
         </is>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>Piazza Anco Marzio, 18/19</t>
+          <t>Via Appia Nuova, 1095</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t>06/5623344</t>
+          <t>06/7188560</t>
         </is>
       </c>
       <c r="D286" s="1" t="inlineStr"/>
@@ -18008,647 +18168,487 @@
       </c>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Le Levain Café</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Via Piave, 8</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>376/2067672</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>www.lelevainroma.it</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>LeLevainRoma</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>lelevainroma</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>Clementina</t>
+        </is>
+      </c>
+      <c r="B287" s="1" t="inlineStr">
+        <is>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C287" s="1" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="inlineStr"/>
+      <c r="E287" s="1" t="inlineStr"/>
+      <c r="F287" s="1" t="inlineStr"/>
+      <c r="G287" s="1" t="inlineStr"/>
+      <c r="H287" s="1" t="inlineStr"/>
+      <c r="I287" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J287" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O287" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q287" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (LeLevainRoma) | IG: trovato (lelevainroma)</t>
-        </is>
-      </c>
-      <c r="R287" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K287" s="1" t="inlineStr"/>
+      <c r="L287" s="1" t="inlineStr"/>
+      <c r="M287" s="1" t="inlineStr"/>
+      <c r="N287" s="1" t="inlineStr"/>
+      <c r="O287" s="1" t="inlineStr"/>
+      <c r="P287" s="1" t="inlineStr"/>
+      <c r="Q287" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R287" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Lievito Francesco Arnesano</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Via Simone Martini, 6/8</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>06/69363592</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>lievitofrancescoarnesano</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>lievitopizzapane</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>Da Antonio</t>
+        </is>
+      </c>
+      <c r="B288" s="1" t="inlineStr">
+        <is>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C288" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
+      <c r="D288" s="1" t="inlineStr"/>
+      <c r="E288" s="1" t="inlineStr"/>
+      <c r="F288" s="1" t="inlineStr"/>
+      <c r="G288" s="1" t="inlineStr"/>
+      <c r="H288" s="1" t="inlineStr"/>
+      <c r="I288" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J288" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O288" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (lievitofrancescoarnesano) | IG: trovato (lievitopizzapane)</t>
-        </is>
-      </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K288" s="1" t="inlineStr"/>
+      <c r="L288" s="1" t="inlineStr"/>
+      <c r="M288" s="1" t="inlineStr"/>
+      <c r="N288" s="1" t="inlineStr"/>
+      <c r="O288" s="1" t="inlineStr"/>
+      <c r="P288" s="1" t="inlineStr"/>
+      <c r="Q288" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R288" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>Love</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Via Tunisi, 51</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>06/96525119</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>www.love4caffeine.com</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>Love-Specialty-Croissants</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>love.roma_</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>Diego Vitagliano</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="inlineStr">
+        <is>
+          <t>Via Chiana, 80</t>
+        </is>
+      </c>
+      <c r="C289" s="1" t="inlineStr">
+        <is>
+          <t>06/72276443</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="inlineStr"/>
+      <c r="E289" s="1" t="inlineStr"/>
+      <c r="F289" s="1" t="inlineStr"/>
+      <c r="G289" s="1" t="inlineStr"/>
+      <c r="H289" s="1" t="inlineStr"/>
+      <c r="I289" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J289" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O289" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q289" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Love-Specialty-Croissants) | IG: trovato (love.roma_)</t>
-        </is>
-      </c>
-      <c r="R289" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K289" s="1" t="inlineStr"/>
+      <c r="L289" s="1" t="inlineStr"/>
+      <c r="M289" s="1" t="inlineStr"/>
+      <c r="N289" s="1" t="inlineStr"/>
+      <c r="O289" s="1" t="inlineStr"/>
+      <c r="P289" s="1" t="inlineStr"/>
+      <c r="Q289" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R289" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>Marzapane Café &amp; Bakery</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Via Flaminia, 64</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>06/64781692</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>www.marzapaneroma.com</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>marzapaneroma</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>marzapaneroma</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>GioMà</t>
+        </is>
+      </c>
+      <c r="B290" s="1" t="inlineStr">
+        <is>
+          <t>Via Calpurnio Fiamma, 40/44</t>
+        </is>
+      </c>
+      <c r="C290" s="1" t="inlineStr">
+        <is>
+          <t>06/7674717</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="inlineStr"/>
+      <c r="E290" s="1" t="inlineStr"/>
+      <c r="F290" s="1" t="inlineStr"/>
+      <c r="G290" s="1" t="inlineStr"/>
+      <c r="H290" s="1" t="inlineStr"/>
+      <c r="I290" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J290" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O290" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q290" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (marzapaneroma) | IG: trovato (marzapaneroma)</t>
-        </is>
-      </c>
-      <c r="R290" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K290" s="1" t="inlineStr"/>
+      <c r="L290" s="1" t="inlineStr"/>
+      <c r="M290" s="1" t="inlineStr"/>
+      <c r="N290" s="1" t="inlineStr"/>
+      <c r="O290" s="1" t="inlineStr"/>
+      <c r="P290" s="1" t="inlineStr"/>
+      <c r="Q290" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R290" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>Otaleg!</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Viale dei Quattro Venti, 70</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>338/6515450</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>www.otaleg.com</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>otaleg.radicioni</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>Pupillo Pura Pizza</t>
+        </is>
+      </c>
+      <c r="B291" s="1" t="inlineStr">
+        <is>
+          <t>Via Giacomo Matteotti, 29</t>
+        </is>
+      </c>
+      <c r="C291" s="1" t="inlineStr">
+        <is>
+          <t>339/4143148</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="inlineStr"/>
+      <c r="E291" s="1" t="inlineStr"/>
+      <c r="F291" s="1" t="inlineStr"/>
+      <c r="G291" s="1" t="inlineStr"/>
+      <c r="H291" s="1" t="inlineStr"/>
+      <c r="I291" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J291" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O291" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q291" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (otaleg.radicioni)</t>
-        </is>
-      </c>
-      <c r="R291" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K291" s="1" t="inlineStr"/>
+      <c r="L291" s="1" t="inlineStr"/>
+      <c r="M291" s="1" t="inlineStr"/>
+      <c r="N291" s="1" t="inlineStr"/>
+      <c r="O291" s="1" t="inlineStr"/>
+      <c r="P291" s="1" t="inlineStr"/>
+      <c r="Q291" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R291" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>Pasticceria Barberini</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Via Marmorata, 41</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>06/57250431</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>www.pasticceriabarberini.it</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>pasticceriabarberini</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>pasticceria_barberini</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>Santa Romana</t>
+        </is>
+      </c>
+      <c r="B292" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Certaldo, 12</t>
+        </is>
+      </c>
+      <c r="C292" s="1" t="inlineStr">
+        <is>
+          <t>06/69317674</t>
+        </is>
+      </c>
+      <c r="D292" s="1" t="inlineStr"/>
+      <c r="E292" s="1" t="inlineStr"/>
+      <c r="F292" s="1" t="inlineStr"/>
+      <c r="G292" s="1" t="inlineStr"/>
+      <c r="H292" s="1" t="inlineStr"/>
+      <c r="I292" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J292" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (pasticceriabarberini) | IG: trovato (pasticceria_barberini)</t>
-        </is>
-      </c>
-      <c r="R292" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K292" s="1" t="inlineStr"/>
+      <c r="L292" s="1" t="inlineStr"/>
+      <c r="M292" s="1" t="inlineStr"/>
+      <c r="N292" s="1" t="inlineStr"/>
+      <c r="O292" s="1" t="inlineStr"/>
+      <c r="P292" s="1" t="inlineStr"/>
+      <c r="Q292" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R292" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>Pasticceria Walter Musco</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Largo Benedetto Bompiani, 8/10</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>06/5124103</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>www.pasticceriawaltermusco.it</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>pasticceriawaltermuscobompiani</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>pasticceriawaltermuscobompiani</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J293" t="inlineStr">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>Seu Pizza Illuminati</t>
+        </is>
+      </c>
+      <c r="B293" s="1" t="inlineStr">
+        <is>
+          <t>Via Angelo Bargoni, 10/18</t>
+        </is>
+      </c>
+      <c r="C293" s="1" t="inlineStr">
+        <is>
+          <t>06/5883384</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="inlineStr"/>
+      <c r="E293" s="1" t="inlineStr"/>
+      <c r="F293" s="1" t="inlineStr"/>
+      <c r="G293" s="1" t="inlineStr"/>
+      <c r="H293" s="1" t="inlineStr"/>
+      <c r="I293" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J293" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (pasticceriawaltermuscobompiani) | IG: trovato (pasticceriawaltermuscobompiani)</t>
-        </is>
-      </c>
-      <c r="R293" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K293" s="1" t="inlineStr"/>
+      <c r="L293" s="1" t="inlineStr"/>
+      <c r="M293" s="1" t="inlineStr"/>
+      <c r="N293" s="1" t="inlineStr"/>
+      <c r="O293" s="1" t="inlineStr"/>
+      <c r="P293" s="1" t="inlineStr"/>
+      <c r="Q293" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R293" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>Pontisso</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Via Antonio Cantore, 3</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>06/86214524</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>pontissobar</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>Forno Ritorno</t>
+        </is>
+      </c>
+      <c r="B294" s="1" t="inlineStr">
+        <is>
+          <t>Via Amerigo Vespucci, 20</t>
+        </is>
+      </c>
+      <c r="C294" s="1" t="inlineStr">
+        <is>
+          <t>392/7768427</t>
+        </is>
+      </c>
+      <c r="D294" s="1" t="inlineStr"/>
+      <c r="E294" s="1" t="inlineStr"/>
+      <c r="F294" s="1" t="inlineStr"/>
+      <c r="G294" s="1" t="inlineStr"/>
+      <c r="H294" s="1" t="inlineStr"/>
+      <c r="I294" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J294" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q294" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (pontissobar)</t>
-        </is>
-      </c>
-      <c r="R294" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K294" s="1" t="inlineStr"/>
+      <c r="L294" s="1" t="inlineStr"/>
+      <c r="M294" s="1" t="inlineStr"/>
+      <c r="N294" s="1" t="inlineStr"/>
+      <c r="O294" s="1" t="inlineStr"/>
+      <c r="P294" s="1" t="inlineStr"/>
+      <c r="Q294" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R294" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>Roscioli Caffè</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Piazza Benedetto Cairoli, 16</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>06/89165330</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>www.rosciolicaffe.com</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>Rosciolicaffe</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Rosciolicaffe</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>Il tuo fornaio</t>
+        </is>
+      </c>
+      <c r="B295" s="1" t="inlineStr">
+        <is>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C295" s="1" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="inlineStr"/>
+      <c r="E295" s="1" t="inlineStr"/>
+      <c r="F295" s="1" t="inlineStr"/>
+      <c r="G295" s="1" t="inlineStr"/>
+      <c r="H295" s="1" t="inlineStr"/>
+      <c r="I295" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J295" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O295" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q295" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Rosciolicaffe) | IG: trovato (Rosciolicaffe)</t>
-        </is>
-      </c>
-      <c r="R295" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K295" s="1" t="inlineStr"/>
+      <c r="L295" s="1" t="inlineStr"/>
+      <c r="M295" s="1" t="inlineStr"/>
+      <c r="N295" s="1" t="inlineStr"/>
+      <c r="O295" s="1" t="inlineStr"/>
+      <c r="P295" s="1" t="inlineStr"/>
+      <c r="Q295" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R295" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>Santi Sebastiano e Valentino</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Via Tirso, 107</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>06/87568048</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>www.santisebastianoevalentino.it</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>santisebastianoevalentino</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>santisebastianoevalentino</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>23/02/2026</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J296" t="inlineStr">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>Krapfen Paglia</t>
+        </is>
+      </c>
+      <c r="B296" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Anco Marzio, 18/19</t>
+        </is>
+      </c>
+      <c r="C296" s="1" t="inlineStr">
+        <is>
+          <t>06/5623344</t>
+        </is>
+      </c>
+      <c r="D296" s="1" t="inlineStr"/>
+      <c r="E296" s="1" t="inlineStr"/>
+      <c r="F296" s="1" t="inlineStr"/>
+      <c r="G296" s="1" t="inlineStr"/>
+      <c r="H296" s="1" t="inlineStr"/>
+      <c r="I296" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J296" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O296" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q296" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (santisebastianoevalentino) | IG: trovato (santisebastianoevalentino)</t>
-        </is>
-      </c>
-      <c r="R296" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
+      <c r="K296" s="1" t="inlineStr"/>
+      <c r="L296" s="1" t="inlineStr"/>
+      <c r="M296" s="1" t="inlineStr"/>
+      <c r="N296" s="1" t="inlineStr"/>
+      <c r="O296" s="1" t="inlineStr"/>
+      <c r="P296" s="1" t="inlineStr"/>
+      <c r="Q296" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R296" s="1" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -18692,307 +18692,317 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="inlineStr">
+      <c r="A298" t="inlineStr">
         <is>
           <t>Sordoni</t>
         </is>
       </c>
-      <c r="B298" s="1" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t>Via Cassia, 1839</t>
         </is>
       </c>
-      <c r="C298" s="1" t="inlineStr">
+      <c r="C298" t="inlineStr">
         <is>
           <t>06/94379873</t>
         </is>
       </c>
-      <c r="D298" s="1" t="inlineStr">
+      <c r="D298" t="inlineStr">
         <is>
           <t>www.pasticceriasordoni.it</t>
         </is>
       </c>
-      <c r="E298" s="1" t="inlineStr">
+      <c r="E298" t="inlineStr">
         <is>
           <t>PasticceriaSordoni</t>
         </is>
       </c>
-      <c r="F298" s="1" t="inlineStr">
+      <c r="F298" t="inlineStr">
         <is>
           <t>pasticceria_sordoni</t>
         </is>
       </c>
-      <c r="G298" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H298" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I298" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J298" s="1" t="inlineStr"/>
-      <c r="K298" s="1" t="inlineStr"/>
-      <c r="L298" s="1" t="inlineStr"/>
-      <c r="M298" s="1" t="inlineStr"/>
-      <c r="N298" s="1" t="inlineStr"/>
-      <c r="O298" s="1" t="inlineStr"/>
-      <c r="P298" s="1" t="inlineStr"/>
-      <c r="Q298" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R298" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (PasticceriaSordoni) | IG: trovato (pasticceria_sordoni)</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="inlineStr">
+      <c r="A299" t="inlineStr">
         <is>
           <t>TE Caffè</t>
         </is>
       </c>
-      <c r="B299" s="1" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>Via Sforza Pallavicini, 19/25</t>
         </is>
       </c>
-      <c r="C299" s="1" t="inlineStr">
+      <c r="C299" t="inlineStr">
         <is>
           <t>375/7051217</t>
         </is>
       </c>
-      <c r="D299" s="1" t="inlineStr">
+      <c r="D299" t="inlineStr">
         <is>
           <t>www.tecioccolateria.com</t>
         </is>
       </c>
-      <c r="E299" s="1" t="inlineStr"/>
-      <c r="F299" s="1" t="inlineStr">
+      <c r="F299" t="inlineStr">
         <is>
           <t>tecioccolateria</t>
         </is>
       </c>
-      <c r="G299" s="1" t="inlineStr"/>
-      <c r="H299" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I299" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J299" s="1" t="inlineStr"/>
-      <c r="K299" s="1" t="inlineStr"/>
-      <c r="L299" s="1" t="inlineStr"/>
-      <c r="M299" s="1" t="inlineStr"/>
-      <c r="N299" s="1" t="inlineStr"/>
-      <c r="O299" s="1" t="inlineStr"/>
-      <c r="P299" s="1" t="inlineStr"/>
-      <c r="Q299" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R299" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (tecioccolateria)</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="inlineStr">
+      <c r="A300" t="inlineStr">
         <is>
           <t>Aqla</t>
         </is>
       </c>
-      <c r="B300" s="1" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>Via Andrea Busiri Vici, 13</t>
         </is>
       </c>
-      <c r="C300" s="1" t="inlineStr">
+      <c r="C300" t="inlineStr">
         <is>
           <t>333/6776681</t>
         </is>
       </c>
-      <c r="D300" s="1" t="inlineStr"/>
-      <c r="E300" s="1" t="inlineStr">
+      <c r="E300" t="inlineStr">
         <is>
           <t>Aqla-Street-food-medio-orientale</t>
         </is>
       </c>
-      <c r="F300" s="1" t="inlineStr">
+      <c r="F300" t="inlineStr">
         <is>
           <t>aqla_streetfood</t>
         </is>
       </c>
-      <c r="G300" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H300" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I300" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J300" s="1" t="inlineStr"/>
-      <c r="K300" s="1" t="inlineStr"/>
-      <c r="L300" s="1" t="inlineStr"/>
-      <c r="M300" s="1" t="inlineStr"/>
-      <c r="N300" s="1" t="inlineStr"/>
-      <c r="O300" s="1" t="inlineStr"/>
-      <c r="P300" s="1" t="inlineStr"/>
-      <c r="Q300" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R300" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Aqla-Street-food-medio-orientale) | IG: trovato (aqla_streetfood)</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="inlineStr">
+      <c r="A301" t="inlineStr">
         <is>
           <t>Aromaticus</t>
         </is>
       </c>
-      <c r="B301" s="1" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>Via Urbana, 134</t>
         </is>
       </c>
-      <c r="C301" s="1" t="inlineStr">
+      <c r="C301" t="inlineStr">
         <is>
           <t>06/4881355</t>
         </is>
       </c>
-      <c r="D301" s="1" t="inlineStr">
+      <c r="D301" t="inlineStr">
         <is>
           <t>www.aromaticus.it</t>
         </is>
       </c>
-      <c r="E301" s="1" t="inlineStr">
+      <c r="E301" t="inlineStr">
         <is>
           <t>ArOmAticUs</t>
         </is>
       </c>
-      <c r="F301" s="1" t="inlineStr">
+      <c r="F301" t="inlineStr">
         <is>
           <t>aromaticus_</t>
         </is>
       </c>
-      <c r="G301" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H301" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I301" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J301" s="1" t="inlineStr"/>
-      <c r="K301" s="1" t="inlineStr"/>
-      <c r="L301" s="1" t="inlineStr"/>
-      <c r="M301" s="1" t="inlineStr"/>
-      <c r="N301" s="1" t="inlineStr"/>
-      <c r="O301" s="1" t="inlineStr"/>
-      <c r="P301" s="1" t="inlineStr"/>
-      <c r="Q301" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R301" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ArOmAticUs) | IG: trovato (aromaticus_)</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="inlineStr">
+      <c r="A302" t="inlineStr">
         <is>
           <t>Bar Sota</t>
         </is>
       </c>
-      <c r="B302" s="1" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>Via della Frezza, 55</t>
         </is>
       </c>
-      <c r="C302" s="1" t="inlineStr">
+      <c r="C302" t="inlineStr">
         <is>
           <t>06/69221898</t>
         </is>
       </c>
-      <c r="D302" s="1" t="inlineStr">
+      <c r="D302" t="inlineStr">
         <is>
           <t>www.barsota.it</t>
         </is>
       </c>
-      <c r="E302" s="1" t="inlineStr"/>
-      <c r="F302" s="1" t="inlineStr">
+      <c r="F302" t="inlineStr">
         <is>
           <t>barsota_rome</t>
         </is>
       </c>
-      <c r="G302" s="1" t="inlineStr"/>
-      <c r="H302" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I302" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J302" s="1" t="inlineStr"/>
-      <c r="K302" s="1" t="inlineStr"/>
-      <c r="L302" s="1" t="inlineStr"/>
-      <c r="M302" s="1" t="inlineStr"/>
-      <c r="N302" s="1" t="inlineStr"/>
-      <c r="O302" s="1" t="inlineStr"/>
-      <c r="P302" s="1" t="inlineStr"/>
-      <c r="Q302" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R302" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (barsota_rome)</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -19022,7 +19032,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J303" s="1" t="inlineStr"/>
+      <c r="J303" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K303" s="1" t="inlineStr"/>
       <c r="L303" s="1" t="inlineStr"/>
       <c r="M303" s="1" t="inlineStr"/>
@@ -19031,12 +19045,12 @@
       <c r="P303" s="1" t="inlineStr"/>
       <c r="Q303" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19080,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J304" s="1" t="inlineStr"/>
+      <c r="J304" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K304" s="1" t="inlineStr"/>
       <c r="L304" s="1" t="inlineStr"/>
       <c r="M304" s="1" t="inlineStr"/>
@@ -19075,136 +19093,141 @@
       <c r="P304" s="1" t="inlineStr"/>
       <c r="Q304" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="inlineStr">
+      <c r="A305" t="inlineStr">
         <is>
           <t>Ciao Checca</t>
         </is>
       </c>
-      <c r="B305" s="1" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>Piazza di Firenze, 25/26</t>
         </is>
       </c>
-      <c r="C305" s="1" t="inlineStr">
+      <c r="C305" t="inlineStr">
         <is>
           <t>06/68300368</t>
         </is>
       </c>
-      <c r="D305" s="1" t="inlineStr">
+      <c r="D305" t="inlineStr">
         <is>
           <t>www.ciaochecca.com</t>
         </is>
       </c>
-      <c r="E305" s="1" t="inlineStr">
+      <c r="E305" t="inlineStr">
         <is>
           <t>ciaochecca</t>
         </is>
       </c>
-      <c r="F305" s="1" t="inlineStr">
+      <c r="F305" t="inlineStr">
         <is>
           <t>ciaochecca</t>
         </is>
       </c>
-      <c r="G305" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H305" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I305" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J305" s="1" t="inlineStr"/>
-      <c r="K305" s="1" t="inlineStr"/>
-      <c r="L305" s="1" t="inlineStr"/>
-      <c r="M305" s="1" t="inlineStr"/>
-      <c r="N305" s="1" t="inlineStr"/>
-      <c r="O305" s="1" t="inlineStr"/>
-      <c r="P305" s="1" t="inlineStr"/>
-      <c r="Q305" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R305" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ciaochecca) | IG: trovato (ciaochecca)</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="inlineStr">
+      <c r="A306" t="inlineStr">
         <is>
           <t>Cus Cus</t>
         </is>
       </c>
-      <c r="B306" s="1" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>Via Arezzo, 39</t>
         </is>
       </c>
-      <c r="C306" s="1" t="inlineStr">
+      <c r="C306" t="inlineStr">
         <is>
           <t>06/97997519 - 349/3603694</t>
         </is>
       </c>
-      <c r="D306" s="1" t="inlineStr"/>
-      <c r="E306" s="1" t="inlineStr">
+      <c r="E306" t="inlineStr">
         <is>
           <t>cuscusroma</t>
         </is>
       </c>
-      <c r="F306" s="1" t="inlineStr">
+      <c r="F306" t="inlineStr">
         <is>
           <t>cuscusroma</t>
         </is>
       </c>
-      <c r="G306" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H306" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I306" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J306" s="1" t="inlineStr"/>
-      <c r="K306" s="1" t="inlineStr"/>
-      <c r="L306" s="1" t="inlineStr"/>
-      <c r="M306" s="1" t="inlineStr"/>
-      <c r="N306" s="1" t="inlineStr"/>
-      <c r="O306" s="1" t="inlineStr"/>
-      <c r="P306" s="1" t="inlineStr"/>
-      <c r="Q306" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R306" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (cuscusroma) | IG: trovato (cuscusroma)</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19257,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J307" s="1" t="inlineStr"/>
+      <c r="J307" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K307" s="1" t="inlineStr"/>
       <c r="L307" s="1" t="inlineStr"/>
       <c r="M307" s="1" t="inlineStr"/>
@@ -19243,200 +19270,208 @@
       <c r="P307" s="1" t="inlineStr"/>
       <c r="Q307" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="inlineStr">
+      <c r="A308" t="inlineStr">
         <is>
           <t>Drogherie del Mare</t>
         </is>
       </c>
-      <c r="B308" s="1" t="inlineStr">
+      <c r="B308" t="inlineStr">
         <is>
           <t>Via Savoia, 38/42</t>
         </is>
       </c>
-      <c r="C308" s="1" t="inlineStr">
+      <c r="C308" t="inlineStr">
         <is>
           <t>333/2256285</t>
         </is>
       </c>
-      <c r="D308" s="1" t="inlineStr">
+      <c r="D308" t="inlineStr">
         <is>
           <t>www.drogheriedelmare.it</t>
         </is>
       </c>
-      <c r="E308" s="1" t="inlineStr">
+      <c r="E308" t="inlineStr">
         <is>
           <t>Drogherie-del-Mare</t>
         </is>
       </c>
-      <c r="F308" s="1" t="inlineStr">
+      <c r="F308" t="inlineStr">
         <is>
           <t>drogheriedelmare_</t>
         </is>
       </c>
-      <c r="G308" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H308" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I308" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J308" s="1" t="inlineStr"/>
-      <c r="K308" s="1" t="inlineStr"/>
-      <c r="L308" s="1" t="inlineStr"/>
-      <c r="M308" s="1" t="inlineStr"/>
-      <c r="N308" s="1" t="inlineStr"/>
-      <c r="O308" s="1" t="inlineStr"/>
-      <c r="P308" s="1" t="inlineStr"/>
-      <c r="Q308" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R308" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Drogherie-del-Mare) | IG: trovato (drogheriedelmare_)</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="inlineStr">
+      <c r="A309" t="inlineStr">
         <is>
           <t>Il Maritozzo Rosso</t>
         </is>
       </c>
-      <c r="B309" s="1" t="inlineStr">
+      <c r="B309" t="inlineStr">
         <is>
           <t>Via Pietro Cavallini, 25</t>
         </is>
       </c>
-      <c r="C309" s="1" t="inlineStr">
+      <c r="C309" t="inlineStr">
         <is>
           <t>06/90543525</t>
         </is>
       </c>
-      <c r="D309" s="1" t="inlineStr">
+      <c r="D309" t="inlineStr">
         <is>
           <t>www.ilmaritozzorosso.com</t>
         </is>
       </c>
-      <c r="E309" s="1" t="inlineStr">
+      <c r="E309" t="inlineStr">
         <is>
           <t>Il-Maritozzo-Rosso</t>
         </is>
       </c>
-      <c r="F309" s="1" t="inlineStr">
+      <c r="F309" t="inlineStr">
         <is>
           <t>il_maritozzo_rosso</t>
         </is>
       </c>
-      <c r="G309" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H309" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I309" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J309" s="1" t="inlineStr"/>
-      <c r="K309" s="1" t="inlineStr"/>
-      <c r="L309" s="1" t="inlineStr"/>
-      <c r="M309" s="1" t="inlineStr"/>
-      <c r="N309" s="1" t="inlineStr"/>
-      <c r="O309" s="1" t="inlineStr"/>
-      <c r="P309" s="1" t="inlineStr"/>
-      <c r="Q309" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R309" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Il-Maritozzo-Rosso) | IG: trovato (il_maritozzo_rosso)</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="inlineStr">
+      <c r="A310" t="inlineStr">
         <is>
           <t>Jiamo Lab</t>
         </is>
       </c>
-      <c r="B310" s="1" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>Via Bergamo, 15</t>
         </is>
       </c>
-      <c r="C310" s="1" t="inlineStr">
+      <c r="C310" t="inlineStr">
         <is>
           <t>388/8348616</t>
         </is>
       </c>
-      <c r="D310" s="1" t="inlineStr"/>
-      <c r="E310" s="1" t="inlineStr">
+      <c r="E310" t="inlineStr">
         <is>
           <t>JiaMopaninocroccante</t>
         </is>
       </c>
-      <c r="F310" s="1" t="inlineStr">
+      <c r="F310" t="inlineStr">
         <is>
           <t>jiamolab</t>
         </is>
       </c>
-      <c r="G310" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H310" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I310" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J310" s="1" t="inlineStr"/>
-      <c r="K310" s="1" t="inlineStr"/>
-      <c r="L310" s="1" t="inlineStr"/>
-      <c r="M310" s="1" t="inlineStr"/>
-      <c r="N310" s="1" t="inlineStr"/>
-      <c r="O310" s="1" t="inlineStr"/>
-      <c r="P310" s="1" t="inlineStr"/>
-      <c r="Q310" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R310" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (JiaMopaninocroccante) | IG: trovato (jiamolab)</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -17693,480 +17693,635 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B277" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C277" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D277" s="1" t="inlineStr"/>
-      <c r="E277" s="1" t="inlineStr"/>
-      <c r="F277" s="1" t="inlineStr"/>
-      <c r="G277" s="1" t="inlineStr"/>
-      <c r="H277" s="1" t="inlineStr"/>
-      <c r="I277" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J277" s="1" t="inlineStr">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Sordoni</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Via Cassia, 1839</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>06/94379873</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>www.pasticceriasordoni.it</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>PasticceriaSordoni</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>pasticceria_sordoni</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K277" s="1" t="inlineStr"/>
-      <c r="L277" s="1" t="inlineStr"/>
-      <c r="M277" s="1" t="inlineStr"/>
-      <c r="N277" s="1" t="inlineStr"/>
-      <c r="O277" s="1" t="inlineStr"/>
-      <c r="P277" s="1" t="inlineStr"/>
-      <c r="Q277" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R277" s="1" t="inlineStr">
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (PasticceriaSordoni) | IG: trovato (pasticceria_sordoni)</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="inlineStr">
-        <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
-        </is>
-      </c>
-      <c r="B278" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Erbe, 16</t>
-        </is>
-      </c>
-      <c r="C278" s="1" t="inlineStr">
-        <is>
-          <t>348/7277746</t>
-        </is>
-      </c>
-      <c r="D278" s="1" t="inlineStr"/>
-      <c r="E278" s="1" t="inlineStr"/>
-      <c r="F278" s="1" t="inlineStr"/>
-      <c r="G278" s="1" t="inlineStr"/>
-      <c r="H278" s="1" t="inlineStr"/>
-      <c r="I278" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J278" s="1" t="inlineStr">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>TE Caffè</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Via Sforza Pallavicini, 19/25</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>375/7051217</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>www.tecioccolateria.com</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>tecioccolateria</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K278" s="1" t="inlineStr"/>
-      <c r="L278" s="1" t="inlineStr"/>
-      <c r="M278" s="1" t="inlineStr"/>
-      <c r="N278" s="1" t="inlineStr"/>
-      <c r="O278" s="1" t="inlineStr"/>
-      <c r="P278" s="1" t="inlineStr"/>
-      <c r="Q278" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R278" s="1" t="inlineStr">
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (tecioccolateria)</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="inlineStr">
-        <is>
-          <t>Osteria del Vicolo Fatato</t>
-        </is>
-      </c>
-      <c r="B279" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Forno Fatato, 11</t>
-        </is>
-      </c>
-      <c r="C279" s="1" t="inlineStr">
-        <is>
-          <t>0775/503035</t>
-        </is>
-      </c>
-      <c r="D279" s="1" t="inlineStr"/>
-      <c r="E279" s="1" t="inlineStr"/>
-      <c r="F279" s="1" t="inlineStr"/>
-      <c r="G279" s="1" t="inlineStr"/>
-      <c r="H279" s="1" t="inlineStr"/>
-      <c r="I279" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J279" s="1" t="inlineStr">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Aqla</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Via Andrea Busiri Vici, 13</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>333/6776681</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Aqla-Street-food-medio-orientale</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>aqla_streetfood</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K279" s="1" t="inlineStr"/>
-      <c r="L279" s="1" t="inlineStr"/>
-      <c r="M279" s="1" t="inlineStr"/>
-      <c r="N279" s="1" t="inlineStr"/>
-      <c r="O279" s="1" t="inlineStr"/>
-      <c r="P279" s="1" t="inlineStr"/>
-      <c r="Q279" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R279" s="1" t="inlineStr">
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Aqla-Street-food-medio-orientale) | IG: trovato (aqla_streetfood)</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="inlineStr">
-        <is>
-          <t>Poldo e Gianna</t>
-        </is>
-      </c>
-      <c r="B280" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Rosini, 6</t>
-        </is>
-      </c>
-      <c r="C280" s="1" t="inlineStr">
-        <is>
-          <t>06/6893499</t>
-        </is>
-      </c>
-      <c r="D280" s="1" t="inlineStr"/>
-      <c r="E280" s="1" t="inlineStr"/>
-      <c r="F280" s="1" t="inlineStr"/>
-      <c r="G280" s="1" t="inlineStr"/>
-      <c r="H280" s="1" t="inlineStr"/>
-      <c r="I280" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J280" s="1" t="inlineStr">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Aromaticus</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Via Urbana, 134</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>06/4881355</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>www.aromaticus.it</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>ArOmAticUs</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>aromaticus_</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K280" s="1" t="inlineStr"/>
-      <c r="L280" s="1" t="inlineStr"/>
-      <c r="M280" s="1" t="inlineStr"/>
-      <c r="N280" s="1" t="inlineStr"/>
-      <c r="O280" s="1" t="inlineStr"/>
-      <c r="P280" s="1" t="inlineStr"/>
-      <c r="Q280" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R280" s="1" t="inlineStr">
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ArOmAticUs) | IG: trovato (aromaticus_)</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria A Casa Di Rita</t>
-        </is>
-      </c>
-      <c r="B281" s="1" t="inlineStr">
-        <is>
-          <t>Via delle Ciliegie, 145</t>
-        </is>
-      </c>
-      <c r="C281" s="1" t="inlineStr">
-        <is>
-          <t>338/9860960</t>
-        </is>
-      </c>
-      <c r="D281" s="1" t="inlineStr"/>
-      <c r="E281" s="1" t="inlineStr"/>
-      <c r="F281" s="1" t="inlineStr"/>
-      <c r="G281" s="1" t="inlineStr"/>
-      <c r="H281" s="1" t="inlineStr"/>
-      <c r="I281" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J281" s="1" t="inlineStr">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Bar Sota</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Via della Frezza, 55</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>06/69221898</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>www.barsota.it</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>barsota_rome</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K281" s="1" t="inlineStr"/>
-      <c r="L281" s="1" t="inlineStr"/>
-      <c r="M281" s="1" t="inlineStr"/>
-      <c r="N281" s="1" t="inlineStr"/>
-      <c r="O281" s="1" t="inlineStr"/>
-      <c r="P281" s="1" t="inlineStr"/>
-      <c r="Q281" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R281" s="1" t="inlineStr">
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (barsota_rome)</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="inlineStr">
-        <is>
-          <t>Ie Koji Japanese Izakaya</t>
-        </is>
-      </c>
-      <c r="B282" s="1" t="inlineStr">
-        <is>
-          <t>Via Marcantonio Bragadin, 13</t>
-        </is>
-      </c>
-      <c r="C282" s="1" t="inlineStr">
-        <is>
-          <t>348/4302368 - 06/69459860</t>
-        </is>
-      </c>
-      <c r="D282" s="1" t="inlineStr"/>
-      <c r="E282" s="1" t="inlineStr"/>
-      <c r="F282" s="1" t="inlineStr"/>
-      <c r="G282" s="1" t="inlineStr"/>
-      <c r="H282" s="1" t="inlineStr"/>
-      <c r="I282" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J282" s="1" t="inlineStr">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Ciao Checca</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Piazza di Firenze, 25/26</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>06/68300368</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>www.ciaochecca.com</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>ciaochecca</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>ciaochecca</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K282" s="1" t="inlineStr"/>
-      <c r="L282" s="1" t="inlineStr"/>
-      <c r="M282" s="1" t="inlineStr"/>
-      <c r="N282" s="1" t="inlineStr"/>
-      <c r="O282" s="1" t="inlineStr"/>
-      <c r="P282" s="1" t="inlineStr"/>
-      <c r="Q282" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R282" s="1" t="inlineStr">
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ciaochecca) | IG: trovato (ciaochecca)</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B283" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C283" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D283" s="1" t="inlineStr"/>
-      <c r="E283" s="1" t="inlineStr"/>
-      <c r="F283" s="1" t="inlineStr"/>
-      <c r="G283" s="1" t="inlineStr"/>
-      <c r="H283" s="1" t="inlineStr"/>
-      <c r="I283" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J283" s="1" t="inlineStr">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Cus Cus</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Via Arezzo, 39</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>06/97997519 - 349/3603694</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>cuscusroma</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>cuscusroma</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K283" s="1" t="inlineStr"/>
-      <c r="L283" s="1" t="inlineStr"/>
-      <c r="M283" s="1" t="inlineStr"/>
-      <c r="N283" s="1" t="inlineStr"/>
-      <c r="O283" s="1" t="inlineStr"/>
-      <c r="P283" s="1" t="inlineStr"/>
-      <c r="Q283" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R283" s="1" t="inlineStr">
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (cuscusroma) | IG: trovato (cuscusroma)</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="inlineStr">
-        <is>
-          <t>Nomisan</t>
-        </is>
-      </c>
-      <c r="B284" s="1" t="inlineStr">
-        <is>
-          <t>Viale Gianluigi Bonelli, 237</t>
-        </is>
-      </c>
-      <c r="C284" s="1" t="inlineStr">
-        <is>
-          <t>342/8036080</t>
-        </is>
-      </c>
-      <c r="D284" s="1" t="inlineStr"/>
-      <c r="E284" s="1" t="inlineStr"/>
-      <c r="F284" s="1" t="inlineStr"/>
-      <c r="G284" s="1" t="inlineStr"/>
-      <c r="H284" s="1" t="inlineStr"/>
-      <c r="I284" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J284" s="1" t="inlineStr">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Drogherie del Mare</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Via Savoia, 38/42</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>333/2256285</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>www.drogheriedelmare.it</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Drogherie-del-Mare</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>drogheriedelmare_</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K284" s="1" t="inlineStr"/>
-      <c r="L284" s="1" t="inlineStr"/>
-      <c r="M284" s="1" t="inlineStr"/>
-      <c r="N284" s="1" t="inlineStr"/>
-      <c r="O284" s="1" t="inlineStr"/>
-      <c r="P284" s="1" t="inlineStr"/>
-      <c r="Q284" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R284" s="1" t="inlineStr">
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Drogherie-del-Mare) | IG: trovato (drogheriedelmare_)</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="inlineStr">
-        <is>
-          <t>Al Setaccio</t>
-        </is>
-      </c>
-      <c r="B285" s="1" t="inlineStr">
-        <is>
-          <t>Via di Mezzocammino, 193</t>
-        </is>
-      </c>
-      <c r="C285" s="1" t="inlineStr">
-        <is>
-          <t>06/52372056</t>
-        </is>
-      </c>
-      <c r="D285" s="1" t="inlineStr"/>
-      <c r="E285" s="1" t="inlineStr"/>
-      <c r="F285" s="1" t="inlineStr"/>
-      <c r="G285" s="1" t="inlineStr"/>
-      <c r="H285" s="1" t="inlineStr"/>
-      <c r="I285" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J285" s="1" t="inlineStr">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Il Maritozzo Rosso</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Via Pietro Cavallini, 25</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>06/90543525</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>www.ilmaritozzorosso.com</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Il-Maritozzo-Rosso</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>il_maritozzo_rosso</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K285" s="1" t="inlineStr"/>
-      <c r="L285" s="1" t="inlineStr"/>
-      <c r="M285" s="1" t="inlineStr"/>
-      <c r="N285" s="1" t="inlineStr"/>
-      <c r="O285" s="1" t="inlineStr"/>
-      <c r="P285" s="1" t="inlineStr"/>
-      <c r="Q285" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R285" s="1" t="inlineStr">
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (Il-Maritozzo-Rosso) | IG: trovato (il_maritozzo_rosso)</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="inlineStr">
-        <is>
-          <t>Angelo Pezzella</t>
-        </is>
-      </c>
-      <c r="B286" s="1" t="inlineStr">
-        <is>
-          <t>Via Appia Nuova, 1095</t>
-        </is>
-      </c>
-      <c r="C286" s="1" t="inlineStr">
-        <is>
-          <t>06/7188560</t>
-        </is>
-      </c>
-      <c r="D286" s="1" t="inlineStr"/>
-      <c r="E286" s="1" t="inlineStr"/>
-      <c r="F286" s="1" t="inlineStr"/>
-      <c r="G286" s="1" t="inlineStr"/>
-      <c r="H286" s="1" t="inlineStr"/>
-      <c r="I286" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J286" s="1" t="inlineStr">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Jiamo Lab</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Via Bergamo, 15</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>388/8348616</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>JiaMopaninocroccante</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>jiamolab</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K286" s="1" t="inlineStr"/>
-      <c r="L286" s="1" t="inlineStr"/>
-      <c r="M286" s="1" t="inlineStr"/>
-      <c r="N286" s="1" t="inlineStr"/>
-      <c r="O286" s="1" t="inlineStr"/>
-      <c r="P286" s="1" t="inlineStr"/>
-      <c r="Q286" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R286" s="1" t="inlineStr">
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (JiaMopaninocroccante) | IG: trovato (jiamolab)</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
@@ -18175,17 +18330,17 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>Clementina</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>Via della Torre Clementina, 158</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t>328/8181651</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr"/>
@@ -18216,24 +18371,24 @@
       </c>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>Da Antonio</t>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
         </is>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>Via Mario Lizzani, 21</t>
+          <t>Piazza delle Erbe, 16</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t>391/7475549</t>
+          <t>348/7277746</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr"/>
@@ -18264,24 +18419,24 @@
       </c>
       <c r="R288" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>Diego Vitagliano</t>
+          <t>Osteria del Vicolo Fatato</t>
         </is>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>Via Chiana, 80</t>
+          <t>Vicolo Forno Fatato, 11</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t>06/72276443</t>
+          <t>0775/503035</t>
         </is>
       </c>
       <c r="D289" s="1" t="inlineStr"/>
@@ -18312,24 +18467,24 @@
       </c>
       <c r="R289" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>GioMà</t>
+          <t>Poldo e Gianna</t>
         </is>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Via Calpurnio Fiamma, 40/44</t>
+          <t>Vicolo Rosini, 6</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>06/7674717</t>
+          <t>06/6893499</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr"/>
@@ -18360,24 +18515,24 @@
       </c>
       <c r="R290" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>Pupillo Pura Pizza</t>
+          <t>Trattoria A Casa Di Rita</t>
         </is>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>Via Giacomo Matteotti, 29</t>
+          <t>Via delle Ciliegie, 145</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
         <is>
-          <t>339/4143148</t>
+          <t>338/9860960</t>
         </is>
       </c>
       <c r="D291" s="1" t="inlineStr"/>
@@ -18408,24 +18563,24 @@
       </c>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>Santa Romana</t>
+          <t>Ie Koji Japanese Izakaya</t>
         </is>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>Piazza Certaldo, 12</t>
+          <t>Via Marcantonio Bragadin, 13</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>06/69317674</t>
+          <t>348/4302368 - 06/69459860</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr"/>
@@ -18456,24 +18611,24 @@
       </c>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>Seu Pizza Illuminati</t>
+          <t>Mrgda Ristorante</t>
         </is>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>Via Angelo Bargoni, 10/18</t>
+          <t>Via Prenestina, 182</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
         <is>
-          <t>06/5883384</t>
+          <t>329/933355</t>
         </is>
       </c>
       <c r="D293" s="1" t="inlineStr"/>
@@ -18504,24 +18659,24 @@
       </c>
       <c r="R293" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>Forno Ritorno</t>
+          <t>Nomisan</t>
         </is>
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>Via Amerigo Vespucci, 20</t>
+          <t>Viale Gianluigi Bonelli, 237</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t>392/7768427</t>
+          <t>342/8036080</t>
         </is>
       </c>
       <c r="D294" s="1" t="inlineStr"/>
@@ -18552,24 +18707,24 @@
       </c>
       <c r="R294" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>Il tuo fornaio</t>
+          <t>Al Setaccio</t>
         </is>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>Via Francesco Sapori, 35</t>
+          <t>Via di Mezzocammino, 193</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t>06/5017873</t>
+          <t>06/52372056</t>
         </is>
       </c>
       <c r="D295" s="1" t="inlineStr"/>
@@ -18600,24 +18755,24 @@
       </c>
       <c r="R295" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>Krapfen Paglia</t>
+          <t>Angelo Pezzella</t>
         </is>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>Piazza Anco Marzio, 18/19</t>
+          <t>Via Appia Nuova, 1095</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
         <is>
-          <t>06/5623344</t>
+          <t>06/7188560</t>
         </is>
       </c>
       <c r="D296" s="1" t="inlineStr"/>
@@ -18648,22 +18803,26 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>Slow</t>
+          <t>Clementina</t>
         </is>
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>Corso Vittorio Emanuele II, 73</t>
-        </is>
-      </c>
-      <c r="C297" s="1" t="inlineStr"/>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C297" s="1" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
       <c r="D297" s="1" t="inlineStr"/>
       <c r="E297" s="1" t="inlineStr"/>
       <c r="F297" s="1" t="inlineStr"/>
@@ -18692,334 +18851,264 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>Sordoni</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Via Cassia, 1839</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>06/94379873</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>www.pasticceriasordoni.it</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>PasticceriaSordoni</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>pasticceria_sordoni</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>Da Antonio</t>
+        </is>
+      </c>
+      <c r="B298" s="1" t="inlineStr">
+        <is>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C298" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
+      <c r="D298" s="1" t="inlineStr"/>
+      <c r="E298" s="1" t="inlineStr"/>
+      <c r="F298" s="1" t="inlineStr"/>
+      <c r="G298" s="1" t="inlineStr"/>
+      <c r="H298" s="1" t="inlineStr"/>
+      <c r="I298" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J298" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q298" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (PasticceriaSordoni) | IG: trovato (pasticceria_sordoni)</t>
-        </is>
-      </c>
-      <c r="R298" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
+      <c r="K298" s="1" t="inlineStr"/>
+      <c r="L298" s="1" t="inlineStr"/>
+      <c r="M298" s="1" t="inlineStr"/>
+      <c r="N298" s="1" t="inlineStr"/>
+      <c r="O298" s="1" t="inlineStr"/>
+      <c r="P298" s="1" t="inlineStr"/>
+      <c r="Q298" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R298" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>TE Caffè</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Via Sforza Pallavicini, 19/25</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>375/7051217</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>www.tecioccolateria.com</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>tecioccolateria</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>Diego Vitagliano</t>
+        </is>
+      </c>
+      <c r="B299" s="1" t="inlineStr">
+        <is>
+          <t>Via Chiana, 80</t>
+        </is>
+      </c>
+      <c r="C299" s="1" t="inlineStr">
+        <is>
+          <t>06/72276443</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="inlineStr"/>
+      <c r="E299" s="1" t="inlineStr"/>
+      <c r="F299" s="1" t="inlineStr"/>
+      <c r="G299" s="1" t="inlineStr"/>
+      <c r="H299" s="1" t="inlineStr"/>
+      <c r="I299" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J299" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q299" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (tecioccolateria)</t>
-        </is>
-      </c>
-      <c r="R299" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
+      <c r="K299" s="1" t="inlineStr"/>
+      <c r="L299" s="1" t="inlineStr"/>
+      <c r="M299" s="1" t="inlineStr"/>
+      <c r="N299" s="1" t="inlineStr"/>
+      <c r="O299" s="1" t="inlineStr"/>
+      <c r="P299" s="1" t="inlineStr"/>
+      <c r="Q299" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R299" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>Aqla</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Via Andrea Busiri Vici, 13</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>333/6776681</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>Aqla-Street-food-medio-orientale</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>aqla_streetfood</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J300" t="inlineStr">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>GioMà</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="inlineStr">
+        <is>
+          <t>Via Calpurnio Fiamma, 40/44</t>
+        </is>
+      </c>
+      <c r="C300" s="1" t="inlineStr">
+        <is>
+          <t>06/7674717</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="inlineStr"/>
+      <c r="E300" s="1" t="inlineStr"/>
+      <c r="F300" s="1" t="inlineStr"/>
+      <c r="G300" s="1" t="inlineStr"/>
+      <c r="H300" s="1" t="inlineStr"/>
+      <c r="I300" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J300" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q300" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Aqla-Street-food-medio-orientale) | IG: trovato (aqla_streetfood)</t>
-        </is>
-      </c>
-      <c r="R300" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
+      <c r="K300" s="1" t="inlineStr"/>
+      <c r="L300" s="1" t="inlineStr"/>
+      <c r="M300" s="1" t="inlineStr"/>
+      <c r="N300" s="1" t="inlineStr"/>
+      <c r="O300" s="1" t="inlineStr"/>
+      <c r="P300" s="1" t="inlineStr"/>
+      <c r="Q300" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R300" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>Aromaticus</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Via Urbana, 134</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>06/4881355</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>www.aromaticus.it</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>ArOmAticUs</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>aromaticus_</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>Pupillo Pura Pizza</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t>Via Giacomo Matteotti, 29</t>
+        </is>
+      </c>
+      <c r="C301" s="1" t="inlineStr">
+        <is>
+          <t>339/4143148</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr"/>
+      <c r="E301" s="1" t="inlineStr"/>
+      <c r="F301" s="1" t="inlineStr"/>
+      <c r="G301" s="1" t="inlineStr"/>
+      <c r="H301" s="1" t="inlineStr"/>
+      <c r="I301" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J301" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q301" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (ArOmAticUs) | IG: trovato (aromaticus_)</t>
-        </is>
-      </c>
-      <c r="R301" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
+      <c r="K301" s="1" t="inlineStr"/>
+      <c r="L301" s="1" t="inlineStr"/>
+      <c r="M301" s="1" t="inlineStr"/>
+      <c r="N301" s="1" t="inlineStr"/>
+      <c r="O301" s="1" t="inlineStr"/>
+      <c r="P301" s="1" t="inlineStr"/>
+      <c r="Q301" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R301" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>Bar Sota</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Via della Frezza, 55</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>06/69221898</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>www.barsota.it</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>barsota_rome</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>Santa Romana</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Certaldo, 12</t>
+        </is>
+      </c>
+      <c r="C302" s="1" t="inlineStr">
+        <is>
+          <t>06/69317674</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="inlineStr"/>
+      <c r="E302" s="1" t="inlineStr"/>
+      <c r="F302" s="1" t="inlineStr"/>
+      <c r="G302" s="1" t="inlineStr"/>
+      <c r="H302" s="1" t="inlineStr"/>
+      <c r="I302" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J302" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q302" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (barsota_rome)</t>
-        </is>
-      </c>
-      <c r="R302" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
+      <c r="K302" s="1" t="inlineStr"/>
+      <c r="L302" s="1" t="inlineStr"/>
+      <c r="M302" s="1" t="inlineStr"/>
+      <c r="N302" s="1" t="inlineStr"/>
+      <c r="O302" s="1" t="inlineStr"/>
+      <c r="P302" s="1" t="inlineStr"/>
+      <c r="Q302" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R302" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>Bottega Popolare</t>
+          <t>Seu Pizza Illuminati</t>
         </is>
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>Via Andrea Doria, 41 Mercato Trionfale Box 113</t>
+          <t>Via Angelo Bargoni, 10/18</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t>334/3351068</t>
+          <t>06/5883384</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr"/>
@@ -19050,24 +19139,24 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>Cheebo</t>
+          <t>Forno Ritorno</t>
         </is>
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>Via Aretusa, 6</t>
+          <t>Via Amerigo Vespucci, 20</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t>351/7598556</t>
+          <t>392/7768427</t>
         </is>
       </c>
       <c r="D304" s="1" t="inlineStr"/>
@@ -19098,155 +19187,118 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Ciao Checca</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Piazza di Firenze, 25/26</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>06/68300368</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>www.ciaochecca.com</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>ciaochecca</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>ciaochecca</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J305" t="inlineStr">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>Il tuo fornaio</t>
+        </is>
+      </c>
+      <c r="B305" s="1" t="inlineStr">
+        <is>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C305" s="1" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="inlineStr"/>
+      <c r="E305" s="1" t="inlineStr"/>
+      <c r="F305" s="1" t="inlineStr"/>
+      <c r="G305" s="1" t="inlineStr"/>
+      <c r="H305" s="1" t="inlineStr"/>
+      <c r="I305" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J305" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O305" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q305" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (ciaochecca) | IG: trovato (ciaochecca)</t>
-        </is>
-      </c>
-      <c r="R305" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
+      <c r="K305" s="1" t="inlineStr"/>
+      <c r="L305" s="1" t="inlineStr"/>
+      <c r="M305" s="1" t="inlineStr"/>
+      <c r="N305" s="1" t="inlineStr"/>
+      <c r="O305" s="1" t="inlineStr"/>
+      <c r="P305" s="1" t="inlineStr"/>
+      <c r="Q305" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R305" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Cus Cus</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Via Arezzo, 39</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>06/97997519 - 349/3603694</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>cuscusroma</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>cuscusroma</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>Krapfen Paglia</t>
+        </is>
+      </c>
+      <c r="B306" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Anco Marzio, 18/19</t>
+        </is>
+      </c>
+      <c r="C306" s="1" t="inlineStr">
+        <is>
+          <t>06/5623344</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="inlineStr"/>
+      <c r="E306" s="1" t="inlineStr"/>
+      <c r="F306" s="1" t="inlineStr"/>
+      <c r="G306" s="1" t="inlineStr"/>
+      <c r="H306" s="1" t="inlineStr"/>
+      <c r="I306" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J306" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O306" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q306" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (cuscusroma) | IG: trovato (cuscusroma)</t>
-        </is>
-      </c>
-      <c r="R306" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
+      <c r="K306" s="1" t="inlineStr"/>
+      <c r="L306" s="1" t="inlineStr"/>
+      <c r="M306" s="1" t="inlineStr"/>
+      <c r="N306" s="1" t="inlineStr"/>
+      <c r="O306" s="1" t="inlineStr"/>
+      <c r="P306" s="1" t="inlineStr"/>
+      <c r="Q306" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R306" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>Dondolo</t>
+          <t>Slow</t>
         </is>
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>Via di Monte Sacro, 23</t>
-        </is>
-      </c>
-      <c r="C307" s="1" t="inlineStr">
-        <is>
-          <t>06/45752197</t>
-        </is>
-      </c>
+          <t>Corso Vittorio Emanuele II, 73</t>
+        </is>
+      </c>
+      <c r="C307" s="1" t="inlineStr"/>
       <c r="D307" s="1" t="inlineStr"/>
       <c r="E307" s="1" t="inlineStr"/>
       <c r="F307" s="1" t="inlineStr"/>
@@ -19275,263 +19327,213 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Drogherie del Mare</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Via Savoia, 38/42</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>333/2256285</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>www.drogheriedelmare.it</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>Drogherie-del-Mare</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>drogheriedelmare_</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>Bottega Popolare</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="inlineStr">
+        <is>
+          <t>Via Andrea Doria, 41 Mercato Trionfale Box 113</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>334/3351068</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="inlineStr"/>
+      <c r="E308" s="1" t="inlineStr"/>
+      <c r="F308" s="1" t="inlineStr"/>
+      <c r="G308" s="1" t="inlineStr"/>
+      <c r="H308" s="1" t="inlineStr"/>
+      <c r="I308" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J308" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O308" t="inlineStr">
+      <c r="K308" s="1" t="inlineStr"/>
+      <c r="L308" s="1" t="inlineStr"/>
+      <c r="M308" s="1" t="inlineStr"/>
+      <c r="N308" s="1" t="inlineStr"/>
+      <c r="O308" s="1" t="inlineStr"/>
+      <c r="P308" s="1" t="inlineStr"/>
+      <c r="Q308" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R308" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>Cheebo</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="inlineStr">
+        <is>
+          <t>Via Aretusa, 6</t>
+        </is>
+      </c>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>351/7598556</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="inlineStr"/>
+      <c r="E309" s="1" t="inlineStr"/>
+      <c r="F309" s="1" t="inlineStr"/>
+      <c r="G309" s="1" t="inlineStr"/>
+      <c r="H309" s="1" t="inlineStr"/>
+      <c r="I309" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J309" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K309" s="1" t="inlineStr"/>
+      <c r="L309" s="1" t="inlineStr"/>
+      <c r="M309" s="1" t="inlineStr"/>
+      <c r="N309" s="1" t="inlineStr"/>
+      <c r="O309" s="1" t="inlineStr"/>
+      <c r="P309" s="1" t="inlineStr"/>
+      <c r="Q309" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R309" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>Dondolo</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="inlineStr">
+        <is>
+          <t>Via di Monte Sacro, 23</t>
+        </is>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>06/45752197</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="inlineStr"/>
+      <c r="E310" s="1" t="inlineStr"/>
+      <c r="F310" s="1" t="inlineStr"/>
+      <c r="G310" s="1" t="inlineStr"/>
+      <c r="H310" s="1" t="inlineStr"/>
+      <c r="I310" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J310" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K310" s="1" t="inlineStr"/>
+      <c r="L310" s="1" t="inlineStr"/>
+      <c r="M310" s="1" t="inlineStr"/>
+      <c r="N310" s="1" t="inlineStr"/>
+      <c r="O310" s="1" t="inlineStr"/>
+      <c r="P310" s="1" t="inlineStr"/>
+      <c r="Q310" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R310" s="1" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>La Differenza</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Largo Magna Grecia, 4</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>06/70496477</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>ladifferenzaroma</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>ladifferenza.roma</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q308" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Drogherie-del-Mare) | IG: trovato (drogheriedelmare_)</t>
-        </is>
-      </c>
-      <c r="R308" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Il Maritozzo Rosso</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Via Pietro Cavallini, 25</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>06/90543525</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>www.ilmaritozzorosso.com</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>Il-Maritozzo-Rosso</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>il_maritozzo_rosso</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O309" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q309" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (Il-Maritozzo-Rosso) | IG: trovato (il_maritozzo_rosso)</t>
-        </is>
-      </c>
-      <c r="R309" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Jiamo Lab</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Via Bergamo, 15</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>388/8348616</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>JiaMopaninocroccante</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>jiamolab</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O310" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q310" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (JiaMopaninocroccante) | IG: trovato (jiamolab)</t>
-        </is>
-      </c>
-      <c r="R310" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="1" t="inlineStr">
-        <is>
-          <t>La Differenza</t>
-        </is>
-      </c>
-      <c r="B311" s="1" t="inlineStr">
-        <is>
-          <t>Largo Magna Grecia, 4</t>
-        </is>
-      </c>
-      <c r="C311" s="1" t="inlineStr">
-        <is>
-          <t>06/70496477</t>
-        </is>
-      </c>
-      <c r="D311" s="1" t="inlineStr"/>
-      <c r="E311" s="1" t="inlineStr">
-        <is>
-          <t>ladifferenzaroma</t>
-        </is>
-      </c>
-      <c r="F311" s="1" t="inlineStr">
-        <is>
-          <t>ladifferenza.roma</t>
-        </is>
-      </c>
-      <c r="G311" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H311" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I311" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J311" s="1" t="inlineStr"/>
-      <c r="K311" s="1" t="inlineStr"/>
-      <c r="L311" s="1" t="inlineStr"/>
-      <c r="M311" s="1" t="inlineStr"/>
-      <c r="N311" s="1" t="inlineStr"/>
-      <c r="O311" s="1" t="inlineStr"/>
-      <c r="P311" s="1" t="inlineStr"/>
-      <c r="Q311" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R311" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ladifferenzaroma) | IG: trovato (ladifferenza.roma)</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
@@ -19561,7 +19563,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J312" s="1" t="inlineStr"/>
+      <c r="J312" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K312" s="1" t="inlineStr"/>
       <c r="L312" s="1" t="inlineStr"/>
       <c r="M312" s="1" t="inlineStr"/>
@@ -19570,500 +19576,518 @@
       <c r="P312" s="1" t="inlineStr"/>
       <c r="Q312" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="inlineStr">
+      <c r="A313" t="inlineStr">
         <is>
           <t>Mordi &amp; Vai</t>
         </is>
       </c>
-      <c r="B313" s="1" t="inlineStr">
+      <c r="B313" t="inlineStr">
         <is>
           <t>Via Beniamino Franklin, 12/E</t>
         </is>
       </c>
-      <c r="C313" s="1" t="inlineStr">
+      <c r="C313" t="inlineStr">
         <is>
           <t>347/6632731</t>
         </is>
       </c>
-      <c r="D313" s="1" t="inlineStr"/>
-      <c r="E313" s="1" t="inlineStr">
+      <c r="E313" t="inlineStr">
         <is>
           <t>mordievai</t>
         </is>
       </c>
-      <c r="F313" s="1" t="inlineStr"/>
-      <c r="G313" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H313" s="1" t="inlineStr"/>
-      <c r="I313" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J313" s="1" t="inlineStr"/>
-      <c r="K313" s="1" t="inlineStr"/>
-      <c r="L313" s="1" t="inlineStr"/>
-      <c r="M313" s="1" t="inlineStr"/>
-      <c r="N313" s="1" t="inlineStr"/>
-      <c r="O313" s="1" t="inlineStr"/>
-      <c r="P313" s="1" t="inlineStr"/>
-      <c r="Q313" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R313" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (mordievai) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="inlineStr">
+      <c r="A314" t="inlineStr">
         <is>
           <t>Mordi Roma</t>
         </is>
       </c>
-      <c r="B314" s="1" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>Piazza Alessandria c/o Mercato Nomentano - box A2</t>
         </is>
       </c>
-      <c r="C314" s="1" t="inlineStr">
+      <c r="C314" t="inlineStr">
         <is>
           <t>334/7301833</t>
         </is>
       </c>
-      <c r="D314" s="1" t="inlineStr">
+      <c r="D314" t="inlineStr">
         <is>
           <t>www.mordiroma.it</t>
         </is>
       </c>
-      <c r="E314" s="1" t="inlineStr">
+      <c r="E314" t="inlineStr">
         <is>
           <t>mordiroma2024</t>
         </is>
       </c>
-      <c r="F314" s="1" t="inlineStr">
+      <c r="F314" t="inlineStr">
         <is>
           <t>mordi.roma</t>
         </is>
       </c>
-      <c r="G314" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H314" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I314" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J314" s="1" t="inlineStr"/>
-      <c r="K314" s="1" t="inlineStr"/>
-      <c r="L314" s="1" t="inlineStr"/>
-      <c r="M314" s="1" t="inlineStr"/>
-      <c r="N314" s="1" t="inlineStr"/>
-      <c r="O314" s="1" t="inlineStr"/>
-      <c r="P314" s="1" t="inlineStr"/>
-      <c r="Q314" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R314" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (mordiroma2024) | IG: trovato (mordi.roma)</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="inlineStr">
+      <c r="A315" t="inlineStr">
         <is>
           <t>Radici - pizzicheria salentina</t>
         </is>
       </c>
-      <c r="B315" s="1" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>Via Emanuele Filiberto, 38</t>
         </is>
       </c>
-      <c r="C315" s="1" t="inlineStr">
+      <c r="C315" t="inlineStr">
         <is>
           <t>06/89021483</t>
         </is>
       </c>
-      <c r="D315" s="1" t="inlineStr">
+      <c r="D315" t="inlineStr">
         <is>
           <t>www.pizzicheriasalentina.it</t>
         </is>
       </c>
-      <c r="E315" s="1" t="inlineStr">
+      <c r="E315" t="inlineStr">
         <is>
           <t>PizzicheriaSalentina</t>
         </is>
       </c>
-      <c r="F315" s="1" t="inlineStr">
+      <c r="F315" t="inlineStr">
         <is>
           <t>RadiciRoma</t>
         </is>
       </c>
-      <c r="G315" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H315" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I315" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J315" s="1" t="inlineStr"/>
-      <c r="K315" s="1" t="inlineStr"/>
-      <c r="L315" s="1" t="inlineStr"/>
-      <c r="M315" s="1" t="inlineStr"/>
-      <c r="N315" s="1" t="inlineStr"/>
-      <c r="O315" s="1" t="inlineStr"/>
-      <c r="P315" s="1" t="inlineStr"/>
-      <c r="Q315" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R315" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (PizzicheriaSalentina) | IG: trovato (RadiciRoma)</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="inlineStr">
+      <c r="A316" t="inlineStr">
         <is>
           <t>Sicché - Roba toscana</t>
         </is>
       </c>
-      <c r="B316" s="1" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>Via Beniamino Franklin, 12/C</t>
         </is>
       </c>
-      <c r="C316" s="1" t="inlineStr">
+      <c r="C316" t="inlineStr">
         <is>
           <t>333/4327944</t>
         </is>
       </c>
-      <c r="D316" s="1" t="inlineStr"/>
-      <c r="E316" s="1" t="inlineStr"/>
-      <c r="F316" s="1" t="inlineStr">
+      <c r="F316" t="inlineStr">
         <is>
           <t>sicche_robatoscana</t>
         </is>
       </c>
-      <c r="G316" s="1" t="inlineStr"/>
-      <c r="H316" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I316" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J316" s="1" t="inlineStr"/>
-      <c r="K316" s="1" t="inlineStr"/>
-      <c r="L316" s="1" t="inlineStr"/>
-      <c r="M316" s="1" t="inlineStr"/>
-      <c r="N316" s="1" t="inlineStr"/>
-      <c r="O316" s="1" t="inlineStr"/>
-      <c r="P316" s="1" t="inlineStr"/>
-      <c r="Q316" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R316" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (sicche_robatoscana)</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="inlineStr">
+      <c r="A317" t="inlineStr">
         <is>
           <t>Tulipane</t>
         </is>
       </c>
-      <c r="B317" s="1" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>Via del Pavone, 28</t>
         </is>
       </c>
-      <c r="C317" s="1" t="inlineStr">
+      <c r="C317" t="inlineStr">
         <is>
           <t>06/01903840</t>
         </is>
       </c>
-      <c r="D317" s="1" t="inlineStr">
+      <c r="D317" t="inlineStr">
         <is>
           <t>www.tulipane.it</t>
         </is>
       </c>
-      <c r="E317" s="1" t="inlineStr">
+      <c r="E317" t="inlineStr">
         <is>
           <t>tulipane.roma</t>
         </is>
       </c>
-      <c r="F317" s="1" t="inlineStr">
+      <c r="F317" t="inlineStr">
         <is>
           <t>tulipane.roma</t>
         </is>
       </c>
-      <c r="G317" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H317" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I317" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J317" s="1" t="inlineStr"/>
-      <c r="K317" s="1" t="inlineStr"/>
-      <c r="L317" s="1" t="inlineStr"/>
-      <c r="M317" s="1" t="inlineStr"/>
-      <c r="N317" s="1" t="inlineStr"/>
-      <c r="O317" s="1" t="inlineStr"/>
-      <c r="P317" s="1" t="inlineStr"/>
-      <c r="Q317" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R317" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (tulipane.roma) | IG: trovato (tulipane.roma)</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="inlineStr">
+      <c r="A318" t="inlineStr">
         <is>
           <t>Babingtons</t>
         </is>
       </c>
-      <c r="B318" s="1" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>Piazza di Spagna, 23</t>
         </is>
       </c>
-      <c r="C318" s="1" t="inlineStr">
+      <c r="C318" t="inlineStr">
         <is>
           <t>06/6786027</t>
         </is>
       </c>
-      <c r="D318" s="1" t="inlineStr">
+      <c r="D318" t="inlineStr">
         <is>
           <t>www.babingtons.com</t>
         </is>
       </c>
-      <c r="E318" s="1" t="inlineStr">
+      <c r="E318" t="inlineStr">
         <is>
           <t>babingtonstearoom</t>
         </is>
       </c>
-      <c r="F318" s="1" t="inlineStr">
+      <c r="F318" t="inlineStr">
         <is>
           <t>babingtonstearoom</t>
         </is>
       </c>
-      <c r="G318" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H318" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I318" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J318" s="1" t="inlineStr"/>
-      <c r="K318" s="1" t="inlineStr"/>
-      <c r="L318" s="1" t="inlineStr"/>
-      <c r="M318" s="1" t="inlineStr"/>
-      <c r="N318" s="1" t="inlineStr"/>
-      <c r="O318" s="1" t="inlineStr"/>
-      <c r="P318" s="1" t="inlineStr"/>
-      <c r="Q318" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R318" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (babingtonstearoom) | IG: trovato (babingtonstearoom)</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="inlineStr">
+      <c r="A319" t="inlineStr">
         <is>
           <t>Caffè Doria</t>
         </is>
       </c>
-      <c r="B319" s="1" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>Galleria Doria Pamphilj, Via della Gatta, 1</t>
         </is>
       </c>
-      <c r="C319" s="1" t="inlineStr">
+      <c r="C319" t="inlineStr">
         <is>
           <t>06/6793805</t>
         </is>
       </c>
-      <c r="D319" s="1" t="inlineStr">
+      <c r="D319" t="inlineStr">
         <is>
           <t>www.caffedoria.it</t>
         </is>
       </c>
-      <c r="E319" s="1" t="inlineStr">
+      <c r="E319" t="inlineStr">
         <is>
           <t>caffedoriaroma</t>
         </is>
       </c>
-      <c r="F319" s="1" t="inlineStr">
+      <c r="F319" t="inlineStr">
         <is>
           <t>caffedoria</t>
         </is>
       </c>
-      <c r="G319" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H319" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I319" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J319" s="1" t="inlineStr"/>
-      <c r="K319" s="1" t="inlineStr"/>
-      <c r="L319" s="1" t="inlineStr"/>
-      <c r="M319" s="1" t="inlineStr"/>
-      <c r="N319" s="1" t="inlineStr"/>
-      <c r="O319" s="1" t="inlineStr"/>
-      <c r="P319" s="1" t="inlineStr"/>
-      <c r="Q319" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R319" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (caffedoriaroma) | IG: trovato (caffedoria)</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="inlineStr">
+      <c r="A320" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
       </c>
-      <c r="B320" s="1" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>Via Vercelli, 12/14</t>
         </is>
       </c>
-      <c r="C320" s="1" t="inlineStr">
+      <c r="C320" t="inlineStr">
         <is>
           <t>06/25399727</t>
         </is>
       </c>
-      <c r="D320" s="1" t="inlineStr">
+      <c r="D320" t="inlineStr">
         <is>
           <t>www.charlotteroma.it</t>
         </is>
       </c>
-      <c r="E320" s="1" t="inlineStr">
+      <c r="E320" t="inlineStr">
         <is>
           <t>profile.php?id=100063718505068</t>
         </is>
       </c>
-      <c r="F320" s="1" t="inlineStr">
+      <c r="F320" t="inlineStr">
         <is>
           <t>charlotte_pasticceria</t>
         </is>
       </c>
-      <c r="G320" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H320" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I320" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J320" s="1" t="inlineStr"/>
-      <c r="K320" s="1" t="inlineStr"/>
-      <c r="L320" s="1" t="inlineStr"/>
-      <c r="M320" s="1" t="inlineStr"/>
-      <c r="N320" s="1" t="inlineStr"/>
-      <c r="O320" s="1" t="inlineStr"/>
-      <c r="P320" s="1" t="inlineStr"/>
-      <c r="Q320" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R320" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=100063718505068) | IG: trovato (charlotte_pasticceria)</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -18328,432 +18328,568 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B287" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C287" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D287" s="1" t="inlineStr"/>
-      <c r="E287" s="1" t="inlineStr"/>
-      <c r="F287" s="1" t="inlineStr"/>
-      <c r="G287" s="1" t="inlineStr"/>
-      <c r="H287" s="1" t="inlineStr"/>
-      <c r="I287" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J287" s="1" t="inlineStr">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>La Differenza</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Largo Magna Grecia, 4</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>06/70496477</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>ladifferenzaroma</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>ladifferenza.roma</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K287" s="1" t="inlineStr"/>
-      <c r="L287" s="1" t="inlineStr"/>
-      <c r="M287" s="1" t="inlineStr"/>
-      <c r="N287" s="1" t="inlineStr"/>
-      <c r="O287" s="1" t="inlineStr"/>
-      <c r="P287" s="1" t="inlineStr"/>
-      <c r="Q287" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R287" s="1" t="inlineStr">
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (ladifferenzaroma) | IG: trovato (ladifferenza.roma)</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="inlineStr">
-        <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
-        </is>
-      </c>
-      <c r="B288" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Erbe, 16</t>
-        </is>
-      </c>
-      <c r="C288" s="1" t="inlineStr">
-        <is>
-          <t>348/7277746</t>
-        </is>
-      </c>
-      <c r="D288" s="1" t="inlineStr"/>
-      <c r="E288" s="1" t="inlineStr"/>
-      <c r="F288" s="1" t="inlineStr"/>
-      <c r="G288" s="1" t="inlineStr"/>
-      <c r="H288" s="1" t="inlineStr"/>
-      <c r="I288" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J288" s="1" t="inlineStr">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Mordi &amp; Vai</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Via Beniamino Franklin, 12/E</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>347/6632731</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>mordievai</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K288" s="1" t="inlineStr"/>
-      <c r="L288" s="1" t="inlineStr"/>
-      <c r="M288" s="1" t="inlineStr"/>
-      <c r="N288" s="1" t="inlineStr"/>
-      <c r="O288" s="1" t="inlineStr"/>
-      <c r="P288" s="1" t="inlineStr"/>
-      <c r="Q288" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R288" s="1" t="inlineStr">
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (mordievai) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="inlineStr">
-        <is>
-          <t>Osteria del Vicolo Fatato</t>
-        </is>
-      </c>
-      <c r="B289" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Forno Fatato, 11</t>
-        </is>
-      </c>
-      <c r="C289" s="1" t="inlineStr">
-        <is>
-          <t>0775/503035</t>
-        </is>
-      </c>
-      <c r="D289" s="1" t="inlineStr"/>
-      <c r="E289" s="1" t="inlineStr"/>
-      <c r="F289" s="1" t="inlineStr"/>
-      <c r="G289" s="1" t="inlineStr"/>
-      <c r="H289" s="1" t="inlineStr"/>
-      <c r="I289" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J289" s="1" t="inlineStr">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Mordi Roma</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Piazza Alessandria c/o Mercato Nomentano - box A2</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>334/7301833</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>www.mordiroma.it</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>mordiroma2024</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>mordi.roma</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K289" s="1" t="inlineStr"/>
-      <c r="L289" s="1" t="inlineStr"/>
-      <c r="M289" s="1" t="inlineStr"/>
-      <c r="N289" s="1" t="inlineStr"/>
-      <c r="O289" s="1" t="inlineStr"/>
-      <c r="P289" s="1" t="inlineStr"/>
-      <c r="Q289" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R289" s="1" t="inlineStr">
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (mordiroma2024) | IG: trovato (mordi.roma)</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="inlineStr">
-        <is>
-          <t>Poldo e Gianna</t>
-        </is>
-      </c>
-      <c r="B290" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Rosini, 6</t>
-        </is>
-      </c>
-      <c r="C290" s="1" t="inlineStr">
-        <is>
-          <t>06/6893499</t>
-        </is>
-      </c>
-      <c r="D290" s="1" t="inlineStr"/>
-      <c r="E290" s="1" t="inlineStr"/>
-      <c r="F290" s="1" t="inlineStr"/>
-      <c r="G290" s="1" t="inlineStr"/>
-      <c r="H290" s="1" t="inlineStr"/>
-      <c r="I290" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J290" s="1" t="inlineStr">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Radici - pizzicheria salentina</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Via Emanuele Filiberto, 38</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>06/89021483</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>www.pizzicheriasalentina.it</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>PizzicheriaSalentina</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>RadiciRoma</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K290" s="1" t="inlineStr"/>
-      <c r="L290" s="1" t="inlineStr"/>
-      <c r="M290" s="1" t="inlineStr"/>
-      <c r="N290" s="1" t="inlineStr"/>
-      <c r="O290" s="1" t="inlineStr"/>
-      <c r="P290" s="1" t="inlineStr"/>
-      <c r="Q290" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R290" s="1" t="inlineStr">
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (PizzicheriaSalentina) | IG: trovato (RadiciRoma)</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria A Casa Di Rita</t>
-        </is>
-      </c>
-      <c r="B291" s="1" t="inlineStr">
-        <is>
-          <t>Via delle Ciliegie, 145</t>
-        </is>
-      </c>
-      <c r="C291" s="1" t="inlineStr">
-        <is>
-          <t>338/9860960</t>
-        </is>
-      </c>
-      <c r="D291" s="1" t="inlineStr"/>
-      <c r="E291" s="1" t="inlineStr"/>
-      <c r="F291" s="1" t="inlineStr"/>
-      <c r="G291" s="1" t="inlineStr"/>
-      <c r="H291" s="1" t="inlineStr"/>
-      <c r="I291" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J291" s="1" t="inlineStr">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Sicché - Roba toscana</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Via Beniamino Franklin, 12/C</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>333/4327944</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>sicche_robatoscana</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K291" s="1" t="inlineStr"/>
-      <c r="L291" s="1" t="inlineStr"/>
-      <c r="M291" s="1" t="inlineStr"/>
-      <c r="N291" s="1" t="inlineStr"/>
-      <c r="O291" s="1" t="inlineStr"/>
-      <c r="P291" s="1" t="inlineStr"/>
-      <c r="Q291" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R291" s="1" t="inlineStr">
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: trovato (sicche_robatoscana)</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="inlineStr">
-        <is>
-          <t>Ie Koji Japanese Izakaya</t>
-        </is>
-      </c>
-      <c r="B292" s="1" t="inlineStr">
-        <is>
-          <t>Via Marcantonio Bragadin, 13</t>
-        </is>
-      </c>
-      <c r="C292" s="1" t="inlineStr">
-        <is>
-          <t>348/4302368 - 06/69459860</t>
-        </is>
-      </c>
-      <c r="D292" s="1" t="inlineStr"/>
-      <c r="E292" s="1" t="inlineStr"/>
-      <c r="F292" s="1" t="inlineStr"/>
-      <c r="G292" s="1" t="inlineStr"/>
-      <c r="H292" s="1" t="inlineStr"/>
-      <c r="I292" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J292" s="1" t="inlineStr">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Tulipane</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Via del Pavone, 28</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>06/01903840</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>www.tulipane.it</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>tulipane.roma</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>tulipane.roma</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K292" s="1" t="inlineStr"/>
-      <c r="L292" s="1" t="inlineStr"/>
-      <c r="M292" s="1" t="inlineStr"/>
-      <c r="N292" s="1" t="inlineStr"/>
-      <c r="O292" s="1" t="inlineStr"/>
-      <c r="P292" s="1" t="inlineStr"/>
-      <c r="Q292" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R292" s="1" t="inlineStr">
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (tulipane.roma) | IG: trovato (tulipane.roma)</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B293" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C293" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D293" s="1" t="inlineStr"/>
-      <c r="E293" s="1" t="inlineStr"/>
-      <c r="F293" s="1" t="inlineStr"/>
-      <c r="G293" s="1" t="inlineStr"/>
-      <c r="H293" s="1" t="inlineStr"/>
-      <c r="I293" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J293" s="1" t="inlineStr">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Babingtons</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Piazza di Spagna, 23</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>06/6786027</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>www.babingtons.com</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>babingtonstearoom</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>babingtonstearoom</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K293" s="1" t="inlineStr"/>
-      <c r="L293" s="1" t="inlineStr"/>
-      <c r="M293" s="1" t="inlineStr"/>
-      <c r="N293" s="1" t="inlineStr"/>
-      <c r="O293" s="1" t="inlineStr"/>
-      <c r="P293" s="1" t="inlineStr"/>
-      <c r="Q293" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R293" s="1" t="inlineStr">
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (babingtonstearoom) | IG: trovato (babingtonstearoom)</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="inlineStr">
-        <is>
-          <t>Nomisan</t>
-        </is>
-      </c>
-      <c r="B294" s="1" t="inlineStr">
-        <is>
-          <t>Viale Gianluigi Bonelli, 237</t>
-        </is>
-      </c>
-      <c r="C294" s="1" t="inlineStr">
-        <is>
-          <t>342/8036080</t>
-        </is>
-      </c>
-      <c r="D294" s="1" t="inlineStr"/>
-      <c r="E294" s="1" t="inlineStr"/>
-      <c r="F294" s="1" t="inlineStr"/>
-      <c r="G294" s="1" t="inlineStr"/>
-      <c r="H294" s="1" t="inlineStr"/>
-      <c r="I294" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J294" s="1" t="inlineStr">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Caffè Doria</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Galleria Doria Pamphilj, Via della Gatta, 1</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>06/6793805</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>www.caffedoria.it</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>caffedoriaroma</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>caffedoria</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K294" s="1" t="inlineStr"/>
-      <c r="L294" s="1" t="inlineStr"/>
-      <c r="M294" s="1" t="inlineStr"/>
-      <c r="N294" s="1" t="inlineStr"/>
-      <c r="O294" s="1" t="inlineStr"/>
-      <c r="P294" s="1" t="inlineStr"/>
-      <c r="Q294" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R294" s="1" t="inlineStr">
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (caffedoriaroma) | IG: trovato (caffedoria)</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="inlineStr">
-        <is>
-          <t>Al Setaccio</t>
-        </is>
-      </c>
-      <c r="B295" s="1" t="inlineStr">
-        <is>
-          <t>Via di Mezzocammino, 193</t>
-        </is>
-      </c>
-      <c r="C295" s="1" t="inlineStr">
-        <is>
-          <t>06/52372056</t>
-        </is>
-      </c>
-      <c r="D295" s="1" t="inlineStr"/>
-      <c r="E295" s="1" t="inlineStr"/>
-      <c r="F295" s="1" t="inlineStr"/>
-      <c r="G295" s="1" t="inlineStr"/>
-      <c r="H295" s="1" t="inlineStr"/>
-      <c r="I295" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J295" s="1" t="inlineStr">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Via Vercelli, 12/14</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>06/25399727</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>www.charlotteroma.it</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>profile.php?id=100063718505068</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>charlotte_pasticceria</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K295" s="1" t="inlineStr"/>
-      <c r="L295" s="1" t="inlineStr"/>
-      <c r="M295" s="1" t="inlineStr"/>
-      <c r="N295" s="1" t="inlineStr"/>
-      <c r="O295" s="1" t="inlineStr"/>
-      <c r="P295" s="1" t="inlineStr"/>
-      <c r="Q295" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R295" s="1" t="inlineStr">
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=100063718505068) | IG: trovato (charlotte_pasticceria)</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
@@ -18762,17 +18898,17 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>Angelo Pezzella</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>Via Appia Nuova, 1095</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
         <is>
-          <t>06/7188560</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D296" s="1" t="inlineStr"/>
@@ -18803,24 +18939,24 @@
       </c>
       <c r="R296" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>Clementina</t>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
         </is>
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>Via della Torre Clementina, 158</t>
+          <t>Piazza delle Erbe, 16</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t>328/8181651</t>
+          <t>348/7277746</t>
         </is>
       </c>
       <c r="D297" s="1" t="inlineStr"/>
@@ -18851,24 +18987,24 @@
       </c>
       <c r="R297" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>Da Antonio</t>
+          <t>Osteria del Vicolo Fatato</t>
         </is>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t>Via Mario Lizzani, 21</t>
+          <t>Vicolo Forno Fatato, 11</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
         <is>
-          <t>391/7475549</t>
+          <t>0775/503035</t>
         </is>
       </c>
       <c r="D298" s="1" t="inlineStr"/>
@@ -18899,24 +19035,24 @@
       </c>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>Diego Vitagliano</t>
+          <t>Poldo e Gianna</t>
         </is>
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>Via Chiana, 80</t>
+          <t>Vicolo Rosini, 6</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
         <is>
-          <t>06/72276443</t>
+          <t>06/6893499</t>
         </is>
       </c>
       <c r="D299" s="1" t="inlineStr"/>
@@ -18947,24 +19083,24 @@
       </c>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>GioMà</t>
+          <t>Trattoria A Casa Di Rita</t>
         </is>
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>Via Calpurnio Fiamma, 40/44</t>
+          <t>Via delle Ciliegie, 145</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t>06/7674717</t>
+          <t>338/9860960</t>
         </is>
       </c>
       <c r="D300" s="1" t="inlineStr"/>
@@ -18995,24 +19131,24 @@
       </c>
       <c r="R300" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>Pupillo Pura Pizza</t>
+          <t>Ie Koji Japanese Izakaya</t>
         </is>
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>Via Giacomo Matteotti, 29</t>
+          <t>Via Marcantonio Bragadin, 13</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t>339/4143148</t>
+          <t>348/4302368 - 06/69459860</t>
         </is>
       </c>
       <c r="D301" s="1" t="inlineStr"/>
@@ -19043,24 +19179,24 @@
       </c>
       <c r="R301" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>Santa Romana</t>
+          <t>Mrgda Ristorante</t>
         </is>
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>Piazza Certaldo, 12</t>
+          <t>Via Prenestina, 182</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
         <is>
-          <t>06/69317674</t>
+          <t>329/933355</t>
         </is>
       </c>
       <c r="D302" s="1" t="inlineStr"/>
@@ -19091,24 +19227,24 @@
       </c>
       <c r="R302" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>Seu Pizza Illuminati</t>
+          <t>Nomisan</t>
         </is>
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>Via Angelo Bargoni, 10/18</t>
+          <t>Viale Gianluigi Bonelli, 237</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t>06/5883384</t>
+          <t>342/8036080</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr"/>
@@ -19139,24 +19275,24 @@
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>Forno Ritorno</t>
+          <t>Al Setaccio</t>
         </is>
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>Via Amerigo Vespucci, 20</t>
+          <t>Via di Mezzocammino, 193</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t>392/7768427</t>
+          <t>06/52372056</t>
         </is>
       </c>
       <c r="D304" s="1" t="inlineStr"/>
@@ -19187,24 +19323,24 @@
       </c>
       <c r="R304" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>Il tuo fornaio</t>
+          <t>Angelo Pezzella</t>
         </is>
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>Via Francesco Sapori, 35</t>
+          <t>Via Appia Nuova, 1095</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t>06/5017873</t>
+          <t>06/7188560</t>
         </is>
       </c>
       <c r="D305" s="1" t="inlineStr"/>
@@ -19235,24 +19371,24 @@
       </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>Krapfen Paglia</t>
+          <t>Clementina</t>
         </is>
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>Piazza Anco Marzio, 18/19</t>
+          <t>Via della Torre Clementina, 158</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t>06/5623344</t>
+          <t>328/8181651</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr"/>
@@ -19283,22 +19419,26 @@
       </c>
       <c r="R306" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>Slow</t>
+          <t>Da Antonio</t>
         </is>
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>Corso Vittorio Emanuele II, 73</t>
-        </is>
-      </c>
-      <c r="C307" s="1" t="inlineStr"/>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C307" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
       <c r="D307" s="1" t="inlineStr"/>
       <c r="E307" s="1" t="inlineStr"/>
       <c r="F307" s="1" t="inlineStr"/>
@@ -19327,24 +19467,24 @@
       </c>
       <c r="R307" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>Bottega Popolare</t>
+          <t>Diego Vitagliano</t>
         </is>
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>Via Andrea Doria, 41 Mercato Trionfale Box 113</t>
+          <t>Via Chiana, 80</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t>334/3351068</t>
+          <t>06/72276443</t>
         </is>
       </c>
       <c r="D308" s="1" t="inlineStr"/>
@@ -19375,24 +19515,24 @@
       </c>
       <c r="R308" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>Cheebo</t>
+          <t>GioMà</t>
         </is>
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>Via Aretusa, 6</t>
+          <t>Via Calpurnio Fiamma, 40/44</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t>351/7598556</t>
+          <t>06/7674717</t>
         </is>
       </c>
       <c r="D309" s="1" t="inlineStr"/>
@@ -19423,24 +19563,24 @@
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>Dondolo</t>
+          <t>Pupillo Pura Pizza</t>
         </is>
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t>Via di Monte Sacro, 23</t>
+          <t>Via Giacomo Matteotti, 29</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
         <is>
-          <t>06/45752197</t>
+          <t>339/4143148</t>
         </is>
       </c>
       <c r="D310" s="1" t="inlineStr"/>
@@ -19471,86 +19611,72 @@
       </c>
       <c r="R310" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>La Differenza</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Largo Magna Grecia, 4</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>06/70496477</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>ladifferenzaroma</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>ladifferenza.roma</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>Santa Romana</t>
+        </is>
+      </c>
+      <c r="B311" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Certaldo, 12</t>
+        </is>
+      </c>
+      <c r="C311" s="1" t="inlineStr">
+        <is>
+          <t>06/69317674</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="inlineStr"/>
+      <c r="E311" s="1" t="inlineStr"/>
+      <c r="F311" s="1" t="inlineStr"/>
+      <c r="G311" s="1" t="inlineStr"/>
+      <c r="H311" s="1" t="inlineStr"/>
+      <c r="I311" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J311" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O311" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q311" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (ladifferenzaroma) | IG: trovato (ladifferenza.roma)</t>
-        </is>
-      </c>
-      <c r="R311" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
+      <c r="K311" s="1" t="inlineStr"/>
+      <c r="L311" s="1" t="inlineStr"/>
+      <c r="M311" s="1" t="inlineStr"/>
+      <c r="N311" s="1" t="inlineStr"/>
+      <c r="O311" s="1" t="inlineStr"/>
+      <c r="P311" s="1" t="inlineStr"/>
+      <c r="Q311" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R311" s="1" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>MAE - Slow Brunchers</t>
+          <t>Seu Pizza Illuminati</t>
         </is>
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>Via della Giuliana, 33</t>
+          <t>Via Angelo Bargoni, 10/18</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
-          <t>06/98874558</t>
+          <t>06/5883384</t>
         </is>
       </c>
       <c r="D312" s="1" t="inlineStr"/>
@@ -19581,957 +19707,851 @@
       </c>
       <c r="R312" s="1" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Mordi &amp; Vai</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Via Beniamino Franklin, 12/E</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>347/6632731</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>mordievai</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J313" t="inlineStr">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>Forno Ritorno</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="inlineStr">
+        <is>
+          <t>Via Amerigo Vespucci, 20</t>
+        </is>
+      </c>
+      <c r="C313" s="1" t="inlineStr">
+        <is>
+          <t>392/7768427</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="inlineStr"/>
+      <c r="E313" s="1" t="inlineStr"/>
+      <c r="F313" s="1" t="inlineStr"/>
+      <c r="G313" s="1" t="inlineStr"/>
+      <c r="H313" s="1" t="inlineStr"/>
+      <c r="I313" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J313" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O313" t="inlineStr">
+      <c r="K313" s="1" t="inlineStr"/>
+      <c r="L313" s="1" t="inlineStr"/>
+      <c r="M313" s="1" t="inlineStr"/>
+      <c r="N313" s="1" t="inlineStr"/>
+      <c r="O313" s="1" t="inlineStr"/>
+      <c r="P313" s="1" t="inlineStr"/>
+      <c r="Q313" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R313" s="1" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>Il tuo fornaio</t>
+        </is>
+      </c>
+      <c r="B314" s="1" t="inlineStr">
+        <is>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C314" s="1" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
+      <c r="D314" s="1" t="inlineStr"/>
+      <c r="E314" s="1" t="inlineStr"/>
+      <c r="F314" s="1" t="inlineStr"/>
+      <c r="G314" s="1" t="inlineStr"/>
+      <c r="H314" s="1" t="inlineStr"/>
+      <c r="I314" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J314" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K314" s="1" t="inlineStr"/>
+      <c r="L314" s="1" t="inlineStr"/>
+      <c r="M314" s="1" t="inlineStr"/>
+      <c r="N314" s="1" t="inlineStr"/>
+      <c r="O314" s="1" t="inlineStr"/>
+      <c r="P314" s="1" t="inlineStr"/>
+      <c r="Q314" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R314" s="1" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>Krapfen Paglia</t>
+        </is>
+      </c>
+      <c r="B315" s="1" t="inlineStr">
+        <is>
+          <t>Piazza Anco Marzio, 18/19</t>
+        </is>
+      </c>
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>06/5623344</t>
+        </is>
+      </c>
+      <c r="D315" s="1" t="inlineStr"/>
+      <c r="E315" s="1" t="inlineStr"/>
+      <c r="F315" s="1" t="inlineStr"/>
+      <c r="G315" s="1" t="inlineStr"/>
+      <c r="H315" s="1" t="inlineStr"/>
+      <c r="I315" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J315" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K315" s="1" t="inlineStr"/>
+      <c r="L315" s="1" t="inlineStr"/>
+      <c r="M315" s="1" t="inlineStr"/>
+      <c r="N315" s="1" t="inlineStr"/>
+      <c r="O315" s="1" t="inlineStr"/>
+      <c r="P315" s="1" t="inlineStr"/>
+      <c r="Q315" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R315" s="1" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="B316" s="1" t="inlineStr">
+        <is>
+          <t>Corso Vittorio Emanuele II, 73</t>
+        </is>
+      </c>
+      <c r="C316" s="1" t="inlineStr"/>
+      <c r="D316" s="1" t="inlineStr"/>
+      <c r="E316" s="1" t="inlineStr"/>
+      <c r="F316" s="1" t="inlineStr"/>
+      <c r="G316" s="1" t="inlineStr"/>
+      <c r="H316" s="1" t="inlineStr"/>
+      <c r="I316" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J316" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K316" s="1" t="inlineStr"/>
+      <c r="L316" s="1" t="inlineStr"/>
+      <c r="M316" s="1" t="inlineStr"/>
+      <c r="N316" s="1" t="inlineStr"/>
+      <c r="O316" s="1" t="inlineStr"/>
+      <c r="P316" s="1" t="inlineStr"/>
+      <c r="Q316" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R316" s="1" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>Bottega Popolare</t>
+        </is>
+      </c>
+      <c r="B317" s="1" t="inlineStr">
+        <is>
+          <t>Via Andrea Doria, 41 Mercato Trionfale Box 113</t>
+        </is>
+      </c>
+      <c r="C317" s="1" t="inlineStr">
+        <is>
+          <t>334/3351068</t>
+        </is>
+      </c>
+      <c r="D317" s="1" t="inlineStr"/>
+      <c r="E317" s="1" t="inlineStr"/>
+      <c r="F317" s="1" t="inlineStr"/>
+      <c r="G317" s="1" t="inlineStr"/>
+      <c r="H317" s="1" t="inlineStr"/>
+      <c r="I317" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J317" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K317" s="1" t="inlineStr"/>
+      <c r="L317" s="1" t="inlineStr"/>
+      <c r="M317" s="1" t="inlineStr"/>
+      <c r="N317" s="1" t="inlineStr"/>
+      <c r="O317" s="1" t="inlineStr"/>
+      <c r="P317" s="1" t="inlineStr"/>
+      <c r="Q317" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R317" s="1" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>Cheebo</t>
+        </is>
+      </c>
+      <c r="B318" s="1" t="inlineStr">
+        <is>
+          <t>Via Aretusa, 6</t>
+        </is>
+      </c>
+      <c r="C318" s="1" t="inlineStr">
+        <is>
+          <t>351/7598556</t>
+        </is>
+      </c>
+      <c r="D318" s="1" t="inlineStr"/>
+      <c r="E318" s="1" t="inlineStr"/>
+      <c r="F318" s="1" t="inlineStr"/>
+      <c r="G318" s="1" t="inlineStr"/>
+      <c r="H318" s="1" t="inlineStr"/>
+      <c r="I318" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J318" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K318" s="1" t="inlineStr"/>
+      <c r="L318" s="1" t="inlineStr"/>
+      <c r="M318" s="1" t="inlineStr"/>
+      <c r="N318" s="1" t="inlineStr"/>
+      <c r="O318" s="1" t="inlineStr"/>
+      <c r="P318" s="1" t="inlineStr"/>
+      <c r="Q318" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R318" s="1" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>Dondolo</t>
+        </is>
+      </c>
+      <c r="B319" s="1" t="inlineStr">
+        <is>
+          <t>Via di Monte Sacro, 23</t>
+        </is>
+      </c>
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>06/45752197</t>
+        </is>
+      </c>
+      <c r="D319" s="1" t="inlineStr"/>
+      <c r="E319" s="1" t="inlineStr"/>
+      <c r="F319" s="1" t="inlineStr"/>
+      <c r="G319" s="1" t="inlineStr"/>
+      <c r="H319" s="1" t="inlineStr"/>
+      <c r="I319" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J319" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K319" s="1" t="inlineStr"/>
+      <c r="L319" s="1" t="inlineStr"/>
+      <c r="M319" s="1" t="inlineStr"/>
+      <c r="N319" s="1" t="inlineStr"/>
+      <c r="O319" s="1" t="inlineStr"/>
+      <c r="P319" s="1" t="inlineStr"/>
+      <c r="Q319" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R319" s="1" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>MAE - Slow Brunchers</t>
+        </is>
+      </c>
+      <c r="B320" s="1" t="inlineStr">
+        <is>
+          <t>Via della Giuliana, 33</t>
+        </is>
+      </c>
+      <c r="C320" s="1" t="inlineStr">
+        <is>
+          <t>06/98874558</t>
+        </is>
+      </c>
+      <c r="D320" s="1" t="inlineStr"/>
+      <c r="E320" s="1" t="inlineStr"/>
+      <c r="F320" s="1" t="inlineStr"/>
+      <c r="G320" s="1" t="inlineStr"/>
+      <c r="H320" s="1" t="inlineStr"/>
+      <c r="I320" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J320" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K320" s="1" t="inlineStr"/>
+      <c r="L320" s="1" t="inlineStr"/>
+      <c r="M320" s="1" t="inlineStr"/>
+      <c r="N320" s="1" t="inlineStr"/>
+      <c r="O320" s="1" t="inlineStr"/>
+      <c r="P320" s="1" t="inlineStr"/>
+      <c r="Q320" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R320" s="1" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Hotel De' Ricci</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Via della Barchetta, 14</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>06/6874775</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>www.hoteldericci.com</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>hoteldericci</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>hoteldericci</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q313" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (mordievai) | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R313" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>Mordi Roma</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Piazza Alessandria c/o Mercato Nomentano - box A2</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>334/7301833</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>www.mordiroma.it</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>mordiroma2024</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>mordi.roma</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J314" t="inlineStr">
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (hoteldericci) | IG: trovato (hoteldericci)</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Hotel Vilòn</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Via dell'Arancio, 68/69</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>06/878187</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>www.hotelvilon.com</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>hotelvilon</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>hotelvilon</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O314" t="inlineStr">
+      <c r="O322" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q314" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (mordiroma2024) | IG: trovato (mordi.roma)</t>
-        </is>
-      </c>
-      <c r="R314" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Radici - pizzicheria salentina</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Via Emanuele Filiberto, 38</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>06/89021483</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>www.pizzicheriasalentina.it</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>PizzicheriaSalentina</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>RadiciRoma</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr">
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (hotelvilon) | IG: trovato (hotelvilon)</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Libera</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Via Luigi Tosti, 54</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>06/90537554</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>LiberaPasticceriaCaffetteria</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>liberapasticceriacaffetteria</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O315" t="inlineStr">
+      <c r="O323" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q315" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (PizzicheriaSalentina) | IG: trovato (RadiciRoma)</t>
-        </is>
-      </c>
-      <c r="R315" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Sicché - Roba toscana</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Via Beniamino Franklin, 12/C</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>333/4327944</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>sicche_robatoscana</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr">
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (LiberaPasticceriaCaffetteria) | IG: trovato (liberapasticceriacaffetteria)</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Madeleine</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Via Monte Santo, 64</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>06/3728537</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>www.madeleinerome.com</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>madeleineroma</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>madeleineroma</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O316" t="inlineStr">
+      <c r="O324" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q316" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: trovato (sicche_robatoscana)</t>
-        </is>
-      </c>
-      <c r="R316" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Tulipane</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Via del Pavone, 28</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>06/01903840</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>www.tulipane.it</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>tulipane.roma</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>tulipane.roma</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr">
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (madeleineroma) | IG: trovato (madeleineroma)</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Said dal 1923</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Via Tiburtina, 135</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>06/4469204</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>www.said.it</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>said1923</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>saiddal1923</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O317" t="inlineStr">
+      <c r="O325" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (tulipane.roma) | IG: trovato (tulipane.roma)</t>
-        </is>
-      </c>
-      <c r="R317" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Babingtons</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Piazza di Spagna, 23</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>06/6786027</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>www.babingtons.com</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>babingtonstearoom</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>babingtonstearoom</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (said1923) | IG: trovato (saiddal1923)</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Vicolo della Fontana, 28</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>06/86726388</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>www.shellroma.it</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>profile.php?id=61571778928939</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>shell_libreria_bistrot</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O318" t="inlineStr">
+      <c r="O326" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (babingtonstearoom) | IG: trovato (babingtonstearoom)</t>
-        </is>
-      </c>
-      <c r="R318" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Caffè Doria</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Galleria Doria Pamphilj, Via della Gatta, 1</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>06/6793805</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>www.caffedoria.it</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>caffedoriaroma</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>caffedoria</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=61571778928939) | IG: trovato (shell_libreria_bistrot)</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Velo Pasticceria</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Via del Corso, 63</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>06/45427861</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>www.velopasticceria.it</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>velopasticceria</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>velopasticceria</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O319" t="inlineStr">
+      <c r="O327" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q319" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (caffedoriaroma) | IG: trovato (caffedoria)</t>
-        </is>
-      </c>
-      <c r="R319" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Via Vercelli, 12/14</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>06/25399727</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>www.charlotteroma.it</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>profile.php?id=100063718505068</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>charlotte_pasticceria</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O320" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q320" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (profile.php?id=100063718505068) | IG: trovato (charlotte_pasticceria)</t>
-        </is>
-      </c>
-      <c r="R320" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="1" t="inlineStr">
-        <is>
-          <t>Hotel De' Ricci</t>
-        </is>
-      </c>
-      <c r="B321" s="1" t="inlineStr">
-        <is>
-          <t>Via della Barchetta, 14</t>
-        </is>
-      </c>
-      <c r="C321" s="1" t="inlineStr">
-        <is>
-          <t>06/6874775</t>
-        </is>
-      </c>
-      <c r="D321" s="1" t="inlineStr">
-        <is>
-          <t>www.hoteldericci.com</t>
-        </is>
-      </c>
-      <c r="E321" s="1" t="inlineStr">
-        <is>
-          <t>hoteldericci</t>
-        </is>
-      </c>
-      <c r="F321" s="1" t="inlineStr">
-        <is>
-          <t>hoteldericci</t>
-        </is>
-      </c>
-      <c r="G321" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H321" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I321" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J321" s="1" t="inlineStr"/>
-      <c r="K321" s="1" t="inlineStr"/>
-      <c r="L321" s="1" t="inlineStr"/>
-      <c r="M321" s="1" t="inlineStr"/>
-      <c r="N321" s="1" t="inlineStr"/>
-      <c r="O321" s="1" t="inlineStr"/>
-      <c r="P321" s="1" t="inlineStr"/>
-      <c r="Q321" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R321" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="1" t="inlineStr">
-        <is>
-          <t>Hotel Vilòn</t>
-        </is>
-      </c>
-      <c r="B322" s="1" t="inlineStr">
-        <is>
-          <t>Via dell'Arancio, 68/69</t>
-        </is>
-      </c>
-      <c r="C322" s="1" t="inlineStr">
-        <is>
-          <t>06/878187</t>
-        </is>
-      </c>
-      <c r="D322" s="1" t="inlineStr">
-        <is>
-          <t>www.hotelvilon.com</t>
-        </is>
-      </c>
-      <c r="E322" s="1" t="inlineStr">
-        <is>
-          <t>hotelvilon</t>
-        </is>
-      </c>
-      <c r="F322" s="1" t="inlineStr">
-        <is>
-          <t>hotelvilon</t>
-        </is>
-      </c>
-      <c r="G322" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H322" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I322" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J322" s="1" t="inlineStr"/>
-      <c r="K322" s="1" t="inlineStr"/>
-      <c r="L322" s="1" t="inlineStr"/>
-      <c r="M322" s="1" t="inlineStr"/>
-      <c r="N322" s="1" t="inlineStr"/>
-      <c r="O322" s="1" t="inlineStr"/>
-      <c r="P322" s="1" t="inlineStr"/>
-      <c r="Q322" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R322" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="1" t="inlineStr">
-        <is>
-          <t>Libera</t>
-        </is>
-      </c>
-      <c r="B323" s="1" t="inlineStr">
-        <is>
-          <t>Via Luigi Tosti, 54</t>
-        </is>
-      </c>
-      <c r="C323" s="1" t="inlineStr">
-        <is>
-          <t>06/90537554</t>
-        </is>
-      </c>
-      <c r="D323" s="1" t="inlineStr"/>
-      <c r="E323" s="1" t="inlineStr">
-        <is>
-          <t>LiberaPasticceriaCaffetteria</t>
-        </is>
-      </c>
-      <c r="F323" s="1" t="inlineStr">
-        <is>
-          <t>liberapasticceriacaffetteria</t>
-        </is>
-      </c>
-      <c r="G323" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H323" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I323" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J323" s="1" t="inlineStr"/>
-      <c r="K323" s="1" t="inlineStr"/>
-      <c r="L323" s="1" t="inlineStr"/>
-      <c r="M323" s="1" t="inlineStr"/>
-      <c r="N323" s="1" t="inlineStr"/>
-      <c r="O323" s="1" t="inlineStr"/>
-      <c r="P323" s="1" t="inlineStr"/>
-      <c r="Q323" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R323" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="1" t="inlineStr">
-        <is>
-          <t>Madeleine</t>
-        </is>
-      </c>
-      <c r="B324" s="1" t="inlineStr">
-        <is>
-          <t>Via Monte Santo, 64</t>
-        </is>
-      </c>
-      <c r="C324" s="1" t="inlineStr">
-        <is>
-          <t>06/3728537</t>
-        </is>
-      </c>
-      <c r="D324" s="1" t="inlineStr">
-        <is>
-          <t>www.madeleinerome.com</t>
-        </is>
-      </c>
-      <c r="E324" s="1" t="inlineStr">
-        <is>
-          <t>madeleineroma</t>
-        </is>
-      </c>
-      <c r="F324" s="1" t="inlineStr">
-        <is>
-          <t>madeleineroma</t>
-        </is>
-      </c>
-      <c r="G324" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H324" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I324" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J324" s="1" t="inlineStr"/>
-      <c r="K324" s="1" t="inlineStr"/>
-      <c r="L324" s="1" t="inlineStr"/>
-      <c r="M324" s="1" t="inlineStr"/>
-      <c r="N324" s="1" t="inlineStr"/>
-      <c r="O324" s="1" t="inlineStr"/>
-      <c r="P324" s="1" t="inlineStr"/>
-      <c r="Q324" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R324" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="1" t="inlineStr">
-        <is>
-          <t>Said dal 1923</t>
-        </is>
-      </c>
-      <c r="B325" s="1" t="inlineStr">
-        <is>
-          <t>Via Tiburtina, 135</t>
-        </is>
-      </c>
-      <c r="C325" s="1" t="inlineStr">
-        <is>
-          <t>06/4469204</t>
-        </is>
-      </c>
-      <c r="D325" s="1" t="inlineStr">
-        <is>
-          <t>www.said.it</t>
-        </is>
-      </c>
-      <c r="E325" s="1" t="inlineStr">
-        <is>
-          <t>said1923</t>
-        </is>
-      </c>
-      <c r="F325" s="1" t="inlineStr">
-        <is>
-          <t>saiddal1923</t>
-        </is>
-      </c>
-      <c r="G325" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H325" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I325" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J325" s="1" t="inlineStr"/>
-      <c r="K325" s="1" t="inlineStr"/>
-      <c r="L325" s="1" t="inlineStr"/>
-      <c r="M325" s="1" t="inlineStr"/>
-      <c r="N325" s="1" t="inlineStr"/>
-      <c r="O325" s="1" t="inlineStr"/>
-      <c r="P325" s="1" t="inlineStr"/>
-      <c r="Q325" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R325" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="1" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="B326" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo della Fontana, 28</t>
-        </is>
-      </c>
-      <c r="C326" s="1" t="inlineStr">
-        <is>
-          <t>06/86726388</t>
-        </is>
-      </c>
-      <c r="D326" s="1" t="inlineStr">
-        <is>
-          <t>www.shellroma.it</t>
-        </is>
-      </c>
-      <c r="E326" s="1" t="inlineStr">
-        <is>
-          <t>profile.php?id=61571778928939</t>
-        </is>
-      </c>
-      <c r="F326" s="1" t="inlineStr">
-        <is>
-          <t>shell_libreria_bistrot</t>
-        </is>
-      </c>
-      <c r="G326" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H326" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I326" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J326" s="1" t="inlineStr"/>
-      <c r="K326" s="1" t="inlineStr"/>
-      <c r="L326" s="1" t="inlineStr"/>
-      <c r="M326" s="1" t="inlineStr"/>
-      <c r="N326" s="1" t="inlineStr"/>
-      <c r="O326" s="1" t="inlineStr"/>
-      <c r="P326" s="1" t="inlineStr"/>
-      <c r="Q326" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R326" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="1" t="inlineStr">
-        <is>
-          <t>Velo Pasticceria</t>
-        </is>
-      </c>
-      <c r="B327" s="1" t="inlineStr">
-        <is>
-          <t>Via del Corso, 63</t>
-        </is>
-      </c>
-      <c r="C327" s="1" t="inlineStr">
-        <is>
-          <t>06/45427861</t>
-        </is>
-      </c>
-      <c r="D327" s="1" t="inlineStr">
-        <is>
-          <t>www.velopasticceria.it</t>
-        </is>
-      </c>
-      <c r="E327" s="1" t="inlineStr">
-        <is>
-          <t>velopasticceria</t>
-        </is>
-      </c>
-      <c r="F327" s="1" t="inlineStr">
-        <is>
-          <t>velopasticceria</t>
-        </is>
-      </c>
-      <c r="G327" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H327" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I327" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J327" s="1" t="inlineStr"/>
-      <c r="K327" s="1" t="inlineStr"/>
-      <c r="L327" s="1" t="inlineStr"/>
-      <c r="M327" s="1" t="inlineStr"/>
-      <c r="N327" s="1" t="inlineStr"/>
-      <c r="O327" s="1" t="inlineStr"/>
-      <c r="P327" s="1" t="inlineStr"/>
-      <c r="Q327" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R327" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (velopasticceria) | IG: trovato (velopasticceria)</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -20561,7 +20581,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J328" s="1" t="inlineStr"/>
+      <c r="J328" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K328" s="1" t="inlineStr"/>
       <c r="L328" s="1" t="inlineStr"/>
       <c r="M328" s="1" t="inlineStr"/>
@@ -20570,12 +20594,12 @@
       <c r="P328" s="1" t="inlineStr"/>
       <c r="Q328" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R328" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -20605,7 +20629,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J329" s="1" t="inlineStr"/>
+      <c r="J329" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K329" s="1" t="inlineStr"/>
       <c r="L329" s="1" t="inlineStr"/>
       <c r="M329" s="1" t="inlineStr"/>
@@ -20614,12 +20642,12 @@
       <c r="P329" s="1" t="inlineStr"/>
       <c r="Q329" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -18896,336 +18896,464 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B296" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C296" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D296" s="1" t="inlineStr"/>
-      <c r="E296" s="1" t="inlineStr"/>
-      <c r="F296" s="1" t="inlineStr"/>
-      <c r="G296" s="1" t="inlineStr"/>
-      <c r="H296" s="1" t="inlineStr"/>
-      <c r="I296" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J296" s="1" t="inlineStr">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Hotel De' Ricci</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Via della Barchetta, 14</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>06/6874775</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>www.hoteldericci.com</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>hoteldericci</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>hoteldericci</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K296" s="1" t="inlineStr"/>
-      <c r="L296" s="1" t="inlineStr"/>
-      <c r="M296" s="1" t="inlineStr"/>
-      <c r="N296" s="1" t="inlineStr"/>
-      <c r="O296" s="1" t="inlineStr"/>
-      <c r="P296" s="1" t="inlineStr"/>
-      <c r="Q296" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R296" s="1" t="inlineStr">
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (hoteldericci) | IG: trovato (hoteldericci)</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="inlineStr">
-        <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
-        </is>
-      </c>
-      <c r="B297" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Erbe, 16</t>
-        </is>
-      </c>
-      <c r="C297" s="1" t="inlineStr">
-        <is>
-          <t>348/7277746</t>
-        </is>
-      </c>
-      <c r="D297" s="1" t="inlineStr"/>
-      <c r="E297" s="1" t="inlineStr"/>
-      <c r="F297" s="1" t="inlineStr"/>
-      <c r="G297" s="1" t="inlineStr"/>
-      <c r="H297" s="1" t="inlineStr"/>
-      <c r="I297" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J297" s="1" t="inlineStr">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Hotel Vilòn</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Via dell'Arancio, 68/69</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>06/878187</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>www.hotelvilon.com</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>hotelvilon</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>hotelvilon</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K297" s="1" t="inlineStr"/>
-      <c r="L297" s="1" t="inlineStr"/>
-      <c r="M297" s="1" t="inlineStr"/>
-      <c r="N297" s="1" t="inlineStr"/>
-      <c r="O297" s="1" t="inlineStr"/>
-      <c r="P297" s="1" t="inlineStr"/>
-      <c r="Q297" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R297" s="1" t="inlineStr">
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (hotelvilon) | IG: trovato (hotelvilon)</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="inlineStr">
-        <is>
-          <t>Osteria del Vicolo Fatato</t>
-        </is>
-      </c>
-      <c r="B298" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Forno Fatato, 11</t>
-        </is>
-      </c>
-      <c r="C298" s="1" t="inlineStr">
-        <is>
-          <t>0775/503035</t>
-        </is>
-      </c>
-      <c r="D298" s="1" t="inlineStr"/>
-      <c r="E298" s="1" t="inlineStr"/>
-      <c r="F298" s="1" t="inlineStr"/>
-      <c r="G298" s="1" t="inlineStr"/>
-      <c r="H298" s="1" t="inlineStr"/>
-      <c r="I298" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J298" s="1" t="inlineStr">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Libera</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Via Luigi Tosti, 54</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>06/90537554</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>LiberaPasticceriaCaffetteria</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>liberapasticceriacaffetteria</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K298" s="1" t="inlineStr"/>
-      <c r="L298" s="1" t="inlineStr"/>
-      <c r="M298" s="1" t="inlineStr"/>
-      <c r="N298" s="1" t="inlineStr"/>
-      <c r="O298" s="1" t="inlineStr"/>
-      <c r="P298" s="1" t="inlineStr"/>
-      <c r="Q298" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R298" s="1" t="inlineStr">
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (LiberaPasticceriaCaffetteria) | IG: trovato (liberapasticceriacaffetteria)</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="inlineStr">
-        <is>
-          <t>Poldo e Gianna</t>
-        </is>
-      </c>
-      <c r="B299" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo Rosini, 6</t>
-        </is>
-      </c>
-      <c r="C299" s="1" t="inlineStr">
-        <is>
-          <t>06/6893499</t>
-        </is>
-      </c>
-      <c r="D299" s="1" t="inlineStr"/>
-      <c r="E299" s="1" t="inlineStr"/>
-      <c r="F299" s="1" t="inlineStr"/>
-      <c r="G299" s="1" t="inlineStr"/>
-      <c r="H299" s="1" t="inlineStr"/>
-      <c r="I299" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J299" s="1" t="inlineStr">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Madeleine</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Via Monte Santo, 64</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>06/3728537</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>www.madeleinerome.com</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>madeleineroma</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>madeleineroma</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K299" s="1" t="inlineStr"/>
-      <c r="L299" s="1" t="inlineStr"/>
-      <c r="M299" s="1" t="inlineStr"/>
-      <c r="N299" s="1" t="inlineStr"/>
-      <c r="O299" s="1" t="inlineStr"/>
-      <c r="P299" s="1" t="inlineStr"/>
-      <c r="Q299" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R299" s="1" t="inlineStr">
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (madeleineroma) | IG: trovato (madeleineroma)</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="inlineStr">
-        <is>
-          <t>Trattoria A Casa Di Rita</t>
-        </is>
-      </c>
-      <c r="B300" s="1" t="inlineStr">
-        <is>
-          <t>Via delle Ciliegie, 145</t>
-        </is>
-      </c>
-      <c r="C300" s="1" t="inlineStr">
-        <is>
-          <t>338/9860960</t>
-        </is>
-      </c>
-      <c r="D300" s="1" t="inlineStr"/>
-      <c r="E300" s="1" t="inlineStr"/>
-      <c r="F300" s="1" t="inlineStr"/>
-      <c r="G300" s="1" t="inlineStr"/>
-      <c r="H300" s="1" t="inlineStr"/>
-      <c r="I300" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J300" s="1" t="inlineStr">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Said dal 1923</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Via Tiburtina, 135</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>06/4469204</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>www.said.it</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>said1923</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>saiddal1923</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K300" s="1" t="inlineStr"/>
-      <c r="L300" s="1" t="inlineStr"/>
-      <c r="M300" s="1" t="inlineStr"/>
-      <c r="N300" s="1" t="inlineStr"/>
-      <c r="O300" s="1" t="inlineStr"/>
-      <c r="P300" s="1" t="inlineStr"/>
-      <c r="Q300" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R300" s="1" t="inlineStr">
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (said1923) | IG: trovato (saiddal1923)</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="inlineStr">
-        <is>
-          <t>Ie Koji Japanese Izakaya</t>
-        </is>
-      </c>
-      <c r="B301" s="1" t="inlineStr">
-        <is>
-          <t>Via Marcantonio Bragadin, 13</t>
-        </is>
-      </c>
-      <c r="C301" s="1" t="inlineStr">
-        <is>
-          <t>348/4302368 - 06/69459860</t>
-        </is>
-      </c>
-      <c r="D301" s="1" t="inlineStr"/>
-      <c r="E301" s="1" t="inlineStr"/>
-      <c r="F301" s="1" t="inlineStr"/>
-      <c r="G301" s="1" t="inlineStr"/>
-      <c r="H301" s="1" t="inlineStr"/>
-      <c r="I301" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J301" s="1" t="inlineStr">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Vicolo della Fontana, 28</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>06/86726388</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>www.shellroma.it</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>profile.php?id=61571778928939</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>shell_libreria_bistrot</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K301" s="1" t="inlineStr"/>
-      <c r="L301" s="1" t="inlineStr"/>
-      <c r="M301" s="1" t="inlineStr"/>
-      <c r="N301" s="1" t="inlineStr"/>
-      <c r="O301" s="1" t="inlineStr"/>
-      <c r="P301" s="1" t="inlineStr"/>
-      <c r="Q301" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R301" s="1" t="inlineStr">
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (profile.php?id=61571778928939) | IG: trovato (shell_libreria_bistrot)</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B302" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C302" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D302" s="1" t="inlineStr"/>
-      <c r="E302" s="1" t="inlineStr"/>
-      <c r="F302" s="1" t="inlineStr"/>
-      <c r="G302" s="1" t="inlineStr"/>
-      <c r="H302" s="1" t="inlineStr"/>
-      <c r="I302" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J302" s="1" t="inlineStr">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Velo Pasticceria</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Via del Corso, 63</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>06/45427861</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>www.velopasticceria.it</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>velopasticceria</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>velopasticceria</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K302" s="1" t="inlineStr"/>
-      <c r="L302" s="1" t="inlineStr"/>
-      <c r="M302" s="1" t="inlineStr"/>
-      <c r="N302" s="1" t="inlineStr"/>
-      <c r="O302" s="1" t="inlineStr"/>
-      <c r="P302" s="1" t="inlineStr"/>
-      <c r="Q302" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R302" s="1" t="inlineStr">
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: trovato (velopasticceria) | IG: trovato (velopasticceria)</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
@@ -19234,17 +19362,17 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>Nomisan</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>Viale Gianluigi Bonelli, 237</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t>342/8036080</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr"/>
@@ -19270,269 +19398,234 @@
       <c r="P303" s="1" t="inlineStr"/>
       <c r="Q303" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R303" s="1" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="inlineStr">
-        <is>
-          <t>Al Setaccio</t>
-        </is>
-      </c>
-      <c r="B304" s="1" t="inlineStr">
-        <is>
-          <t>Via di Mezzocammino, 193</t>
-        </is>
-      </c>
-      <c r="C304" s="1" t="inlineStr">
-        <is>
-          <t>06/52372056</t>
-        </is>
-      </c>
-      <c r="D304" s="1" t="inlineStr"/>
-      <c r="E304" s="1" t="inlineStr"/>
-      <c r="F304" s="1" t="inlineStr"/>
-      <c r="G304" s="1" t="inlineStr"/>
-      <c r="H304" s="1" t="inlineStr"/>
-      <c r="I304" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J304" s="1" t="inlineStr">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Piazza delle Erbe, 16</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>348/7277746</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K304" s="1" t="inlineStr"/>
-      <c r="L304" s="1" t="inlineStr"/>
-      <c r="M304" s="1" t="inlineStr"/>
-      <c r="N304" s="1" t="inlineStr"/>
-      <c r="O304" s="1" t="inlineStr"/>
-      <c r="P304" s="1" t="inlineStr"/>
-      <c r="Q304" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R304" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 18:30', 'closes': '14:30, 22:30', 'break': '14:30–</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="inlineStr">
-        <is>
-          <t>Angelo Pezzella</t>
-        </is>
-      </c>
-      <c r="B305" s="1" t="inlineStr">
-        <is>
-          <t>Via Appia Nuova, 1095</t>
-        </is>
-      </c>
-      <c r="C305" s="1" t="inlineStr">
-        <is>
-          <t>06/7188560</t>
-        </is>
-      </c>
-      <c r="D305" s="1" t="inlineStr"/>
-      <c r="E305" s="1" t="inlineStr"/>
-      <c r="F305" s="1" t="inlineStr"/>
-      <c r="G305" s="1" t="inlineStr"/>
-      <c r="H305" s="1" t="inlineStr"/>
-      <c r="I305" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J305" s="1" t="inlineStr">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Osteria del Vicolo Fatato</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Vicolo Forno Fatato, 11</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>0775/503035</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K305" s="1" t="inlineStr"/>
-      <c r="L305" s="1" t="inlineStr"/>
-      <c r="M305" s="1" t="inlineStr"/>
-      <c r="N305" s="1" t="inlineStr"/>
-      <c r="O305" s="1" t="inlineStr"/>
-      <c r="P305" s="1" t="inlineStr"/>
-      <c r="Q305" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R305" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="inlineStr">
-        <is>
-          <t>Clementina</t>
-        </is>
-      </c>
-      <c r="B306" s="1" t="inlineStr">
-        <is>
-          <t>Via della Torre Clementina, 158</t>
-        </is>
-      </c>
-      <c r="C306" s="1" t="inlineStr">
-        <is>
-          <t>328/8181651</t>
-        </is>
-      </c>
-      <c r="D306" s="1" t="inlineStr"/>
-      <c r="E306" s="1" t="inlineStr"/>
-      <c r="F306" s="1" t="inlineStr"/>
-      <c r="G306" s="1" t="inlineStr"/>
-      <c r="H306" s="1" t="inlineStr"/>
-      <c r="I306" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J306" s="1" t="inlineStr">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Poldo e Gianna</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Vicolo Rosini, 6</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>06/6893499</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K306" s="1" t="inlineStr"/>
-      <c r="L306" s="1" t="inlineStr"/>
-      <c r="M306" s="1" t="inlineStr"/>
-      <c r="N306" s="1" t="inlineStr"/>
-      <c r="O306" s="1" t="inlineStr"/>
-      <c r="P306" s="1" t="inlineStr"/>
-      <c r="Q306" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R306" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="inlineStr">
-        <is>
-          <t>Da Antonio</t>
-        </is>
-      </c>
-      <c r="B307" s="1" t="inlineStr">
-        <is>
-          <t>Via Mario Lizzani, 21</t>
-        </is>
-      </c>
-      <c r="C307" s="1" t="inlineStr">
-        <is>
-          <t>391/7475549</t>
-        </is>
-      </c>
-      <c r="D307" s="1" t="inlineStr"/>
-      <c r="E307" s="1" t="inlineStr"/>
-      <c r="F307" s="1" t="inlineStr"/>
-      <c r="G307" s="1" t="inlineStr"/>
-      <c r="H307" s="1" t="inlineStr"/>
-      <c r="I307" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J307" s="1" t="inlineStr">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Trattoria A Casa Di Rita</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Via delle Ciliegie, 145</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>338/9860960</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K307" s="1" t="inlineStr"/>
-      <c r="L307" s="1" t="inlineStr"/>
-      <c r="M307" s="1" t="inlineStr"/>
-      <c r="N307" s="1" t="inlineStr"/>
-      <c r="O307" s="1" t="inlineStr"/>
-      <c r="P307" s="1" t="inlineStr"/>
-      <c r="Q307" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R307" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '22'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="inlineStr">
-        <is>
-          <t>Diego Vitagliano</t>
-        </is>
-      </c>
-      <c r="B308" s="1" t="inlineStr">
-        <is>
-          <t>Via Chiana, 80</t>
-        </is>
-      </c>
-      <c r="C308" s="1" t="inlineStr">
-        <is>
-          <t>06/72276443</t>
-        </is>
-      </c>
-      <c r="D308" s="1" t="inlineStr"/>
-      <c r="E308" s="1" t="inlineStr"/>
-      <c r="F308" s="1" t="inlineStr"/>
-      <c r="G308" s="1" t="inlineStr"/>
-      <c r="H308" s="1" t="inlineStr"/>
-      <c r="I308" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J308" s="1" t="inlineStr">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Ie Koji Japanese Izakaya</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Via Marcantonio Bragadin, 13</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>348/4302368 - 06/69459860</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K308" s="1" t="inlineStr"/>
-      <c r="L308" s="1" t="inlineStr"/>
-      <c r="M308" s="1" t="inlineStr"/>
-      <c r="N308" s="1" t="inlineStr"/>
-      <c r="O308" s="1" t="inlineStr"/>
-      <c r="P308" s="1" t="inlineStr"/>
-      <c r="Q308" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R308" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19', 'closes': '23'}, 'venerdì': {'opens': '19', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>GioMà</t>
+          <t>Mrgda Ristorante</t>
         </is>
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>Via Calpurnio Fiamma, 40/44</t>
+          <t>Via Prenestina, 182</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t>06/7674717</t>
+          <t>329/933355</t>
         </is>
       </c>
       <c r="D309" s="1" t="inlineStr"/>
@@ -19558,173 +19651,145 @@
       <c r="P309" s="1" t="inlineStr"/>
       <c r="Q309" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R309" s="1" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="inlineStr">
-        <is>
-          <t>Pupillo Pura Pizza</t>
-        </is>
-      </c>
-      <c r="B310" s="1" t="inlineStr">
-        <is>
-          <t>Via Giacomo Matteotti, 29</t>
-        </is>
-      </c>
-      <c r="C310" s="1" t="inlineStr">
-        <is>
-          <t>339/4143148</t>
-        </is>
-      </c>
-      <c r="D310" s="1" t="inlineStr"/>
-      <c r="E310" s="1" t="inlineStr"/>
-      <c r="F310" s="1" t="inlineStr"/>
-      <c r="G310" s="1" t="inlineStr"/>
-      <c r="H310" s="1" t="inlineStr"/>
-      <c r="I310" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J310" s="1" t="inlineStr">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Nomisan</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Viale Gianluigi Bonelli, 237</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>342/8036080</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K310" s="1" t="inlineStr"/>
-      <c r="L310" s="1" t="inlineStr"/>
-      <c r="M310" s="1" t="inlineStr"/>
-      <c r="N310" s="1" t="inlineStr"/>
-      <c r="O310" s="1" t="inlineStr"/>
-      <c r="P310" s="1" t="inlineStr"/>
-      <c r="Q310" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R310" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="inlineStr">
-        <is>
-          <t>Santa Romana</t>
-        </is>
-      </c>
-      <c r="B311" s="1" t="inlineStr">
-        <is>
-          <t>Piazza Certaldo, 12</t>
-        </is>
-      </c>
-      <c r="C311" s="1" t="inlineStr">
-        <is>
-          <t>06/69317674</t>
-        </is>
-      </c>
-      <c r="D311" s="1" t="inlineStr"/>
-      <c r="E311" s="1" t="inlineStr"/>
-      <c r="F311" s="1" t="inlineStr"/>
-      <c r="G311" s="1" t="inlineStr"/>
-      <c r="H311" s="1" t="inlineStr"/>
-      <c r="I311" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J311" s="1" t="inlineStr">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Al Setaccio</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Via di Mezzocammino, 193</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>06/52372056</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K311" s="1" t="inlineStr"/>
-      <c r="L311" s="1" t="inlineStr"/>
-      <c r="M311" s="1" t="inlineStr"/>
-      <c r="N311" s="1" t="inlineStr"/>
-      <c r="O311" s="1" t="inlineStr"/>
-      <c r="P311" s="1" t="inlineStr"/>
-      <c r="Q311" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R311" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="inlineStr">
-        <is>
-          <t>Seu Pizza Illuminati</t>
-        </is>
-      </c>
-      <c r="B312" s="1" t="inlineStr">
-        <is>
-          <t>Via Angelo Bargoni, 10/18</t>
-        </is>
-      </c>
-      <c r="C312" s="1" t="inlineStr">
-        <is>
-          <t>06/5883384</t>
-        </is>
-      </c>
-      <c r="D312" s="1" t="inlineStr"/>
-      <c r="E312" s="1" t="inlineStr"/>
-      <c r="F312" s="1" t="inlineStr"/>
-      <c r="G312" s="1" t="inlineStr"/>
-      <c r="H312" s="1" t="inlineStr"/>
-      <c r="I312" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J312" s="1" t="inlineStr">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Angelo Pezzella</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Via Appia Nuova, 1095</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>06/7188560</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K312" s="1" t="inlineStr"/>
-      <c r="L312" s="1" t="inlineStr"/>
-      <c r="M312" s="1" t="inlineStr"/>
-      <c r="N312" s="1" t="inlineStr"/>
-      <c r="O312" s="1" t="inlineStr"/>
-      <c r="P312" s="1" t="inlineStr"/>
-      <c r="Q312" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R312" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '00'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>Forno Ritorno</t>
+          <t>Clementina</t>
         </is>
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>Via Amerigo Vespucci, 20</t>
+          <t>Via della Torre Clementina, 158</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t>392/7768427</t>
+          <t>328/8181651</t>
         </is>
       </c>
       <c r="D313" s="1" t="inlineStr"/>
@@ -19750,29 +19815,29 @@
       <c r="P313" s="1" t="inlineStr"/>
       <c r="Q313" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>Il tuo fornaio</t>
+          <t>Da Antonio</t>
         </is>
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>Via Francesco Sapori, 35</t>
+          <t>Via Mario Lizzani, 21</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t>06/5017873</t>
+          <t>391/7475549</t>
         </is>
       </c>
       <c r="D314" s="1" t="inlineStr"/>
@@ -19798,121 +19863,113 @@
       <c r="P314" s="1" t="inlineStr"/>
       <c r="Q314" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="inlineStr">
-        <is>
-          <t>Krapfen Paglia</t>
-        </is>
-      </c>
-      <c r="B315" s="1" t="inlineStr">
-        <is>
-          <t>Piazza Anco Marzio, 18/19</t>
-        </is>
-      </c>
-      <c r="C315" s="1" t="inlineStr">
-        <is>
-          <t>06/5623344</t>
-        </is>
-      </c>
-      <c r="D315" s="1" t="inlineStr"/>
-      <c r="E315" s="1" t="inlineStr"/>
-      <c r="F315" s="1" t="inlineStr"/>
-      <c r="G315" s="1" t="inlineStr"/>
-      <c r="H315" s="1" t="inlineStr"/>
-      <c r="I315" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J315" s="1" t="inlineStr">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Diego Vitagliano</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Via Chiana, 80</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>06/72276443</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K315" s="1" t="inlineStr"/>
-      <c r="L315" s="1" t="inlineStr"/>
-      <c r="M315" s="1" t="inlineStr"/>
-      <c r="N315" s="1" t="inlineStr"/>
-      <c r="O315" s="1" t="inlineStr"/>
-      <c r="P315" s="1" t="inlineStr"/>
-      <c r="Q315" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R315" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '12, 19', 'clo</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="inlineStr">
-        <is>
-          <t>Slow</t>
-        </is>
-      </c>
-      <c r="B316" s="1" t="inlineStr">
-        <is>
-          <t>Corso Vittorio Emanuele II, 73</t>
-        </is>
-      </c>
-      <c r="C316" s="1" t="inlineStr"/>
-      <c r="D316" s="1" t="inlineStr"/>
-      <c r="E316" s="1" t="inlineStr"/>
-      <c r="F316" s="1" t="inlineStr"/>
-      <c r="G316" s="1" t="inlineStr"/>
-      <c r="H316" s="1" t="inlineStr"/>
-      <c r="I316" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J316" s="1" t="inlineStr">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>GioMà</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Via Calpurnio Fiamma, 40/44</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>06/7674717</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K316" s="1" t="inlineStr"/>
-      <c r="L316" s="1" t="inlineStr"/>
-      <c r="M316" s="1" t="inlineStr"/>
-      <c r="N316" s="1" t="inlineStr"/>
-      <c r="O316" s="1" t="inlineStr"/>
-      <c r="P316" s="1" t="inlineStr"/>
-      <c r="Q316" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R316" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19:30', 'closes': '23'}, 'venerdì': {'opens': '19:30', 'c</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>Bottega Popolare</t>
+          <t>Pupillo Pura Pizza</t>
         </is>
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>Via Andrea Doria, 41 Mercato Trionfale Box 113</t>
+          <t>Via Giacomo Matteotti, 29</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t>334/3351068</t>
+          <t>339/4143148</t>
         </is>
       </c>
       <c r="D317" s="1" t="inlineStr"/>
@@ -19938,265 +19995,193 @@
       <c r="P317" s="1" t="inlineStr"/>
       <c r="Q317" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R317" s="1" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="inlineStr">
-        <is>
-          <t>Cheebo</t>
-        </is>
-      </c>
-      <c r="B318" s="1" t="inlineStr">
-        <is>
-          <t>Via Aretusa, 6</t>
-        </is>
-      </c>
-      <c r="C318" s="1" t="inlineStr">
-        <is>
-          <t>351/7598556</t>
-        </is>
-      </c>
-      <c r="D318" s="1" t="inlineStr"/>
-      <c r="E318" s="1" t="inlineStr"/>
-      <c r="F318" s="1" t="inlineStr"/>
-      <c r="G318" s="1" t="inlineStr"/>
-      <c r="H318" s="1" t="inlineStr"/>
-      <c r="I318" s="1" t="inlineStr">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Santa Romana</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Piazza Certaldo, 12</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>06/69317674</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18:30', 'closes': '23'}, 'venerdì': {'opens': '18:30', 'c</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Seu Pizza Illuminati</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Via Angelo Bargoni, 10/18</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>06/5883384</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Forno Ritorno</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Via Amerigo Vespucci, 20</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>392/7768427</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>Il tuo fornaio</t>
+        </is>
+      </c>
+      <c r="B321" s="1" t="inlineStr">
+        <is>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C321" s="1" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
+      <c r="D321" s="1" t="inlineStr"/>
+      <c r="E321" s="1" t="inlineStr"/>
+      <c r="F321" s="1" t="inlineStr"/>
+      <c r="G321" s="1" t="inlineStr"/>
+      <c r="H321" s="1" t="inlineStr"/>
+      <c r="I321" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J318" s="1" t="inlineStr">
+      <c r="J321" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K318" s="1" t="inlineStr"/>
-      <c r="L318" s="1" t="inlineStr"/>
-      <c r="M318" s="1" t="inlineStr"/>
-      <c r="N318" s="1" t="inlineStr"/>
-      <c r="O318" s="1" t="inlineStr"/>
-      <c r="P318" s="1" t="inlineStr"/>
-      <c r="Q318" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R318" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="1" t="inlineStr">
-        <is>
-          <t>Dondolo</t>
-        </is>
-      </c>
-      <c r="B319" s="1" t="inlineStr">
-        <is>
-          <t>Via di Monte Sacro, 23</t>
-        </is>
-      </c>
-      <c r="C319" s="1" t="inlineStr">
-        <is>
-          <t>06/45752197</t>
-        </is>
-      </c>
-      <c r="D319" s="1" t="inlineStr"/>
-      <c r="E319" s="1" t="inlineStr"/>
-      <c r="F319" s="1" t="inlineStr"/>
-      <c r="G319" s="1" t="inlineStr"/>
-      <c r="H319" s="1" t="inlineStr"/>
-      <c r="I319" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J319" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K319" s="1" t="inlineStr"/>
-      <c r="L319" s="1" t="inlineStr"/>
-      <c r="M319" s="1" t="inlineStr"/>
-      <c r="N319" s="1" t="inlineStr"/>
-      <c r="O319" s="1" t="inlineStr"/>
-      <c r="P319" s="1" t="inlineStr"/>
-      <c r="Q319" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R319" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="1" t="inlineStr">
-        <is>
-          <t>MAE - Slow Brunchers</t>
-        </is>
-      </c>
-      <c r="B320" s="1" t="inlineStr">
-        <is>
-          <t>Via della Giuliana, 33</t>
-        </is>
-      </c>
-      <c r="C320" s="1" t="inlineStr">
-        <is>
-          <t>06/98874558</t>
-        </is>
-      </c>
-      <c r="D320" s="1" t="inlineStr"/>
-      <c r="E320" s="1" t="inlineStr"/>
-      <c r="F320" s="1" t="inlineStr"/>
-      <c r="G320" s="1" t="inlineStr"/>
-      <c r="H320" s="1" t="inlineStr"/>
-      <c r="I320" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J320" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K320" s="1" t="inlineStr"/>
-      <c r="L320" s="1" t="inlineStr"/>
-      <c r="M320" s="1" t="inlineStr"/>
-      <c r="N320" s="1" t="inlineStr"/>
-      <c r="O320" s="1" t="inlineStr"/>
-      <c r="P320" s="1" t="inlineStr"/>
-      <c r="Q320" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R320" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Hotel De' Ricci</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Via della Barchetta, 14</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>06/6874775</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>www.hoteldericci.com</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>hoteldericci</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>hoteldericci</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O321" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q321" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (hoteldericci) | IG: trovato (hoteldericci)</t>
-        </is>
-      </c>
-      <c r="R321" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="K321" s="1" t="inlineStr"/>
+      <c r="L321" s="1" t="inlineStr"/>
+      <c r="M321" s="1" t="inlineStr"/>
+      <c r="N321" s="1" t="inlineStr"/>
+      <c r="O321" s="1" t="inlineStr"/>
+      <c r="P321" s="1" t="inlineStr"/>
+      <c r="Q321" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R321" s="1" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Hotel Vilòn</t>
+          <t>Krapfen Paglia</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Via dell'Arancio, 68/69</t>
+          <t>Piazza Anco Marzio, 18/19</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>06/878187</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>www.hotelvilon.com</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>hotelvilon</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>hotelvilon</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/5623344</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20209,123 +20194,75 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O322" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (hotelvilon) | IG: trovato (hotelvilon)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Libera</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Via Luigi Tosti, 54</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>06/90537554</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>LiberaPasticceriaCaffetteria</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>liberapasticceriacaffetteria</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="B323" s="1" t="inlineStr">
+        <is>
+          <t>Corso Vittorio Emanuele II, 73</t>
+        </is>
+      </c>
+      <c r="C323" s="1" t="inlineStr"/>
+      <c r="D323" s="1" t="inlineStr"/>
+      <c r="E323" s="1" t="inlineStr"/>
+      <c r="F323" s="1" t="inlineStr"/>
+      <c r="G323" s="1" t="inlineStr"/>
+      <c r="H323" s="1" t="inlineStr"/>
+      <c r="I323" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J323" s="1" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O323" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q323" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (LiberaPasticceriaCaffetteria) | IG: trovato (liberapasticceriacaffetteria)</t>
-        </is>
-      </c>
-      <c r="R323" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
+      <c r="K323" s="1" t="inlineStr"/>
+      <c r="L323" s="1" t="inlineStr"/>
+      <c r="M323" s="1" t="inlineStr"/>
+      <c r="N323" s="1" t="inlineStr"/>
+      <c r="O323" s="1" t="inlineStr"/>
+      <c r="P323" s="1" t="inlineStr"/>
+      <c r="Q323" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R323" s="1" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Madeleine</t>
+          <t>Bottega Popolare</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Via Monte Santo, 64</t>
+          <t>Via Andrea Doria, 41 Mercato Trionfale Box 113</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>06/3728537</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>www.madeleinerome.com</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>madeleineroma</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>madeleineroma</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>334/3351068</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20338,61 +20275,36 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O324" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '08', 'closes': '21:30'}, 'venerdì': {'opens': '08', 'clos</t>
         </is>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (madeleineroma) | IG: trovato (madeleineroma)</t>
+          <t>Rating Google: 3.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Said dal 1923</t>
+          <t>Cheebo</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Via Tiburtina, 135</t>
+          <t>Via Aretusa, 6</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>06/4469204</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>www.said.it</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>said1923</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>saiddal1923</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>351/7598556</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20405,61 +20317,36 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O325" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–</t>
         </is>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (said1923) | IG: trovato (saiddal1923)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Dondolo</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Vicolo della Fontana, 28</t>
+          <t>Via di Monte Sacro, 23</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>06/86726388</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>www.shellroma.it</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>profile.php?id=61571778928939</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>shell_libreria_bistrot</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/45752197</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20472,61 +20359,36 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O326" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '23'}, 'venerdì': {'opens': '18', 'closes'</t>
         </is>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: trovato (profile.php?id=61571778928939) | IG: trovato (shell_libreria_bistrot)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Velo Pasticceria</t>
+          <t>MAE - Slow Brunchers</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Via del Corso, 63</t>
+          <t>Via della Giuliana, 33</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>06/45427861</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>www.velopasticceria.it</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>velopasticceria</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>velopasticceria</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/98874558</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20539,539 +20401,547 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O327" t="inlineStr">
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>19.2 Winebar Enoteca</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Largo Benito Jacovitti, 16</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>347/4387426</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Bosco - Officine del Tartufo</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Via Macerata, 8/C</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>06/701 8134</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 18:30', 'closes': '14:30, 23', 'break': '14:30–18:</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Duke's - Fine Casual Bar &amp; Restaurant</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Viale Parioli, 200</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>06/80662455</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Enoteca L'Antidoto</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Vicolo del Bologna, 19</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>342/3006808</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>www.enotecalantidoto.com</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>enotecalantidoto</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>enotecalantidoto</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: trovato (velopasticceria) | IG: trovato (velopasticceria)</t>
-        </is>
-      </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="1" t="inlineStr">
-        <is>
-          <t>19.2 Winebar Enoteca</t>
-        </is>
-      </c>
-      <c r="B328" s="1" t="inlineStr">
-        <is>
-          <t>Largo Benito Jacovitti, 16</t>
-        </is>
-      </c>
-      <c r="C328" s="1" t="inlineStr">
-        <is>
-          <t>347/4387426</t>
-        </is>
-      </c>
-      <c r="D328" s="1" t="inlineStr"/>
-      <c r="E328" s="1" t="inlineStr"/>
-      <c r="F328" s="1" t="inlineStr"/>
-      <c r="G328" s="1" t="inlineStr"/>
-      <c r="H328" s="1" t="inlineStr"/>
-      <c r="I328" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J328" s="1" t="inlineStr">
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (enotecalantidoto) | IG: trovato (enotecalantidoto)</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Il Goccetto</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Via dei Banchi Vecchi, 14</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>06/99448583</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>www.ilgoccetto.com</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Ilgoccetto</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Ilgoccetto</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K328" s="1" t="inlineStr"/>
-      <c r="L328" s="1" t="inlineStr"/>
-      <c r="M328" s="1" t="inlineStr"/>
-      <c r="N328" s="1" t="inlineStr"/>
-      <c r="O328" s="1" t="inlineStr"/>
-      <c r="P328" s="1" t="inlineStr"/>
-      <c r="Q328" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R328" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="1" t="inlineStr">
-        <is>
-          <t>Bosco - Officine del Tartufo</t>
-        </is>
-      </c>
-      <c r="B329" s="1" t="inlineStr">
-        <is>
-          <t>Via Macerata, 8/C</t>
-        </is>
-      </c>
-      <c r="C329" s="1" t="inlineStr">
-        <is>
-          <t>06/701 8134</t>
-        </is>
-      </c>
-      <c r="D329" s="1" t="inlineStr"/>
-      <c r="E329" s="1" t="inlineStr"/>
-      <c r="F329" s="1" t="inlineStr"/>
-      <c r="G329" s="1" t="inlineStr"/>
-      <c r="H329" s="1" t="inlineStr"/>
-      <c r="I329" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J329" s="1" t="inlineStr">
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (Ilgoccetto) | IG: trovato (Ilgoccetto)</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>LATTA - Fermenti e miscele</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Via Antonio Pacinotti, 83</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>06/88923791</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>www.latta-roma.it</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>lattaroma</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>latta_roma</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K329" s="1" t="inlineStr"/>
-      <c r="L329" s="1" t="inlineStr"/>
-      <c r="M329" s="1" t="inlineStr"/>
-      <c r="N329" s="1" t="inlineStr"/>
-      <c r="O329" s="1" t="inlineStr"/>
-      <c r="P329" s="1" t="inlineStr"/>
-      <c r="Q329" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R329" s="1" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="1" t="inlineStr">
-        <is>
-          <t>Duke's - Fine Casual Bar &amp; Restaurant</t>
-        </is>
-      </c>
-      <c r="B330" s="1" t="inlineStr">
-        <is>
-          <t>Viale Parioli, 200</t>
-        </is>
-      </c>
-      <c r="C330" s="1" t="inlineStr">
-        <is>
-          <t>06/80662455</t>
-        </is>
-      </c>
-      <c r="D330" s="1" t="inlineStr"/>
-      <c r="E330" s="1" t="inlineStr"/>
-      <c r="F330" s="1" t="inlineStr"/>
-      <c r="G330" s="1" t="inlineStr"/>
-      <c r="H330" s="1" t="inlineStr"/>
-      <c r="I330" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J330" s="1" t="inlineStr"/>
-      <c r="K330" s="1" t="inlineStr"/>
-      <c r="L330" s="1" t="inlineStr"/>
-      <c r="M330" s="1" t="inlineStr"/>
-      <c r="N330" s="1" t="inlineStr"/>
-      <c r="O330" s="1" t="inlineStr"/>
-      <c r="P330" s="1" t="inlineStr"/>
-      <c r="Q330" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R330" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="1" t="inlineStr">
-        <is>
-          <t>Enoteca L'Antidoto</t>
-        </is>
-      </c>
-      <c r="B331" s="1" t="inlineStr">
-        <is>
-          <t>Vicolo del Bologna, 19</t>
-        </is>
-      </c>
-      <c r="C331" s="1" t="inlineStr">
-        <is>
-          <t>342/3006808</t>
-        </is>
-      </c>
-      <c r="D331" s="1" t="inlineStr">
-        <is>
-          <t>www.enotecalantidoto.com</t>
-        </is>
-      </c>
-      <c r="E331" s="1" t="inlineStr">
-        <is>
-          <t>enotecalantidoto</t>
-        </is>
-      </c>
-      <c r="F331" s="1" t="inlineStr">
-        <is>
-          <t>enotecalantidoto</t>
-        </is>
-      </c>
-      <c r="G331" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H331" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I331" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J331" s="1" t="inlineStr"/>
-      <c r="K331" s="1" t="inlineStr"/>
-      <c r="L331" s="1" t="inlineStr"/>
-      <c r="M331" s="1" t="inlineStr"/>
-      <c r="N331" s="1" t="inlineStr"/>
-      <c r="O331" s="1" t="inlineStr"/>
-      <c r="P331" s="1" t="inlineStr"/>
-      <c r="Q331" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R331" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="1" t="inlineStr">
-        <is>
-          <t>Il Goccetto</t>
-        </is>
-      </c>
-      <c r="B332" s="1" t="inlineStr">
-        <is>
-          <t>Via dei Banchi Vecchi, 14</t>
-        </is>
-      </c>
-      <c r="C332" s="1" t="inlineStr">
-        <is>
-          <t>06/99448583</t>
-        </is>
-      </c>
-      <c r="D332" s="1" t="inlineStr">
-        <is>
-          <t>www.ilgoccetto.com</t>
-        </is>
-      </c>
-      <c r="E332" s="1" t="inlineStr">
-        <is>
-          <t>Ilgoccetto</t>
-        </is>
-      </c>
-      <c r="F332" s="1" t="inlineStr">
-        <is>
-          <t>Ilgoccetto</t>
-        </is>
-      </c>
-      <c r="G332" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H332" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I332" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J332" s="1" t="inlineStr"/>
-      <c r="K332" s="1" t="inlineStr"/>
-      <c r="L332" s="1" t="inlineStr"/>
-      <c r="M332" s="1" t="inlineStr"/>
-      <c r="N332" s="1" t="inlineStr"/>
-      <c r="O332" s="1" t="inlineStr"/>
-      <c r="P332" s="1" t="inlineStr"/>
-      <c r="Q332" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R332" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="1" t="inlineStr">
-        <is>
-          <t>LATTA - Fermenti e miscele</t>
-        </is>
-      </c>
-      <c r="B333" s="1" t="inlineStr">
-        <is>
-          <t>Via Antonio Pacinotti, 83</t>
-        </is>
-      </c>
-      <c r="C333" s="1" t="inlineStr">
-        <is>
-          <t>06/88923791</t>
-        </is>
-      </c>
-      <c r="D333" s="1" t="inlineStr">
-        <is>
-          <t>www.latta-roma.it</t>
-        </is>
-      </c>
-      <c r="E333" s="1" t="inlineStr">
-        <is>
-          <t>lattaroma</t>
-        </is>
-      </c>
-      <c r="F333" s="1" t="inlineStr">
-        <is>
-          <t>latta_roma</t>
-        </is>
-      </c>
-      <c r="G333" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H333" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I333" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J333" s="1" t="inlineStr"/>
-      <c r="K333" s="1" t="inlineStr"/>
-      <c r="L333" s="1" t="inlineStr"/>
-      <c r="M333" s="1" t="inlineStr"/>
-      <c r="N333" s="1" t="inlineStr"/>
-      <c r="O333" s="1" t="inlineStr"/>
-      <c r="P333" s="1" t="inlineStr"/>
-      <c r="Q333" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R333" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '17', 'closes': '01'}, 'venerdì': {'opens': '17', 'closes'</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (lattaroma) | IG: trovato (latta_roma)</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="inlineStr">
+      <c r="A334" t="inlineStr">
         <is>
           <t>Metà - sorsi e assaggi</t>
         </is>
       </c>
-      <c r="B334" s="1" t="inlineStr">
+      <c r="B334" t="inlineStr">
         <is>
           <t>Viale Gottardo, 18/20</t>
         </is>
       </c>
-      <c r="C334" s="1" t="inlineStr">
+      <c r="C334" t="inlineStr">
         <is>
           <t>320/9563284</t>
         </is>
       </c>
-      <c r="D334" s="1" t="inlineStr"/>
-      <c r="E334" s="1" t="inlineStr">
+      <c r="E334" t="inlineStr">
         <is>
           <t>profile.php?id=100076435981688</t>
         </is>
       </c>
-      <c r="F334" s="1" t="inlineStr">
+      <c r="F334" t="inlineStr">
         <is>
           <t>meta_roma</t>
         </is>
       </c>
-      <c r="G334" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H334" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I334" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J334" s="1" t="inlineStr"/>
-      <c r="K334" s="1" t="inlineStr"/>
-      <c r="L334" s="1" t="inlineStr"/>
-      <c r="M334" s="1" t="inlineStr"/>
-      <c r="N334" s="1" t="inlineStr"/>
-      <c r="O334" s="1" t="inlineStr"/>
-      <c r="P334" s="1" t="inlineStr"/>
-      <c r="Q334" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R334" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100076435981688) | IG: trovato (meta_roma)</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="inlineStr">
+      <c r="A335" t="inlineStr">
         <is>
           <t>Mine</t>
         </is>
       </c>
-      <c r="B335" s="1" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>Via Flaminia, 732/B</t>
         </is>
       </c>
-      <c r="C335" s="1" t="inlineStr">
+      <c r="C335" t="inlineStr">
         <is>
           <t>06/3337879</t>
         </is>
       </c>
-      <c r="D335" s="1" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>www.minefleming.com</t>
         </is>
       </c>
-      <c r="E335" s="1" t="inlineStr">
+      <c r="E335" t="inlineStr">
         <is>
           <t>minebistrobottega</t>
         </is>
       </c>
-      <c r="F335" s="1" t="inlineStr">
+      <c r="F335" t="inlineStr">
         <is>
           <t>minefleming</t>
         </is>
       </c>
-      <c r="G335" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H335" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I335" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J335" s="1" t="inlineStr"/>
-      <c r="K335" s="1" t="inlineStr"/>
-      <c r="L335" s="1" t="inlineStr"/>
-      <c r="M335" s="1" t="inlineStr"/>
-      <c r="N335" s="1" t="inlineStr"/>
-      <c r="O335" s="1" t="inlineStr"/>
-      <c r="P335" s="1" t="inlineStr"/>
-      <c r="Q335" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R335" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '00'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (minebistrobottega) | IG: trovato (minefleming)</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="inlineStr">
+      <c r="A336" t="inlineStr">
         <is>
           <t>Mostò</t>
         </is>
       </c>
-      <c r="B336" s="1" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>Viale Pinturicchio, 32</t>
         </is>
       </c>
-      <c r="C336" s="1" t="inlineStr">
+      <c r="C336" t="inlineStr">
         <is>
           <t>392/2579616</t>
         </is>
       </c>
-      <c r="D336" s="1" t="inlineStr">
+      <c r="D336" t="inlineStr">
         <is>
           <t>www.enotecamosto.it</t>
         </is>
       </c>
-      <c r="E336" s="1" t="inlineStr">
+      <c r="E336" t="inlineStr">
         <is>
           <t>enotecamosto</t>
         </is>
       </c>
-      <c r="F336" s="1" t="inlineStr">
+      <c r="F336" t="inlineStr">
         <is>
           <t>enotecamosto</t>
         </is>
       </c>
-      <c r="G336" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H336" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I336" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J336" s="1" t="inlineStr"/>
-      <c r="K336" s="1" t="inlineStr"/>
-      <c r="L336" s="1" t="inlineStr"/>
-      <c r="M336" s="1" t="inlineStr"/>
-      <c r="N336" s="1" t="inlineStr"/>
-      <c r="O336" s="1" t="inlineStr"/>
-      <c r="P336" s="1" t="inlineStr"/>
-      <c r="Q336" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R336" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '17:30', 'closes': '23:30'}, 'venerdì': {'opens': '17:30',</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (enotecamosto) | IG: trovato (enotecamosto)</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -19360,48 +19360,42 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B303" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C303" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D303" s="1" t="inlineStr"/>
-      <c r="E303" s="1" t="inlineStr"/>
-      <c r="F303" s="1" t="inlineStr"/>
-      <c r="G303" s="1" t="inlineStr"/>
-      <c r="H303" s="1" t="inlineStr"/>
-      <c r="I303" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J303" s="1" t="inlineStr">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Schenardino - Cucina Pizza &amp; Vino</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Piazza delle Erbe, 16</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>348/7277746</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K303" s="1" t="inlineStr"/>
-      <c r="L303" s="1" t="inlineStr"/>
-      <c r="M303" s="1" t="inlineStr"/>
-      <c r="N303" s="1" t="inlineStr"/>
-      <c r="O303" s="1" t="inlineStr"/>
-      <c r="P303" s="1" t="inlineStr"/>
-      <c r="Q303" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R303" s="1" t="inlineStr">
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 18:30', 'closes': '14:30, 22:30', 'break': '14:30–</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
@@ -19410,17 +19404,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Schenardino - Cucina Pizza &amp; Vino</t>
+          <t>Osteria del Vicolo Fatato</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Piazza delle Erbe, 16</t>
+          <t>Vicolo Forno Fatato, 11</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>348/7277746</t>
+          <t>0775/503035</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19433,14 +19427,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12:30, 18:30', 'closes': '14:30, 22:30', 'break': '14:30–</t>
-        </is>
-      </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -19452,17 +19441,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Osteria del Vicolo Fatato</t>
+          <t>Poldo e Gianna</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Vicolo Forno Fatato, 11</t>
+          <t>Vicolo Rosini, 6</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0775/503035</t>
+          <t>06/6893499</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19475,9 +19464,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
+        </is>
+      </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -19489,17 +19483,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Poldo e Gianna</t>
+          <t>Trattoria A Casa Di Rita</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Vicolo Rosini, 6</t>
+          <t>Via delle Ciliegie, 145</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>06/6893499</t>
+          <t>338/9860960</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19514,12 +19508,12 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
+          <t>{'giovedì': {'opens': '18', 'closes': '22'}, 'venerdì': {'opens': '18', 'closes'</t>
         </is>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -19531,17 +19525,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Trattoria A Casa Di Rita</t>
+          <t>Ie Koji Japanese Izakaya</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Via delle Ciliegie, 145</t>
+          <t>Via Marcantonio Bragadin, 13</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>338/9860960</t>
+          <t>348/4302368 - 06/69459860</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19556,12 +19550,12 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '18', 'closes': '22'}, 'venerdì': {'opens': '18', 'closes'</t>
+          <t>{'giovedì': {'opens': '19', 'closes': '23'}, 'venerdì': {'opens': '19', 'closes'</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -19573,17 +19567,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Ie Koji Japanese Izakaya</t>
+          <t>Nomisan</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Via Marcantonio Bragadin, 13</t>
+          <t>Viale Gianluigi Bonelli, 237</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>348/4302368 - 06/69459860</t>
+          <t>342/8036080</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19596,11 +19590,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '19', 'closes': '23'}, 'venerdì': {'opens': '19', 'closes'</t>
-        </is>
-      </c>
       <c r="Q308" t="inlineStr">
         <is>
           <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
@@ -19613,48 +19602,37 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B309" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C309" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D309" s="1" t="inlineStr"/>
-      <c r="E309" s="1" t="inlineStr"/>
-      <c r="F309" s="1" t="inlineStr"/>
-      <c r="G309" s="1" t="inlineStr"/>
-      <c r="H309" s="1" t="inlineStr"/>
-      <c r="I309" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J309" s="1" t="inlineStr">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Al Setaccio</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Via di Mezzocammino, 193</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>06/52372056</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K309" s="1" t="inlineStr"/>
-      <c r="L309" s="1" t="inlineStr"/>
-      <c r="M309" s="1" t="inlineStr"/>
-      <c r="N309" s="1" t="inlineStr"/>
-      <c r="O309" s="1" t="inlineStr"/>
-      <c r="P309" s="1" t="inlineStr"/>
-      <c r="Q309" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R309" s="1" t="inlineStr">
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
@@ -19663,17 +19641,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Nomisan</t>
+          <t>Angelo Pezzella</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Viale Gianluigi Bonelli, 237</t>
+          <t>Via Appia Nuova, 1095</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>342/8036080</t>
+          <t>06/7188560</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19686,9 +19664,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '00'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -19700,17 +19683,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Al Setaccio</t>
+          <t>Diego Vitagliano</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Via di Mezzocammino, 193</t>
+          <t>Via Chiana, 80</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>06/52372056</t>
+          <t>06/72276443</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19723,9 +19706,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '12, 19', 'clo</t>
+        </is>
+      </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -19737,17 +19725,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Angelo Pezzella</t>
+          <t>GioMà</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Via Appia Nuova, 1095</t>
+          <t>Via Calpurnio Fiamma, 40/44</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>06/7188560</t>
+          <t>06/7674717</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19762,12 +19750,12 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '18', 'closes': '00'}, 'venerdì': {'opens': '18', 'closes'</t>
+          <t>{'giovedì': {'opens': '19:30', 'closes': '23'}, 'venerdì': {'opens': '19:30', 'c</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -19777,96 +19765,79 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="inlineStr">
-        <is>
-          <t>Clementina</t>
-        </is>
-      </c>
-      <c r="B313" s="1" t="inlineStr">
-        <is>
-          <t>Via della Torre Clementina, 158</t>
-        </is>
-      </c>
-      <c r="C313" s="1" t="inlineStr">
-        <is>
-          <t>328/8181651</t>
-        </is>
-      </c>
-      <c r="D313" s="1" t="inlineStr"/>
-      <c r="E313" s="1" t="inlineStr"/>
-      <c r="F313" s="1" t="inlineStr"/>
-      <c r="G313" s="1" t="inlineStr"/>
-      <c r="H313" s="1" t="inlineStr"/>
-      <c r="I313" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J313" s="1" t="inlineStr">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Santa Romana</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Piazza Certaldo, 12</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>06/69317674</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K313" s="1" t="inlineStr"/>
-      <c r="L313" s="1" t="inlineStr"/>
-      <c r="M313" s="1" t="inlineStr"/>
-      <c r="N313" s="1" t="inlineStr"/>
-      <c r="O313" s="1" t="inlineStr"/>
-      <c r="P313" s="1" t="inlineStr"/>
-      <c r="Q313" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R313" s="1" t="inlineStr">
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18:30', 'closes': '23'}, 'venerdì': {'opens': '18:30', 'c</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="inlineStr">
-        <is>
-          <t>Da Antonio</t>
-        </is>
-      </c>
-      <c r="B314" s="1" t="inlineStr">
-        <is>
-          <t>Via Mario Lizzani, 21</t>
-        </is>
-      </c>
-      <c r="C314" s="1" t="inlineStr">
-        <is>
-          <t>391/7475549</t>
-        </is>
-      </c>
-      <c r="D314" s="1" t="inlineStr"/>
-      <c r="E314" s="1" t="inlineStr"/>
-      <c r="F314" s="1" t="inlineStr"/>
-      <c r="G314" s="1" t="inlineStr"/>
-      <c r="H314" s="1" t="inlineStr"/>
-      <c r="I314" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J314" s="1" t="inlineStr">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Seu Pizza Illuminati</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Via Angelo Bargoni, 10/18</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>06/5883384</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K314" s="1" t="inlineStr"/>
-      <c r="L314" s="1" t="inlineStr"/>
-      <c r="M314" s="1" t="inlineStr"/>
-      <c r="N314" s="1" t="inlineStr"/>
-      <c r="O314" s="1" t="inlineStr"/>
-      <c r="P314" s="1" t="inlineStr"/>
-      <c r="Q314" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R314" s="1" t="inlineStr">
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
@@ -19875,17 +19846,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Diego Vitagliano</t>
+          <t>Forno Ritorno</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Via Chiana, 80</t>
+          <t>Via Amerigo Vespucci, 20</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>06/72276443</t>
+          <t>392/7768427</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19898,14 +19869,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '12, 19', 'clo</t>
-        </is>
-      </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -19917,17 +19883,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>GioMà</t>
+          <t>Krapfen Paglia</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Via Calpurnio Fiamma, 40/44</t>
+          <t>Piazza Anco Marzio, 18/19</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>06/7674717</t>
+          <t>06/5623344</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19940,14 +19906,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '19:30', 'closes': '23'}, 'venerdì': {'opens': '19:30', 'c</t>
-        </is>
-      </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -19957,48 +19918,42 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="inlineStr">
-        <is>
-          <t>Pupillo Pura Pizza</t>
-        </is>
-      </c>
-      <c r="B317" s="1" t="inlineStr">
-        <is>
-          <t>Via Giacomo Matteotti, 29</t>
-        </is>
-      </c>
-      <c r="C317" s="1" t="inlineStr">
-        <is>
-          <t>339/4143148</t>
-        </is>
-      </c>
-      <c r="D317" s="1" t="inlineStr"/>
-      <c r="E317" s="1" t="inlineStr"/>
-      <c r="F317" s="1" t="inlineStr"/>
-      <c r="G317" s="1" t="inlineStr"/>
-      <c r="H317" s="1" t="inlineStr"/>
-      <c r="I317" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J317" s="1" t="inlineStr">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Bottega Popolare</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Via Andrea Doria, 41 Mercato Trionfale Box 113</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>334/3351068</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K317" s="1" t="inlineStr"/>
-      <c r="L317" s="1" t="inlineStr"/>
-      <c r="M317" s="1" t="inlineStr"/>
-      <c r="N317" s="1" t="inlineStr"/>
-      <c r="O317" s="1" t="inlineStr"/>
-      <c r="P317" s="1" t="inlineStr"/>
-      <c r="Q317" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R317" s="1" t="inlineStr">
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '08', 'closes': '21:30'}, 'venerdì': {'opens': '08', 'clos</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Rating Google: 3.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
@@ -20007,17 +19962,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Santa Romana</t>
+          <t>Cheebo</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Piazza Certaldo, 12</t>
+          <t>Via Aretusa, 6</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>06/69317674</t>
+          <t>351/7598556</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20032,12 +19987,12 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '18:30', 'closes': '23'}, 'venerdì': {'opens': '18:30', 'c</t>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–</t>
         </is>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -20049,17 +20004,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Seu Pizza Illuminati</t>
+          <t>Dondolo</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Via Angelo Bargoni, 10/18</t>
+          <t>Via di Monte Sacro, 23</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>06/5883384</t>
+          <t>06/45752197</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -20072,9 +20027,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '23'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -20086,17 +20046,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Forno Ritorno</t>
+          <t>MAE - Slow Brunchers</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Via Amerigo Vespucci, 20</t>
+          <t>Via della Giuliana, 33</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>392/7768427</t>
+          <t>06/98874558</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20111,7 +20071,7 @@
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -20121,48 +20081,37 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="inlineStr">
-        <is>
-          <t>Il tuo fornaio</t>
-        </is>
-      </c>
-      <c r="B321" s="1" t="inlineStr">
-        <is>
-          <t>Via Francesco Sapori, 35</t>
-        </is>
-      </c>
-      <c r="C321" s="1" t="inlineStr">
-        <is>
-          <t>06/5017873</t>
-        </is>
-      </c>
-      <c r="D321" s="1" t="inlineStr"/>
-      <c r="E321" s="1" t="inlineStr"/>
-      <c r="F321" s="1" t="inlineStr"/>
-      <c r="G321" s="1" t="inlineStr"/>
-      <c r="H321" s="1" t="inlineStr"/>
-      <c r="I321" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J321" s="1" t="inlineStr">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>19.2 Winebar Enoteca</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Largo Benito Jacovitti, 16</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>347/4387426</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K321" s="1" t="inlineStr"/>
-      <c r="L321" s="1" t="inlineStr"/>
-      <c r="M321" s="1" t="inlineStr"/>
-      <c r="N321" s="1" t="inlineStr"/>
-      <c r="O321" s="1" t="inlineStr"/>
-      <c r="P321" s="1" t="inlineStr"/>
-      <c r="Q321" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R321" s="1" t="inlineStr">
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
@@ -20171,17 +20120,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Krapfen Paglia</t>
+          <t>Bosco - Officine del Tartufo</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Piazza Anco Marzio, 18/19</t>
+          <t>Via Macerata, 8/C</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>06/5623344</t>
+          <t>06/701 8134</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20194,9 +20143,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 18:30', 'closes': '14:30, 23', 'break': '14:30–18:</t>
+        </is>
+      </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -20206,44 +20160,37 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="inlineStr">
-        <is>
-          <t>Slow</t>
-        </is>
-      </c>
-      <c r="B323" s="1" t="inlineStr">
-        <is>
-          <t>Corso Vittorio Emanuele II, 73</t>
-        </is>
-      </c>
-      <c r="C323" s="1" t="inlineStr"/>
-      <c r="D323" s="1" t="inlineStr"/>
-      <c r="E323" s="1" t="inlineStr"/>
-      <c r="F323" s="1" t="inlineStr"/>
-      <c r="G323" s="1" t="inlineStr"/>
-      <c r="H323" s="1" t="inlineStr"/>
-      <c r="I323" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J323" s="1" t="inlineStr">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Duke's - Fine Casual Bar &amp; Restaurant</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Viale Parioli, 200</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>06/80662455</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K323" s="1" t="inlineStr"/>
-      <c r="L323" s="1" t="inlineStr"/>
-      <c r="M323" s="1" t="inlineStr"/>
-      <c r="N323" s="1" t="inlineStr"/>
-      <c r="O323" s="1" t="inlineStr"/>
-      <c r="P323" s="1" t="inlineStr"/>
-      <c r="Q323" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R323" s="1" t="inlineStr">
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
@@ -20252,17 +20199,42 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Bottega Popolare</t>
+          <t>Enoteca L'Antidoto</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Via Andrea Doria, 41 Mercato Trionfale Box 113</t>
+          <t>Vicolo del Bologna, 19</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>334/3351068</t>
+          <t>342/3006808</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>www.enotecalantidoto.com</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>enotecalantidoto</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>enotecalantidoto</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20275,14 +20247,14 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '08', 'closes': '21:30'}, 'venerdì': {'opens': '08', 'clos</t>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>Rating Google: 3.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (enotecalantidoto) | IG: trovato (enotecalantidoto)</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -20294,17 +20266,42 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Cheebo</t>
+          <t>Il Goccetto</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Via Aretusa, 6</t>
+          <t>Via dei Banchi Vecchi, 14</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>351/7598556</t>
+          <t>06/99448583</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>www.ilgoccetto.com</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Ilgoccetto</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Ilgoccetto</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20319,12 +20316,17 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '14:30, 22:30', 'break': '14:30–</t>
+          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (Ilgoccetto) | IG: trovato (Ilgoccetto)</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -20336,17 +20338,42 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Dondolo</t>
+          <t>LATTA - Fermenti e miscele</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Via di Monte Sacro, 23</t>
+          <t>Via Antonio Pacinotti, 83</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>06/45752197</t>
+          <t>06/88923791</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>www.latta-roma.it</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>lattaroma</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>latta_roma</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20361,12 +20388,17 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '18', 'closes': '23'}, 'venerdì': {'opens': '18', 'closes'</t>
+          <t>{'giovedì': {'opens': '17', 'closes': '01'}, 'venerdì': {'opens': '17', 'closes'</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (lattaroma) | IG: trovato (latta_roma)</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -20378,17 +20410,37 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>MAE - Slow Brunchers</t>
+          <t>Metà - sorsi e assaggi</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Via della Giuliana, 33</t>
+          <t>Viale Gottardo, 18/20</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>06/98874558</t>
+          <t>320/9563284</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>profile.php?id=100076435981688</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>meta_roma</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20401,9 +20453,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100076435981688) | IG: trovato (meta_roma)</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -20415,17 +20472,42 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>19.2 Winebar Enoteca</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Largo Benito Jacovitti, 16</t>
+          <t>Via Flaminia, 732/B</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>347/4387426</t>
+          <t>06/3337879</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>www.minefleming.com</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>minebistrobottega</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>minefleming</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20438,9 +20520,19 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '00'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (minebistrobottega) | IG: trovato (minefleming)</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -20452,17 +20544,42 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Bosco - Officine del Tartufo</t>
+          <t>Mostò</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Via Macerata, 8/C</t>
+          <t>Viale Pinturicchio, 32</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>06/701 8134</t>
+          <t>392/2579616</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>www.enotecamosto.it</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>enotecamosto</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>enotecamosto</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20477,2023 +20594,1973 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12:30, 18:30', 'closes': '14:30, 23', 'break': '14:30–18:</t>
+          <t>{'giovedì': {'opens': '17:30', 'closes': '23:30'}, 'venerdì': {'opens': '17:30',</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q329" t="inlineStr">
         <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (enotecamosto) | IG: trovato (enotecamosto)</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>Bless</t>
+        </is>
+      </c>
+      <c r="B330" s="1" t="inlineStr">
+        <is>
+          <t>Via dell’Indipendenza, 208</t>
+        </is>
+      </c>
+      <c r="C330" s="1" t="inlineStr">
+        <is>
+          <t>0771/030188</t>
+        </is>
+      </c>
+      <c r="D330" s="1" t="inlineStr"/>
+      <c r="E330" s="1" t="inlineStr"/>
+      <c r="F330" s="1" t="inlineStr"/>
+      <c r="G330" s="1" t="inlineStr"/>
+      <c r="H330" s="1" t="inlineStr"/>
+      <c r="I330" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J330" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K330" s="1" t="inlineStr"/>
+      <c r="L330" s="1" t="inlineStr"/>
+      <c r="M330" s="1" t="inlineStr"/>
+      <c r="N330" s="1" t="inlineStr"/>
+      <c r="O330" s="1" t="inlineStr"/>
+      <c r="P330" s="1" t="inlineStr"/>
+      <c r="Q330" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R330" s="1" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>Mrgda Ristorante</t>
+        </is>
+      </c>
+      <c r="B331" s="1" t="inlineStr">
+        <is>
+          <t>Via Prenestina, 182</t>
+        </is>
+      </c>
+      <c r="C331" s="1" t="inlineStr">
+        <is>
+          <t>329/933355</t>
+        </is>
+      </c>
+      <c r="D331" s="1" t="inlineStr"/>
+      <c r="E331" s="1" t="inlineStr"/>
+      <c r="F331" s="1" t="inlineStr"/>
+      <c r="G331" s="1" t="inlineStr"/>
+      <c r="H331" s="1" t="inlineStr"/>
+      <c r="I331" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J331" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K331" s="1" t="inlineStr"/>
+      <c r="L331" s="1" t="inlineStr"/>
+      <c r="M331" s="1" t="inlineStr"/>
+      <c r="N331" s="1" t="inlineStr"/>
+      <c r="O331" s="1" t="inlineStr"/>
+      <c r="P331" s="1" t="inlineStr"/>
+      <c r="Q331" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R331" s="1" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>Clementina</t>
+        </is>
+      </c>
+      <c r="B332" s="1" t="inlineStr">
+        <is>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C332" s="1" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
+      <c r="D332" s="1" t="inlineStr"/>
+      <c r="E332" s="1" t="inlineStr"/>
+      <c r="F332" s="1" t="inlineStr"/>
+      <c r="G332" s="1" t="inlineStr"/>
+      <c r="H332" s="1" t="inlineStr"/>
+      <c r="I332" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J332" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K332" s="1" t="inlineStr"/>
+      <c r="L332" s="1" t="inlineStr"/>
+      <c r="M332" s="1" t="inlineStr"/>
+      <c r="N332" s="1" t="inlineStr"/>
+      <c r="O332" s="1" t="inlineStr"/>
+      <c r="P332" s="1" t="inlineStr"/>
+      <c r="Q332" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R332" s="1" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>Da Antonio</t>
+        </is>
+      </c>
+      <c r="B333" s="1" t="inlineStr">
+        <is>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C333" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
+      <c r="D333" s="1" t="inlineStr"/>
+      <c r="E333" s="1" t="inlineStr"/>
+      <c r="F333" s="1" t="inlineStr"/>
+      <c r="G333" s="1" t="inlineStr"/>
+      <c r="H333" s="1" t="inlineStr"/>
+      <c r="I333" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J333" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K333" s="1" t="inlineStr"/>
+      <c r="L333" s="1" t="inlineStr"/>
+      <c r="M333" s="1" t="inlineStr"/>
+      <c r="N333" s="1" t="inlineStr"/>
+      <c r="O333" s="1" t="inlineStr"/>
+      <c r="P333" s="1" t="inlineStr"/>
+      <c r="Q333" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R333" s="1" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>Pupillo Pura Pizza</t>
+        </is>
+      </c>
+      <c r="B334" s="1" t="inlineStr">
+        <is>
+          <t>Via Giacomo Matteotti, 29</t>
+        </is>
+      </c>
+      <c r="C334" s="1" t="inlineStr">
+        <is>
+          <t>339/4143148</t>
+        </is>
+      </c>
+      <c r="D334" s="1" t="inlineStr"/>
+      <c r="E334" s="1" t="inlineStr"/>
+      <c r="F334" s="1" t="inlineStr"/>
+      <c r="G334" s="1" t="inlineStr"/>
+      <c r="H334" s="1" t="inlineStr"/>
+      <c r="I334" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J334" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K334" s="1" t="inlineStr"/>
+      <c r="L334" s="1" t="inlineStr"/>
+      <c r="M334" s="1" t="inlineStr"/>
+      <c r="N334" s="1" t="inlineStr"/>
+      <c r="O334" s="1" t="inlineStr"/>
+      <c r="P334" s="1" t="inlineStr"/>
+      <c r="Q334" s="1" t="inlineStr">
+        <is>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R334" s="1" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>Il tuo fornaio</t>
+        </is>
+      </c>
+      <c r="B335" s="1" t="inlineStr">
+        <is>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C335" s="1" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
+      <c r="D335" s="1" t="inlineStr"/>
+      <c r="E335" s="1" t="inlineStr"/>
+      <c r="F335" s="1" t="inlineStr"/>
+      <c r="G335" s="1" t="inlineStr"/>
+      <c r="H335" s="1" t="inlineStr"/>
+      <c r="I335" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J335" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K335" s="1" t="inlineStr"/>
+      <c r="L335" s="1" t="inlineStr"/>
+      <c r="M335" s="1" t="inlineStr"/>
+      <c r="N335" s="1" t="inlineStr"/>
+      <c r="O335" s="1" t="inlineStr"/>
+      <c r="P335" s="1" t="inlineStr"/>
+      <c r="Q335" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R335" s="1" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="B336" s="1" t="inlineStr">
+        <is>
+          <t>Corso Vittorio Emanuele II, 73</t>
+        </is>
+      </c>
+      <c r="C336" s="1" t="inlineStr"/>
+      <c r="D336" s="1" t="inlineStr"/>
+      <c r="E336" s="1" t="inlineStr"/>
+      <c r="F336" s="1" t="inlineStr"/>
+      <c r="G336" s="1" t="inlineStr"/>
+      <c r="H336" s="1" t="inlineStr"/>
+      <c r="I336" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J336" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K336" s="1" t="inlineStr"/>
+      <c r="L336" s="1" t="inlineStr"/>
+      <c r="M336" s="1" t="inlineStr"/>
+      <c r="N336" s="1" t="inlineStr"/>
+      <c r="O336" s="1" t="inlineStr"/>
+      <c r="P336" s="1" t="inlineStr"/>
+      <c r="Q336" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R336" s="1" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>oWine</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Via Guido de Ruggiero, 64</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>06/95938970</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '17', 'closes': '01'}, 'martedì': {'opens': 'Chiuso'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Piano C - Circolo del vino</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Via Faleria, 12</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>06/97278919</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>www.pianoccircolodelvino.com</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>PianoCcircolodelvino</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>pianoc_circolodelvino</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (PianoCcircolodelvino) | IG: non trovato (pianoc_circolodelvino)</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Sottobanco</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Via Paolo Frisi, 1</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>06/85857447</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>www.sottobancoroma.it</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>aipianisottobanco</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>aipianisottobanco</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18:30', 'closes': '01'}, '</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (aipianisottobanco) | IG: non trovato (aipianisottobanco)</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Spaccio Grosso</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Via Ancona, 40</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>331/4428878</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>www.spacciogrosso.it</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Spacciogross0</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>_spacciogrosso</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '17:30', 'closes': '23'}, 'martedì': {'opens': '12:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Spacciogross0) | IG: non trovato (_spacciogrosso)</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Tante Care Cose</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Via Carlo Errera, 46</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>tantecarecosearoma</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '23'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (tantecarecosearoma)</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Aromaticus</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Via Natale del Grande, 6/7</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>06/88798381</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>www.aromaticus.it</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>ArOmAticUs</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>aromaticus_</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '10', 'closes': '22:30'}, '</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (ArOmAticUs) | IG: non trovato (aromaticus_)</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Avanvera</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Via Luigi Tosti, 33</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>06/45596021</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>www.avanveraroma.it</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>avanveraroma</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>avanveraroma</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '00'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (avanveraroma) | IG: non trovato (avanveraroma)</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Ciaparat</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Piazza San Donà del Piave, 14</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>06/89716513</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Ciaparat-Enoteca-100092133858205</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>ciaparat_enoteca</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '00'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Ciaparat-Enoteca-100092133858205) | IG: non trovato (ciaparat_enoteca)</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Concreto Cucina e Vino</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Via Marianna Dionigi, 4</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>06/5415084</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
           <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
-      <c r="R329" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Duke's - Fine Casual Bar &amp; Restaurant</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Viale Parioli, 200</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>06/80662455</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Dumpling Bar</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Piazza Antonio Meucci, 1</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>344/0658913</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>www.dumplingbar.it</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>dumplingbarroma</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>dumplingbarroma</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Q330" t="inlineStr">
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19', 'closes': '15,</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (dumplingbarroma) | IG: non trovato (dumplingbarroma)</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Enofficina</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Via Trionfale, 50</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>06/39742353</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>enofficina</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>enofficina_roma</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (enofficina) | IG: non trovato (enofficina_roma)</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Enoteca La Mescita</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Via Luigi Fincati, 44</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>333/3015847</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>www.enotecalamescita.it</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>enotecalamescita</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>enotecalamescita</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '01'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (enotecalamescita) | IG: non trovato (enotecalamescita)</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Er Macellaio</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Viale Aurelio Galleppini, 60/66</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>06/52831571</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
         <is>
           <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
-      <c r="R330" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Enoteca L'Antidoto</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Vicolo del Bologna, 19</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>342/3006808</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>www.enotecalantidoto.com</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>enotecalantidoto</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>enotecalantidoto</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Ie Koji Sakaba</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Via Emilio Faà di Bruno, 31</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>392/4799773</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O331" t="inlineStr">
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '23'}, 'martedì': {'opens': '19:30', 'cl</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Indigeno - Osteria Ribelle</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Via Renzo da Ceri, 6/6A</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>389/4358878</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>indigenoroma</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q331" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (enotecalantidoto) | IG: trovato (enotecalantidoto)</t>
-        </is>
-      </c>
-      <c r="R331" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Il Goccetto</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Via dei Banchi Vecchi, 14</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>06/99448583</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>www.ilgoccetto.com</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>Ilgoccetto</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>Ilgoccetto</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (indigenoroma) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Lento - Vineria con Cucina</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Piazza di Santa Maria Ausiliatrice, 17/18</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>327/9470778</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>lentoroma</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
-        </is>
-      </c>
-      <c r="O332" t="inlineStr">
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (lentoroma)</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Magazzino Scipioni</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Via degli Scipioni, 30-30/A</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>06/39745233</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '17:30', 'closes': '01'}, '</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Open Baladin</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Via degli Specchi, 6</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>06/6838989</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>www.baladin.it/open-baladin-roma</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>openbaladin.roma.5</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>openbaladinroma</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '01'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q332" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (Ilgoccetto) | IG: trovato (Ilgoccetto)</t>
-        </is>
-      </c>
-      <c r="R332" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>LATTA - Fermenti e miscele</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Via Antonio Pacinotti, 83</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>06/88923791</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>www.latta-roma.it</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>lattaroma</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>latta_roma</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr">
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (openbaladin.roma.5) | IG: non trovato (openbaladinroma)</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Santí - tradizione contadina</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Via Latina, 80</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>06/86675708</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>santitradizionecontadina</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>santi_tradizionecontadina</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M333" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '17', 'closes': '01'}, 'venerdì': {'opens': '17', 'closes'</t>
-        </is>
-      </c>
-      <c r="O333" t="inlineStr">
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18:30', 'closes': '23:30'}, 'martedì': {'opens': 'Chiuso'}</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q333" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (lattaroma) | IG: trovato (latta_roma)</t>
-        </is>
-      </c>
-      <c r="R333" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Metà - sorsi e assaggi</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Viale Gottardo, 18/20</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>320/9563284</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>profile.php?id=100076435981688</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>meta_roma</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (santitradizionecontadina) | IG: non trovato (santi_tradizionecontadina)</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Scima</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Via Annia Regilla, 110</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>339/8743355</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Scima-Roma-61561040349051</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>scima_roma</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (Scima-Roma-61561040349051) | IG: non trovato (scima_roma)</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Taps</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Via Gaio Melisso, 32</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>370/1411858</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>www.lynnpeakbeer.com</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>lynnpeakbeer</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>tapsroma</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (lynnpeakbeer) | IG: non trovato (tapsroma)</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Vineria Risorgimento</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Piazza del Risorgimento, 7</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>06/89533745</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="O334" t="inlineStr">
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11', 'closes': '00'}, 'martedì': {'opens': '11', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Vinificio</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Piazza dell’Emporio, 1</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>389/1798451</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>www.vinificionaturale.it</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>vinificioroma</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>vinificio_roma</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q334" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100076435981688) | IG: trovato (meta_roma)</t>
-        </is>
-      </c>
-      <c r="R334" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Mine</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Via Flaminia, 732/B</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>06/3337879</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>www.minefleming.com</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>minebistrobottega</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>minefleming</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (vinificioroma) | IG: non trovato (vinificio_roma)</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Da Brando</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Via Flaminia, 532</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>06/33225327</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>dabrandoristorante</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>da.brando</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M335" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '18', 'closes': '00'}, 'venerdì': {'opens': '18', 'closes'</t>
-        </is>
-      </c>
-      <c r="O335" t="inlineStr">
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '01'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q335" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (minebistrobottega) | IG: trovato (minefleming)</t>
-        </is>
-      </c>
-      <c r="R335" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Mostò</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Viale Pinturicchio, 32</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>392/2579616</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>www.enotecamosto.it</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>enotecamosto</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>enotecamosto</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr">
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: trovato (dabrandoristorante) | IG: non trovato (da.brando)</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Drink Kong</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Piazza di San Martino ai Monti, 8</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>06/23488666</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>www.drinkkong.com</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>drinkkong</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>drinkkongbar</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '17:30', 'closes': '23:30'}, 'venerdì': {'opens': '17:30',</t>
-        </is>
-      </c>
-      <c r="O336" t="inlineStr">
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18:30', 'closes': '02'}, 'martedì': {'opens': '18:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q336" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (enotecamosto) | IG: trovato (enotecamosto)</t>
-        </is>
-      </c>
-      <c r="R336" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="1" t="inlineStr">
-        <is>
-          <t>oWine</t>
-        </is>
-      </c>
-      <c r="B337" s="1" t="inlineStr">
-        <is>
-          <t>Via Guido de Ruggiero, 64</t>
-        </is>
-      </c>
-      <c r="C337" s="1" t="inlineStr">
-        <is>
-          <t>06/95938970</t>
-        </is>
-      </c>
-      <c r="D337" s="1" t="inlineStr"/>
-      <c r="E337" s="1" t="inlineStr"/>
-      <c r="F337" s="1" t="inlineStr"/>
-      <c r="G337" s="1" t="inlineStr"/>
-      <c r="H337" s="1" t="inlineStr"/>
-      <c r="I337" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J337" s="1" t="inlineStr"/>
-      <c r="K337" s="1" t="inlineStr"/>
-      <c r="L337" s="1" t="inlineStr"/>
-      <c r="M337" s="1" t="inlineStr"/>
-      <c r="N337" s="1" t="inlineStr"/>
-      <c r="O337" s="1" t="inlineStr"/>
-      <c r="P337" s="1" t="inlineStr"/>
-      <c r="Q337" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R337" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="1" t="inlineStr">
-        <is>
-          <t>Piano C - Circolo del vino</t>
-        </is>
-      </c>
-      <c r="B338" s="1" t="inlineStr">
-        <is>
-          <t>Via Faleria, 12</t>
-        </is>
-      </c>
-      <c r="C338" s="1" t="inlineStr">
-        <is>
-          <t>06/97278919</t>
-        </is>
-      </c>
-      <c r="D338" s="1" t="inlineStr">
-        <is>
-          <t>www.pianoccircolodelvino.com</t>
-        </is>
-      </c>
-      <c r="E338" s="1" t="inlineStr">
-        <is>
-          <t>PianoCcircolodelvino</t>
-        </is>
-      </c>
-      <c r="F338" s="1" t="inlineStr">
-        <is>
-          <t>pianoc_circolodelvino</t>
-        </is>
-      </c>
-      <c r="G338" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H338" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I338" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J338" s="1" t="inlineStr"/>
-      <c r="K338" s="1" t="inlineStr"/>
-      <c r="L338" s="1" t="inlineStr"/>
-      <c r="M338" s="1" t="inlineStr"/>
-      <c r="N338" s="1" t="inlineStr"/>
-      <c r="O338" s="1" t="inlineStr"/>
-      <c r="P338" s="1" t="inlineStr"/>
-      <c r="Q338" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R338" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="1" t="inlineStr">
-        <is>
-          <t>Sottobanco</t>
-        </is>
-      </c>
-      <c r="B339" s="1" t="inlineStr">
-        <is>
-          <t>Via Paolo Frisi, 1</t>
-        </is>
-      </c>
-      <c r="C339" s="1" t="inlineStr">
-        <is>
-          <t>06/85857447</t>
-        </is>
-      </c>
-      <c r="D339" s="1" t="inlineStr">
-        <is>
-          <t>www.sottobancoroma.it</t>
-        </is>
-      </c>
-      <c r="E339" s="1" t="inlineStr">
-        <is>
-          <t>aipianisottobanco</t>
-        </is>
-      </c>
-      <c r="F339" s="1" t="inlineStr">
-        <is>
-          <t>aipianisottobanco</t>
-        </is>
-      </c>
-      <c r="G339" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H339" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I339" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J339" s="1" t="inlineStr"/>
-      <c r="K339" s="1" t="inlineStr"/>
-      <c r="L339" s="1" t="inlineStr"/>
-      <c r="M339" s="1" t="inlineStr"/>
-      <c r="N339" s="1" t="inlineStr"/>
-      <c r="O339" s="1" t="inlineStr"/>
-      <c r="P339" s="1" t="inlineStr"/>
-      <c r="Q339" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R339" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="1" t="inlineStr">
-        <is>
-          <t>Spaccio Grosso</t>
-        </is>
-      </c>
-      <c r="B340" s="1" t="inlineStr">
-        <is>
-          <t>Via Ancona, 40</t>
-        </is>
-      </c>
-      <c r="C340" s="1" t="inlineStr">
-        <is>
-          <t>331/4428878</t>
-        </is>
-      </c>
-      <c r="D340" s="1" t="inlineStr">
-        <is>
-          <t>www.spacciogrosso.it</t>
-        </is>
-      </c>
-      <c r="E340" s="1" t="inlineStr">
-        <is>
-          <t>Spacciogross0</t>
-        </is>
-      </c>
-      <c r="F340" s="1" t="inlineStr">
-        <is>
-          <t>_spacciogrosso</t>
-        </is>
-      </c>
-      <c r="G340" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H340" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I340" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J340" s="1" t="inlineStr"/>
-      <c r="K340" s="1" t="inlineStr"/>
-      <c r="L340" s="1" t="inlineStr"/>
-      <c r="M340" s="1" t="inlineStr"/>
-      <c r="N340" s="1" t="inlineStr"/>
-      <c r="O340" s="1" t="inlineStr"/>
-      <c r="P340" s="1" t="inlineStr"/>
-      <c r="Q340" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R340" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="1" t="inlineStr">
-        <is>
-          <t>Tante Care Cose</t>
-        </is>
-      </c>
-      <c r="B341" s="1" t="inlineStr">
-        <is>
-          <t>Via Carlo Errera, 46</t>
-        </is>
-      </c>
-      <c r="C341" s="1" t="inlineStr">
-        <is>
-          <t>n.d.</t>
-        </is>
-      </c>
-      <c r="D341" s="1" t="inlineStr"/>
-      <c r="E341" s="1" t="inlineStr"/>
-      <c r="F341" s="1" t="inlineStr">
-        <is>
-          <t>tantecarecosearoma</t>
-        </is>
-      </c>
-      <c r="G341" s="1" t="inlineStr"/>
-      <c r="H341" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I341" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J341" s="1" t="inlineStr"/>
-      <c r="K341" s="1" t="inlineStr"/>
-      <c r="L341" s="1" t="inlineStr"/>
-      <c r="M341" s="1" t="inlineStr"/>
-      <c r="N341" s="1" t="inlineStr"/>
-      <c r="O341" s="1" t="inlineStr"/>
-      <c r="P341" s="1" t="inlineStr"/>
-      <c r="Q341" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R341" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="1" t="inlineStr">
-        <is>
-          <t>Aromaticus</t>
-        </is>
-      </c>
-      <c r="B342" s="1" t="inlineStr">
-        <is>
-          <t>Via Natale del Grande, 6/7</t>
-        </is>
-      </c>
-      <c r="C342" s="1" t="inlineStr">
-        <is>
-          <t>06/88798381</t>
-        </is>
-      </c>
-      <c r="D342" s="1" t="inlineStr">
-        <is>
-          <t>www.aromaticus.it</t>
-        </is>
-      </c>
-      <c r="E342" s="1" t="inlineStr">
-        <is>
-          <t>ArOmAticUs</t>
-        </is>
-      </c>
-      <c r="F342" s="1" t="inlineStr">
-        <is>
-          <t>aromaticus_</t>
-        </is>
-      </c>
-      <c r="G342" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H342" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I342" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J342" s="1" t="inlineStr"/>
-      <c r="K342" s="1" t="inlineStr"/>
-      <c r="L342" s="1" t="inlineStr"/>
-      <c r="M342" s="1" t="inlineStr"/>
-      <c r="N342" s="1" t="inlineStr"/>
-      <c r="O342" s="1" t="inlineStr"/>
-      <c r="P342" s="1" t="inlineStr"/>
-      <c r="Q342" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R342" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="1" t="inlineStr">
-        <is>
-          <t>Avanvera</t>
-        </is>
-      </c>
-      <c r="B343" s="1" t="inlineStr">
-        <is>
-          <t>Via Luigi Tosti, 33</t>
-        </is>
-      </c>
-      <c r="C343" s="1" t="inlineStr">
-        <is>
-          <t>06/45596021</t>
-        </is>
-      </c>
-      <c r="D343" s="1" t="inlineStr">
-        <is>
-          <t>www.avanveraroma.it</t>
-        </is>
-      </c>
-      <c r="E343" s="1" t="inlineStr">
-        <is>
-          <t>avanveraroma</t>
-        </is>
-      </c>
-      <c r="F343" s="1" t="inlineStr">
-        <is>
-          <t>avanveraroma</t>
-        </is>
-      </c>
-      <c r="G343" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H343" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I343" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J343" s="1" t="inlineStr"/>
-      <c r="K343" s="1" t="inlineStr"/>
-      <c r="L343" s="1" t="inlineStr"/>
-      <c r="M343" s="1" t="inlineStr"/>
-      <c r="N343" s="1" t="inlineStr"/>
-      <c r="O343" s="1" t="inlineStr"/>
-      <c r="P343" s="1" t="inlineStr"/>
-      <c r="Q343" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R343" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="1" t="inlineStr">
-        <is>
-          <t>Ciaparat</t>
-        </is>
-      </c>
-      <c r="B344" s="1" t="inlineStr">
-        <is>
-          <t>Piazza San Donà del Piave, 14</t>
-        </is>
-      </c>
-      <c r="C344" s="1" t="inlineStr">
-        <is>
-          <t>06/89716513</t>
-        </is>
-      </c>
-      <c r="D344" s="1" t="inlineStr"/>
-      <c r="E344" s="1" t="inlineStr">
-        <is>
-          <t>Ciaparat-Enoteca-100092133858205</t>
-        </is>
-      </c>
-      <c r="F344" s="1" t="inlineStr">
-        <is>
-          <t>ciaparat_enoteca</t>
-        </is>
-      </c>
-      <c r="G344" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H344" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I344" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J344" s="1" t="inlineStr"/>
-      <c r="K344" s="1" t="inlineStr"/>
-      <c r="L344" s="1" t="inlineStr"/>
-      <c r="M344" s="1" t="inlineStr"/>
-      <c r="N344" s="1" t="inlineStr"/>
-      <c r="O344" s="1" t="inlineStr"/>
-      <c r="P344" s="1" t="inlineStr"/>
-      <c r="Q344" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R344" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="1" t="inlineStr">
-        <is>
-          <t>Concreto Cucina e Vino</t>
-        </is>
-      </c>
-      <c r="B345" s="1" t="inlineStr">
-        <is>
-          <t>Via Marianna Dionigi, 4</t>
-        </is>
-      </c>
-      <c r="C345" s="1" t="inlineStr">
-        <is>
-          <t>06/5415084</t>
-        </is>
-      </c>
-      <c r="D345" s="1" t="inlineStr"/>
-      <c r="E345" s="1" t="inlineStr"/>
-      <c r="F345" s="1" t="inlineStr"/>
-      <c r="G345" s="1" t="inlineStr"/>
-      <c r="H345" s="1" t="inlineStr"/>
-      <c r="I345" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J345" s="1" t="inlineStr"/>
-      <c r="K345" s="1" t="inlineStr"/>
-      <c r="L345" s="1" t="inlineStr"/>
-      <c r="M345" s="1" t="inlineStr"/>
-      <c r="N345" s="1" t="inlineStr"/>
-      <c r="O345" s="1" t="inlineStr"/>
-      <c r="P345" s="1" t="inlineStr"/>
-      <c r="Q345" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R345" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="1" t="inlineStr">
-        <is>
-          <t>Dumpling Bar</t>
-        </is>
-      </c>
-      <c r="B346" s="1" t="inlineStr">
-        <is>
-          <t>Piazza Antonio Meucci, 1</t>
-        </is>
-      </c>
-      <c r="C346" s="1" t="inlineStr">
-        <is>
-          <t>344/0658913</t>
-        </is>
-      </c>
-      <c r="D346" s="1" t="inlineStr">
-        <is>
-          <t>www.dumplingbar.it</t>
-        </is>
-      </c>
-      <c r="E346" s="1" t="inlineStr">
-        <is>
-          <t>dumplingbarroma</t>
-        </is>
-      </c>
-      <c r="F346" s="1" t="inlineStr">
-        <is>
-          <t>dumplingbarroma</t>
-        </is>
-      </c>
-      <c r="G346" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H346" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I346" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J346" s="1" t="inlineStr"/>
-      <c r="K346" s="1" t="inlineStr"/>
-      <c r="L346" s="1" t="inlineStr"/>
-      <c r="M346" s="1" t="inlineStr"/>
-      <c r="N346" s="1" t="inlineStr"/>
-      <c r="O346" s="1" t="inlineStr"/>
-      <c r="P346" s="1" t="inlineStr"/>
-      <c r="Q346" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R346" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="1" t="inlineStr">
-        <is>
-          <t>Enofficina</t>
-        </is>
-      </c>
-      <c r="B347" s="1" t="inlineStr">
-        <is>
-          <t>Via Trionfale, 50</t>
-        </is>
-      </c>
-      <c r="C347" s="1" t="inlineStr">
-        <is>
-          <t>06/39742353</t>
-        </is>
-      </c>
-      <c r="D347" s="1" t="inlineStr"/>
-      <c r="E347" s="1" t="inlineStr">
-        <is>
-          <t>enofficina</t>
-        </is>
-      </c>
-      <c r="F347" s="1" t="inlineStr">
-        <is>
-          <t>enofficina_roma</t>
-        </is>
-      </c>
-      <c r="G347" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H347" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I347" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J347" s="1" t="inlineStr"/>
-      <c r="K347" s="1" t="inlineStr"/>
-      <c r="L347" s="1" t="inlineStr"/>
-      <c r="M347" s="1" t="inlineStr"/>
-      <c r="N347" s="1" t="inlineStr"/>
-      <c r="O347" s="1" t="inlineStr"/>
-      <c r="P347" s="1" t="inlineStr"/>
-      <c r="Q347" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R347" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="1" t="inlineStr">
-        <is>
-          <t>Enoteca La Mescita</t>
-        </is>
-      </c>
-      <c r="B348" s="1" t="inlineStr">
-        <is>
-          <t>Via Luigi Fincati, 44</t>
-        </is>
-      </c>
-      <c r="C348" s="1" t="inlineStr">
-        <is>
-          <t>333/3015847</t>
-        </is>
-      </c>
-      <c r="D348" s="1" t="inlineStr">
-        <is>
-          <t>www.enotecalamescita.it</t>
-        </is>
-      </c>
-      <c r="E348" s="1" t="inlineStr">
-        <is>
-          <t>enotecalamescita</t>
-        </is>
-      </c>
-      <c r="F348" s="1" t="inlineStr">
-        <is>
-          <t>enotecalamescita</t>
-        </is>
-      </c>
-      <c r="G348" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H348" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I348" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J348" s="1" t="inlineStr"/>
-      <c r="K348" s="1" t="inlineStr"/>
-      <c r="L348" s="1" t="inlineStr"/>
-      <c r="M348" s="1" t="inlineStr"/>
-      <c r="N348" s="1" t="inlineStr"/>
-      <c r="O348" s="1" t="inlineStr"/>
-      <c r="P348" s="1" t="inlineStr"/>
-      <c r="Q348" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R348" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="1" t="inlineStr">
-        <is>
-          <t>Er Macellaio</t>
-        </is>
-      </c>
-      <c r="B349" s="1" t="inlineStr">
-        <is>
-          <t>Viale Aurelio Galleppini, 60/66</t>
-        </is>
-      </c>
-      <c r="C349" s="1" t="inlineStr">
-        <is>
-          <t>06/52831571</t>
-        </is>
-      </c>
-      <c r="D349" s="1" t="inlineStr"/>
-      <c r="E349" s="1" t="inlineStr"/>
-      <c r="F349" s="1" t="inlineStr"/>
-      <c r="G349" s="1" t="inlineStr"/>
-      <c r="H349" s="1" t="inlineStr"/>
-      <c r="I349" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J349" s="1" t="inlineStr"/>
-      <c r="K349" s="1" t="inlineStr"/>
-      <c r="L349" s="1" t="inlineStr"/>
-      <c r="M349" s="1" t="inlineStr"/>
-      <c r="N349" s="1" t="inlineStr"/>
-      <c r="O349" s="1" t="inlineStr"/>
-      <c r="P349" s="1" t="inlineStr"/>
-      <c r="Q349" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R349" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="1" t="inlineStr">
-        <is>
-          <t>Ie Koji Sakaba</t>
-        </is>
-      </c>
-      <c r="B350" s="1" t="inlineStr">
-        <is>
-          <t>Via Emilio Faà di Bruno, 31</t>
-        </is>
-      </c>
-      <c r="C350" s="1" t="inlineStr">
-        <is>
-          <t>392/4799773</t>
-        </is>
-      </c>
-      <c r="D350" s="1" t="inlineStr"/>
-      <c r="E350" s="1" t="inlineStr"/>
-      <c r="F350" s="1" t="inlineStr"/>
-      <c r="G350" s="1" t="inlineStr"/>
-      <c r="H350" s="1" t="inlineStr"/>
-      <c r="I350" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J350" s="1" t="inlineStr"/>
-      <c r="K350" s="1" t="inlineStr"/>
-      <c r="L350" s="1" t="inlineStr"/>
-      <c r="M350" s="1" t="inlineStr"/>
-      <c r="N350" s="1" t="inlineStr"/>
-      <c r="O350" s="1" t="inlineStr"/>
-      <c r="P350" s="1" t="inlineStr"/>
-      <c r="Q350" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R350" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="1" t="inlineStr">
-        <is>
-          <t>Indigeno - Osteria Ribelle</t>
-        </is>
-      </c>
-      <c r="B351" s="1" t="inlineStr">
-        <is>
-          <t>Via Renzo da Ceri, 6/6A</t>
-        </is>
-      </c>
-      <c r="C351" s="1" t="inlineStr">
-        <is>
-          <t>389/4358878</t>
-        </is>
-      </c>
-      <c r="D351" s="1" t="inlineStr"/>
-      <c r="E351" s="1" t="inlineStr">
-        <is>
-          <t>indigenoroma</t>
-        </is>
-      </c>
-      <c r="F351" s="1" t="inlineStr"/>
-      <c r="G351" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H351" s="1" t="inlineStr"/>
-      <c r="I351" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J351" s="1" t="inlineStr"/>
-      <c r="K351" s="1" t="inlineStr"/>
-      <c r="L351" s="1" t="inlineStr"/>
-      <c r="M351" s="1" t="inlineStr"/>
-      <c r="N351" s="1" t="inlineStr"/>
-      <c r="O351" s="1" t="inlineStr"/>
-      <c r="P351" s="1" t="inlineStr"/>
-      <c r="Q351" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R351" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="1" t="inlineStr">
-        <is>
-          <t>Lento - Vineria con Cucina</t>
-        </is>
-      </c>
-      <c r="B352" s="1" t="inlineStr">
-        <is>
-          <t>Piazza di Santa Maria Ausiliatrice, 17/18</t>
-        </is>
-      </c>
-      <c r="C352" s="1" t="inlineStr">
-        <is>
-          <t>327/9470778</t>
-        </is>
-      </c>
-      <c r="D352" s="1" t="inlineStr"/>
-      <c r="E352" s="1" t="inlineStr"/>
-      <c r="F352" s="1" t="inlineStr">
-        <is>
-          <t>lentoroma</t>
-        </is>
-      </c>
-      <c r="G352" s="1" t="inlineStr"/>
-      <c r="H352" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I352" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J352" s="1" t="inlineStr"/>
-      <c r="K352" s="1" t="inlineStr"/>
-      <c r="L352" s="1" t="inlineStr"/>
-      <c r="M352" s="1" t="inlineStr"/>
-      <c r="N352" s="1" t="inlineStr"/>
-      <c r="O352" s="1" t="inlineStr"/>
-      <c r="P352" s="1" t="inlineStr"/>
-      <c r="Q352" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R352" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="1" t="inlineStr">
-        <is>
-          <t>Magazzino Scipioni</t>
-        </is>
-      </c>
-      <c r="B353" s="1" t="inlineStr">
-        <is>
-          <t>Via degli Scipioni, 30-30/A</t>
-        </is>
-      </c>
-      <c r="C353" s="1" t="inlineStr">
-        <is>
-          <t>06/39745233</t>
-        </is>
-      </c>
-      <c r="D353" s="1" t="inlineStr"/>
-      <c r="E353" s="1" t="inlineStr"/>
-      <c r="F353" s="1" t="inlineStr"/>
-      <c r="G353" s="1" t="inlineStr"/>
-      <c r="H353" s="1" t="inlineStr"/>
-      <c r="I353" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J353" s="1" t="inlineStr"/>
-      <c r="K353" s="1" t="inlineStr"/>
-      <c r="L353" s="1" t="inlineStr"/>
-      <c r="M353" s="1" t="inlineStr"/>
-      <c r="N353" s="1" t="inlineStr"/>
-      <c r="O353" s="1" t="inlineStr"/>
-      <c r="P353" s="1" t="inlineStr"/>
-      <c r="Q353" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R353" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="1" t="inlineStr">
-        <is>
-          <t>Open Baladin</t>
-        </is>
-      </c>
-      <c r="B354" s="1" t="inlineStr">
-        <is>
-          <t>Via degli Specchi, 6</t>
-        </is>
-      </c>
-      <c r="C354" s="1" t="inlineStr">
-        <is>
-          <t>06/6838989</t>
-        </is>
-      </c>
-      <c r="D354" s="1" t="inlineStr">
-        <is>
-          <t>www.baladin.it/open-baladin-roma</t>
-        </is>
-      </c>
-      <c r="E354" s="1" t="inlineStr">
-        <is>
-          <t>openbaladin.roma.5</t>
-        </is>
-      </c>
-      <c r="F354" s="1" t="inlineStr">
-        <is>
-          <t>openbaladinroma</t>
-        </is>
-      </c>
-      <c r="G354" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H354" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I354" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J354" s="1" t="inlineStr"/>
-      <c r="K354" s="1" t="inlineStr"/>
-      <c r="L354" s="1" t="inlineStr"/>
-      <c r="M354" s="1" t="inlineStr"/>
-      <c r="N354" s="1" t="inlineStr"/>
-      <c r="O354" s="1" t="inlineStr"/>
-      <c r="P354" s="1" t="inlineStr"/>
-      <c r="Q354" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R354" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="1" t="inlineStr">
-        <is>
-          <t>Santí - tradizione contadina</t>
-        </is>
-      </c>
-      <c r="B355" s="1" t="inlineStr">
-        <is>
-          <t>Via Latina, 80</t>
-        </is>
-      </c>
-      <c r="C355" s="1" t="inlineStr">
-        <is>
-          <t>06/86675708</t>
-        </is>
-      </c>
-      <c r="D355" s="1" t="inlineStr"/>
-      <c r="E355" s="1" t="inlineStr">
-        <is>
-          <t>santitradizionecontadina</t>
-        </is>
-      </c>
-      <c r="F355" s="1" t="inlineStr">
-        <is>
-          <t>santi_tradizionecontadina</t>
-        </is>
-      </c>
-      <c r="G355" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H355" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I355" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J355" s="1" t="inlineStr"/>
-      <c r="K355" s="1" t="inlineStr"/>
-      <c r="L355" s="1" t="inlineStr"/>
-      <c r="M355" s="1" t="inlineStr"/>
-      <c r="N355" s="1" t="inlineStr"/>
-      <c r="O355" s="1" t="inlineStr"/>
-      <c r="P355" s="1" t="inlineStr"/>
-      <c r="Q355" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R355" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="1" t="inlineStr">
-        <is>
-          <t>Scima</t>
-        </is>
-      </c>
-      <c r="B356" s="1" t="inlineStr">
-        <is>
-          <t>Via Annia Regilla, 110</t>
-        </is>
-      </c>
-      <c r="C356" s="1" t="inlineStr">
-        <is>
-          <t>339/8743355</t>
-        </is>
-      </c>
-      <c r="D356" s="1" t="inlineStr"/>
-      <c r="E356" s="1" t="inlineStr">
-        <is>
-          <t>Scima-Roma-61561040349051</t>
-        </is>
-      </c>
-      <c r="F356" s="1" t="inlineStr">
-        <is>
-          <t>scima_roma</t>
-        </is>
-      </c>
-      <c r="G356" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H356" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I356" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J356" s="1" t="inlineStr"/>
-      <c r="K356" s="1" t="inlineStr"/>
-      <c r="L356" s="1" t="inlineStr"/>
-      <c r="M356" s="1" t="inlineStr"/>
-      <c r="N356" s="1" t="inlineStr"/>
-      <c r="O356" s="1" t="inlineStr"/>
-      <c r="P356" s="1" t="inlineStr"/>
-      <c r="Q356" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R356" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="1" t="inlineStr">
-        <is>
-          <t>Taps</t>
-        </is>
-      </c>
-      <c r="B357" s="1" t="inlineStr">
-        <is>
-          <t>Via Gaio Melisso, 32</t>
-        </is>
-      </c>
-      <c r="C357" s="1" t="inlineStr">
-        <is>
-          <t>370/1411858</t>
-        </is>
-      </c>
-      <c r="D357" s="1" t="inlineStr">
-        <is>
-          <t>www.lynnpeakbeer.com</t>
-        </is>
-      </c>
-      <c r="E357" s="1" t="inlineStr">
-        <is>
-          <t>lynnpeakbeer</t>
-        </is>
-      </c>
-      <c r="F357" s="1" t="inlineStr">
-        <is>
-          <t>tapsroma</t>
-        </is>
-      </c>
-      <c r="G357" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H357" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I357" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J357" s="1" t="inlineStr"/>
-      <c r="K357" s="1" t="inlineStr"/>
-      <c r="L357" s="1" t="inlineStr"/>
-      <c r="M357" s="1" t="inlineStr"/>
-      <c r="N357" s="1" t="inlineStr"/>
-      <c r="O357" s="1" t="inlineStr"/>
-      <c r="P357" s="1" t="inlineStr"/>
-      <c r="Q357" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R357" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="1" t="inlineStr">
-        <is>
-          <t>Vineria Risorgimento</t>
-        </is>
-      </c>
-      <c r="B358" s="1" t="inlineStr">
-        <is>
-          <t>Piazza del Risorgimento, 7</t>
-        </is>
-      </c>
-      <c r="C358" s="1" t="inlineStr">
-        <is>
-          <t>06/89533745</t>
-        </is>
-      </c>
-      <c r="D358" s="1" t="inlineStr"/>
-      <c r="E358" s="1" t="inlineStr"/>
-      <c r="F358" s="1" t="inlineStr"/>
-      <c r="G358" s="1" t="inlineStr"/>
-      <c r="H358" s="1" t="inlineStr"/>
-      <c r="I358" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J358" s="1" t="inlineStr"/>
-      <c r="K358" s="1" t="inlineStr"/>
-      <c r="L358" s="1" t="inlineStr"/>
-      <c r="M358" s="1" t="inlineStr"/>
-      <c r="N358" s="1" t="inlineStr"/>
-      <c r="O358" s="1" t="inlineStr"/>
-      <c r="P358" s="1" t="inlineStr"/>
-      <c r="Q358" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R358" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="1" t="inlineStr">
-        <is>
-          <t>Vinificio</t>
-        </is>
-      </c>
-      <c r="B359" s="1" t="inlineStr">
-        <is>
-          <t>Piazza dell’Emporio, 1</t>
-        </is>
-      </c>
-      <c r="C359" s="1" t="inlineStr">
-        <is>
-          <t>389/1798451</t>
-        </is>
-      </c>
-      <c r="D359" s="1" t="inlineStr">
-        <is>
-          <t>www.vinificionaturale.it</t>
-        </is>
-      </c>
-      <c r="E359" s="1" t="inlineStr">
-        <is>
-          <t>vinificioroma</t>
-        </is>
-      </c>
-      <c r="F359" s="1" t="inlineStr">
-        <is>
-          <t>vinificio_roma</t>
-        </is>
-      </c>
-      <c r="G359" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H359" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I359" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J359" s="1" t="inlineStr"/>
-      <c r="K359" s="1" t="inlineStr"/>
-      <c r="L359" s="1" t="inlineStr"/>
-      <c r="M359" s="1" t="inlineStr"/>
-      <c r="N359" s="1" t="inlineStr"/>
-      <c r="O359" s="1" t="inlineStr"/>
-      <c r="P359" s="1" t="inlineStr"/>
-      <c r="Q359" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R359" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="1" t="inlineStr">
-        <is>
-          <t>Da Brando</t>
-        </is>
-      </c>
-      <c r="B360" s="1" t="inlineStr">
-        <is>
-          <t>Via Flaminia, 532</t>
-        </is>
-      </c>
-      <c r="C360" s="1" t="inlineStr">
-        <is>
-          <t>06/33225327</t>
-        </is>
-      </c>
-      <c r="D360" s="1" t="inlineStr"/>
-      <c r="E360" s="1" t="inlineStr">
-        <is>
-          <t>dabrandoristorante</t>
-        </is>
-      </c>
-      <c r="F360" s="1" t="inlineStr">
-        <is>
-          <t>da.brando</t>
-        </is>
-      </c>
-      <c r="G360" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H360" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I360" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J360" s="1" t="inlineStr"/>
-      <c r="K360" s="1" t="inlineStr"/>
-      <c r="L360" s="1" t="inlineStr"/>
-      <c r="M360" s="1" t="inlineStr"/>
-      <c r="N360" s="1" t="inlineStr"/>
-      <c r="O360" s="1" t="inlineStr"/>
-      <c r="P360" s="1" t="inlineStr"/>
-      <c r="Q360" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R360" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="1" t="inlineStr">
-        <is>
-          <t>Drink Kong</t>
-        </is>
-      </c>
-      <c r="B361" s="1" t="inlineStr">
-        <is>
-          <t>Piazza di San Martino ai Monti, 8</t>
-        </is>
-      </c>
-      <c r="C361" s="1" t="inlineStr">
-        <is>
-          <t>06/23488666</t>
-        </is>
-      </c>
-      <c r="D361" s="1" t="inlineStr">
-        <is>
-          <t>www.drinkkong.com</t>
-        </is>
-      </c>
-      <c r="E361" s="1" t="inlineStr">
-        <is>
-          <t>drinkkong</t>
-        </is>
-      </c>
-      <c r="F361" s="1" t="inlineStr">
-        <is>
-          <t>drinkkongbar</t>
-        </is>
-      </c>
-      <c r="G361" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H361" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I361" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J361" s="1" t="inlineStr"/>
-      <c r="K361" s="1" t="inlineStr"/>
-      <c r="L361" s="1" t="inlineStr"/>
-      <c r="M361" s="1" t="inlineStr"/>
-      <c r="N361" s="1" t="inlineStr"/>
-      <c r="O361" s="1" t="inlineStr"/>
-      <c r="P361" s="1" t="inlineStr"/>
-      <c r="Q361" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R361" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (drinkkong) | IG: non trovato (drinkkongbar)</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="inlineStr">
+      <c r="A362" t="inlineStr">
         <is>
           <t>Jerry Thomas Speakeasy</t>
         </is>
       </c>
-      <c r="B362" s="1" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>Vicolo Cellini, 30</t>
         </is>
       </c>
-      <c r="C362" s="1" t="inlineStr">
+      <c r="C362" t="inlineStr">
         <is>
           <t>06/96845937</t>
         </is>
       </c>
-      <c r="D362" s="1" t="inlineStr">
+      <c r="D362" t="inlineStr">
         <is>
           <t>www.thejerrythomasproject.it</t>
         </is>
       </c>
-      <c r="E362" s="1" t="inlineStr">
+      <c r="E362" t="inlineStr">
         <is>
           <t>TheJerryThomas</t>
         </is>
       </c>
-      <c r="F362" s="1" t="inlineStr">
+      <c r="F362" t="inlineStr">
         <is>
           <t>jerrythomasproject_rome</t>
         </is>
       </c>
-      <c r="G362" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H362" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I362" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J362" s="1" t="inlineStr"/>
-      <c r="K362" s="1" t="inlineStr"/>
-      <c r="L362" s="1" t="inlineStr"/>
-      <c r="M362" s="1" t="inlineStr"/>
-      <c r="N362" s="1" t="inlineStr"/>
-      <c r="O362" s="1" t="inlineStr"/>
-      <c r="P362" s="1" t="inlineStr"/>
-      <c r="Q362" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R362" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '21', 'closes': '04:30'}, 'martedì': {'opens': '21', 'close</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (TheJerryThomas) | IG: non trovato (jerrythomasproject_rome)</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="inlineStr">
+      <c r="A363" t="inlineStr">
         <is>
           <t>Metropolita</t>
         </is>
       </c>
-      <c r="B363" s="1" t="inlineStr">
+      <c r="B363" t="inlineStr">
         <is>
           <t>Piazza Gentile da Fabriano, 2</t>
         </is>
       </c>
-      <c r="C363" s="1" t="inlineStr">
+      <c r="C363" t="inlineStr">
         <is>
           <t>06/84381895</t>
         </is>
       </c>
-      <c r="D363" s="1" t="inlineStr">
+      <c r="D363" t="inlineStr">
         <is>
           <t>www.metropolita.it</t>
         </is>
       </c>
-      <c r="E363" s="1" t="inlineStr">
+      <c r="E363" t="inlineStr">
         <is>
           <t>metropolita.roma</t>
         </is>
       </c>
-      <c r="F363" s="1" t="inlineStr">
+      <c r="F363" t="inlineStr">
         <is>
           <t>metropolita.roma</t>
         </is>
       </c>
-      <c r="G363" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H363" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I363" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J363" s="1" t="inlineStr"/>
-      <c r="K363" s="1" t="inlineStr"/>
-      <c r="L363" s="1" t="inlineStr"/>
-      <c r="M363" s="1" t="inlineStr"/>
-      <c r="N363" s="1" t="inlineStr"/>
-      <c r="O363" s="1" t="inlineStr"/>
-      <c r="P363" s="1" t="inlineStr"/>
-      <c r="Q363" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R363" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (metropolita.roma) | IG: non trovato (metropolita.roma)</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -20614,332 +20614,449 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B330" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C330" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D330" s="1" t="inlineStr"/>
-      <c r="E330" s="1" t="inlineStr"/>
-      <c r="F330" s="1" t="inlineStr"/>
-      <c r="G330" s="1" t="inlineStr"/>
-      <c r="H330" s="1" t="inlineStr"/>
-      <c r="I330" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J330" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K330" s="1" t="inlineStr"/>
-      <c r="L330" s="1" t="inlineStr"/>
-      <c r="M330" s="1" t="inlineStr"/>
-      <c r="N330" s="1" t="inlineStr"/>
-      <c r="O330" s="1" t="inlineStr"/>
-      <c r="P330" s="1" t="inlineStr"/>
-      <c r="Q330" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R330" s="1" t="inlineStr">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>oWine</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Via Guido de Ruggiero, 64</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>06/95938970</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '17', 'closes': '01'}, 'martedì': {'opens': 'Chiuso'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B331" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C331" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D331" s="1" t="inlineStr"/>
-      <c r="E331" s="1" t="inlineStr"/>
-      <c r="F331" s="1" t="inlineStr"/>
-      <c r="G331" s="1" t="inlineStr"/>
-      <c r="H331" s="1" t="inlineStr"/>
-      <c r="I331" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J331" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K331" s="1" t="inlineStr"/>
-      <c r="L331" s="1" t="inlineStr"/>
-      <c r="M331" s="1" t="inlineStr"/>
-      <c r="N331" s="1" t="inlineStr"/>
-      <c r="O331" s="1" t="inlineStr"/>
-      <c r="P331" s="1" t="inlineStr"/>
-      <c r="Q331" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R331" s="1" t="inlineStr">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Piano C - Circolo del vino</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Via Faleria, 12</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>06/97278919</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>www.pianoccircolodelvino.com</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>PianoCcircolodelvino</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>pianoc_circolodelvino</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (PianoCcircolodelvino) | IG: non trovato (pianoc_circolodelvino)</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="inlineStr">
-        <is>
-          <t>Clementina</t>
-        </is>
-      </c>
-      <c r="B332" s="1" t="inlineStr">
-        <is>
-          <t>Via della Torre Clementina, 158</t>
-        </is>
-      </c>
-      <c r="C332" s="1" t="inlineStr">
-        <is>
-          <t>328/8181651</t>
-        </is>
-      </c>
-      <c r="D332" s="1" t="inlineStr"/>
-      <c r="E332" s="1" t="inlineStr"/>
-      <c r="F332" s="1" t="inlineStr"/>
-      <c r="G332" s="1" t="inlineStr"/>
-      <c r="H332" s="1" t="inlineStr"/>
-      <c r="I332" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J332" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K332" s="1" t="inlineStr"/>
-      <c r="L332" s="1" t="inlineStr"/>
-      <c r="M332" s="1" t="inlineStr"/>
-      <c r="N332" s="1" t="inlineStr"/>
-      <c r="O332" s="1" t="inlineStr"/>
-      <c r="P332" s="1" t="inlineStr"/>
-      <c r="Q332" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R332" s="1" t="inlineStr">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Sottobanco</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Via Paolo Frisi, 1</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>06/85857447</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>www.sottobancoroma.it</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>aipianisottobanco</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>aipianisottobanco</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18:30', 'closes': '01'}, '</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (aipianisottobanco) | IG: non trovato (aipianisottobanco)</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="inlineStr">
-        <is>
-          <t>Da Antonio</t>
-        </is>
-      </c>
-      <c r="B333" s="1" t="inlineStr">
-        <is>
-          <t>Via Mario Lizzani, 21</t>
-        </is>
-      </c>
-      <c r="C333" s="1" t="inlineStr">
-        <is>
-          <t>391/7475549</t>
-        </is>
-      </c>
-      <c r="D333" s="1" t="inlineStr"/>
-      <c r="E333" s="1" t="inlineStr"/>
-      <c r="F333" s="1" t="inlineStr"/>
-      <c r="G333" s="1" t="inlineStr"/>
-      <c r="H333" s="1" t="inlineStr"/>
-      <c r="I333" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J333" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K333" s="1" t="inlineStr"/>
-      <c r="L333" s="1" t="inlineStr"/>
-      <c r="M333" s="1" t="inlineStr"/>
-      <c r="N333" s="1" t="inlineStr"/>
-      <c r="O333" s="1" t="inlineStr"/>
-      <c r="P333" s="1" t="inlineStr"/>
-      <c r="Q333" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R333" s="1" t="inlineStr">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Spaccio Grosso</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Via Ancona, 40</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>331/4428878</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>www.spacciogrosso.it</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Spacciogross0</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>_spacciogrosso</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '17:30', 'closes': '23'}, 'martedì': {'opens': '12:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Spacciogross0) | IG: non trovato (_spacciogrosso)</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="inlineStr">
-        <is>
-          <t>Pupillo Pura Pizza</t>
-        </is>
-      </c>
-      <c r="B334" s="1" t="inlineStr">
-        <is>
-          <t>Via Giacomo Matteotti, 29</t>
-        </is>
-      </c>
-      <c r="C334" s="1" t="inlineStr">
-        <is>
-          <t>339/4143148</t>
-        </is>
-      </c>
-      <c r="D334" s="1" t="inlineStr"/>
-      <c r="E334" s="1" t="inlineStr"/>
-      <c r="F334" s="1" t="inlineStr"/>
-      <c r="G334" s="1" t="inlineStr"/>
-      <c r="H334" s="1" t="inlineStr"/>
-      <c r="I334" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J334" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K334" s="1" t="inlineStr"/>
-      <c r="L334" s="1" t="inlineStr"/>
-      <c r="M334" s="1" t="inlineStr"/>
-      <c r="N334" s="1" t="inlineStr"/>
-      <c r="O334" s="1" t="inlineStr"/>
-      <c r="P334" s="1" t="inlineStr"/>
-      <c r="Q334" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R334" s="1" t="inlineStr">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Tante Care Cose</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Via Carlo Errera, 46</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>tantecarecosearoma</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '23'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (tantecarecosearoma)</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="inlineStr">
-        <is>
-          <t>Il tuo fornaio</t>
-        </is>
-      </c>
-      <c r="B335" s="1" t="inlineStr">
-        <is>
-          <t>Via Francesco Sapori, 35</t>
-        </is>
-      </c>
-      <c r="C335" s="1" t="inlineStr">
-        <is>
-          <t>06/5017873</t>
-        </is>
-      </c>
-      <c r="D335" s="1" t="inlineStr"/>
-      <c r="E335" s="1" t="inlineStr"/>
-      <c r="F335" s="1" t="inlineStr"/>
-      <c r="G335" s="1" t="inlineStr"/>
-      <c r="H335" s="1" t="inlineStr"/>
-      <c r="I335" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J335" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K335" s="1" t="inlineStr"/>
-      <c r="L335" s="1" t="inlineStr"/>
-      <c r="M335" s="1" t="inlineStr"/>
-      <c r="N335" s="1" t="inlineStr"/>
-      <c r="O335" s="1" t="inlineStr"/>
-      <c r="P335" s="1" t="inlineStr"/>
-      <c r="Q335" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R335" s="1" t="inlineStr">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Aromaticus</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Via Natale del Grande, 6/7</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>06/88798381</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>www.aromaticus.it</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>ArOmAticUs</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>aromaticus_</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '10', 'closes': '22:30'}, '</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (ArOmAticUs) | IG: non trovato (aromaticus_)</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="inlineStr">
-        <is>
-          <t>Slow</t>
-        </is>
-      </c>
-      <c r="B336" s="1" t="inlineStr">
-        <is>
-          <t>Corso Vittorio Emanuele II, 73</t>
-        </is>
-      </c>
-      <c r="C336" s="1" t="inlineStr"/>
-      <c r="D336" s="1" t="inlineStr"/>
-      <c r="E336" s="1" t="inlineStr"/>
-      <c r="F336" s="1" t="inlineStr"/>
-      <c r="G336" s="1" t="inlineStr"/>
-      <c r="H336" s="1" t="inlineStr"/>
-      <c r="I336" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J336" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K336" s="1" t="inlineStr"/>
-      <c r="L336" s="1" t="inlineStr"/>
-      <c r="M336" s="1" t="inlineStr"/>
-      <c r="N336" s="1" t="inlineStr"/>
-      <c r="O336" s="1" t="inlineStr"/>
-      <c r="P336" s="1" t="inlineStr"/>
-      <c r="Q336" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R336" s="1" t="inlineStr">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Avanvera</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Via Luigi Tosti, 33</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>06/45596021</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>www.avanveraroma.it</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>avanveraroma</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>avanveraroma</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '00'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (avanveraroma) | IG: non trovato (avanveraroma)</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
@@ -20948,17 +21065,37 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>oWine</t>
+          <t>Ciaparat</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Via Guido de Ruggiero, 64</t>
+          <t>Piazza San Donà del Piave, 14</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>06/95938970</t>
+          <t>06/89716513</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Ciaparat-Enoteca-100092133858205</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>ciaparat_enoteca</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -20973,12 +21110,17 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '17', 'closes': '01'}, 'martedì': {'opens': 'Chiuso'}, 'mer</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '00'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Ciaparat-Enoteca-100092133858205) | IG: non trovato (ciaparat_enoteca)</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -20990,42 +21132,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Piano C - Circolo del vino</t>
+          <t>Concreto Cucina e Vino</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Via Faleria, 12</t>
+          <t>Via Marianna Dionigi, 4</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>06/97278919</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>www.pianoccircolodelvino.com</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>PianoCcircolodelvino</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>pianoc_circolodelvino</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/5415084</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21038,14 +21155,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O338" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (PianoCcircolodelvino) | IG: non trovato (pianoc_circolodelvino)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -21057,32 +21169,32 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Sottobanco</t>
+          <t>Dumpling Bar</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Via Paolo Frisi, 1</t>
+          <t>Piazza Antonio Meucci, 1</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>06/85857447</t>
+          <t>344/0658913</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>www.sottobancoroma.it</t>
+          <t>www.dumplingbar.it</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>aipianisottobanco</t>
+          <t>dumplingbarroma</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>aipianisottobanco</t>
+          <t>dumplingbarroma</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -21107,7 +21219,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18:30', 'closes': '01'}, '</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19', 'closes': '15,</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -21117,7 +21229,7 @@
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (aipianisottobanco) | IG: non trovato (aipianisottobanco)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (dumplingbarroma) | IG: non trovato (dumplingbarroma)</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -21129,32 +21241,27 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Spaccio Grosso</t>
+          <t>Enofficina</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Via Ancona, 40</t>
+          <t>Via Trionfale, 50</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>331/4428878</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>www.spacciogrosso.it</t>
+          <t>06/39742353</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Spacciogross0</t>
+          <t>enofficina</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>_spacciogrosso</t>
+          <t>enofficina_roma</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -21177,11 +21284,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '17:30', 'closes': '23'}, 'martedì': {'opens': '12:30', 'cl</t>
-        </is>
-      </c>
       <c r="O340" t="inlineStr">
         <is>
           <t>Si</t>
@@ -21189,7 +21291,7 @@
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Spacciogross0) | IG: non trovato (_spacciogrosso)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (enofficina) | IG: non trovato (enofficina_roma)</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -21201,22 +21303,37 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Tante Care Cose</t>
+          <t>Enoteca La Mescita</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Via Carlo Errera, 46</t>
+          <t>Via Luigi Fincati, 44</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>333/3015847</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>www.enotecalamescita.it</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>enotecalamescita</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>tantecarecosearoma</t>
+          <t>enotecalamescita</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21236,12 +21353,17 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '23'}, 'mer</t>
+          <t>{'lunedì': {'opens': '18', 'closes': '01'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (tantecarecosearoma)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (enotecalamescita) | IG: non trovato (enotecalamescita)</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -21253,42 +21375,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Aromaticus</t>
+          <t>Er Macellaio</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Via Natale del Grande, 6/7</t>
+          <t>Viale Aurelio Galleppini, 60/66</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>06/88798381</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>www.aromaticus.it</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>ArOmAticUs</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>aromaticus_</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/52831571</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21301,19 +21398,9 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '10', 'closes': '22:30'}, '</t>
-        </is>
-      </c>
-      <c r="O342" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
       <c r="Q342" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (ArOmAticUs) | IG: non trovato (aromaticus_)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -21325,42 +21412,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Avanvera</t>
+          <t>Ie Koji Sakaba</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Via Luigi Tosti, 33</t>
+          <t>Via Emilio Faà di Bruno, 31</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>06/45596021</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>www.avanveraroma.it</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>avanveraroma</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>avanveraroma</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>392/4799773</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21375,17 +21437,12 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '00'}, 'mer</t>
-        </is>
-      </c>
-      <c r="O343" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': '19:30', 'closes': '23'}, 'martedì': {'opens': '19:30', 'cl</t>
         </is>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (avanveraroma) | IG: non trovato (avanveraroma)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -21397,27 +21454,22 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ciaparat</t>
+          <t>Indigeno - Osteria Ribelle</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Piazza San Donà del Piave, 14</t>
+          <t>Via Renzo da Ceri, 6/6A</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>06/89716513</t>
+          <t>389/4358878</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Ciaparat-Enoteca-100092133858205</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>ciaparat_enoteca</t>
+          <t>indigenoroma</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -21425,11 +21477,6 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I344" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -21440,11 +21487,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '00'}, 'mer</t>
-        </is>
-      </c>
       <c r="O344" t="inlineStr">
         <is>
           <t>Si</t>
@@ -21452,7 +21494,7 @@
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Ciaparat-Enoteca-100092133858205) | IG: non trovato (ciaparat_enoteca)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (indigenoroma) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -21464,17 +21506,27 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Concreto Cucina e Vino</t>
+          <t>Lento - Vineria con Cucina</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Via Marianna Dionigi, 4</t>
+          <t>Piazza di Santa Maria Ausiliatrice, 17/18</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>06/5415084</t>
+          <t>327/9470778</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>lentoroma</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21489,7 +21541,7 @@
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (lentoroma)</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -21501,42 +21553,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Dumpling Bar</t>
+          <t>Magazzino Scipioni</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Piazza Antonio Meucci, 1</t>
+          <t>Via degli Scipioni, 30-30/A</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>344/0658913</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>www.dumplingbar.it</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>dumplingbarroma</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>dumplingbarroma</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/39745233</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21551,17 +21578,12 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12:30, 19', 'closes': '15,</t>
-        </is>
-      </c>
-      <c r="O346" t="inlineStr">
-        <is>
-          <t>Si</t>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '17:30', 'closes': '01'}, '</t>
         </is>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (dumplingbarroma) | IG: non trovato (dumplingbarroma)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -21573,27 +21595,32 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Enofficina</t>
+          <t>Open Baladin</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Via Trionfale, 50</t>
+          <t>Via degli Specchi, 6</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>06/39742353</t>
+          <t>06/6838989</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>www.baladin.it/open-baladin-roma</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>enofficina</t>
+          <t>openbaladin.roma.5</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>enofficina_roma</t>
+          <t>openbaladinroma</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -21616,6 +21643,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '01'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
       <c r="O347" t="inlineStr">
         <is>
           <t>Si</t>
@@ -21623,7 +21655,7 @@
       </c>
       <c r="Q347" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (enofficina) | IG: non trovato (enofficina_roma)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (openbaladin.roma.5) | IG: non trovato (openbaladinroma)</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -21635,32 +21667,27 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Enoteca La Mescita</t>
+          <t>Santí - tradizione contadina</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Via Luigi Fincati, 44</t>
+          <t>Via Latina, 80</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>333/3015847</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>www.enotecalamescita.it</t>
+          <t>06/86675708</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>enotecalamescita</t>
+          <t>santitradizionecontadina</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>enotecalamescita</t>
+          <t>santi_tradizionecontadina</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -21685,7 +21712,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18', 'closes': '01'}, 'martedì': {'opens': '18', 'closes':</t>
+          <t>{'lunedì': {'opens': '18:30', 'closes': '23:30'}, 'martedì': {'opens': 'Chiuso'}</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -21695,7 +21722,7 @@
       </c>
       <c r="Q348" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (enotecalamescita) | IG: non trovato (enotecalamescita)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (santitradizionecontadina) | IG: non trovato (santi_tradizionecontadina)</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -21707,17 +21734,37 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Er Macellaio</t>
+          <t>Scima</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Viale Aurelio Galleppini, 60/66</t>
+          <t>Via Annia Regilla, 110</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>06/52831571</t>
+          <t>339/8743355</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Scima-Roma-61561040349051</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>scima_roma</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21725,14 +21772,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>2026</t>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q349" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (Scima-Roma-61561040349051) | IG: non trovato (scima_roma)</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -21744,17 +21791,42 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Ie Koji Sakaba</t>
+          <t>Taps</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Via Emilio Faà di Bruno, 31</t>
+          <t>Via Gaio Melisso, 32</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>392/4799773</t>
+          <t>370/1411858</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>www.lynnpeakbeer.com</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>lynnpeakbeer</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>tapsroma</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21762,19 +21834,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '19:30', 'closes': '23'}, 'martedì': {'opens': '19:30', 'cl</t>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (lynnpeakbeer) | IG: non trovato (tapsroma)</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -21786,27 +21853,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Indigeno - Osteria Ribelle</t>
+          <t>Vineria Risorgimento</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Via Renzo da Ceri, 6/6A</t>
+          <t>Piazza del Risorgimento, 7</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>389/4358878</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>indigenoroma</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/89533745</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21819,14 +21876,14 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="O351" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11', 'closes': '00'}, 'martedì': {'opens': '11', 'closes':</t>
         </is>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (indigenoroma) | IG: nessun handle</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -21838,22 +21895,37 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Lento - Vineria con Cucina</t>
+          <t>Vinificio</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Piazza di Santa Maria Ausiliatrice, 17/18</t>
+          <t>Piazza dell’Emporio, 1</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>327/9470778</t>
+          <t>389/1798451</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>www.vinificionaturale.it</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>vinificioroma</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>lentoroma</t>
+          <t>vinificio_roma</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -21871,9 +21943,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (lentoroma)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (vinificioroma) | IG: non trovato (vinificio_roma)</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -21885,17 +21962,37 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Magazzino Scipioni</t>
+          <t>Da Brando</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Via degli Scipioni, 30-30/A</t>
+          <t>Via Flaminia, 532</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>06/39745233</t>
+          <t>06/33225327</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>dabrandoristorante</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>da.brando</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -21910,12 +22007,17 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '17:30', 'closes': '01'}, '</t>
+          <t>{'lunedì': {'opens': '12', 'closes': '01'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q353" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: trovato (dabrandoristorante) | IG: non trovato (da.brando)</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -21927,32 +22029,32 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Open Baladin</t>
+          <t>Drink Kong</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Via degli Specchi, 6</t>
+          <t>Piazza di San Martino ai Monti, 8</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>06/6838989</t>
+          <t>06/23488666</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>www.baladin.it/open-baladin-roma</t>
+          <t>www.drinkkong.com</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>openbaladin.roma.5</t>
+          <t>drinkkong</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>openbaladinroma</t>
+          <t>drinkkongbar</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -21977,7 +22079,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '12', 'closes': '01'}, 'martedì': {'opens': '12', 'closes':</t>
+          <t>{'lunedì': {'opens': '18:30', 'closes': '02'}, 'martedì': {'opens': '18:30', 'cl</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -21987,7 +22089,7 @@
       </c>
       <c r="Q354" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (openbaladin.roma.5) | IG: non trovato (openbaladinroma)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (drinkkong) | IG: non trovato (drinkkongbar)</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -21999,27 +22101,32 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Santí - tradizione contadina</t>
+          <t>Jerry Thomas Speakeasy</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Via Latina, 80</t>
+          <t>Vicolo Cellini, 30</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>06/86675708</t>
+          <t>06/96845937</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>www.thejerrythomasproject.it</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>santitradizionecontadina</t>
+          <t>TheJerryThomas</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>santi_tradizionecontadina</t>
+          <t>jerrythomasproject_rome</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -22044,7 +22151,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '18:30', 'closes': '23:30'}, 'martedì': {'opens': 'Chiuso'}</t>
+          <t>{'lunedì': {'opens': '21', 'closes': '04:30'}, 'martedì': {'opens': '21', 'close</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -22054,7 +22161,7 @@
       </c>
       <c r="Q355" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (santitradizionecontadina) | IG: non trovato (santi_tradizionecontadina)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (TheJerryThomas) | IG: non trovato (jerrythomasproject_rome)</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -22066,27 +22173,32 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Scima</t>
+          <t>Metropolita</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Via Annia Regilla, 110</t>
+          <t>Piazza Gentile da Fabriano, 2</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>339/8743355</t>
+          <t>06/84381895</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>www.metropolita.it</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Scima-Roma-61561040349051</t>
+          <t>metropolita.roma</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>scima_roma</t>
+          <t>metropolita.roma</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -22111,7 +22223,7 @@
       </c>
       <c r="Q356" t="inlineStr">
         <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (Scima-Roma-61561040349051) | IG: non trovato (scima_roma)</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (metropolita.roma) | IG: non trovato (metropolita.roma)</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -22121,2078 +22233,2062 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Taps</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Via Gaio Melisso, 32</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>370/1411858</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>www.lynnpeakbeer.com</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>lynnpeakbeer</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>tapsroma</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O357" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q357" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (lynnpeakbeer) | IG: non trovato (tapsroma)</t>
-        </is>
-      </c>
-      <c r="R357" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>Bless</t>
+        </is>
+      </c>
+      <c r="B357" s="1" t="inlineStr">
+        <is>
+          <t>Via dell’Indipendenza, 208</t>
+        </is>
+      </c>
+      <c r="C357" s="1" t="inlineStr">
+        <is>
+          <t>0771/030188</t>
+        </is>
+      </c>
+      <c r="D357" s="1" t="inlineStr"/>
+      <c r="E357" s="1" t="inlineStr"/>
+      <c r="F357" s="1" t="inlineStr"/>
+      <c r="G357" s="1" t="inlineStr"/>
+      <c r="H357" s="1" t="inlineStr"/>
+      <c r="I357" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J357" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K357" s="1" t="inlineStr"/>
+      <c r="L357" s="1" t="inlineStr"/>
+      <c r="M357" s="1" t="inlineStr"/>
+      <c r="N357" s="1" t="inlineStr"/>
+      <c r="O357" s="1" t="inlineStr"/>
+      <c r="P357" s="1" t="inlineStr"/>
+      <c r="Q357" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R357" s="1" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Vineria Risorgimento</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Piazza del Risorgimento, 7</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>06/89533745</t>
-        </is>
-      </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '11', 'closes': '00'}, 'martedì': {'opens': '11', 'closes':</t>
-        </is>
-      </c>
-      <c r="Q358" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R358" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>Mrgda Ristorante</t>
+        </is>
+      </c>
+      <c r="B358" s="1" t="inlineStr">
+        <is>
+          <t>Via Prenestina, 182</t>
+        </is>
+      </c>
+      <c r="C358" s="1" t="inlineStr">
+        <is>
+          <t>329/933355</t>
+        </is>
+      </c>
+      <c r="D358" s="1" t="inlineStr"/>
+      <c r="E358" s="1" t="inlineStr"/>
+      <c r="F358" s="1" t="inlineStr"/>
+      <c r="G358" s="1" t="inlineStr"/>
+      <c r="H358" s="1" t="inlineStr"/>
+      <c r="I358" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J358" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K358" s="1" t="inlineStr"/>
+      <c r="L358" s="1" t="inlineStr"/>
+      <c r="M358" s="1" t="inlineStr"/>
+      <c r="N358" s="1" t="inlineStr"/>
+      <c r="O358" s="1" t="inlineStr"/>
+      <c r="P358" s="1" t="inlineStr"/>
+      <c r="Q358" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R358" s="1" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Vinificio</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Piazza dell’Emporio, 1</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>389/1798451</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>www.vinificionaturale.it</t>
-        </is>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>vinificioroma</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>vinificio_roma</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O359" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q359" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (vinificioroma) | IG: non trovato (vinificio_roma)</t>
-        </is>
-      </c>
-      <c r="R359" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>Clementina</t>
+        </is>
+      </c>
+      <c r="B359" s="1" t="inlineStr">
+        <is>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C359" s="1" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
+      <c r="D359" s="1" t="inlineStr"/>
+      <c r="E359" s="1" t="inlineStr"/>
+      <c r="F359" s="1" t="inlineStr"/>
+      <c r="G359" s="1" t="inlineStr"/>
+      <c r="H359" s="1" t="inlineStr"/>
+      <c r="I359" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J359" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K359" s="1" t="inlineStr"/>
+      <c r="L359" s="1" t="inlineStr"/>
+      <c r="M359" s="1" t="inlineStr"/>
+      <c r="N359" s="1" t="inlineStr"/>
+      <c r="O359" s="1" t="inlineStr"/>
+      <c r="P359" s="1" t="inlineStr"/>
+      <c r="Q359" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R359" s="1" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Da Brando</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Via Flaminia, 532</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>06/33225327</t>
-        </is>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>dabrandoristorante</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>da.brando</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J360" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12', 'closes': '01'}, 'martedì': {'opens': '12', 'closes':</t>
-        </is>
-      </c>
-      <c r="O360" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q360" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.0 ( rec.) | TF: non trovato | FB: trovato (dabrandoristorante) | IG: non trovato (da.brando)</t>
-        </is>
-      </c>
-      <c r="R360" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>Da Antonio</t>
+        </is>
+      </c>
+      <c r="B360" s="1" t="inlineStr">
+        <is>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C360" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
+      <c r="D360" s="1" t="inlineStr"/>
+      <c r="E360" s="1" t="inlineStr"/>
+      <c r="F360" s="1" t="inlineStr"/>
+      <c r="G360" s="1" t="inlineStr"/>
+      <c r="H360" s="1" t="inlineStr"/>
+      <c r="I360" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J360" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K360" s="1" t="inlineStr"/>
+      <c r="L360" s="1" t="inlineStr"/>
+      <c r="M360" s="1" t="inlineStr"/>
+      <c r="N360" s="1" t="inlineStr"/>
+      <c r="O360" s="1" t="inlineStr"/>
+      <c r="P360" s="1" t="inlineStr"/>
+      <c r="Q360" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R360" s="1" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Drink Kong</t>
+          <t>Pupillo Pura Pizza</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
+          <t>Via Giacomo Matteotti, 29</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>339/4143148</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '19', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>Il tuo fornaio</t>
+        </is>
+      </c>
+      <c r="B362" s="1" t="inlineStr">
+        <is>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C362" s="1" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
+      <c r="D362" s="1" t="inlineStr"/>
+      <c r="E362" s="1" t="inlineStr"/>
+      <c r="F362" s="1" t="inlineStr"/>
+      <c r="G362" s="1" t="inlineStr"/>
+      <c r="H362" s="1" t="inlineStr"/>
+      <c r="I362" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J362" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K362" s="1" t="inlineStr"/>
+      <c r="L362" s="1" t="inlineStr"/>
+      <c r="M362" s="1" t="inlineStr"/>
+      <c r="N362" s="1" t="inlineStr"/>
+      <c r="O362" s="1" t="inlineStr"/>
+      <c r="P362" s="1" t="inlineStr"/>
+      <c r="Q362" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R362" s="1" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="B363" s="1" t="inlineStr">
+        <is>
+          <t>Corso Vittorio Emanuele II, 73</t>
+        </is>
+      </c>
+      <c r="C363" s="1" t="inlineStr"/>
+      <c r="D363" s="1" t="inlineStr"/>
+      <c r="E363" s="1" t="inlineStr"/>
+      <c r="F363" s="1" t="inlineStr"/>
+      <c r="G363" s="1" t="inlineStr"/>
+      <c r="H363" s="1" t="inlineStr"/>
+      <c r="I363" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J363" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K363" s="1" t="inlineStr"/>
+      <c r="L363" s="1" t="inlineStr"/>
+      <c r="M363" s="1" t="inlineStr"/>
+      <c r="N363" s="1" t="inlineStr"/>
+      <c r="O363" s="1" t="inlineStr"/>
+      <c r="P363" s="1" t="inlineStr"/>
+      <c r="Q363" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R363" s="1" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>N.O.D.O.</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Piazza delle Coppelle, 52</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>06/94376334</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>www.nodoroma.it</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>NodoRoma-108837454790526</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>nodoroma</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '17', 'closes': '01'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (NodoRoma-108837454790526) | IG: non trovato (nodoroma)</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Nite Kong</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
           <t>Piazza di San Martino ai Monti, 8</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C365" t="inlineStr">
         <is>
           <t>06/23488666</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>www.drinkkong.com</t>
-        </is>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>drinkkong</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>drinkkongbar</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '18:30', 'closes': '02'}, 'martedì': {'opens': '18:30', 'cl</t>
-        </is>
-      </c>
-      <c r="O361" t="inlineStr">
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>www.nitekong.com</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>nitekong</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (nitekong)</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Pork’n’Roll</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Via Carlo Caneva, 15</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>06/45551271</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>www.porknroll.com</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>porknrollpub</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>porknrollpub</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '01:30'}, 'venerdì': {'opens': '18', 'clos</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q361" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (drinkkong) | IG: non trovato (drinkkongbar)</t>
-        </is>
-      </c>
-      <c r="R361" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Jerry Thomas Speakeasy</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Vicolo Cellini, 30</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>06/96845937</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>www.thejerrythomasproject.it</t>
-        </is>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>TheJerryThomas</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>jerrythomasproject_rome</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I362" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J362" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M362" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '21', 'closes': '04:30'}, 'martedì': {'opens': '21', 'close</t>
-        </is>
-      </c>
-      <c r="O362" t="inlineStr">
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (porknrollpub) | IG: non trovato (porknrollpub)</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>amARanto</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Via Adige, 19/21</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>06/93374742</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>pizzamaranto</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>pizzamaranto</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q362" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (TheJerryThomas) | IG: non trovato (jerrythomasproject_rome)</t>
-        </is>
-      </c>
-      <c r="R362" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Metropolita</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Piazza Gentile da Fabriano, 2</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>06/84381895</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>www.metropolita.it</t>
-        </is>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>metropolita.roma</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>metropolita.roma</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I363" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O363" t="inlineStr">
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (pizzamaranto) | IG: non trovato (pizzamaranto)</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Amerina - la pizzetta</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Largo dei Librari, 82</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>06/45495604</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>www.amerinalapizzetta.it</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>amerinalapizzetta</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>amerina_lapizzetta</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '17', 'closes': '23'}, 'venerdì': {'opens': '11', 'closes'</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="Q363" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (metropolita.roma) | IG: non trovato (metropolita.roma)</t>
-        </is>
-      </c>
-      <c r="R363" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="1" t="inlineStr">
-        <is>
-          <t>N.O.D.O.</t>
-        </is>
-      </c>
-      <c r="B364" s="1" t="inlineStr">
-        <is>
-          <t>Piazza delle Coppelle, 52</t>
-        </is>
-      </c>
-      <c r="C364" s="1" t="inlineStr">
-        <is>
-          <t>06/94376334</t>
-        </is>
-      </c>
-      <c r="D364" s="1" t="inlineStr">
-        <is>
-          <t>www.nodoroma.it</t>
-        </is>
-      </c>
-      <c r="E364" s="1" t="inlineStr">
-        <is>
-          <t>NodoRoma-108837454790526</t>
-        </is>
-      </c>
-      <c r="F364" s="1" t="inlineStr">
-        <is>
-          <t>nodoroma</t>
-        </is>
-      </c>
-      <c r="G364" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H364" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I364" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J364" s="1" t="inlineStr"/>
-      <c r="K364" s="1" t="inlineStr"/>
-      <c r="L364" s="1" t="inlineStr"/>
-      <c r="M364" s="1" t="inlineStr"/>
-      <c r="N364" s="1" t="inlineStr"/>
-      <c r="O364" s="1" t="inlineStr"/>
-      <c r="P364" s="1" t="inlineStr"/>
-      <c r="Q364" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R364" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="1" t="inlineStr">
-        <is>
-          <t>Nite Kong</t>
-        </is>
-      </c>
-      <c r="B365" s="1" t="inlineStr">
-        <is>
-          <t>Piazza di San Martino ai Monti, 8</t>
-        </is>
-      </c>
-      <c r="C365" s="1" t="inlineStr">
-        <is>
-          <t>06/23488666</t>
-        </is>
-      </c>
-      <c r="D365" s="1" t="inlineStr">
-        <is>
-          <t>www.nitekong.com</t>
-        </is>
-      </c>
-      <c r="E365" s="1" t="inlineStr"/>
-      <c r="F365" s="1" t="inlineStr">
-        <is>
-          <t>nitekong</t>
-        </is>
-      </c>
-      <c r="G365" s="1" t="inlineStr"/>
-      <c r="H365" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I365" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J365" s="1" t="inlineStr"/>
-      <c r="K365" s="1" t="inlineStr"/>
-      <c r="L365" s="1" t="inlineStr"/>
-      <c r="M365" s="1" t="inlineStr"/>
-      <c r="N365" s="1" t="inlineStr"/>
-      <c r="O365" s="1" t="inlineStr"/>
-      <c r="P365" s="1" t="inlineStr"/>
-      <c r="Q365" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R365" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="1" t="inlineStr">
-        <is>
-          <t>Pork’n’Roll</t>
-        </is>
-      </c>
-      <c r="B366" s="1" t="inlineStr">
-        <is>
-          <t>Via Carlo Caneva, 15</t>
-        </is>
-      </c>
-      <c r="C366" s="1" t="inlineStr">
-        <is>
-          <t>06/45551271</t>
-        </is>
-      </c>
-      <c r="D366" s="1" t="inlineStr">
-        <is>
-          <t>www.porknroll.com</t>
-        </is>
-      </c>
-      <c r="E366" s="1" t="inlineStr">
-        <is>
-          <t>porknrollpub</t>
-        </is>
-      </c>
-      <c r="F366" s="1" t="inlineStr">
-        <is>
-          <t>porknrollpub</t>
-        </is>
-      </c>
-      <c r="G366" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H366" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I366" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J366" s="1" t="inlineStr"/>
-      <c r="K366" s="1" t="inlineStr"/>
-      <c r="L366" s="1" t="inlineStr"/>
-      <c r="M366" s="1" t="inlineStr"/>
-      <c r="N366" s="1" t="inlineStr"/>
-      <c r="O366" s="1" t="inlineStr"/>
-      <c r="P366" s="1" t="inlineStr"/>
-      <c r="Q366" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R366" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="1" t="inlineStr">
-        <is>
-          <t>amARanto</t>
-        </is>
-      </c>
-      <c r="B367" s="1" t="inlineStr">
-        <is>
-          <t>Via Adige, 19/21</t>
-        </is>
-      </c>
-      <c r="C367" s="1" t="inlineStr">
-        <is>
-          <t>06/93374742</t>
-        </is>
-      </c>
-      <c r="D367" s="1" t="inlineStr"/>
-      <c r="E367" s="1" t="inlineStr">
-        <is>
-          <t>pizzamaranto</t>
-        </is>
-      </c>
-      <c r="F367" s="1" t="inlineStr">
-        <is>
-          <t>pizzamaranto</t>
-        </is>
-      </c>
-      <c r="G367" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H367" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I367" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J367" s="1" t="inlineStr"/>
-      <c r="K367" s="1" t="inlineStr"/>
-      <c r="L367" s="1" t="inlineStr"/>
-      <c r="M367" s="1" t="inlineStr"/>
-      <c r="N367" s="1" t="inlineStr"/>
-      <c r="O367" s="1" t="inlineStr"/>
-      <c r="P367" s="1" t="inlineStr"/>
-      <c r="Q367" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R367" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="1" t="inlineStr">
-        <is>
-          <t>Amerina - la pizzetta</t>
-        </is>
-      </c>
-      <c r="B368" s="1" t="inlineStr">
-        <is>
-          <t>Largo dei Librari, 82</t>
-        </is>
-      </c>
-      <c r="C368" s="1" t="inlineStr">
-        <is>
-          <t>06/45495604</t>
-        </is>
-      </c>
-      <c r="D368" s="1" t="inlineStr">
-        <is>
-          <t>www.amerinalapizzetta.it</t>
-        </is>
-      </c>
-      <c r="E368" s="1" t="inlineStr">
-        <is>
-          <t>amerinalapizzetta</t>
-        </is>
-      </c>
-      <c r="F368" s="1" t="inlineStr">
-        <is>
-          <t>amerina_lapizzetta</t>
-        </is>
-      </c>
-      <c r="G368" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H368" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I368" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J368" s="1" t="inlineStr"/>
-      <c r="K368" s="1" t="inlineStr"/>
-      <c r="L368" s="1" t="inlineStr"/>
-      <c r="M368" s="1" t="inlineStr"/>
-      <c r="N368" s="1" t="inlineStr"/>
-      <c r="O368" s="1" t="inlineStr"/>
-      <c r="P368" s="1" t="inlineStr"/>
-      <c r="Q368" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R368" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (amerinalapizzetta) | IG: non trovato (amerina_lapizzetta)</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="inlineStr">
+      <c r="A369" t="inlineStr">
         <is>
           <t>Antico Forno Roscioli</t>
         </is>
       </c>
-      <c r="B369" s="1" t="inlineStr">
+      <c r="B369" t="inlineStr">
         <is>
           <t>Via dei Chiavari, 34</t>
         </is>
       </c>
-      <c r="C369" s="1" t="inlineStr">
+      <c r="C369" t="inlineStr">
         <is>
           <t>06/6864045</t>
         </is>
       </c>
-      <c r="D369" s="1" t="inlineStr">
+      <c r="D369" t="inlineStr">
         <is>
           <t>www.anticofornoroscioli.it</t>
         </is>
       </c>
-      <c r="E369" s="1" t="inlineStr">
+      <c r="E369" t="inlineStr">
         <is>
           <t>AnticoFornoRoscioli</t>
         </is>
       </c>
-      <c r="F369" s="1" t="inlineStr">
+      <c r="F369" t="inlineStr">
         <is>
           <t>anticofornoroscioli</t>
         </is>
       </c>
-      <c r="G369" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H369" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I369" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J369" s="1" t="inlineStr"/>
-      <c r="K369" s="1" t="inlineStr"/>
-      <c r="L369" s="1" t="inlineStr"/>
-      <c r="M369" s="1" t="inlineStr"/>
-      <c r="N369" s="1" t="inlineStr"/>
-      <c r="O369" s="1" t="inlineStr"/>
-      <c r="P369" s="1" t="inlineStr"/>
-      <c r="Q369" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R369" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '07:30', 'closes': '20'}, 'venerdì': {'opens': '07:30', 'c</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (AnticoFornoRoscioli) | IG: non trovato (anticofornoroscioli)</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="inlineStr">
+      <c r="A370" t="inlineStr">
         <is>
           <t>Arte Bianca di Gabriele</t>
         </is>
       </c>
-      <c r="B370" s="1" t="inlineStr">
+      <c r="B370" t="inlineStr">
         <is>
           <t>Largo Sangemini, 7/B-C</t>
         </is>
       </c>
-      <c r="C370" s="1" t="inlineStr">
+      <c r="C370" t="inlineStr">
         <is>
           <t>06/2757763</t>
         </is>
       </c>
-      <c r="D370" s="1" t="inlineStr"/>
-      <c r="E370" s="1" t="inlineStr">
+      <c r="E370" t="inlineStr">
         <is>
           <t>profile.php?id=100086435003228</t>
         </is>
       </c>
-      <c r="F370" s="1" t="inlineStr">
+      <c r="F370" t="inlineStr">
         <is>
           <t>artebianca_digabriele</t>
         </is>
       </c>
-      <c r="G370" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H370" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I370" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J370" s="1" t="inlineStr"/>
-      <c r="K370" s="1" t="inlineStr"/>
-      <c r="L370" s="1" t="inlineStr"/>
-      <c r="M370" s="1" t="inlineStr"/>
-      <c r="N370" s="1" t="inlineStr"/>
-      <c r="O370" s="1" t="inlineStr"/>
-      <c r="P370" s="1" t="inlineStr"/>
-      <c r="Q370" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R370" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100086435003228) | IG: non trovato (artebianca_digabriele)</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="inlineStr">
+      <c r="A371" t="inlineStr">
         <is>
           <t>Becco</t>
         </is>
       </c>
-      <c r="B371" s="1" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>Piazzale degli Eroi, 7</t>
         </is>
       </c>
-      <c r="C371" s="1" t="inlineStr">
+      <c r="C371" t="inlineStr">
         <is>
           <t>06/98183647</t>
         </is>
       </c>
-      <c r="D371" s="1" t="inlineStr"/>
-      <c r="E371" s="1" t="inlineStr"/>
-      <c r="F371" s="1" t="inlineStr">
+      <c r="F371" t="inlineStr">
         <is>
           <t>beccoroma</t>
         </is>
       </c>
-      <c r="G371" s="1" t="inlineStr"/>
-      <c r="H371" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I371" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J371" s="1" t="inlineStr"/>
-      <c r="K371" s="1" t="inlineStr"/>
-      <c r="L371" s="1" t="inlineStr"/>
-      <c r="M371" s="1" t="inlineStr"/>
-      <c r="N371" s="1" t="inlineStr"/>
-      <c r="O371" s="1" t="inlineStr"/>
-      <c r="P371" s="1" t="inlineStr"/>
-      <c r="Q371" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R371" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 18', 'closes': '15, 22:30', 'break': '15–18'}, 've</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (beccoroma)</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="inlineStr">
+      <c r="A372" t="inlineStr">
         <is>
           <t>Claudio Torcè</t>
         </is>
       </c>
-      <c r="B372" s="1" t="inlineStr">
+      <c r="B372" t="inlineStr">
         <is>
           <t>Piazza Euclide, 25</t>
         </is>
       </c>
-      <c r="C372" s="1" t="inlineStr">
+      <c r="C372" t="inlineStr">
         <is>
           <t>06/5746876</t>
         </is>
       </c>
-      <c r="D372" s="1" t="inlineStr">
+      <c r="D372" t="inlineStr">
         <is>
           <t>www.gelateriatorce.it</t>
         </is>
       </c>
-      <c r="E372" s="1" t="inlineStr">
+      <c r="E372" t="inlineStr">
         <is>
           <t>gelateriatorce</t>
         </is>
       </c>
-      <c r="F372" s="1" t="inlineStr">
+      <c r="F372" t="inlineStr">
         <is>
           <t>gelateria_torce</t>
         </is>
       </c>
-      <c r="G372" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H372" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I372" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J372" s="1" t="inlineStr"/>
-      <c r="K372" s="1" t="inlineStr"/>
-      <c r="L372" s="1" t="inlineStr"/>
-      <c r="M372" s="1" t="inlineStr"/>
-      <c r="N372" s="1" t="inlineStr"/>
-      <c r="O372" s="1" t="inlineStr"/>
-      <c r="P372" s="1" t="inlineStr"/>
-      <c r="Q372" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R372" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gelateriatorce) | IG: non trovato (gelateria_torce)</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="inlineStr">
+      <c r="A373" t="inlineStr">
         <is>
           <t>Come il Latte</t>
         </is>
       </c>
-      <c r="B373" s="1" t="inlineStr">
+      <c r="B373" t="inlineStr">
         <is>
           <t>Via Silvio Spaventa 24/26</t>
         </is>
       </c>
-      <c r="C373" s="1" t="inlineStr">
+      <c r="C373" t="inlineStr">
         <is>
           <t>06/42903882</t>
         </is>
       </c>
-      <c r="D373" s="1" t="inlineStr">
+      <c r="D373" t="inlineStr">
         <is>
           <t>www.comeillatte.it</t>
         </is>
       </c>
-      <c r="E373" s="1" t="inlineStr">
+      <c r="E373" t="inlineStr">
         <is>
           <t>comeillatte</t>
         </is>
       </c>
-      <c r="F373" s="1" t="inlineStr">
+      <c r="F373" t="inlineStr">
         <is>
           <t>comeillatte</t>
         </is>
       </c>
-      <c r="G373" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H373" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I373" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J373" s="1" t="inlineStr"/>
-      <c r="K373" s="1" t="inlineStr"/>
-      <c r="L373" s="1" t="inlineStr"/>
-      <c r="M373" s="1" t="inlineStr"/>
-      <c r="N373" s="1" t="inlineStr"/>
-      <c r="O373" s="1" t="inlineStr"/>
-      <c r="P373" s="1" t="inlineStr"/>
-      <c r="Q373" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R373" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (comeillatte) | IG: non trovato (comeillatte)</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="inlineStr">
+      <c r="A374" t="inlineStr">
         <is>
           <t>Cremeria Alpi</t>
         </is>
       </c>
-      <c r="B374" s="1" t="inlineStr">
+      <c r="B374" t="inlineStr">
         <is>
           <t>Via Padre Reginaldo Giuliani, 16</t>
         </is>
       </c>
-      <c r="C374" s="1" t="inlineStr">
+      <c r="C374" t="inlineStr">
         <is>
           <t>06/88921386</t>
         </is>
       </c>
-      <c r="D374" s="1" t="inlineStr">
+      <c r="D374" t="inlineStr">
         <is>
           <t>www.cremeriaalpi.it</t>
         </is>
       </c>
-      <c r="E374" s="1" t="inlineStr">
+      <c r="E374" t="inlineStr">
         <is>
           <t>cremeriaalpi</t>
         </is>
       </c>
-      <c r="F374" s="1" t="inlineStr">
+      <c r="F374" t="inlineStr">
         <is>
           <t>cremeriaalpi</t>
         </is>
       </c>
-      <c r="G374" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H374" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I374" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J374" s="1" t="inlineStr"/>
-      <c r="K374" s="1" t="inlineStr"/>
-      <c r="L374" s="1" t="inlineStr"/>
-      <c r="M374" s="1" t="inlineStr"/>
-      <c r="N374" s="1" t="inlineStr"/>
-      <c r="O374" s="1" t="inlineStr"/>
-      <c r="P374" s="1" t="inlineStr"/>
-      <c r="Q374" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R374" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (cremeriaalpi) | IG: non trovato (cremeriaalpi)</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="inlineStr">
+      <c r="A375" t="inlineStr">
         <is>
           <t>Cremeria Aurelia</t>
         </is>
       </c>
-      <c r="B375" s="1" t="inlineStr">
+      <c r="B375" t="inlineStr">
         <is>
           <t>Via Aurelia, 388/B</t>
         </is>
       </c>
-      <c r="C375" s="1" t="inlineStr">
+      <c r="C375" t="inlineStr">
         <is>
           <t>06/6632499</t>
         </is>
       </c>
-      <c r="D375" s="1" t="inlineStr"/>
-      <c r="E375" s="1" t="inlineStr">
+      <c r="E375" t="inlineStr">
         <is>
           <t>Cremeria-Aurelia</t>
         </is>
       </c>
-      <c r="F375" s="1" t="inlineStr">
+      <c r="F375" t="inlineStr">
         <is>
           <t>cremeriaaurelia</t>
         </is>
       </c>
-      <c r="G375" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H375" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I375" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J375" s="1" t="inlineStr"/>
-      <c r="K375" s="1" t="inlineStr"/>
-      <c r="L375" s="1" t="inlineStr"/>
-      <c r="M375" s="1" t="inlineStr"/>
-      <c r="N375" s="1" t="inlineStr"/>
-      <c r="O375" s="1" t="inlineStr"/>
-      <c r="P375" s="1" t="inlineStr"/>
-      <c r="Q375" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R375" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '23:30'}, 'venerdì': {'opens': '12', 'clos</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Cremeria-Aurelia) | IG: non trovato (cremeriaaurelia)</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="inlineStr">
+      <c r="A376" t="inlineStr">
         <is>
           <t>Criollo - Il Bistrot Del Gelato</t>
         </is>
       </c>
-      <c r="B376" s="1" t="inlineStr">
+      <c r="B376" t="inlineStr">
         <is>
           <t>Via Giuseppe Bagnera, 59</t>
         </is>
       </c>
-      <c r="C376" s="1" t="inlineStr">
+      <c r="C376" t="inlineStr">
         <is>
           <t>328/2511673</t>
         </is>
       </c>
-      <c r="D376" s="1" t="inlineStr">
+      <c r="D376" t="inlineStr">
         <is>
           <t>www.criollogelato.it</t>
         </is>
       </c>
-      <c r="E376" s="1" t="inlineStr">
+      <c r="E376" t="inlineStr">
         <is>
           <t>Criollo-Il-bistrot-del-gelato</t>
         </is>
       </c>
-      <c r="F376" s="1" t="inlineStr">
+      <c r="F376" t="inlineStr">
         <is>
           <t>criollo_gelato</t>
         </is>
       </c>
-      <c r="G376" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H376" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I376" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J376" s="1" t="inlineStr"/>
-      <c r="K376" s="1" t="inlineStr"/>
-      <c r="L376" s="1" t="inlineStr"/>
-      <c r="M376" s="1" t="inlineStr"/>
-      <c r="N376" s="1" t="inlineStr"/>
-      <c r="O376" s="1" t="inlineStr"/>
-      <c r="P376" s="1" t="inlineStr"/>
-      <c r="Q376" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R376" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': 'Chiuso'}, 'venerdì': {'opens': '15', 'closes': '23'}, 'sa</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (Criollo-Il-bistrot-del-gelato) | IG: non trovato (criollo_gelato)</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="inlineStr">
+      <c r="A377" t="inlineStr">
         <is>
           <t>Crunch Teglia</t>
         </is>
       </c>
-      <c r="B377" s="1" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>Via della Bufalotta, 284</t>
         </is>
       </c>
-      <c r="C377" s="1" t="inlineStr">
+      <c r="C377" t="inlineStr">
         <is>
           <t>06/99606077</t>
         </is>
       </c>
-      <c r="D377" s="1" t="inlineStr"/>
-      <c r="E377" s="1" t="inlineStr"/>
-      <c r="F377" s="1" t="inlineStr"/>
-      <c r="G377" s="1" t="inlineStr"/>
-      <c r="H377" s="1" t="inlineStr"/>
-      <c r="I377" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J377" s="1" t="inlineStr"/>
-      <c r="K377" s="1" t="inlineStr"/>
-      <c r="L377" s="1" t="inlineStr"/>
-      <c r="M377" s="1" t="inlineStr"/>
-      <c r="N377" s="1" t="inlineStr"/>
-      <c r="O377" s="1" t="inlineStr"/>
-      <c r="P377" s="1" t="inlineStr"/>
-      <c r="Q377" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R377" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '10', 'closes': '22'}, 'venerdì': {'opens': '10', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="inlineStr">
+      <c r="A378" t="inlineStr">
         <is>
           <t>Da Tullio</t>
         </is>
       </c>
-      <c r="B378" s="1" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>Via della Balduina, 211</t>
         </is>
       </c>
-      <c r="C378" s="1" t="inlineStr">
+      <c r="C378" t="inlineStr">
         <is>
           <t>06/35347252</t>
         </is>
       </c>
-      <c r="D378" s="1" t="inlineStr">
+      <c r="D378" t="inlineStr">
         <is>
           <t>www.datulliopizza.it</t>
         </is>
       </c>
-      <c r="E378" s="1" t="inlineStr">
+      <c r="E378" t="inlineStr">
         <is>
           <t>DTP-Da-Tullio-Pizza</t>
         </is>
       </c>
-      <c r="F378" s="1" t="inlineStr">
+      <c r="F378" t="inlineStr">
         <is>
           <t>tulliopizza</t>
         </is>
       </c>
-      <c r="G378" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H378" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I378" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J378" s="1" t="inlineStr"/>
-      <c r="K378" s="1" t="inlineStr"/>
-      <c r="L378" s="1" t="inlineStr"/>
-      <c r="M378" s="1" t="inlineStr"/>
-      <c r="N378" s="1" t="inlineStr"/>
-      <c r="O378" s="1" t="inlineStr"/>
-      <c r="P378" s="1" t="inlineStr"/>
-      <c r="Q378" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R378" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (DTP-Da-Tullio-Pizza) | IG: non trovato (tulliopizza)</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="inlineStr">
+      <c r="A379" t="inlineStr">
         <is>
           <t>Don Choc</t>
         </is>
       </c>
-      <c r="B379" s="1" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>Via Flaminia Vecchia, 732/E-F-G-H</t>
         </is>
       </c>
-      <c r="C379" s="1" t="inlineStr">
+      <c r="C379" t="inlineStr">
         <is>
           <t>06/33221585</t>
         </is>
       </c>
-      <c r="D379" s="1" t="inlineStr">
+      <c r="D379" t="inlineStr">
         <is>
           <t>www.donchoc.com</t>
         </is>
       </c>
-      <c r="E379" s="1" t="inlineStr">
+      <c r="E379" t="inlineStr">
         <is>
           <t>donchocfleming</t>
         </is>
       </c>
-      <c r="F379" s="1" t="inlineStr">
+      <c r="F379" t="inlineStr">
         <is>
           <t>donchoc</t>
         </is>
       </c>
-      <c r="G379" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H379" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I379" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J379" s="1" t="inlineStr"/>
-      <c r="K379" s="1" t="inlineStr"/>
-      <c r="L379" s="1" t="inlineStr"/>
-      <c r="M379" s="1" t="inlineStr"/>
-      <c r="N379" s="1" t="inlineStr"/>
-      <c r="O379" s="1" t="inlineStr"/>
-      <c r="P379" s="1" t="inlineStr"/>
-      <c r="Q379" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R379" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '11:30', 'closes': '23'}, 'venerdì': {'opens': '11:30', 'c</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (donchocfleming) | IG: non trovato (donchoc)</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="inlineStr">
+      <c r="A380" t="inlineStr">
         <is>
           <t>El maiz</t>
         </is>
       </c>
-      <c r="B380" s="1" t="inlineStr">
+      <c r="B380" t="inlineStr">
         <is>
           <t>Via Tolemaide, 16</t>
         </is>
       </c>
-      <c r="C380" s="1" t="inlineStr">
+      <c r="C380" t="inlineStr">
         <is>
           <t>06/66006878</t>
         </is>
       </c>
-      <c r="D380" s="1" t="inlineStr">
+      <c r="D380" t="inlineStr">
         <is>
           <t>www.elmaiz.it</t>
         </is>
       </c>
-      <c r="E380" s="1" t="inlineStr">
+      <c r="E380" t="inlineStr">
         <is>
           <t>elmaizroma</t>
         </is>
       </c>
-      <c r="F380" s="1" t="inlineStr">
+      <c r="F380" t="inlineStr">
         <is>
           <t>elmaiz.roma</t>
         </is>
       </c>
-      <c r="G380" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H380" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I380" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J380" s="1" t="inlineStr"/>
-      <c r="K380" s="1" t="inlineStr"/>
-      <c r="L380" s="1" t="inlineStr"/>
-      <c r="M380" s="1" t="inlineStr"/>
-      <c r="N380" s="1" t="inlineStr"/>
-      <c r="O380" s="1" t="inlineStr"/>
-      <c r="P380" s="1" t="inlineStr"/>
-      <c r="Q380" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R380" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '22'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (elmaizroma) | IG: trovato (elmaiz.roma)</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="inlineStr">
+      <c r="A381" t="inlineStr">
         <is>
           <t>Fatamorgana</t>
         </is>
       </c>
-      <c r="B381" s="1" t="inlineStr">
+      <c r="B381" t="inlineStr">
         <is>
           <t>Via Lago di Lesina, 9/11</t>
         </is>
       </c>
-      <c r="C381" s="1" t="inlineStr">
+      <c r="C381" t="inlineStr">
         <is>
           <t>06/86391589</t>
         </is>
       </c>
-      <c r="D381" s="1" t="inlineStr">
+      <c r="D381" t="inlineStr">
         <is>
           <t>www.gelateriafatamorgana.it</t>
         </is>
       </c>
-      <c r="E381" s="1" t="inlineStr">
+      <c r="E381" t="inlineStr">
         <is>
           <t>Fatamorgana.Gelaterie</t>
         </is>
       </c>
-      <c r="F381" s="1" t="inlineStr">
+      <c r="F381" t="inlineStr">
         <is>
           <t>gelateriafatamorgana</t>
         </is>
       </c>
-      <c r="G381" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H381" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I381" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J381" s="1" t="inlineStr"/>
-      <c r="K381" s="1" t="inlineStr"/>
-      <c r="L381" s="1" t="inlineStr"/>
-      <c r="M381" s="1" t="inlineStr"/>
-      <c r="N381" s="1" t="inlineStr"/>
-      <c r="O381" s="1" t="inlineStr"/>
-      <c r="P381" s="1" t="inlineStr"/>
-      <c r="Q381" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R381" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '13:30', 'closes': '21:30'}, 'venerdì': {'opens': '13:30',</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (Fatamorgana.Gelaterie) | IG: trovato (gelateriafatamorgana)</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="inlineStr">
+      <c r="A382" t="inlineStr">
         <is>
           <t>Fior di Luna</t>
         </is>
       </c>
-      <c r="B382" s="1" t="inlineStr">
+      <c r="B382" t="inlineStr">
         <is>
           <t>Via della Lungaretta, 96</t>
         </is>
       </c>
-      <c r="C382" s="1" t="inlineStr">
+      <c r="C382" t="inlineStr">
         <is>
           <t>06/64561314</t>
         </is>
       </c>
-      <c r="D382" s="1" t="inlineStr"/>
-      <c r="E382" s="1" t="inlineStr">
+      <c r="E382" t="inlineStr">
         <is>
           <t>GelateriaFiordiluna</t>
         </is>
       </c>
-      <c r="F382" s="1" t="inlineStr">
+      <c r="F382" t="inlineStr">
         <is>
           <t>gelateria_fiordiluna</t>
         </is>
       </c>
-      <c r="G382" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H382" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I382" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J382" s="1" t="inlineStr"/>
-      <c r="K382" s="1" t="inlineStr"/>
-      <c r="L382" s="1" t="inlineStr"/>
-      <c r="M382" s="1" t="inlineStr"/>
-      <c r="N382" s="1" t="inlineStr"/>
-      <c r="O382" s="1" t="inlineStr"/>
-      <c r="P382" s="1" t="inlineStr"/>
-      <c r="Q382" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R382" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (GelateriaFiordiluna) | IG: trovato (gelateria_fiordiluna)</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="inlineStr">
+      <c r="A383" t="inlineStr">
         <is>
           <t>Forno Bianchi</t>
         </is>
       </c>
-      <c r="B383" s="1" t="inlineStr">
+      <c r="B383" t="inlineStr">
         <is>
           <t>Largo delle Sette Chiese, 16</t>
         </is>
       </c>
-      <c r="C383" s="1" t="inlineStr">
+      <c r="C383" t="inlineStr">
         <is>
           <t>n.d.</t>
         </is>
       </c>
-      <c r="D383" s="1" t="inlineStr"/>
-      <c r="E383" s="1" t="inlineStr"/>
-      <c r="F383" s="1" t="inlineStr"/>
-      <c r="G383" s="1" t="inlineStr"/>
-      <c r="H383" s="1" t="inlineStr"/>
-      <c r="I383" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J383" s="1" t="inlineStr"/>
-      <c r="K383" s="1" t="inlineStr"/>
-      <c r="L383" s="1" t="inlineStr"/>
-      <c r="M383" s="1" t="inlineStr"/>
-      <c r="N383" s="1" t="inlineStr"/>
-      <c r="O383" s="1" t="inlineStr"/>
-      <c r="P383" s="1" t="inlineStr"/>
-      <c r="Q383" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R383" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '08, 17:30', 'closes': '14:30, 21:30', 'break': '14:30–17:</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="inlineStr">
+      <c r="A384" t="inlineStr">
         <is>
           <t>Frumentario</t>
         </is>
       </c>
-      <c r="B384" s="1" t="inlineStr">
+      <c r="B384" t="inlineStr">
         <is>
           <t>Via Tuscolana, 26</t>
         </is>
       </c>
-      <c r="C384" s="1" t="inlineStr">
+      <c r="C384" t="inlineStr">
         <is>
           <t>324/0578982</t>
         </is>
       </c>
-      <c r="D384" s="1" t="inlineStr"/>
-      <c r="E384" s="1" t="inlineStr">
+      <c r="E384" t="inlineStr">
         <is>
           <t>frumentariopizzaromana</t>
         </is>
       </c>
-      <c r="F384" s="1" t="inlineStr">
+      <c r="F384" t="inlineStr">
         <is>
           <t>frumentario_</t>
         </is>
       </c>
-      <c r="G384" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H384" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I384" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J384" s="1" t="inlineStr"/>
-      <c r="K384" s="1" t="inlineStr"/>
-      <c r="L384" s="1" t="inlineStr"/>
-      <c r="M384" s="1" t="inlineStr"/>
-      <c r="N384" s="1" t="inlineStr"/>
-      <c r="O384" s="1" t="inlineStr"/>
-      <c r="P384" s="1" t="inlineStr"/>
-      <c r="Q384" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R384" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '11', 'closes': '22'}, 'venerdì': {'opens': '11', 'closes'</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (frumentariopizzaromana) | IG: trovato (frumentario_)</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="inlineStr">
+      <c r="A385" t="inlineStr">
         <is>
           <t>Garage Forno</t>
         </is>
       </c>
-      <c r="B385" s="1" t="inlineStr">
+      <c r="B385" t="inlineStr">
         <is>
           <t>Via Paolo II, 14</t>
         </is>
       </c>
-      <c r="C385" s="1" t="inlineStr">
+      <c r="C385" t="inlineStr">
         <is>
           <t>392/2984896</t>
         </is>
       </c>
-      <c r="D385" s="1" t="inlineStr">
+      <c r="D385" t="inlineStr">
         <is>
           <t>www.garageforno.it</t>
         </is>
       </c>
-      <c r="E385" s="1" t="inlineStr"/>
-      <c r="F385" s="1" t="inlineStr">
+      <c r="F385" t="inlineStr">
         <is>
           <t>garageforno</t>
         </is>
       </c>
-      <c r="G385" s="1" t="inlineStr"/>
-      <c r="H385" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I385" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J385" s="1" t="inlineStr"/>
-      <c r="K385" s="1" t="inlineStr"/>
-      <c r="L385" s="1" t="inlineStr"/>
-      <c r="M385" s="1" t="inlineStr"/>
-      <c r="N385" s="1" t="inlineStr"/>
-      <c r="O385" s="1" t="inlineStr"/>
-      <c r="P385" s="1" t="inlineStr"/>
-      <c r="Q385" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R385" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '07:30', 'closes': '21'}, 'venerdì': {'opens': '07:30', 'c</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (garageforno)</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="inlineStr">
+      <c r="A386" t="inlineStr">
         <is>
           <t>Gelasio</t>
         </is>
       </c>
-      <c r="B386" s="1" t="inlineStr">
+      <c r="B386" t="inlineStr">
         <is>
           <t>Via Portuense, 727 F/G</t>
         </is>
       </c>
-      <c r="C386" s="1" t="inlineStr">
+      <c r="C386" t="inlineStr">
         <is>
           <t>06/6858 5315</t>
         </is>
       </c>
-      <c r="D386" s="1" t="inlineStr"/>
-      <c r="E386" s="1" t="inlineStr">
+      <c r="E386" t="inlineStr">
         <is>
           <t>GelasioOltreIlGelato</t>
         </is>
       </c>
-      <c r="F386" s="1" t="inlineStr">
+      <c r="F386" t="inlineStr">
         <is>
           <t>gelasio.oltreilgelato</t>
         </is>
       </c>
-      <c r="G386" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H386" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I386" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J386" s="1" t="inlineStr"/>
-      <c r="K386" s="1" t="inlineStr"/>
-      <c r="L386" s="1" t="inlineStr"/>
-      <c r="M386" s="1" t="inlineStr"/>
-      <c r="N386" s="1" t="inlineStr"/>
-      <c r="O386" s="1" t="inlineStr"/>
-      <c r="P386" s="1" t="inlineStr"/>
-      <c r="Q386" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R386" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '13', 'closes': '00:30'}, 'venerdì': {'opens': '13', 'clos</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (GelasioOltreIlGelato) | IG: trovato (gelasio.oltreilgelato)</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="inlineStr">
+      <c r="A387" t="inlineStr">
         <is>
           <t>Gelateria dei Gracchi</t>
         </is>
       </c>
-      <c r="B387" s="1" t="inlineStr">
+      <c r="B387" t="inlineStr">
         <is>
           <t>Viale delle Province, 30</t>
         </is>
       </c>
-      <c r="C387" s="1" t="inlineStr">
+      <c r="C387" t="inlineStr">
         <is>
           <t>06/89831448</t>
         </is>
       </c>
-      <c r="D387" s="1" t="inlineStr">
+      <c r="D387" t="inlineStr">
         <is>
           <t>www.gelateriadeigracchi.it</t>
         </is>
       </c>
-      <c r="E387" s="1" t="inlineStr">
+      <c r="E387" t="inlineStr">
         <is>
           <t>profile.php?id=100063635528660</t>
         </is>
       </c>
-      <c r="F387" s="1" t="inlineStr">
+      <c r="F387" t="inlineStr">
         <is>
           <t>gelateriadeigracchi</t>
         </is>
       </c>
-      <c r="G387" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H387" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I387" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J387" s="1" t="inlineStr"/>
-      <c r="K387" s="1" t="inlineStr"/>
-      <c r="L387" s="1" t="inlineStr"/>
-      <c r="M387" s="1" t="inlineStr"/>
-      <c r="N387" s="1" t="inlineStr"/>
-      <c r="O387" s="1" t="inlineStr"/>
-      <c r="P387" s="1" t="inlineStr"/>
-      <c r="Q387" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R387" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (profile.php?id=100063635528660) | IG: trovato (gelateriadeigracchi)</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="inlineStr">
+      <c r="A388" t="inlineStr">
         <is>
           <t>Gelateria I Gemelli</t>
         </is>
       </c>
-      <c r="B388" s="1" t="inlineStr">
+      <c r="B388" t="inlineStr">
         <is>
           <t>Via Fonte Buono, 114</t>
         </is>
       </c>
-      <c r="C388" s="1" t="inlineStr">
+      <c r="C388" t="inlineStr">
         <is>
           <t>349/8360994</t>
         </is>
       </c>
-      <c r="D388" s="1" t="inlineStr"/>
-      <c r="E388" s="1" t="inlineStr">
+      <c r="E388" t="inlineStr">
         <is>
           <t>Igemelligelateria</t>
         </is>
       </c>
-      <c r="F388" s="1" t="inlineStr">
+      <c r="F388" t="inlineStr">
         <is>
           <t>igemelligelateria</t>
         </is>
       </c>
-      <c r="G388" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H388" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I388" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J388" s="1" t="inlineStr"/>
-      <c r="K388" s="1" t="inlineStr"/>
-      <c r="L388" s="1" t="inlineStr"/>
-      <c r="M388" s="1" t="inlineStr"/>
-      <c r="N388" s="1" t="inlineStr"/>
-      <c r="O388" s="1" t="inlineStr"/>
-      <c r="P388" s="1" t="inlineStr"/>
-      <c r="Q388" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R388" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (Igemelligelateria) | IG: trovato (igemelligelateria)</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="inlineStr">
+      <c r="A389" t="inlineStr">
         <is>
           <t>Gelateria I Mannari</t>
         </is>
       </c>
-      <c r="B389" s="1" t="inlineStr">
+      <c r="B389" t="inlineStr">
         <is>
           <t>Via di Grotta Perfetta, 125</t>
         </is>
       </c>
-      <c r="C389" s="1" t="inlineStr">
+      <c r="C389" t="inlineStr">
         <is>
           <t>06/5410448</t>
         </is>
       </c>
-      <c r="D389" s="1" t="inlineStr">
+      <c r="D389" t="inlineStr">
         <is>
           <t>www.gelateriaimannari.com</t>
         </is>
       </c>
-      <c r="E389" s="1" t="inlineStr">
+      <c r="E389" t="inlineStr">
         <is>
           <t>gelateriaimannari</t>
         </is>
       </c>
-      <c r="F389" s="1" t="inlineStr">
+      <c r="F389" t="inlineStr">
         <is>
           <t>gelateriaimannari</t>
         </is>
       </c>
-      <c r="G389" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H389" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I389" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J389" s="1" t="inlineStr"/>
-      <c r="K389" s="1" t="inlineStr"/>
-      <c r="L389" s="1" t="inlineStr"/>
-      <c r="M389" s="1" t="inlineStr"/>
-      <c r="N389" s="1" t="inlineStr"/>
-      <c r="O389" s="1" t="inlineStr"/>
-      <c r="P389" s="1" t="inlineStr"/>
-      <c r="Q389" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R389" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '01'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (gelateriaimannari) | IG: trovato (gelateriaimannari)</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="inlineStr">
+      <c r="A390" t="inlineStr">
         <is>
           <t>Gelato d'Essai</t>
         </is>
       </c>
-      <c r="B390" s="1" t="inlineStr">
+      <c r="B390" t="inlineStr">
         <is>
           <t>Viale B. Bardanzellu, 77</t>
         </is>
       </c>
-      <c r="C390" s="1" t="inlineStr">
+      <c r="C390" t="inlineStr">
         <is>
           <t>06/64264692</t>
         </is>
       </c>
-      <c r="D390" s="1" t="inlineStr">
+      <c r="D390" t="inlineStr">
         <is>
           <t>www.gelatodessai.it</t>
         </is>
       </c>
-      <c r="E390" s="1" t="inlineStr">
+      <c r="E390" t="inlineStr">
         <is>
           <t>gelatodessai</t>
         </is>
       </c>
-      <c r="F390" s="1" t="inlineStr">
+      <c r="F390" t="inlineStr">
         <is>
           <t>gelatodessai</t>
         </is>
       </c>
-      <c r="G390" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H390" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I390" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J390" s="1" t="inlineStr"/>
-      <c r="K390" s="1" t="inlineStr"/>
-      <c r="L390" s="1" t="inlineStr"/>
-      <c r="M390" s="1" t="inlineStr"/>
-      <c r="N390" s="1" t="inlineStr"/>
-      <c r="O390" s="1" t="inlineStr"/>
-      <c r="P390" s="1" t="inlineStr"/>
-      <c r="Q390" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R390" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gelatodessai) | IG: trovato (gelatodessai)</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -22233,192 +22233,238 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B357" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C357" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D357" s="1" t="inlineStr"/>
-      <c r="E357" s="1" t="inlineStr"/>
-      <c r="F357" s="1" t="inlineStr"/>
-      <c r="G357" s="1" t="inlineStr"/>
-      <c r="H357" s="1" t="inlineStr"/>
-      <c r="I357" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J357" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K357" s="1" t="inlineStr"/>
-      <c r="L357" s="1" t="inlineStr"/>
-      <c r="M357" s="1" t="inlineStr"/>
-      <c r="N357" s="1" t="inlineStr"/>
-      <c r="O357" s="1" t="inlineStr"/>
-      <c r="P357" s="1" t="inlineStr"/>
-      <c r="Q357" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R357" s="1" t="inlineStr">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Pupillo Pura Pizza</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Via Giacomo Matteotti, 29</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>339/4143148</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '19', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B358" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C358" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D358" s="1" t="inlineStr"/>
-      <c r="E358" s="1" t="inlineStr"/>
-      <c r="F358" s="1" t="inlineStr"/>
-      <c r="G358" s="1" t="inlineStr"/>
-      <c r="H358" s="1" t="inlineStr"/>
-      <c r="I358" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J358" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K358" s="1" t="inlineStr"/>
-      <c r="L358" s="1" t="inlineStr"/>
-      <c r="M358" s="1" t="inlineStr"/>
-      <c r="N358" s="1" t="inlineStr"/>
-      <c r="O358" s="1" t="inlineStr"/>
-      <c r="P358" s="1" t="inlineStr"/>
-      <c r="Q358" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R358" s="1" t="inlineStr">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>N.O.D.O.</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Piazza delle Coppelle, 52</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>06/94376334</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>www.nodoroma.it</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>NodoRoma-108837454790526</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>nodoroma</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '17', 'closes': '01'}, 'venerdì': {'opens': '18', 'closes'</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (NodoRoma-108837454790526) | IG: non trovato (nodoroma)</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="inlineStr">
-        <is>
-          <t>Clementina</t>
-        </is>
-      </c>
-      <c r="B359" s="1" t="inlineStr">
-        <is>
-          <t>Via della Torre Clementina, 158</t>
-        </is>
-      </c>
-      <c r="C359" s="1" t="inlineStr">
-        <is>
-          <t>328/8181651</t>
-        </is>
-      </c>
-      <c r="D359" s="1" t="inlineStr"/>
-      <c r="E359" s="1" t="inlineStr"/>
-      <c r="F359" s="1" t="inlineStr"/>
-      <c r="G359" s="1" t="inlineStr"/>
-      <c r="H359" s="1" t="inlineStr"/>
-      <c r="I359" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J359" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K359" s="1" t="inlineStr"/>
-      <c r="L359" s="1" t="inlineStr"/>
-      <c r="M359" s="1" t="inlineStr"/>
-      <c r="N359" s="1" t="inlineStr"/>
-      <c r="O359" s="1" t="inlineStr"/>
-      <c r="P359" s="1" t="inlineStr"/>
-      <c r="Q359" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R359" s="1" t="inlineStr">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Nite Kong</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Piazza di San Martino ai Monti, 8</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>06/23488666</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>www.nitekong.com</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>nitekong</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (nitekong)</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="inlineStr">
-        <is>
-          <t>Da Antonio</t>
-        </is>
-      </c>
-      <c r="B360" s="1" t="inlineStr">
-        <is>
-          <t>Via Mario Lizzani, 21</t>
-        </is>
-      </c>
-      <c r="C360" s="1" t="inlineStr">
-        <is>
-          <t>391/7475549</t>
-        </is>
-      </c>
-      <c r="D360" s="1" t="inlineStr"/>
-      <c r="E360" s="1" t="inlineStr"/>
-      <c r="F360" s="1" t="inlineStr"/>
-      <c r="G360" s="1" t="inlineStr"/>
-      <c r="H360" s="1" t="inlineStr"/>
-      <c r="I360" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J360" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K360" s="1" t="inlineStr"/>
-      <c r="L360" s="1" t="inlineStr"/>
-      <c r="M360" s="1" t="inlineStr"/>
-      <c r="N360" s="1" t="inlineStr"/>
-      <c r="O360" s="1" t="inlineStr"/>
-      <c r="P360" s="1" t="inlineStr"/>
-      <c r="Q360" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R360" s="1" t="inlineStr">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Pork’n’Roll</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Via Carlo Caneva, 15</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>06/45551271</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>www.porknroll.com</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>porknrollpub</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>porknrollpub</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '18', 'closes': '01:30'}, 'venerdì': {'opens': '18', 'clos</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (porknrollpub) | IG: non trovato (porknrollpub)</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
@@ -22427,17 +22473,37 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Pupillo Pura Pizza</t>
+          <t>amARanto</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Via Giacomo Matteotti, 29</t>
+          <t>Via Adige, 19/21</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>339/4143148</t>
+          <t>06/93374742</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>pizzamaranto</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>pizzamaranto</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22445,19 +22511,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '19', 'closes': '00'}, 'venerdì': {'opens': '19', 'closes'</t>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (pizzamaranto) | IG: non trovato (pizzamaranto)</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -22467,92 +22528,144 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="inlineStr">
-        <is>
-          <t>Il tuo fornaio</t>
-        </is>
-      </c>
-      <c r="B362" s="1" t="inlineStr">
-        <is>
-          <t>Via Francesco Sapori, 35</t>
-        </is>
-      </c>
-      <c r="C362" s="1" t="inlineStr">
-        <is>
-          <t>06/5017873</t>
-        </is>
-      </c>
-      <c r="D362" s="1" t="inlineStr"/>
-      <c r="E362" s="1" t="inlineStr"/>
-      <c r="F362" s="1" t="inlineStr"/>
-      <c r="G362" s="1" t="inlineStr"/>
-      <c r="H362" s="1" t="inlineStr"/>
-      <c r="I362" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J362" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K362" s="1" t="inlineStr"/>
-      <c r="L362" s="1" t="inlineStr"/>
-      <c r="M362" s="1" t="inlineStr"/>
-      <c r="N362" s="1" t="inlineStr"/>
-      <c r="O362" s="1" t="inlineStr"/>
-      <c r="P362" s="1" t="inlineStr"/>
-      <c r="Q362" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R362" s="1" t="inlineStr">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Amerina - la pizzetta</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Largo dei Librari, 82</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>06/45495604</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>www.amerinalapizzetta.it</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>amerinalapizzetta</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>amerina_lapizzetta</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '17', 'closes': '23'}, 'venerdì': {'opens': '11', 'closes'</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (amerinalapizzetta) | IG: non trovato (amerina_lapizzetta)</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="inlineStr">
-        <is>
-          <t>Slow</t>
-        </is>
-      </c>
-      <c r="B363" s="1" t="inlineStr">
-        <is>
-          <t>Corso Vittorio Emanuele II, 73</t>
-        </is>
-      </c>
-      <c r="C363" s="1" t="inlineStr"/>
-      <c r="D363" s="1" t="inlineStr"/>
-      <c r="E363" s="1" t="inlineStr"/>
-      <c r="F363" s="1" t="inlineStr"/>
-      <c r="G363" s="1" t="inlineStr"/>
-      <c r="H363" s="1" t="inlineStr"/>
-      <c r="I363" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J363" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K363" s="1" t="inlineStr"/>
-      <c r="L363" s="1" t="inlineStr"/>
-      <c r="M363" s="1" t="inlineStr"/>
-      <c r="N363" s="1" t="inlineStr"/>
-      <c r="O363" s="1" t="inlineStr"/>
-      <c r="P363" s="1" t="inlineStr"/>
-      <c r="Q363" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R363" s="1" t="inlineStr">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Antico Forno Roscioli</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Via dei Chiavari, 34</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>06/6864045</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>www.anticofornoroscioli.it</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>AnticoFornoRoscioli</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>anticofornoroscioli</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '07:30', 'closes': '20'}, 'venerdì': {'opens': '07:30', 'c</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (AnticoFornoRoscioli) | IG: non trovato (anticofornoroscioli)</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
@@ -22561,32 +22674,27 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>N.O.D.O.</t>
+          <t>Arte Bianca di Gabriele</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Piazza delle Coppelle, 52</t>
+          <t>Largo Sangemini, 7/B-C</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>06/94376334</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>www.nodoroma.it</t>
+          <t>06/2757763</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>NodoRoma-108837454790526</t>
+          <t>profile.php?id=100086435003228</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>nodoroma</t>
+          <t>artebianca_digabriele</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -22609,11 +22717,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M364" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '17', 'closes': '01'}, 'venerdì': {'opens': '18', 'closes'</t>
-        </is>
-      </c>
       <c r="O364" t="inlineStr">
         <is>
           <t>Si</t>
@@ -22621,7 +22724,7 @@
       </c>
       <c r="Q364" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (NodoRoma-108837454790526) | IG: non trovato (nodoroma)</t>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100086435003228) | IG: non trovato (artebianca_digabriele)</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -22633,27 +22736,22 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Nite Kong</t>
+          <t>Becco</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Piazza di San Martino ai Monti, 8</t>
+          <t>Piazzale degli Eroi, 7</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>06/23488666</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>www.nitekong.com</t>
+          <t>06/98183647</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>nitekong</t>
+          <t>beccoroma</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -22671,9 +22769,14 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 18', 'closes': '15, 22:30', 'break': '15–18'}, 've</t>
+        </is>
+      </c>
       <c r="Q365" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (nitekong)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (beccoroma)</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
@@ -22685,32 +22788,32 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Pork’n’Roll</t>
+          <t>Claudio Torcè</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Via Carlo Caneva, 15</t>
+          <t>Piazza Euclide, 25</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>06/45551271</t>
+          <t>06/5746876</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>www.porknroll.com</t>
+          <t>www.gelateriatorce.it</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>porknrollpub</t>
+          <t>gelateriatorce</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>porknrollpub</t>
+          <t>gelateria_torce</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -22728,16 +22831,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '18', 'closes': '01:30'}, 'venerdì': {'opens': '18', 'clos</t>
-        </is>
-      </c>
       <c r="O366" t="inlineStr">
         <is>
           <t>Si</t>
@@ -22745,7 +22838,7 @@
       </c>
       <c r="Q366" t="inlineStr">
         <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (porknrollpub) | IG: non trovato (porknrollpub)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gelateriatorce) | IG: non trovato (gelateria_torce)</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -22757,27 +22850,32 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>amARanto</t>
+          <t>Come il Latte</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Via Adige, 19/21</t>
+          <t>Via Silvio Spaventa 24/26</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>06/93374742</t>
+          <t>06/42903882</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>www.comeillatte.it</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>pizzamaranto</t>
+          <t>comeillatte</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>pizzamaranto</t>
+          <t>comeillatte</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -22795,6 +22893,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
       <c r="O367" t="inlineStr">
         <is>
           <t>Si</t>
@@ -22802,7 +22910,7 @@
       </c>
       <c r="Q367" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (pizzamaranto) | IG: non trovato (pizzamaranto)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (comeillatte) | IG: non trovato (comeillatte)</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -22814,32 +22922,32 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Amerina - la pizzetta</t>
+          <t>Cremeria Alpi</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Largo dei Librari, 82</t>
+          <t>Via Padre Reginaldo Giuliani, 16</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>06/45495604</t>
+          <t>06/88921386</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>www.amerinalapizzetta.it</t>
+          <t>www.cremeriaalpi.it</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>amerinalapizzetta</t>
+          <t>cremeriaalpi</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>amerina_lapizzetta</t>
+          <t>cremeriaalpi</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -22857,16 +22965,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J368" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '17', 'closes': '23'}, 'venerdì': {'opens': '11', 'closes'</t>
-        </is>
-      </c>
       <c r="O368" t="inlineStr">
         <is>
           <t>Si</t>
@@ -22874,7 +22972,7 @@
       </c>
       <c r="Q368" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (amerinalapizzetta) | IG: non trovato (amerina_lapizzetta)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (cremeriaalpi) | IG: non trovato (cremeriaalpi)</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -22886,32 +22984,27 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Antico Forno Roscioli</t>
+          <t>Cremeria Aurelia</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Via dei Chiavari, 34</t>
+          <t>Via Aurelia, 388/B</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>06/6864045</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>www.anticofornoroscioli.it</t>
+          <t>06/6632499</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>AnticoFornoRoscioli</t>
+          <t>Cremeria-Aurelia</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>anticofornoroscioli</t>
+          <t>cremeriaaurelia</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -22936,7 +23029,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '07:30', 'closes': '20'}, 'venerdì': {'opens': '07:30', 'c</t>
+          <t>{'giovedì': {'opens': '12', 'closes': '23:30'}, 'venerdì': {'opens': '12', 'clos</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -22946,7 +23039,7 @@
       </c>
       <c r="Q369" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (AnticoFornoRoscioli) | IG: non trovato (anticofornoroscioli)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Cremeria-Aurelia) | IG: non trovato (cremeriaaurelia)</t>
         </is>
       </c>
       <c r="R369" t="inlineStr">
@@ -22958,27 +23051,32 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Arte Bianca di Gabriele</t>
+          <t>Criollo - Il Bistrot Del Gelato</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Largo Sangemini, 7/B-C</t>
+          <t>Via Giuseppe Bagnera, 59</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>06/2757763</t>
+          <t>328/2511673</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>www.criollogelato.it</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>profile.php?id=100086435003228</t>
+          <t>Criollo-Il-bistrot-del-gelato</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>artebianca_digabriele</t>
+          <t>criollo_gelato</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -23001,6 +23099,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': 'Chiuso'}, 'venerdì': {'opens': '15', 'closes': '23'}, 'sa</t>
+        </is>
+      </c>
       <c r="O370" t="inlineStr">
         <is>
           <t>Si</t>
@@ -23008,7 +23111,7 @@
       </c>
       <c r="Q370" t="inlineStr">
         <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (profile.php?id=100086435003228) | IG: non trovato (artebianca_digabriele)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (Criollo-Il-bistrot-del-gelato) | IG: non trovato (criollo_gelato)</t>
         </is>
       </c>
       <c r="R370" t="inlineStr">
@@ -23020,27 +23123,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Becco</t>
+          <t>Crunch Teglia</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Piazzale degli Eroi, 7</t>
+          <t>Via della Bufalotta, 284</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>06/98183647</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>beccoroma</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>06/99606077</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23055,12 +23148,12 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12:30, 18', 'closes': '15, 22:30', 'break': '15–18'}, 've</t>
+          <t>{'giovedì': {'opens': '10', 'closes': '22'}, 'venerdì': {'opens': '10', 'closes'</t>
         </is>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: non trovato (beccoroma)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
@@ -23072,32 +23165,32 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Claudio Torcè</t>
+          <t>Da Tullio</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Piazza Euclide, 25</t>
+          <t>Via della Balduina, 211</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>06/5746876</t>
+          <t>06/35347252</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>www.gelateriatorce.it</t>
+          <t>www.datulliopizza.it</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>gelateriatorce</t>
+          <t>DTP-Da-Tullio-Pizza</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>gelateria_torce</t>
+          <t>tulliopizza</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -23115,6 +23208,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
+        </is>
+      </c>
       <c r="O372" t="inlineStr">
         <is>
           <t>Si</t>
@@ -23122,7 +23225,7 @@
       </c>
       <c r="Q372" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gelateriatorce) | IG: non trovato (gelateria_torce)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (DTP-Da-Tullio-Pizza) | IG: non trovato (tulliopizza)</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
@@ -23134,32 +23237,32 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Come il Latte</t>
+          <t>Don Choc</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Via Silvio Spaventa 24/26</t>
+          <t>Via Flaminia Vecchia, 732/E-F-G-H</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>06/42903882</t>
+          <t>06/33221585</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>www.comeillatte.it</t>
+          <t>www.donchoc.com</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>comeillatte</t>
+          <t>donchocfleming</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>comeillatte</t>
+          <t>donchoc</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -23184,7 +23287,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '23'}, 'venerdì': {'opens': '12', 'closes'</t>
+          <t>{'giovedì': {'opens': '11:30', 'closes': '23'}, 'venerdì': {'opens': '11:30', 'c</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
@@ -23194,7 +23297,7 @@
       </c>
       <c r="Q373" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (comeillatte) | IG: non trovato (comeillatte)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (donchocfleming) | IG: non trovato (donchoc)</t>
         </is>
       </c>
       <c r="R373" t="inlineStr">
@@ -23206,32 +23309,32 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Cremeria Alpi</t>
+          <t>El maiz</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Via Padre Reginaldo Giuliani, 16</t>
+          <t>Via Tolemaide, 16</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>06/88921386</t>
+          <t>06/66006878</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>www.cremeriaalpi.it</t>
+          <t>www.elmaiz.it</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>cremeriaalpi</t>
+          <t>elmaizroma</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>cremeriaalpi</t>
+          <t>elmaiz.roma</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -23249,6 +23352,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '22'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
       <c r="O374" t="inlineStr">
         <is>
           <t>Si</t>
@@ -23256,7 +23369,7 @@
       </c>
       <c r="Q374" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (cremeriaalpi) | IG: non trovato (cremeriaalpi)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (elmaizroma) | IG: trovato (elmaiz.roma)</t>
         </is>
       </c>
       <c r="R374" t="inlineStr">
@@ -23268,27 +23381,32 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Cremeria Aurelia</t>
+          <t>Fatamorgana</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Via Aurelia, 388/B</t>
+          <t>Via Lago di Lesina, 9/11</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>06/6632499</t>
+          <t>06/86391589</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>www.gelateriafatamorgana.it</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Cremeria-Aurelia</t>
+          <t>Fatamorgana.Gelaterie</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>cremeriaaurelia</t>
+          <t>gelateriafatamorgana</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -23313,7 +23431,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '23:30'}, 'venerdì': {'opens': '12', 'clos</t>
+          <t>{'giovedì': {'opens': '13:30', 'closes': '21:30'}, 'venerdì': {'opens': '13:30',</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -23323,7 +23441,7 @@
       </c>
       <c r="Q375" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Cremeria-Aurelia) | IG: non trovato (cremeriaaurelia)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (Fatamorgana.Gelaterie) | IG: trovato (gelateriafatamorgana)</t>
         </is>
       </c>
       <c r="R375" t="inlineStr">
@@ -23335,32 +23453,27 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Criollo - Il Bistrot Del Gelato</t>
+          <t>Fior di Luna</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Via Giuseppe Bagnera, 59</t>
+          <t>Via della Lungaretta, 96</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>328/2511673</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>www.criollogelato.it</t>
+          <t>06/64561314</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Criollo-Il-bistrot-del-gelato</t>
+          <t>GelateriaFiordiluna</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>criollo_gelato</t>
+          <t>gelateria_fiordiluna</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -23378,16 +23491,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': 'Chiuso'}, 'venerdì': {'opens': '15', 'closes': '23'}, 'sa</t>
-        </is>
-      </c>
       <c r="O376" t="inlineStr">
         <is>
           <t>Si</t>
@@ -23395,7 +23498,7 @@
       </c>
       <c r="Q376" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (Criollo-Il-bistrot-del-gelato) | IG: non trovato (criollo_gelato)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (GelateriaFiordiluna) | IG: trovato (gelateria_fiordiluna)</t>
         </is>
       </c>
       <c r="R376" t="inlineStr">
@@ -23407,17 +23510,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Crunch Teglia</t>
+          <t>Forno Bianchi</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Via della Bufalotta, 284</t>
+          <t>Largo delle Sette Chiese, 16</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>06/99606077</t>
+          <t>n.d.</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23432,12 +23535,12 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '10', 'closes': '22'}, 'venerdì': {'opens': '10', 'closes'</t>
+          <t>{'giovedì': {'opens': '08, 17:30', 'closes': '14:30, 21:30', 'break': '14:30–17:</t>
         </is>
       </c>
       <c r="Q377" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
@@ -23449,32 +23552,27 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Da Tullio</t>
+          <t>Frumentario</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Via della Balduina, 211</t>
+          <t>Via Tuscolana, 26</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>06/35347252</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>www.datulliopizza.it</t>
+          <t>324/0578982</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>DTP-Da-Tullio-Pizza</t>
+          <t>frumentariopizzaromana</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>tulliopizza</t>
+          <t>frumentario_</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -23499,7 +23597,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12:30, 19:30', 'closes': '15, 23', 'break': '15–19:30'},</t>
+          <t>{'giovedì': {'opens': '11', 'closes': '22'}, 'venerdì': {'opens': '11', 'closes'</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -23509,7 +23607,7 @@
       </c>
       <c r="Q378" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (DTP-Da-Tullio-Pizza) | IG: non trovato (tulliopizza)</t>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (frumentariopizzaromana) | IG: trovato (frumentario_)</t>
         </is>
       </c>
       <c r="R378" t="inlineStr">
@@ -23521,37 +23619,27 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Don Choc</t>
+          <t>Garage Forno</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Via Flaminia Vecchia, 732/E-F-G-H</t>
+          <t>Via Paolo II, 14</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>06/33221585</t>
+          <t>392/2984896</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>www.donchoc.com</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>donchocfleming</t>
+          <t>www.garageforno.it</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>donchoc</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>garageforno</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -23571,7 +23659,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '11:30', 'closes': '23'}, 'venerdì': {'opens': '11:30', 'c</t>
+          <t>{'giovedì': {'opens': '07:30', 'closes': '21'}, 'venerdì': {'opens': '07:30', 'c</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -23581,7 +23669,7 @@
       </c>
       <c r="Q379" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (donchocfleming) | IG: non trovato (donchoc)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (garageforno)</t>
         </is>
       </c>
       <c r="R379" t="inlineStr">
@@ -23593,32 +23681,27 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>El maiz</t>
+          <t>Gelasio</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Via Tolemaide, 16</t>
+          <t>Via Portuense, 727 F/G</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>06/66006878</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>www.elmaiz.it</t>
+          <t>06/6858 5315</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>elmaizroma</t>
+          <t>GelasioOltreIlGelato</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>elmaiz.roma</t>
+          <t>gelasio.oltreilgelato</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -23643,7 +23726,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '22'}, 'venerdì': {'opens': '12', 'closes'</t>
+          <t>{'giovedì': {'opens': '13', 'closes': '00:30'}, 'venerdì': {'opens': '13', 'clos</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -23653,7 +23736,7 @@
       </c>
       <c r="Q380" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (elmaizroma) | IG: trovato (elmaiz.roma)</t>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (GelasioOltreIlGelato) | IG: trovato (gelasio.oltreilgelato)</t>
         </is>
       </c>
       <c r="R380" t="inlineStr">
@@ -23665,32 +23748,32 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Fatamorgana</t>
+          <t>Gelateria dei Gracchi</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Via Lago di Lesina, 9/11</t>
+          <t>Viale delle Province, 30</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>06/86391589</t>
+          <t>06/89831448</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>www.gelateriafatamorgana.it</t>
+          <t>www.gelateriadeigracchi.it</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Fatamorgana.Gelaterie</t>
+          <t>profile.php?id=100063635528660</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>gelateriafatamorgana</t>
+          <t>gelateriadeigracchi</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -23708,16 +23791,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M381" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '13:30', 'closes': '21:30'}, 'venerdì': {'opens': '13:30',</t>
-        </is>
-      </c>
       <c r="O381" t="inlineStr">
         <is>
           <t>Si</t>
@@ -23725,7 +23798,7 @@
       </c>
       <c r="Q381" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (Fatamorgana.Gelaterie) | IG: trovato (gelateriafatamorgana)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (profile.php?id=100063635528660) | IG: trovato (gelateriadeigracchi)</t>
         </is>
       </c>
       <c r="R381" t="inlineStr">
@@ -23737,27 +23810,27 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Fior di Luna</t>
+          <t>Gelateria I Gemelli</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Via della Lungaretta, 96</t>
+          <t>Via Fonte Buono, 114</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>06/64561314</t>
+          <t>349/8360994</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>GelateriaFiordiluna</t>
+          <t>Igemelligelateria</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>gelateria_fiordiluna</t>
+          <t>igemelligelateria</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -23775,6 +23848,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
       <c r="O382" t="inlineStr">
         <is>
           <t>Si</t>
@@ -23782,7 +23865,7 @@
       </c>
       <c r="Q382" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (GelateriaFiordiluna) | IG: trovato (gelateria_fiordiluna)</t>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (Igemelligelateria) | IG: trovato (igemelligelateria)</t>
         </is>
       </c>
       <c r="R382" t="inlineStr">
@@ -23794,17 +23877,42 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Forno Bianchi</t>
+          <t>Gelateria I Mannari</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Largo delle Sette Chiese, 16</t>
+          <t>Via di Grotta Perfetta, 125</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>n.d.</t>
+          <t>06/5410448</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>www.gelateriaimannari.com</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>gelateriaimannari</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>gelateriaimannari</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23819,12 +23927,17 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>{'giovedì': {'opens': '08, 17:30', 'closes': '14:30, 21:30', 'break': '14:30–17:</t>
+          <t>{'giovedì': {'opens': '12', 'closes': '01'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>Si</t>
         </is>
       </c>
       <c r="Q383" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (gelateriaimannari) | IG: trovato (gelateriaimannari)</t>
         </is>
       </c>
       <c r="R383" t="inlineStr">
@@ -23836,27 +23949,32 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Frumentario</t>
+          <t>Gelato d'Essai</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Via Tuscolana, 26</t>
+          <t>Viale B. Bardanzellu, 77</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>324/0578982</t>
+          <t>06/64264692</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>www.gelatodessai.it</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>frumentariopizzaromana</t>
+          <t>gelatodessai</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>frumentario_</t>
+          <t>gelatodessai</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -23874,16 +23992,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M384" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '11', 'closes': '22'}, 'venerdì': {'opens': '11', 'closes'</t>
-        </is>
-      </c>
       <c r="O384" t="inlineStr">
         <is>
           <t>Si</t>
@@ -23891,7 +23999,7 @@
       </c>
       <c r="Q384" t="inlineStr">
         <is>
-          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: trovato (frumentariopizzaromana) | IG: trovato (frumentario_)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gelatodessai) | IG: trovato (gelatodessai)</t>
         </is>
       </c>
       <c r="R384" t="inlineStr">
@@ -23901,450 +24009,348 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Garage Forno</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>Via Paolo II, 14</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>392/2984896</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>www.garageforno.it</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>garageforno</t>
-        </is>
-      </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M385" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '07:30', 'closes': '21'}, 'venerdì': {'opens': '07:30', 'c</t>
-        </is>
-      </c>
-      <c r="O385" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q385" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (garageforno)</t>
-        </is>
-      </c>
-      <c r="R385" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>Bless</t>
+        </is>
+      </c>
+      <c r="B385" s="1" t="inlineStr">
+        <is>
+          <t>Via dell’Indipendenza, 208</t>
+        </is>
+      </c>
+      <c r="C385" s="1" t="inlineStr">
+        <is>
+          <t>0771/030188</t>
+        </is>
+      </c>
+      <c r="D385" s="1" t="inlineStr"/>
+      <c r="E385" s="1" t="inlineStr"/>
+      <c r="F385" s="1" t="inlineStr"/>
+      <c r="G385" s="1" t="inlineStr"/>
+      <c r="H385" s="1" t="inlineStr"/>
+      <c r="I385" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J385" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K385" s="1" t="inlineStr"/>
+      <c r="L385" s="1" t="inlineStr"/>
+      <c r="M385" s="1" t="inlineStr"/>
+      <c r="N385" s="1" t="inlineStr"/>
+      <c r="O385" s="1" t="inlineStr"/>
+      <c r="P385" s="1" t="inlineStr"/>
+      <c r="Q385" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R385" s="1" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Gelasio</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>Via Portuense, 727 F/G</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>06/6858 5315</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>GelasioOltreIlGelato</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>gelasio.oltreilgelato</t>
-        </is>
-      </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I386" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J386" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M386" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '13', 'closes': '00:30'}, 'venerdì': {'opens': '13', 'clos</t>
-        </is>
-      </c>
-      <c r="O386" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q386" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (GelasioOltreIlGelato) | IG: trovato (gelasio.oltreilgelato)</t>
-        </is>
-      </c>
-      <c r="R386" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>Mrgda Ristorante</t>
+        </is>
+      </c>
+      <c r="B386" s="1" t="inlineStr">
+        <is>
+          <t>Via Prenestina, 182</t>
+        </is>
+      </c>
+      <c r="C386" s="1" t="inlineStr">
+        <is>
+          <t>329/933355</t>
+        </is>
+      </c>
+      <c r="D386" s="1" t="inlineStr"/>
+      <c r="E386" s="1" t="inlineStr"/>
+      <c r="F386" s="1" t="inlineStr"/>
+      <c r="G386" s="1" t="inlineStr"/>
+      <c r="H386" s="1" t="inlineStr"/>
+      <c r="I386" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J386" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K386" s="1" t="inlineStr"/>
+      <c r="L386" s="1" t="inlineStr"/>
+      <c r="M386" s="1" t="inlineStr"/>
+      <c r="N386" s="1" t="inlineStr"/>
+      <c r="O386" s="1" t="inlineStr"/>
+      <c r="P386" s="1" t="inlineStr"/>
+      <c r="Q386" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R386" s="1" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Gelateria dei Gracchi</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>Viale delle Province, 30</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>06/89831448</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>www.gelateriadeigracchi.it</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>profile.php?id=100063635528660</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>gelateriadeigracchi</t>
-        </is>
-      </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O387" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q387" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (profile.php?id=100063635528660) | IG: trovato (gelateriadeigracchi)</t>
-        </is>
-      </c>
-      <c r="R387" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>Clementina</t>
+        </is>
+      </c>
+      <c r="B387" s="1" t="inlineStr">
+        <is>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C387" s="1" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
+      <c r="D387" s="1" t="inlineStr"/>
+      <c r="E387" s="1" t="inlineStr"/>
+      <c r="F387" s="1" t="inlineStr"/>
+      <c r="G387" s="1" t="inlineStr"/>
+      <c r="H387" s="1" t="inlineStr"/>
+      <c r="I387" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J387" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K387" s="1" t="inlineStr"/>
+      <c r="L387" s="1" t="inlineStr"/>
+      <c r="M387" s="1" t="inlineStr"/>
+      <c r="N387" s="1" t="inlineStr"/>
+      <c r="O387" s="1" t="inlineStr"/>
+      <c r="P387" s="1" t="inlineStr"/>
+      <c r="Q387" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R387" s="1" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Gelateria I Gemelli</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>Via Fonte Buono, 114</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>349/8360994</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>Igemelligelateria</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>igemelligelateria</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I388" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M388" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '00'}, 'venerdì': {'opens': '12', 'closes'</t>
-        </is>
-      </c>
-      <c r="O388" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q388" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (Igemelligelateria) | IG: trovato (igemelligelateria)</t>
-        </is>
-      </c>
-      <c r="R388" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>Da Antonio</t>
+        </is>
+      </c>
+      <c r="B388" s="1" t="inlineStr">
+        <is>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C388" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
+      <c r="D388" s="1" t="inlineStr"/>
+      <c r="E388" s="1" t="inlineStr"/>
+      <c r="F388" s="1" t="inlineStr"/>
+      <c r="G388" s="1" t="inlineStr"/>
+      <c r="H388" s="1" t="inlineStr"/>
+      <c r="I388" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J388" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K388" s="1" t="inlineStr"/>
+      <c r="L388" s="1" t="inlineStr"/>
+      <c r="M388" s="1" t="inlineStr"/>
+      <c r="N388" s="1" t="inlineStr"/>
+      <c r="O388" s="1" t="inlineStr"/>
+      <c r="P388" s="1" t="inlineStr"/>
+      <c r="Q388" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R388" s="1" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>Gelateria I Mannari</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>Via di Grotta Perfetta, 125</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>06/5410448</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>www.gelateriaimannari.com</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>gelateriaimannari</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>gelateriaimannari</t>
-        </is>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I389" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J389" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '01'}, 'venerdì': {'opens': '12', 'closes'</t>
-        </is>
-      </c>
-      <c r="O389" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q389" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (gelateriaimannari) | IG: trovato (gelateriaimannari)</t>
-        </is>
-      </c>
-      <c r="R389" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>Il tuo fornaio</t>
+        </is>
+      </c>
+      <c r="B389" s="1" t="inlineStr">
+        <is>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C389" s="1" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
+      <c r="D389" s="1" t="inlineStr"/>
+      <c r="E389" s="1" t="inlineStr"/>
+      <c r="F389" s="1" t="inlineStr"/>
+      <c r="G389" s="1" t="inlineStr"/>
+      <c r="H389" s="1" t="inlineStr"/>
+      <c r="I389" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J389" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K389" s="1" t="inlineStr"/>
+      <c r="L389" s="1" t="inlineStr"/>
+      <c r="M389" s="1" t="inlineStr"/>
+      <c r="N389" s="1" t="inlineStr"/>
+      <c r="O389" s="1" t="inlineStr"/>
+      <c r="P389" s="1" t="inlineStr"/>
+      <c r="Q389" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R389" s="1" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Gelato d'Essai</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>Viale B. Bardanzellu, 77</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>06/64264692</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>www.gelatodessai.it</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>gelatodessai</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>gelatodessai</t>
-        </is>
-      </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I390" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O390" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q390" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (gelatodessai) | IG: trovato (gelatodessai)</t>
-        </is>
-      </c>
-      <c r="R390" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="B390" s="1" t="inlineStr">
+        <is>
+          <t>Corso Vittorio Emanuele II, 73</t>
+        </is>
+      </c>
+      <c r="C390" s="1" t="inlineStr"/>
+      <c r="D390" s="1" t="inlineStr"/>
+      <c r="E390" s="1" t="inlineStr"/>
+      <c r="F390" s="1" t="inlineStr"/>
+      <c r="G390" s="1" t="inlineStr"/>
+      <c r="H390" s="1" t="inlineStr"/>
+      <c r="I390" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J390" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K390" s="1" t="inlineStr"/>
+      <c r="L390" s="1" t="inlineStr"/>
+      <c r="M390" s="1" t="inlineStr"/>
+      <c r="N390" s="1" t="inlineStr"/>
+      <c r="O390" s="1" t="inlineStr"/>
+      <c r="P390" s="1" t="inlineStr"/>
+      <c r="Q390" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R390" s="1" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="inlineStr">
+      <c r="A391" t="inlineStr">
         <is>
           <t>Gelato Romano</t>
         </is>
       </c>
-      <c r="B391" s="1" t="inlineStr">
+      <c r="B391" t="inlineStr">
         <is>
           <t>Via Giacomo Boni, 33/35</t>
         </is>
       </c>
-      <c r="C391" s="1" t="inlineStr">
+      <c r="C391" t="inlineStr">
         <is>
           <t>06/24406688</t>
         </is>
       </c>
-      <c r="D391" s="1" t="inlineStr">
+      <c r="D391" t="inlineStr">
         <is>
           <t>www.gelatoromanogr.it</t>
         </is>
       </c>
-      <c r="E391" s="1" t="inlineStr"/>
-      <c r="F391" s="1" t="inlineStr">
+      <c r="F391" t="inlineStr">
         <is>
           <t>gelato_romano</t>
         </is>
       </c>
-      <c r="G391" s="1" t="inlineStr"/>
-      <c r="H391" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I391" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J391" s="1" t="inlineStr"/>
-      <c r="K391" s="1" t="inlineStr"/>
-      <c r="L391" s="1" t="inlineStr"/>
-      <c r="M391" s="1" t="inlineStr"/>
-      <c r="N391" s="1" t="inlineStr"/>
-      <c r="O391" s="1" t="inlineStr"/>
-      <c r="P391" s="1" t="inlineStr"/>
-      <c r="Q391" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R391" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11', 'closes': '22'}, 'martedì': {'opens': '11', 'closes':</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (gelato_romano)</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -24383,1136 +24389,1180 @@
       <c r="P392" s="1" t="inlineStr"/>
       <c r="Q392" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R392" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="inlineStr">
+      <c r="A393" t="inlineStr">
         <is>
           <t>Gori Gelato</t>
         </is>
       </c>
-      <c r="B393" s="1" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>Piazza Menenio Agrippa, 8/B-C</t>
         </is>
       </c>
-      <c r="C393" s="1" t="inlineStr">
+      <c r="C393" t="inlineStr">
         <is>
           <t>06/8272092</t>
         </is>
       </c>
-      <c r="D393" s="1" t="inlineStr">
+      <c r="D393" t="inlineStr">
         <is>
           <t>www.gorigelato.it</t>
         </is>
       </c>
-      <c r="E393" s="1" t="inlineStr">
+      <c r="E393" t="inlineStr">
         <is>
           <t>GORI-Gelateria</t>
         </is>
       </c>
-      <c r="F393" s="1" t="inlineStr">
+      <c r="F393" t="inlineStr">
         <is>
           <t>gorigelato</t>
         </is>
       </c>
-      <c r="G393" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H393" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I393" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J393" s="1" t="inlineStr"/>
-      <c r="K393" s="1" t="inlineStr"/>
-      <c r="L393" s="1" t="inlineStr"/>
-      <c r="M393" s="1" t="inlineStr"/>
-      <c r="N393" s="1" t="inlineStr"/>
-      <c r="O393" s="1" t="inlineStr"/>
-      <c r="P393" s="1" t="inlineStr"/>
-      <c r="Q393" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R393" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '00'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (GORI-Gelateria) | IG: trovato (gorigelato)</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="inlineStr">
+      <c r="A394" t="inlineStr">
         <is>
           <t>Günther Gelato</t>
         </is>
       </c>
-      <c r="B394" s="1" t="inlineStr">
+      <c r="B394" t="inlineStr">
         <is>
           <t>Piazza di Sant'Eustachio, 47</t>
         </is>
       </c>
-      <c r="C394" s="1" t="inlineStr">
+      <c r="C394" t="inlineStr">
         <is>
           <t>06/68808292</t>
         </is>
       </c>
-      <c r="D394" s="1" t="inlineStr">
+      <c r="D394" t="inlineStr">
         <is>
           <t>www.gunthergelatoitaliano.com</t>
         </is>
       </c>
-      <c r="E394" s="1" t="inlineStr">
+      <c r="E394" t="inlineStr">
         <is>
           <t>Gunther-Gelato-Italiano</t>
         </is>
       </c>
-      <c r="F394" s="1" t="inlineStr">
+      <c r="F394" t="inlineStr">
         <is>
           <t>gunthergelatoroma</t>
         </is>
       </c>
-      <c r="G394" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H394" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I394" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J394" s="1" t="inlineStr"/>
-      <c r="K394" s="1" t="inlineStr"/>
-      <c r="L394" s="1" t="inlineStr"/>
-      <c r="M394" s="1" t="inlineStr"/>
-      <c r="N394" s="1" t="inlineStr"/>
-      <c r="O394" s="1" t="inlineStr"/>
-      <c r="P394" s="1" t="inlineStr"/>
-      <c r="Q394" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R394" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (Gunther-Gelato-Italiano) | IG: trovato (gunthergelatoroma)</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="inlineStr">
+      <c r="A395" t="inlineStr">
         <is>
           <t>Inverso</t>
         </is>
       </c>
-      <c r="B395" s="1" t="inlineStr">
+      <c r="B395" t="inlineStr">
         <is>
           <t>Via Vibio Mariano, 5</t>
         </is>
       </c>
-      <c r="C395" s="1" t="inlineStr">
+      <c r="C395" t="inlineStr">
         <is>
           <t>06/33251114 - 334/3112437</t>
         </is>
       </c>
-      <c r="D395" s="1" t="inlineStr">
+      <c r="D395" t="inlineStr">
         <is>
           <t>www.pizzeriainverso.it</t>
         </is>
       </c>
-      <c r="E395" s="1" t="inlineStr"/>
-      <c r="F395" s="1" t="inlineStr">
+      <c r="F395" t="inlineStr">
         <is>
           <t>inverso_progetto_pizza</t>
         </is>
       </c>
-      <c r="G395" s="1" t="inlineStr"/>
-      <c r="H395" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I395" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J395" s="1" t="inlineStr"/>
-      <c r="K395" s="1" t="inlineStr"/>
-      <c r="L395" s="1" t="inlineStr"/>
-      <c r="M395" s="1" t="inlineStr"/>
-      <c r="N395" s="1" t="inlineStr"/>
-      <c r="O395" s="1" t="inlineStr"/>
-      <c r="P395" s="1" t="inlineStr"/>
-      <c r="Q395" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R395" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10:30', 'closes': '00'}, 'martedì': {'opens': '10:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (inverso_progetto_pizza)</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="inlineStr">
+      <c r="A396" t="inlineStr">
         <is>
           <t>La Casa del Cremolato</t>
         </is>
       </c>
-      <c r="B396" s="1" t="inlineStr">
+      <c r="B396" t="inlineStr">
         <is>
           <t>Via di Priscilla, 18</t>
         </is>
       </c>
-      <c r="C396" s="1" t="inlineStr">
+      <c r="C396" t="inlineStr">
         <is>
           <t>06/86200724</t>
         </is>
       </c>
-      <c r="D396" s="1" t="inlineStr">
+      <c r="D396" t="inlineStr">
         <is>
           <t>www.lacasadelcremolato.com</t>
         </is>
       </c>
-      <c r="E396" s="1" t="inlineStr">
+      <c r="E396" t="inlineStr">
         <is>
           <t>LaCasaDelCremolato</t>
         </is>
       </c>
-      <c r="F396" s="1" t="inlineStr">
+      <c r="F396" t="inlineStr">
         <is>
           <t>la_casa_del_cremolato</t>
         </is>
       </c>
-      <c r="G396" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H396" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I396" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J396" s="1" t="inlineStr"/>
-      <c r="K396" s="1" t="inlineStr"/>
-      <c r="L396" s="1" t="inlineStr"/>
-      <c r="M396" s="1" t="inlineStr"/>
-      <c r="N396" s="1" t="inlineStr"/>
-      <c r="O396" s="1" t="inlineStr"/>
-      <c r="P396" s="1" t="inlineStr"/>
-      <c r="Q396" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R396" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '07', 'closes': '00'}, 'martedì': {'opens': '07', 'closes':</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (LaCasaDelCremolato) | IG: trovato (la_casa_del_cremolato)</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="inlineStr">
+      <c r="A397" t="inlineStr">
         <is>
           <t>La Gourmandise</t>
         </is>
       </c>
-      <c r="B397" s="1" t="inlineStr">
+      <c r="B397" t="inlineStr">
         <is>
           <t>Via Felice Cavallotti, 36/B</t>
         </is>
       </c>
-      <c r="C397" s="1" t="inlineStr">
+      <c r="C397" t="inlineStr">
         <is>
           <t>377/4116621</t>
         </is>
       </c>
-      <c r="D397" s="1" t="inlineStr">
+      <c r="D397" t="inlineStr">
         <is>
           <t>www.lagourmandise.it</t>
         </is>
       </c>
-      <c r="E397" s="1" t="inlineStr">
+      <c r="E397" t="inlineStr">
         <is>
           <t>La-Gourmandise-Gelateria-e-arte-del-gusto</t>
         </is>
       </c>
-      <c r="F397" s="1" t="inlineStr"/>
-      <c r="G397" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H397" s="1" t="inlineStr"/>
-      <c r="I397" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J397" s="1" t="inlineStr"/>
-      <c r="K397" s="1" t="inlineStr"/>
-      <c r="L397" s="1" t="inlineStr"/>
-      <c r="M397" s="1" t="inlineStr"/>
-      <c r="N397" s="1" t="inlineStr"/>
-      <c r="O397" s="1" t="inlineStr"/>
-      <c r="P397" s="1" t="inlineStr"/>
-      <c r="Q397" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R397" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11', 'closes': '22'}, 'martedì': {'opens': 'Chiuso'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (La-Gourmandise-Gelateria-e-arte-del-gusto) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="inlineStr">
+      <c r="A398" t="inlineStr">
         <is>
           <t>Lievito Pizza Pane</t>
         </is>
       </c>
-      <c r="B398" s="1" t="inlineStr">
+      <c r="B398" t="inlineStr">
         <is>
           <t>Viale Europa, 339</t>
         </is>
       </c>
-      <c r="C398" s="1" t="inlineStr">
+      <c r="C398" t="inlineStr">
         <is>
           <t>06/69363592</t>
         </is>
       </c>
-      <c r="D398" s="1" t="inlineStr"/>
-      <c r="E398" s="1" t="inlineStr">
+      <c r="E398" t="inlineStr">
         <is>
           <t>lievitopizzapane</t>
         </is>
       </c>
-      <c r="F398" s="1" t="inlineStr">
+      <c r="F398" t="inlineStr">
         <is>
           <t>lievitopizzapane</t>
         </is>
       </c>
-      <c r="G398" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H398" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I398" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J398" s="1" t="inlineStr"/>
-      <c r="K398" s="1" t="inlineStr"/>
-      <c r="L398" s="1" t="inlineStr"/>
-      <c r="M398" s="1" t="inlineStr"/>
-      <c r="N398" s="1" t="inlineStr"/>
-      <c r="O398" s="1" t="inlineStr"/>
-      <c r="P398" s="1" t="inlineStr"/>
-      <c r="Q398" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R398" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (lievitopizzapane) | IG: trovato (lievitopizzapane)</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="inlineStr">
+      <c r="A399" t="inlineStr">
         <is>
           <t>Lina - La Pizza in Teglia</t>
         </is>
       </c>
-      <c r="B399" s="1" t="inlineStr">
+      <c r="B399" t="inlineStr">
         <is>
           <t>Circonvallazione Trionfale, 53</t>
         </is>
       </c>
-      <c r="C399" s="1" t="inlineStr">
+      <c r="C399" t="inlineStr">
         <is>
           <t>351/7747767</t>
         </is>
       </c>
-      <c r="D399" s="1" t="inlineStr">
+      <c r="D399" t="inlineStr">
         <is>
           <t>www.linapizza.com</t>
         </is>
       </c>
-      <c r="E399" s="1" t="inlineStr">
+      <c r="E399" t="inlineStr">
         <is>
           <t>Lina-La-Pizza-In-Teglia</t>
         </is>
       </c>
-      <c r="F399" s="1" t="inlineStr">
+      <c r="F399" t="inlineStr">
         <is>
           <t>linapizza_vs</t>
         </is>
       </c>
-      <c r="G399" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H399" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I399" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J399" s="1" t="inlineStr"/>
-      <c r="K399" s="1" t="inlineStr"/>
-      <c r="L399" s="1" t="inlineStr"/>
-      <c r="M399" s="1" t="inlineStr"/>
-      <c r="N399" s="1" t="inlineStr"/>
-      <c r="O399" s="1" t="inlineStr"/>
-      <c r="P399" s="1" t="inlineStr"/>
-      <c r="Q399" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R399" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (Lina-La-Pizza-In-Teglia) | IG: trovato (linapizza_vs)</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="inlineStr">
+      <c r="A400" t="inlineStr">
         <is>
           <t>Miao Miao</t>
         </is>
       </c>
-      <c r="B400" s="1" t="inlineStr">
+      <c r="B400" t="inlineStr">
         <is>
           <t>Via della Stelletta, 4/A</t>
         </is>
       </c>
-      <c r="C400" s="1" t="inlineStr">
+      <c r="C400" t="inlineStr">
         <is>
           <t>380/6914759</t>
         </is>
       </c>
-      <c r="D400" s="1" t="inlineStr">
+      <c r="D400" t="inlineStr">
         <is>
           <t>www.miaomiaokebab.com</t>
         </is>
       </c>
-      <c r="E400" s="1" t="inlineStr"/>
-      <c r="F400" s="1" t="inlineStr">
+      <c r="F400" t="inlineStr">
         <is>
           <t>miaomiaokebab</t>
         </is>
       </c>
-      <c r="G400" s="1" t="inlineStr"/>
-      <c r="H400" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I400" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J400" s="1" t="inlineStr"/>
-      <c r="K400" s="1" t="inlineStr"/>
-      <c r="L400" s="1" t="inlineStr"/>
-      <c r="M400" s="1" t="inlineStr"/>
-      <c r="N400" s="1" t="inlineStr"/>
-      <c r="O400" s="1" t="inlineStr"/>
-      <c r="P400" s="1" t="inlineStr"/>
-      <c r="Q400" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R400" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (miaomiaokebab)</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="inlineStr">
+      <c r="A401" t="inlineStr">
         <is>
           <t>Neve di Latte</t>
         </is>
       </c>
-      <c r="B401" s="1" t="inlineStr">
+      <c r="B401" t="inlineStr">
         <is>
           <t>Via Nomentana, 335/F</t>
         </is>
       </c>
-      <c r="C401" s="1" t="inlineStr">
+      <c r="C401" t="inlineStr">
         <is>
           <t>06/69346839</t>
         </is>
       </c>
-      <c r="D401" s="1" t="inlineStr">
+      <c r="D401" t="inlineStr">
         <is>
           <t>www.nevedilatte.it</t>
         </is>
       </c>
-      <c r="E401" s="1" t="inlineStr">
+      <c r="E401" t="inlineStr">
         <is>
           <t>NevediLatteRoma</t>
         </is>
       </c>
-      <c r="F401" s="1" t="inlineStr">
+      <c r="F401" t="inlineStr">
         <is>
           <t>nevedilattegelateria</t>
         </is>
       </c>
-      <c r="G401" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H401" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I401" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J401" s="1" t="inlineStr"/>
-      <c r="K401" s="1" t="inlineStr"/>
-      <c r="L401" s="1" t="inlineStr"/>
-      <c r="M401" s="1" t="inlineStr"/>
-      <c r="N401" s="1" t="inlineStr"/>
-      <c r="O401" s="1" t="inlineStr"/>
-      <c r="P401" s="1" t="inlineStr"/>
-      <c r="Q401" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R401" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (NevediLatteRoma) | IG: trovato (nevedilattegelateria)</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="inlineStr">
+      <c r="A402" t="inlineStr">
         <is>
           <t>Nonnarè</t>
         </is>
       </c>
-      <c r="B402" s="1" t="inlineStr">
+      <c r="B402" t="inlineStr">
         <is>
           <t>Piazza Augusto Albini, 10</t>
         </is>
       </c>
-      <c r="C402" s="1" t="inlineStr">
+      <c r="C402" t="inlineStr">
         <is>
           <t>328/5367252</t>
         </is>
       </c>
-      <c r="D402" s="1" t="inlineStr"/>
-      <c r="E402" s="1" t="inlineStr"/>
-      <c r="F402" s="1" t="inlineStr">
+      <c r="F402" t="inlineStr">
         <is>
           <t>nonnare_pizzeriadiquartiere</t>
         </is>
       </c>
-      <c r="G402" s="1" t="inlineStr"/>
-      <c r="H402" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I402" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J402" s="1" t="inlineStr"/>
-      <c r="K402" s="1" t="inlineStr"/>
-      <c r="L402" s="1" t="inlineStr"/>
-      <c r="M402" s="1" t="inlineStr"/>
-      <c r="N402" s="1" t="inlineStr"/>
-      <c r="O402" s="1" t="inlineStr"/>
-      <c r="P402" s="1" t="inlineStr"/>
-      <c r="Q402" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R402" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: trovato (nonnare_pizzeriadiquartiere)</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="inlineStr">
+      <c r="A403" t="inlineStr">
         <is>
           <t>OGGI - Officina Gelato Gusto Italiano</t>
         </is>
       </c>
-      <c r="B403" s="1" t="inlineStr">
+      <c r="B403" t="inlineStr">
         <is>
           <t>Via Tacito, 66</t>
         </is>
       </c>
-      <c r="C403" s="1" t="inlineStr">
+      <c r="C403" t="inlineStr">
         <is>
           <t>06/53099944</t>
         </is>
       </c>
-      <c r="D403" s="1" t="inlineStr">
+      <c r="D403" t="inlineStr">
         <is>
           <t>www.oggigelato.it</t>
         </is>
       </c>
-      <c r="E403" s="1" t="inlineStr">
+      <c r="E403" t="inlineStr">
         <is>
           <t>oggigelatoroma</t>
         </is>
       </c>
-      <c r="F403" s="1" t="inlineStr"/>
-      <c r="G403" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H403" s="1" t="inlineStr"/>
-      <c r="I403" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J403" s="1" t="inlineStr"/>
-      <c r="K403" s="1" t="inlineStr"/>
-      <c r="L403" s="1" t="inlineStr"/>
-      <c r="M403" s="1" t="inlineStr"/>
-      <c r="N403" s="1" t="inlineStr"/>
-      <c r="O403" s="1" t="inlineStr"/>
-      <c r="P403" s="1" t="inlineStr"/>
-      <c r="Q403" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R403" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (oggigelatoroma) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="inlineStr">
+      <c r="A404" t="inlineStr">
         <is>
           <t>Otaleg!</t>
         </is>
       </c>
-      <c r="B404" s="1" t="inlineStr">
+      <c r="B404" t="inlineStr">
         <is>
           <t>Via di San Cosimato, 14/A</t>
         </is>
       </c>
-      <c r="C404" s="1" t="inlineStr">
+      <c r="C404" t="inlineStr">
         <is>
           <t>338/6515450</t>
         </is>
       </c>
-      <c r="D404" s="1" t="inlineStr">
+      <c r="D404" t="inlineStr">
         <is>
           <t>www.otaleg.com</t>
         </is>
       </c>
-      <c r="E404" s="1" t="inlineStr"/>
-      <c r="F404" s="1" t="inlineStr">
+      <c r="F404" t="inlineStr">
         <is>
           <t>otaleg.radicioni</t>
         </is>
       </c>
-      <c r="G404" s="1" t="inlineStr"/>
-      <c r="H404" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I404" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J404" s="1" t="inlineStr"/>
-      <c r="K404" s="1" t="inlineStr"/>
-      <c r="L404" s="1" t="inlineStr"/>
-      <c r="M404" s="1" t="inlineStr"/>
-      <c r="N404" s="1" t="inlineStr"/>
-      <c r="O404" s="1" t="inlineStr"/>
-      <c r="P404" s="1" t="inlineStr"/>
-      <c r="Q404" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R404" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: trovato (otaleg.radicioni)</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="inlineStr">
+      <c r="A405" t="inlineStr">
         <is>
           <t>Pane e Tempesta</t>
         </is>
       </c>
-      <c r="B405" s="1" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>Via Giovanni de Calvi, 23/25</t>
         </is>
       </c>
-      <c r="C405" s="1" t="inlineStr">
+      <c r="C405" t="inlineStr">
         <is>
           <t>06/87725015</t>
         </is>
       </c>
-      <c r="D405" s="1" t="inlineStr">
+      <c r="D405" t="inlineStr">
         <is>
           <t>www.panetempesta.blogspot.it</t>
         </is>
       </c>
-      <c r="E405" s="1" t="inlineStr">
+      <c r="E405" t="inlineStr">
         <is>
           <t>PaneTempesta</t>
         </is>
       </c>
-      <c r="F405" s="1" t="inlineStr">
+      <c r="F405" t="inlineStr">
         <is>
           <t>paneetempesta</t>
         </is>
       </c>
-      <c r="G405" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H405" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I405" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J405" s="1" t="inlineStr"/>
-      <c r="K405" s="1" t="inlineStr"/>
-      <c r="L405" s="1" t="inlineStr"/>
-      <c r="M405" s="1" t="inlineStr"/>
-      <c r="N405" s="1" t="inlineStr"/>
-      <c r="O405" s="1" t="inlineStr"/>
-      <c r="P405" s="1" t="inlineStr"/>
-      <c r="Q405" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R405" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '21'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (PaneTempesta) | IG: trovato (paneetempesta)</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="inlineStr">
+      <c r="A406" t="inlineStr">
         <is>
           <t>Panificio Marè Prati</t>
         </is>
       </c>
-      <c r="B406" s="1" t="inlineStr">
+      <c r="B406" t="inlineStr">
         <is>
           <t>Viale Angelico, 88</t>
         </is>
       </c>
-      <c r="C406" s="1" t="inlineStr">
+      <c r="C406" t="inlineStr">
         <is>
           <t>06/37511594</t>
         </is>
       </c>
-      <c r="D406" s="1" t="inlineStr">
+      <c r="D406" t="inlineStr">
         <is>
           <t>www.panificiomareprati.it</t>
         </is>
       </c>
-      <c r="E406" s="1" t="inlineStr">
+      <c r="E406" t="inlineStr">
         <is>
           <t>panificiomareprati</t>
         </is>
       </c>
-      <c r="F406" s="1" t="inlineStr">
+      <c r="F406" t="inlineStr">
         <is>
           <t>panificio_mare_prati</t>
         </is>
       </c>
-      <c r="G406" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H406" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I406" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J406" s="1" t="inlineStr"/>
-      <c r="K406" s="1" t="inlineStr"/>
-      <c r="L406" s="1" t="inlineStr"/>
-      <c r="M406" s="1" t="inlineStr"/>
-      <c r="N406" s="1" t="inlineStr"/>
-      <c r="O406" s="1" t="inlineStr"/>
-      <c r="P406" s="1" t="inlineStr"/>
-      <c r="Q406" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R406" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08', 'closes': '20'}, 'martedì': {'opens': '08', 'closes':</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (panificiomareprati) | IG: trovato (panificio_mare_prati)</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="inlineStr">
+      <c r="A407" t="inlineStr">
         <is>
           <t>Pinsere</t>
         </is>
       </c>
-      <c r="B407" s="1" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>Via Flavia, 98</t>
         </is>
       </c>
-      <c r="C407" s="1" t="inlineStr">
+      <c r="C407" t="inlineStr">
         <is>
           <t>06/42020924</t>
         </is>
       </c>
-      <c r="D407" s="1" t="inlineStr"/>
-      <c r="E407" s="1" t="inlineStr">
+      <c r="E407" t="inlineStr">
         <is>
           <t>Pinsere</t>
         </is>
       </c>
-      <c r="F407" s="1" t="inlineStr">
+      <c r="F407" t="inlineStr">
         <is>
           <t>pinseparole</t>
         </is>
       </c>
-      <c r="G407" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H407" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I407" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J407" s="1" t="inlineStr"/>
-      <c r="K407" s="1" t="inlineStr"/>
-      <c r="L407" s="1" t="inlineStr"/>
-      <c r="M407" s="1" t="inlineStr"/>
-      <c r="N407" s="1" t="inlineStr"/>
-      <c r="O407" s="1" t="inlineStr"/>
-      <c r="P407" s="1" t="inlineStr"/>
-      <c r="Q407" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R407" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10', 'closes': '21'}, 'martedì': {'opens': '10', 'closes':</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Pinsere) | IG: trovato (pinseparole)</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="inlineStr">
+      <c r="A408" t="inlineStr">
         <is>
           <t>Pizza Baar</t>
         </is>
       </c>
-      <c r="B408" s="1" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>Via di Donna Olimpia, 71</t>
         </is>
       </c>
-      <c r="C408" s="1" t="inlineStr"/>
-      <c r="D408" s="1" t="inlineStr"/>
-      <c r="E408" s="1" t="inlineStr"/>
-      <c r="F408" s="1" t="inlineStr"/>
-      <c r="G408" s="1" t="inlineStr"/>
-      <c r="H408" s="1" t="inlineStr"/>
-      <c r="I408" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J408" s="1" t="inlineStr"/>
-      <c r="K408" s="1" t="inlineStr"/>
-      <c r="L408" s="1" t="inlineStr"/>
-      <c r="M408" s="1" t="inlineStr"/>
-      <c r="N408" s="1" t="inlineStr"/>
-      <c r="O408" s="1" t="inlineStr"/>
-      <c r="P408" s="1" t="inlineStr"/>
-      <c r="Q408" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R408" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="inlineStr">
+      <c r="A409" t="inlineStr">
         <is>
           <t>Pizza Chef</t>
         </is>
       </c>
-      <c r="B409" s="1" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>Via Clelia, 63/A</t>
         </is>
       </c>
-      <c r="C409" s="1" t="inlineStr">
+      <c r="C409" t="inlineStr">
         <is>
           <t>06/87566046</t>
         </is>
       </c>
-      <c r="D409" s="1" t="inlineStr"/>
-      <c r="E409" s="1" t="inlineStr">
+      <c r="E409" t="inlineStr">
         <is>
           <t>pizzachefroma</t>
         </is>
       </c>
-      <c r="F409" s="1" t="inlineStr">
+      <c r="F409" t="inlineStr">
         <is>
           <t>pizzachefroma</t>
         </is>
       </c>
-      <c r="G409" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H409" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I409" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J409" s="1" t="inlineStr"/>
-      <c r="K409" s="1" t="inlineStr"/>
-      <c r="L409" s="1" t="inlineStr"/>
-      <c r="M409" s="1" t="inlineStr"/>
-      <c r="N409" s="1" t="inlineStr"/>
-      <c r="O409" s="1" t="inlineStr"/>
-      <c r="P409" s="1" t="inlineStr"/>
-      <c r="Q409" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R409" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (pizzachefroma) | IG: trovato (pizzachefroma)</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="inlineStr">
+      <c r="A410" t="inlineStr">
         <is>
           <t>Pizzarium</t>
         </is>
       </c>
-      <c r="B410" s="1" t="inlineStr">
+      <c r="B410" t="inlineStr">
         <is>
           <t>Via della Meloria, 43</t>
         </is>
       </c>
-      <c r="C410" s="1" t="inlineStr">
+      <c r="C410" t="inlineStr">
         <is>
           <t>06/39745416</t>
         </is>
       </c>
-      <c r="D410" s="1" t="inlineStr">
+      <c r="D410" t="inlineStr">
         <is>
           <t>www.bonci.it</t>
         </is>
       </c>
-      <c r="E410" s="1" t="inlineStr">
+      <c r="E410" t="inlineStr">
         <is>
           <t>pizzarium-gabrielebonci</t>
         </is>
       </c>
-      <c r="F410" s="1" t="inlineStr">
+      <c r="F410" t="inlineStr">
         <is>
           <t>pizzarium</t>
         </is>
       </c>
-      <c r="G410" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H410" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I410" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J410" s="1" t="inlineStr"/>
-      <c r="K410" s="1" t="inlineStr"/>
-      <c r="L410" s="1" t="inlineStr"/>
-      <c r="M410" s="1" t="inlineStr"/>
-      <c r="N410" s="1" t="inlineStr"/>
-      <c r="O410" s="1" t="inlineStr"/>
-      <c r="P410" s="1" t="inlineStr"/>
-      <c r="Q410" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R410" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11:15', 'closes': '22'}, 'martedì': {'opens': '11:15', 'cl</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: trovato (pizzarium-gabrielebonci) | IG: trovato (pizzarium)</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="inlineStr">
+      <c r="A411" t="inlineStr">
         <is>
           <t>Prelibato</t>
         </is>
       </c>
-      <c r="B411" s="1" t="inlineStr">
+      <c r="B411" t="inlineStr">
         <is>
           <t>Viale di Villa Pamphili, 214</t>
         </is>
       </c>
-      <c r="C411" s="1" t="inlineStr">
+      <c r="C411" t="inlineStr">
         <is>
           <t>06/93577165</t>
         </is>
       </c>
-      <c r="D411" s="1" t="inlineStr"/>
-      <c r="E411" s="1" t="inlineStr">
+      <c r="E411" t="inlineStr">
         <is>
           <t>FornoPrelibato</t>
         </is>
       </c>
-      <c r="F411" s="1" t="inlineStr">
+      <c r="F411" t="inlineStr">
         <is>
           <t>prelibatoroma</t>
         </is>
       </c>
-      <c r="G411" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H411" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I411" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J411" s="1" t="inlineStr"/>
-      <c r="K411" s="1" t="inlineStr"/>
-      <c r="L411" s="1" t="inlineStr"/>
-      <c r="M411" s="1" t="inlineStr"/>
-      <c r="N411" s="1" t="inlineStr"/>
-      <c r="O411" s="1" t="inlineStr"/>
-      <c r="P411" s="1" t="inlineStr"/>
-      <c r="Q411" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R411" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '09, 16', 'closes': '15, 20:30', 'break': '15–16'}, 'marted</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (FornoPrelibato) | IG: trovato (prelibatoroma)</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -25551,384 +25601,404 @@
       <c r="P412" s="1" t="inlineStr"/>
       <c r="Q412" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="inlineStr">
+      <c r="A413" t="inlineStr">
         <is>
           <t>Ruver - teglia frazionata</t>
         </is>
       </c>
-      <c r="B413" s="1" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t>Viale Aventino, 46</t>
         </is>
       </c>
-      <c r="C413" s="1" t="inlineStr">
+      <c r="C413" t="inlineStr">
         <is>
           <t>327/0737999</t>
         </is>
       </c>
-      <c r="D413" s="1" t="inlineStr"/>
-      <c r="E413" s="1" t="inlineStr"/>
-      <c r="F413" s="1" t="inlineStr">
+      <c r="F413" t="inlineStr">
         <is>
           <t>ruver_tegliafrazionata</t>
         </is>
       </c>
-      <c r="G413" s="1" t="inlineStr"/>
-      <c r="H413" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I413" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J413" s="1" t="inlineStr"/>
-      <c r="K413" s="1" t="inlineStr"/>
-      <c r="L413" s="1" t="inlineStr"/>
-      <c r="M413" s="1" t="inlineStr"/>
-      <c r="N413" s="1" t="inlineStr"/>
-      <c r="O413" s="1" t="inlineStr"/>
-      <c r="P413" s="1" t="inlineStr"/>
-      <c r="Q413" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R413" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10', 'closes': '21'}, 'martedì': {'opens': '10', 'closes':</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (ruver_tegliafrazionata)</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="inlineStr">
+      <c r="A414" t="inlineStr">
         <is>
           <t>San Biagio pizza e bolle</t>
         </is>
       </c>
-      <c r="B414" s="1" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>Via Oslavia, 39</t>
         </is>
       </c>
-      <c r="C414" s="1" t="inlineStr">
+      <c r="C414" t="inlineStr">
         <is>
           <t>06/45683049</t>
         </is>
       </c>
-      <c r="D414" s="1" t="inlineStr">
+      <c r="D414" t="inlineStr">
         <is>
           <t>www.pizzaebolle.it</t>
         </is>
       </c>
-      <c r="E414" s="1" t="inlineStr">
+      <c r="E414" t="inlineStr">
         <is>
           <t>sanbiagiopizzaebolle</t>
         </is>
       </c>
-      <c r="F414" s="1" t="inlineStr">
+      <c r="F414" t="inlineStr">
         <is>
           <t>_san_biagio</t>
         </is>
       </c>
-      <c r="G414" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H414" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I414" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J414" s="1" t="inlineStr"/>
-      <c r="K414" s="1" t="inlineStr"/>
-      <c r="L414" s="1" t="inlineStr"/>
-      <c r="M414" s="1" t="inlineStr"/>
-      <c r="N414" s="1" t="inlineStr"/>
-      <c r="O414" s="1" t="inlineStr"/>
-      <c r="P414" s="1" t="inlineStr"/>
-      <c r="Q414" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R414" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11', 'closes': '22'}, 'martedì': {'opens': '11', 'closes':</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (sanbiagiopizzaebolle) | IG: trovato (_san_biagio)</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="inlineStr">
+      <c r="A415" t="inlineStr">
         <is>
           <t>Sancho</t>
         </is>
       </c>
-      <c r="B415" s="1" t="inlineStr">
+      <c r="B415" t="inlineStr">
         <is>
           <t>Via Giuseppe Gioachino Belli, 3/A</t>
         </is>
       </c>
-      <c r="C415" s="1" t="inlineStr">
+      <c r="C415" t="inlineStr">
         <is>
           <t>06/86299316</t>
         </is>
       </c>
-      <c r="D415" s="1" t="inlineStr">
+      <c r="D415" t="inlineStr">
         <is>
           <t>www.pizzeriasancho.it</t>
         </is>
       </c>
-      <c r="E415" s="1" t="inlineStr">
+      <c r="E415" t="inlineStr">
         <is>
           <t>PizzeriaSancho1969</t>
         </is>
       </c>
-      <c r="F415" s="1" t="inlineStr">
+      <c r="F415" t="inlineStr">
         <is>
           <t>pizzeriasancho</t>
         </is>
       </c>
-      <c r="G415" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H415" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I415" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J415" s="1" t="inlineStr"/>
-      <c r="K415" s="1" t="inlineStr"/>
-      <c r="L415" s="1" t="inlineStr"/>
-      <c r="M415" s="1" t="inlineStr"/>
-      <c r="N415" s="1" t="inlineStr"/>
-      <c r="O415" s="1" t="inlineStr"/>
-      <c r="P415" s="1" t="inlineStr"/>
-      <c r="Q415" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R415" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (PizzeriaSancho1969) | IG: trovato (pizzeriasancho)</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="inlineStr">
+      <c r="A416" t="inlineStr">
         <is>
           <t>Stefano Ferrara - Formaessenza</t>
         </is>
       </c>
-      <c r="B416" s="1" t="inlineStr">
+      <c r="B416" t="inlineStr">
         <is>
           <t>Via Enrico Fermi, 102/104</t>
         </is>
       </c>
-      <c r="C416" s="1" t="inlineStr">
+      <c r="C416" t="inlineStr">
         <is>
           <t>06/55296621</t>
         </is>
       </c>
-      <c r="D416" s="1" t="inlineStr">
+      <c r="D416" t="inlineStr">
         <is>
           <t>www.gelatolab.it</t>
         </is>
       </c>
-      <c r="E416" s="1" t="inlineStr">
+      <c r="E416" t="inlineStr">
         <is>
           <t>stefanoferraragelato</t>
         </is>
       </c>
-      <c r="F416" s="1" t="inlineStr">
+      <c r="F416" t="inlineStr">
         <is>
           <t>stefanoferraragelato</t>
         </is>
       </c>
-      <c r="G416" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H416" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I416" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J416" s="1" t="inlineStr"/>
-      <c r="K416" s="1" t="inlineStr"/>
-      <c r="L416" s="1" t="inlineStr"/>
-      <c r="M416" s="1" t="inlineStr"/>
-      <c r="N416" s="1" t="inlineStr"/>
-      <c r="O416" s="1" t="inlineStr"/>
-      <c r="P416" s="1" t="inlineStr"/>
-      <c r="Q416" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R416" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '23'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (stefanoferraragelato) | IG: trovato (stefanoferraragelato)</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="inlineStr">
+      <c r="A417" t="inlineStr">
         <is>
           <t>Terra Gelato</t>
         </is>
       </c>
-      <c r="B417" s="1" t="inlineStr">
+      <c r="B417" t="inlineStr">
         <is>
           <t>Piazza Santa Maria Maggiore, 9</t>
         </is>
       </c>
-      <c r="C417" s="1" t="inlineStr">
+      <c r="C417" t="inlineStr">
         <is>
           <t>06/45666656</t>
         </is>
       </c>
-      <c r="D417" s="1" t="inlineStr">
+      <c r="D417" t="inlineStr">
         <is>
           <t>www.terragelato.it</t>
         </is>
       </c>
-      <c r="E417" s="1" t="inlineStr">
+      <c r="E417" t="inlineStr">
         <is>
           <t>TerraGelato</t>
         </is>
       </c>
-      <c r="F417" s="1" t="inlineStr">
+      <c r="F417" t="inlineStr">
         <is>
           <t>terragelato</t>
         </is>
       </c>
-      <c r="G417" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H417" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I417" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J417" s="1" t="inlineStr"/>
-      <c r="K417" s="1" t="inlineStr"/>
-      <c r="L417" s="1" t="inlineStr"/>
-      <c r="M417" s="1" t="inlineStr"/>
-      <c r="N417" s="1" t="inlineStr"/>
-      <c r="O417" s="1" t="inlineStr"/>
-      <c r="P417" s="1" t="inlineStr"/>
-      <c r="Q417" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R417" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (TerraGelato) | IG: trovato (terragelato)</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="inlineStr">
+      <c r="A418" t="inlineStr">
         <is>
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="B418" s="1" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>Piazzale delle Province, 9</t>
         </is>
       </c>
-      <c r="C418" s="1" t="inlineStr">
+      <c r="C418" t="inlineStr">
         <is>
           <t>06/90239685</t>
         </is>
       </c>
-      <c r="D418" s="1" t="inlineStr">
+      <c r="D418" t="inlineStr">
         <is>
           <t>www.trapizzino.it</t>
         </is>
       </c>
-      <c r="E418" s="1" t="inlineStr">
+      <c r="E418" t="inlineStr">
         <is>
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="F418" s="1" t="inlineStr">
+      <c r="F418" t="inlineStr">
         <is>
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="G418" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H418" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I418" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J418" s="1" t="inlineStr"/>
-      <c r="K418" s="1" t="inlineStr"/>
-      <c r="L418" s="1" t="inlineStr"/>
-      <c r="M418" s="1" t="inlineStr"/>
-      <c r="N418" s="1" t="inlineStr"/>
-      <c r="O418" s="1" t="inlineStr"/>
-      <c r="P418" s="1" t="inlineStr"/>
-      <c r="Q418" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R418" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (Trapizzino) | IG: trovato (Trapizzino)</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -24009,284 +24009,392 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B385" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C385" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D385" s="1" t="inlineStr"/>
-      <c r="E385" s="1" t="inlineStr"/>
-      <c r="F385" s="1" t="inlineStr"/>
-      <c r="G385" s="1" t="inlineStr"/>
-      <c r="H385" s="1" t="inlineStr"/>
-      <c r="I385" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J385" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K385" s="1" t="inlineStr"/>
-      <c r="L385" s="1" t="inlineStr"/>
-      <c r="M385" s="1" t="inlineStr"/>
-      <c r="N385" s="1" t="inlineStr"/>
-      <c r="O385" s="1" t="inlineStr"/>
-      <c r="P385" s="1" t="inlineStr"/>
-      <c r="Q385" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R385" s="1" t="inlineStr">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Gelato Romano</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Via Giacomo Boni, 33/35</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>06/24406688</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>www.gelatoromanogr.it</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>gelato_romano</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11', 'closes': '22'}, 'martedì': {'opens': '11', 'closes':</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (gelato_romano)</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B386" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C386" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D386" s="1" t="inlineStr"/>
-      <c r="E386" s="1" t="inlineStr"/>
-      <c r="F386" s="1" t="inlineStr"/>
-      <c r="G386" s="1" t="inlineStr"/>
-      <c r="H386" s="1" t="inlineStr"/>
-      <c r="I386" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J386" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K386" s="1" t="inlineStr"/>
-      <c r="L386" s="1" t="inlineStr"/>
-      <c r="M386" s="1" t="inlineStr"/>
-      <c r="N386" s="1" t="inlineStr"/>
-      <c r="O386" s="1" t="inlineStr"/>
-      <c r="P386" s="1" t="inlineStr"/>
-      <c r="Q386" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R386" s="1" t="inlineStr">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Gori Gelato</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Piazza Menenio Agrippa, 8/B-C</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>06/8272092</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>www.gorigelato.it</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>GORI-Gelateria</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>gorigelato</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '00'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (GORI-Gelateria) | IG: trovato (gorigelato)</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="inlineStr">
-        <is>
-          <t>Clementina</t>
-        </is>
-      </c>
-      <c r="B387" s="1" t="inlineStr">
-        <is>
-          <t>Via della Torre Clementina, 158</t>
-        </is>
-      </c>
-      <c r="C387" s="1" t="inlineStr">
-        <is>
-          <t>328/8181651</t>
-        </is>
-      </c>
-      <c r="D387" s="1" t="inlineStr"/>
-      <c r="E387" s="1" t="inlineStr"/>
-      <c r="F387" s="1" t="inlineStr"/>
-      <c r="G387" s="1" t="inlineStr"/>
-      <c r="H387" s="1" t="inlineStr"/>
-      <c r="I387" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J387" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K387" s="1" t="inlineStr"/>
-      <c r="L387" s="1" t="inlineStr"/>
-      <c r="M387" s="1" t="inlineStr"/>
-      <c r="N387" s="1" t="inlineStr"/>
-      <c r="O387" s="1" t="inlineStr"/>
-      <c r="P387" s="1" t="inlineStr"/>
-      <c r="Q387" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R387" s="1" t="inlineStr">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Günther Gelato</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Piazza di Sant'Eustachio, 47</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>06/68808292</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>www.gunthergelatoitaliano.com</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Gunther-Gelato-Italiano</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>gunthergelatoroma</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (Gunther-Gelato-Italiano) | IG: trovato (gunthergelatoroma)</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="inlineStr">
-        <is>
-          <t>Da Antonio</t>
-        </is>
-      </c>
-      <c r="B388" s="1" t="inlineStr">
-        <is>
-          <t>Via Mario Lizzani, 21</t>
-        </is>
-      </c>
-      <c r="C388" s="1" t="inlineStr">
-        <is>
-          <t>391/7475549</t>
-        </is>
-      </c>
-      <c r="D388" s="1" t="inlineStr"/>
-      <c r="E388" s="1" t="inlineStr"/>
-      <c r="F388" s="1" t="inlineStr"/>
-      <c r="G388" s="1" t="inlineStr"/>
-      <c r="H388" s="1" t="inlineStr"/>
-      <c r="I388" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J388" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K388" s="1" t="inlineStr"/>
-      <c r="L388" s="1" t="inlineStr"/>
-      <c r="M388" s="1" t="inlineStr"/>
-      <c r="N388" s="1" t="inlineStr"/>
-      <c r="O388" s="1" t="inlineStr"/>
-      <c r="P388" s="1" t="inlineStr"/>
-      <c r="Q388" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R388" s="1" t="inlineStr">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Inverso</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Via Vibio Mariano, 5</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>06/33251114 - 334/3112437</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>www.pizzeriainverso.it</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>inverso_progetto_pizza</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10:30', 'closes': '00'}, 'martedì': {'opens': '10:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (inverso_progetto_pizza)</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="inlineStr">
-        <is>
-          <t>Il tuo fornaio</t>
-        </is>
-      </c>
-      <c r="B389" s="1" t="inlineStr">
-        <is>
-          <t>Via Francesco Sapori, 35</t>
-        </is>
-      </c>
-      <c r="C389" s="1" t="inlineStr">
-        <is>
-          <t>06/5017873</t>
-        </is>
-      </c>
-      <c r="D389" s="1" t="inlineStr"/>
-      <c r="E389" s="1" t="inlineStr"/>
-      <c r="F389" s="1" t="inlineStr"/>
-      <c r="G389" s="1" t="inlineStr"/>
-      <c r="H389" s="1" t="inlineStr"/>
-      <c r="I389" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J389" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K389" s="1" t="inlineStr"/>
-      <c r="L389" s="1" t="inlineStr"/>
-      <c r="M389" s="1" t="inlineStr"/>
-      <c r="N389" s="1" t="inlineStr"/>
-      <c r="O389" s="1" t="inlineStr"/>
-      <c r="P389" s="1" t="inlineStr"/>
-      <c r="Q389" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R389" s="1" t="inlineStr">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>La Casa del Cremolato</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Via di Priscilla, 18</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>06/86200724</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>www.lacasadelcremolato.com</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>LaCasaDelCremolato</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>la_casa_del_cremolato</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '07', 'closes': '00'}, 'martedì': {'opens': '07', 'closes':</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (LaCasaDelCremolato) | IG: trovato (la_casa_del_cremolato)</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="inlineStr">
-        <is>
-          <t>Slow</t>
-        </is>
-      </c>
-      <c r="B390" s="1" t="inlineStr">
-        <is>
-          <t>Corso Vittorio Emanuele II, 73</t>
-        </is>
-      </c>
-      <c r="C390" s="1" t="inlineStr"/>
-      <c r="D390" s="1" t="inlineStr"/>
-      <c r="E390" s="1" t="inlineStr"/>
-      <c r="F390" s="1" t="inlineStr"/>
-      <c r="G390" s="1" t="inlineStr"/>
-      <c r="H390" s="1" t="inlineStr"/>
-      <c r="I390" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J390" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K390" s="1" t="inlineStr"/>
-      <c r="L390" s="1" t="inlineStr"/>
-      <c r="M390" s="1" t="inlineStr"/>
-      <c r="N390" s="1" t="inlineStr"/>
-      <c r="O390" s="1" t="inlineStr"/>
-      <c r="P390" s="1" t="inlineStr"/>
-      <c r="Q390" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R390" s="1" t="inlineStr">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>La Gourmandise</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Via Felice Cavallotti, 36/B</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>377/4116621</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>www.lagourmandise.it</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>La-Gourmandise-Gelateria-e-arte-del-gusto</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11', 'closes': '22'}, 'martedì': {'opens': 'Chiuso'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (La-Gourmandise-Gelateria-e-arte-del-gusto) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
@@ -24295,27 +24403,32 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Gelato Romano</t>
+          <t>Lievito Pizza Pane</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Via Giacomo Boni, 33/35</t>
+          <t>Viale Europa, 339</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>06/24406688</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>www.gelatoromanogr.it</t>
+          <t>06/69363592</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>lievitopizzapane</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>gelato_romano</t>
+          <t>lievitopizzapane</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -24333,11 +24446,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M391" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '11', 'closes': '22'}, 'martedì': {'opens': '11', 'closes':</t>
-        </is>
-      </c>
       <c r="O391" t="inlineStr">
         <is>
           <t>Si</t>
@@ -24345,7 +24453,7 @@
       </c>
       <c r="Q391" t="inlineStr">
         <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (gelato_romano)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (lievitopizzapane) | IG: trovato (lievitopizzapane)</t>
         </is>
       </c>
       <c r="R391" t="inlineStr">
@@ -24355,44 +24463,67 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="inlineStr">
-        <is>
-          <t>Giuffrè forno &amp; gelato</t>
-        </is>
-      </c>
-      <c r="B392" s="1" t="inlineStr">
-        <is>
-          <t>Via Pietro Blaserna, 11</t>
-        </is>
-      </c>
-      <c r="C392" s="1" t="inlineStr">
-        <is>
-          <t>06/77205274</t>
-        </is>
-      </c>
-      <c r="D392" s="1" t="inlineStr"/>
-      <c r="E392" s="1" t="inlineStr"/>
-      <c r="F392" s="1" t="inlineStr"/>
-      <c r="G392" s="1" t="inlineStr"/>
-      <c r="H392" s="1" t="inlineStr"/>
-      <c r="I392" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J392" s="1" t="inlineStr"/>
-      <c r="K392" s="1" t="inlineStr"/>
-      <c r="L392" s="1" t="inlineStr"/>
-      <c r="M392" s="1" t="inlineStr"/>
-      <c r="N392" s="1" t="inlineStr"/>
-      <c r="O392" s="1" t="inlineStr"/>
-      <c r="P392" s="1" t="inlineStr"/>
-      <c r="Q392" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R392" s="1" t="inlineStr">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Lina - La Pizza in Teglia</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Circonvallazione Trionfale, 53</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>351/7747767</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>www.linapizza.com</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Lina-La-Pizza-In-Teglia</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>linapizza_vs</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (Lina-La-Pizza-In-Teglia) | IG: trovato (linapizza_vs)</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
@@ -24401,37 +24532,27 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Gori Gelato</t>
+          <t>Miao Miao</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Piazza Menenio Agrippa, 8/B-C</t>
+          <t>Via della Stelletta, 4/A</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>06/8272092</t>
+          <t>380/6914759</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>www.gorigelato.it</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>GORI-Gelateria</t>
+          <t>www.miaomiaokebab.com</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>gorigelato</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>miaomiaokebab</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24449,11 +24570,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M393" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12', 'closes': '00'}, 'martedì': {'opens': '12', 'closes':</t>
-        </is>
-      </c>
       <c r="O393" t="inlineStr">
         <is>
           <t>Si</t>
@@ -24461,7 +24577,7 @@
       </c>
       <c r="Q393" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (GORI-Gelateria) | IG: trovato (gorigelato)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (miaomiaokebab)</t>
         </is>
       </c>
       <c r="R393" t="inlineStr">
@@ -24473,32 +24589,32 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Günther Gelato</t>
+          <t>Neve di Latte</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Piazza di Sant'Eustachio, 47</t>
+          <t>Via Nomentana, 335/F</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>06/68808292</t>
+          <t>06/69346839</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>www.gunthergelatoitaliano.com</t>
+          <t>www.nevedilatte.it</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Gunther-Gelato-Italiano</t>
+          <t>NevediLatteRoma</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>gunthergelatoroma</t>
+          <t>nevedilattegelateria</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -24523,7 +24639,7 @@
       </c>
       <c r="Q394" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (Gunther-Gelato-Italiano) | IG: trovato (gunthergelatoroma)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (NevediLatteRoma) | IG: trovato (nevedilattegelateria)</t>
         </is>
       </c>
       <c r="R394" t="inlineStr">
@@ -24535,27 +24651,22 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Inverso</t>
+          <t>Nonnarè</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Via Vibio Mariano, 5</t>
+          <t>Piazza Augusto Albini, 10</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>06/33251114 - 334/3112437</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>www.pizzeriainverso.it</t>
+          <t>328/5367252</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>inverso_progetto_pizza</t>
+          <t>nonnare_pizzeriadiquartiere</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24568,16 +24679,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '10:30', 'closes': '00'}, 'martedì': {'opens': '10:30', 'cl</t>
-        </is>
-      </c>
       <c r="O395" t="inlineStr">
         <is>
           <t>Si</t>
@@ -24585,7 +24686,7 @@
       </c>
       <c r="Q395" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (inverso_progetto_pizza)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: trovato (nonnare_pizzeriadiquartiere)</t>
         </is>
       </c>
       <c r="R395" t="inlineStr">
@@ -24597,32 +24698,27 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>La Casa del Cremolato</t>
+          <t>OGGI - Officina Gelato Gusto Italiano</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Via di Priscilla, 18</t>
+          <t>Via Tacito, 66</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>06/86200724</t>
+          <t>06/53099944</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>www.lacasadelcremolato.com</t>
+          <t>www.oggigelato.it</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>LaCasaDelCremolato</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>la_casa_del_cremolato</t>
+          <t>oggigelatoroma</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -24630,26 +24726,11 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I396" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M396" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '07', 'closes': '00'}, 'martedì': {'opens': '07', 'closes':</t>
-        </is>
-      </c>
       <c r="O396" t="inlineStr">
         <is>
           <t>Si</t>
@@ -24657,7 +24738,7 @@
       </c>
       <c r="Q396" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (LaCasaDelCremolato) | IG: trovato (la_casa_del_cremolato)</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (oggigelatoroma) | IG: nessun handle</t>
         </is>
       </c>
       <c r="R396" t="inlineStr">
@@ -24669,30 +24750,30 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>La Gourmandise</t>
+          <t>Otaleg!</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Via Felice Cavallotti, 36/B</t>
+          <t>Via di San Cosimato, 14/A</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>377/4116621</t>
+          <t>338/6515450</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>www.lagourmandise.it</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>La-Gourmandise-Gelateria-e-arte-del-gusto</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr">
+          <t>www.otaleg.com</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>otaleg.radicioni</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
@@ -24702,16 +24783,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J397" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M397" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '11', 'closes': '22'}, 'martedì': {'opens': 'Chiuso'}, 'mer</t>
-        </is>
-      </c>
       <c r="O397" t="inlineStr">
         <is>
           <t>Si</t>
@@ -24719,7 +24790,7 @@
       </c>
       <c r="Q397" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (La-Gourmandise-Gelateria-e-arte-del-gusto) | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: trovato (otaleg.radicioni)</t>
         </is>
       </c>
       <c r="R397" t="inlineStr">
@@ -24731,27 +24802,32 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Lievito Pizza Pane</t>
+          <t>Pane e Tempesta</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Viale Europa, 339</t>
+          <t>Via Giovanni de Calvi, 23/25</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>06/69363592</t>
+          <t>06/87725015</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>www.panetempesta.blogspot.it</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>lievitopizzapane</t>
+          <t>PaneTempesta</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>lievitopizzapane</t>
+          <t>paneetempesta</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -24774,6 +24850,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '21'}, 'mer</t>
+        </is>
+      </c>
       <c r="O398" t="inlineStr">
         <is>
           <t>Si</t>
@@ -24781,7 +24862,7 @@
       </c>
       <c r="Q398" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (lievitopizzapane) | IG: trovato (lievitopizzapane)</t>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (PaneTempesta) | IG: trovato (paneetempesta)</t>
         </is>
       </c>
       <c r="R398" t="inlineStr">
@@ -24793,32 +24874,32 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Lina - La Pizza in Teglia</t>
+          <t>Panificio Marè Prati</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Circonvallazione Trionfale, 53</t>
+          <t>Viale Angelico, 88</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>351/7747767</t>
+          <t>06/37511594</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>www.linapizza.com</t>
+          <t>www.panificiomareprati.it</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Lina-La-Pizza-In-Teglia</t>
+          <t>panificiomareprati</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>linapizza_vs</t>
+          <t>panificio_mare_prati</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -24841,6 +24922,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08', 'closes': '20'}, 'martedì': {'opens': '08', 'closes':</t>
+        </is>
+      </c>
       <c r="O399" t="inlineStr">
         <is>
           <t>Si</t>
@@ -24848,7 +24934,7 @@
       </c>
       <c r="Q399" t="inlineStr">
         <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (Lina-La-Pizza-In-Teglia) | IG: trovato (linapizza_vs)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (panificiomareprati) | IG: trovato (panificio_mare_prati)</t>
         </is>
       </c>
       <c r="R399" t="inlineStr">
@@ -24860,27 +24946,32 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Miao Miao</t>
+          <t>Pinsere</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Via della Stelletta, 4/A</t>
+          <t>Via Flavia, 98</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>380/6914759</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>www.miaomiaokebab.com</t>
+          <t>06/42020924</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Pinsere</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>miaomiaokebab</t>
+          <t>pinseparole</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -24898,6 +24989,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10', 'closes': '21'}, 'martedì': {'opens': '10', 'closes':</t>
+        </is>
+      </c>
       <c r="O400" t="inlineStr">
         <is>
           <t>Si</t>
@@ -24905,7 +25001,7 @@
       </c>
       <c r="Q400" t="inlineStr">
         <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (miaomiaokebab)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Pinsere) | IG: trovato (pinseparole)</t>
         </is>
       </c>
       <c r="R400" t="inlineStr">
@@ -24917,42 +25013,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Neve di Latte</t>
+          <t>Pizza Baar</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Via Nomentana, 335/F</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>06/69346839</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>www.nevedilatte.it</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>NevediLatteRoma</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>nevedilattegelateria</t>
-        </is>
-      </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>Via di Donna Olimpia, 71</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24960,14 +25026,14 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="O401" t="inlineStr">
-        <is>
-          <t>Si</t>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (NevediLatteRoma) | IG: trovato (nevedilattegelateria)</t>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R401" t="inlineStr">
@@ -24979,22 +25045,32 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Nonnarè</t>
+          <t>Pizza Chef</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Piazza Augusto Albini, 10</t>
+          <t>Via Clelia, 63/A</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>328/5367252</t>
+          <t>06/87566046</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>pizzachefroma</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>nonnare_pizzeriadiquartiere</t>
+          <t>pizzachefroma</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -25014,7 +25090,7 @@
       </c>
       <c r="Q402" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: trovato (nonnare_pizzeriadiquartiere)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (pizzachefroma) | IG: trovato (pizzachefroma)</t>
         </is>
       </c>
       <c r="R402" t="inlineStr">
@@ -25026,27 +25102,32 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>OGGI - Officina Gelato Gusto Italiano</t>
+          <t>Pizzarium</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Via Tacito, 66</t>
+          <t>Via della Meloria, 43</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>06/53099944</t>
+          <t>06/39745416</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>www.oggigelato.it</t>
+          <t>www.bonci.it</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>oggigelatoroma</t>
+          <t>pizzarium-gabrielebonci</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>pizzarium</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -25054,11 +25135,26 @@
           <t>N/D</t>
         </is>
       </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I403" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '11:15', 'closes': '22'}, 'martedì': {'opens': '11:15', 'cl</t>
+        </is>
+      </c>
       <c r="O403" t="inlineStr">
         <is>
           <t>Si</t>
@@ -25066,7 +25162,7 @@
       </c>
       <c r="Q403" t="inlineStr">
         <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (oggigelatoroma) | IG: nessun handle</t>
+          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: trovato (pizzarium-gabrielebonci) | IG: trovato (pizzarium)</t>
         </is>
       </c>
       <c r="R403" t="inlineStr">
@@ -25078,27 +25174,32 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Otaleg!</t>
+          <t>Prelibato</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Via di San Cosimato, 14/A</t>
+          <t>Viale di Villa Pamphili, 214</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>338/6515450</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>www.otaleg.com</t>
+          <t>06/93577165</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>FornoPrelibato</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>otaleg.radicioni</t>
+          <t>prelibatoroma</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25111,6 +25212,16 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '09, 16', 'closes': '15, 20:30', 'break': '15–16'}, 'marted</t>
+        </is>
+      </c>
       <c r="O404" t="inlineStr">
         <is>
           <t>Si</t>
@@ -25118,7 +25229,7 @@
       </c>
       <c r="Q404" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: trovato (otaleg.radicioni)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (FornoPrelibato) | IG: trovato (prelibatoroma)</t>
         </is>
       </c>
       <c r="R404" t="inlineStr">
@@ -25130,37 +25241,22 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Pane e Tempesta</t>
+          <t>Ruver - teglia frazionata</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Via Giovanni de Calvi, 23/25</t>
+          <t>Viale Aventino, 46</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>06/87725015</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>www.panetempesta.blogspot.it</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>PaneTempesta</t>
+          <t>327/0737999</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>paneetempesta</t>
-        </is>
-      </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>N/D</t>
+          <t>ruver_tegliafrazionata</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25180,7 +25276,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '08', 'closes': '21'}, 'mer</t>
+          <t>{'lunedì': {'opens': '10', 'closes': '21'}, 'martedì': {'opens': '10', 'closes':</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -25190,7 +25286,7 @@
       </c>
       <c r="Q405" t="inlineStr">
         <is>
-          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (PaneTempesta) | IG: trovato (paneetempesta)</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (ruver_tegliafrazionata)</t>
         </is>
       </c>
       <c r="R405" t="inlineStr">
@@ -25202,32 +25298,32 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Panificio Marè Prati</t>
+          <t>San Biagio pizza e bolle</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Viale Angelico, 88</t>
+          <t>Via Oslavia, 39</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>06/37511594</t>
+          <t>06/45683049</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>www.panificiomareprati.it</t>
+          <t>www.pizzaebolle.it</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>panificiomareprati</t>
+          <t>sanbiagiopizzaebolle</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>panificio_mare_prati</t>
+          <t>_san_biagio</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -25252,7 +25348,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>{'lunedì': {'opens': '08', 'closes': '20'}, 'martedì': {'opens': '08', 'closes':</t>
+          <t>{'lunedì': {'opens': '11', 'closes': '22'}, 'martedì': {'opens': '11', 'closes':</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
@@ -25262,7 +25358,7 @@
       </c>
       <c r="Q406" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (panificiomareprati) | IG: trovato (panificio_mare_prati)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (sanbiagiopizzaebolle) | IG: trovato (_san_biagio)</t>
         </is>
       </c>
       <c r="R406" t="inlineStr">
@@ -25274,27 +25370,32 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Pinsere</t>
+          <t>Sancho</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Via Flavia, 98</t>
+          <t>Via Giuseppe Gioachino Belli, 3/A</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>06/42020924</t>
+          <t>06/86299316</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>www.pizzeriasancho.it</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Pinsere</t>
+          <t>PizzeriaSancho1969</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>pinseparole</t>
+          <t>pizzeriasancho</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -25317,11 +25418,6 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="M407" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '10', 'closes': '21'}, 'martedì': {'opens': '10', 'closes':</t>
-        </is>
-      </c>
       <c r="O407" t="inlineStr">
         <is>
           <t>Si</t>
@@ -25329,7 +25425,7 @@
       </c>
       <c r="Q407" t="inlineStr">
         <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Pinsere) | IG: trovato (pinseparole)</t>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (PizzeriaSancho1969) | IG: trovato (pizzeriasancho)</t>
         </is>
       </c>
       <c r="R407" t="inlineStr">
@@ -25341,12 +25437,42 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Pizza Baar</t>
+          <t>Stefano Ferrara - Formaessenza</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Via di Donna Olimpia, 71</t>
+          <t>Via Enrico Fermi, 102/104</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>06/55296621</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>www.gelatolab.it</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>stefanoferraragelato</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>stefanoferraragelato</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25359,9 +25485,19 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '23'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
       <c r="Q408" t="inlineStr">
         <is>
-          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (stefanoferraragelato) | IG: trovato (stefanoferraragelato)</t>
         </is>
       </c>
       <c r="R408" t="inlineStr">
@@ -25373,27 +25509,32 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Pizza Chef</t>
+          <t>Terra Gelato</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Via Clelia, 63/A</t>
+          <t>Piazza Santa Maria Maggiore, 9</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>06/87566046</t>
+          <t>06/45666656</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>www.terragelato.it</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>pizzachefroma</t>
+          <t>TerraGelato</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>pizzachefroma</t>
+          <t>terragelato</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
@@ -25418,7 +25559,7 @@
       </c>
       <c r="Q409" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (pizzachefroma) | IG: trovato (pizzachefroma)</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (TerraGelato) | IG: trovato (terragelato)</t>
         </is>
       </c>
       <c r="R409" t="inlineStr">
@@ -25430,32 +25571,32 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Pizzarium</t>
+          <t>Trapizzino</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Via della Meloria, 43</t>
+          <t>Piazzale delle Province, 9</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>06/39745416</t>
+          <t>06/90239685</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>www.bonci.it</t>
+          <t>www.trapizzino.it</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>pizzarium-gabrielebonci</t>
+          <t>Trapizzino</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>pizzarium</t>
+          <t>Trapizzino</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -25473,16 +25614,6 @@
           <t>APERTO</t>
         </is>
       </c>
-      <c r="J410" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M410" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '11:15', 'closes': '22'}, 'martedì': {'opens': '11:15', 'cl</t>
-        </is>
-      </c>
       <c r="O410" t="inlineStr">
         <is>
           <t>Si</t>
@@ -25490,7 +25621,7 @@
       </c>
       <c r="Q410" t="inlineStr">
         <is>
-          <t>Rating Google: 4.1 ( rec.) | TF: non trovato | FB: trovato (pizzarium-gabrielebonci) | IG: trovato (pizzarium)</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (Trapizzino) | IG: trovato (Trapizzino)</t>
         </is>
       </c>
       <c r="R410" t="inlineStr">
@@ -25500,86 +25631,67 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Prelibato</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Viale di Villa Pamphili, 214</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>06/93577165</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>FornoPrelibato</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>prelibatoroma</t>
-        </is>
-      </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I411" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J411" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M411" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '09, 16', 'closes': '15, 20:30', 'break': '15–16'}, 'marted</t>
-        </is>
-      </c>
-      <c r="O411" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q411" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (FornoPrelibato) | IG: trovato (prelibatoroma)</t>
-        </is>
-      </c>
-      <c r="R411" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>Bless</t>
+        </is>
+      </c>
+      <c r="B411" s="1" t="inlineStr">
+        <is>
+          <t>Via dell’Indipendenza, 208</t>
+        </is>
+      </c>
+      <c r="C411" s="1" t="inlineStr">
+        <is>
+          <t>0771/030188</t>
+        </is>
+      </c>
+      <c r="D411" s="1" t="inlineStr"/>
+      <c r="E411" s="1" t="inlineStr"/>
+      <c r="F411" s="1" t="inlineStr"/>
+      <c r="G411" s="1" t="inlineStr"/>
+      <c r="H411" s="1" t="inlineStr"/>
+      <c r="I411" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J411" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K411" s="1" t="inlineStr"/>
+      <c r="L411" s="1" t="inlineStr"/>
+      <c r="M411" s="1" t="inlineStr"/>
+      <c r="N411" s="1" t="inlineStr"/>
+      <c r="O411" s="1" t="inlineStr"/>
+      <c r="P411" s="1" t="inlineStr"/>
+      <c r="Q411" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R411" s="1" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
         <is>
-          <t>Retrò</t>
+          <t>Mrgda Ristorante</t>
         </is>
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t>Via Baldo degli Ubaldi, 118</t>
+          <t>Via Prenestina, 182</t>
         </is>
       </c>
       <c r="C412" s="1" t="inlineStr">
         <is>
-          <t>06/6636288</t>
+          <t>329/933355</t>
         </is>
       </c>
       <c r="D412" s="1" t="inlineStr"/>
@@ -25592,7 +25704,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J412" s="1" t="inlineStr"/>
+      <c r="J412" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K412" s="1" t="inlineStr"/>
       <c r="L412" s="1" t="inlineStr"/>
       <c r="M412" s="1" t="inlineStr"/>
@@ -25606,527 +25722,417 @@
       </c>
       <c r="R412" s="1" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Ruver - teglia frazionata</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Viale Aventino, 46</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>327/0737999</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>ruver_tegliafrazionata</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I413" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J413" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M413" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '10', 'closes': '21'}, 'martedì': {'opens': '10', 'closes':</t>
-        </is>
-      </c>
-      <c r="O413" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q413" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (ruver_tegliafrazionata)</t>
-        </is>
-      </c>
-      <c r="R413" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>Clementina</t>
+        </is>
+      </c>
+      <c r="B413" s="1" t="inlineStr">
+        <is>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C413" s="1" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
+      <c r="D413" s="1" t="inlineStr"/>
+      <c r="E413" s="1" t="inlineStr"/>
+      <c r="F413" s="1" t="inlineStr"/>
+      <c r="G413" s="1" t="inlineStr"/>
+      <c r="H413" s="1" t="inlineStr"/>
+      <c r="I413" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J413" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K413" s="1" t="inlineStr"/>
+      <c r="L413" s="1" t="inlineStr"/>
+      <c r="M413" s="1" t="inlineStr"/>
+      <c r="N413" s="1" t="inlineStr"/>
+      <c r="O413" s="1" t="inlineStr"/>
+      <c r="P413" s="1" t="inlineStr"/>
+      <c r="Q413" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R413" s="1" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>San Biagio pizza e bolle</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Via Oslavia, 39</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>06/45683049</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>www.pizzaebolle.it</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>sanbiagiopizzaebolle</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>_san_biagio</t>
-        </is>
-      </c>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I414" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J414" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M414" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '11', 'closes': '22'}, 'martedì': {'opens': '11', 'closes':</t>
-        </is>
-      </c>
-      <c r="O414" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q414" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (sanbiagiopizzaebolle) | IG: trovato (_san_biagio)</t>
-        </is>
-      </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>Da Antonio</t>
+        </is>
+      </c>
+      <c r="B414" s="1" t="inlineStr">
+        <is>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C414" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
+      <c r="D414" s="1" t="inlineStr"/>
+      <c r="E414" s="1" t="inlineStr"/>
+      <c r="F414" s="1" t="inlineStr"/>
+      <c r="G414" s="1" t="inlineStr"/>
+      <c r="H414" s="1" t="inlineStr"/>
+      <c r="I414" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J414" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K414" s="1" t="inlineStr"/>
+      <c r="L414" s="1" t="inlineStr"/>
+      <c r="M414" s="1" t="inlineStr"/>
+      <c r="N414" s="1" t="inlineStr"/>
+      <c r="O414" s="1" t="inlineStr"/>
+      <c r="P414" s="1" t="inlineStr"/>
+      <c r="Q414" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R414" s="1" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Sancho</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Via Giuseppe Gioachino Belli, 3/A</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>06/86299316</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>www.pizzeriasancho.it</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>PizzeriaSancho1969</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>pizzeriasancho</t>
-        </is>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I415" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J415" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O415" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q415" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: trovato (PizzeriaSancho1969) | IG: trovato (pizzeriasancho)</t>
-        </is>
-      </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>Il tuo fornaio</t>
+        </is>
+      </c>
+      <c r="B415" s="1" t="inlineStr">
+        <is>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C415" s="1" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
+      <c r="D415" s="1" t="inlineStr"/>
+      <c r="E415" s="1" t="inlineStr"/>
+      <c r="F415" s="1" t="inlineStr"/>
+      <c r="G415" s="1" t="inlineStr"/>
+      <c r="H415" s="1" t="inlineStr"/>
+      <c r="I415" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J415" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K415" s="1" t="inlineStr"/>
+      <c r="L415" s="1" t="inlineStr"/>
+      <c r="M415" s="1" t="inlineStr"/>
+      <c r="N415" s="1" t="inlineStr"/>
+      <c r="O415" s="1" t="inlineStr"/>
+      <c r="P415" s="1" t="inlineStr"/>
+      <c r="Q415" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R415" s="1" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Stefano Ferrara - Formaessenza</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Via Enrico Fermi, 102/104</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>06/55296621</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>www.gelatolab.it</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>stefanoferraragelato</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>stefanoferraragelato</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J416" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M416" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12', 'closes': '23'}, 'martedì': {'opens': '12', 'closes':</t>
-        </is>
-      </c>
-      <c r="O416" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q416" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (stefanoferraragelato) | IG: trovato (stefanoferraragelato)</t>
-        </is>
-      </c>
-      <c r="R416" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="B416" s="1" t="inlineStr">
+        <is>
+          <t>Corso Vittorio Emanuele II, 73</t>
+        </is>
+      </c>
+      <c r="C416" s="1" t="inlineStr"/>
+      <c r="D416" s="1" t="inlineStr"/>
+      <c r="E416" s="1" t="inlineStr"/>
+      <c r="F416" s="1" t="inlineStr"/>
+      <c r="G416" s="1" t="inlineStr"/>
+      <c r="H416" s="1" t="inlineStr"/>
+      <c r="I416" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J416" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K416" s="1" t="inlineStr"/>
+      <c r="L416" s="1" t="inlineStr"/>
+      <c r="M416" s="1" t="inlineStr"/>
+      <c r="N416" s="1" t="inlineStr"/>
+      <c r="O416" s="1" t="inlineStr"/>
+      <c r="P416" s="1" t="inlineStr"/>
+      <c r="Q416" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R416" s="1" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>Terra Gelato</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Piazza Santa Maria Maggiore, 9</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>06/45666656</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>www.terragelato.it</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>TerraGelato</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>terragelato</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I417" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O417" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q417" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: trovato (TerraGelato) | IG: trovato (terragelato)</t>
-        </is>
-      </c>
-      <c r="R417" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>Giuffrè forno &amp; gelato</t>
+        </is>
+      </c>
+      <c r="B417" s="1" t="inlineStr">
+        <is>
+          <t>Via Pietro Blaserna, 11</t>
+        </is>
+      </c>
+      <c r="C417" s="1" t="inlineStr">
+        <is>
+          <t>06/77205274</t>
+        </is>
+      </c>
+      <c r="D417" s="1" t="inlineStr"/>
+      <c r="E417" s="1" t="inlineStr"/>
+      <c r="F417" s="1" t="inlineStr"/>
+      <c r="G417" s="1" t="inlineStr"/>
+      <c r="H417" s="1" t="inlineStr"/>
+      <c r="I417" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J417" s="1" t="inlineStr"/>
+      <c r="K417" s="1" t="inlineStr"/>
+      <c r="L417" s="1" t="inlineStr"/>
+      <c r="M417" s="1" t="inlineStr"/>
+      <c r="N417" s="1" t="inlineStr"/>
+      <c r="O417" s="1" t="inlineStr"/>
+      <c r="P417" s="1" t="inlineStr"/>
+      <c r="Q417" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R417" s="1" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Trapizzino</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Piazzale delle Province, 9</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>06/90239685</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>www.trapizzino.it</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>Trapizzino</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>Trapizzino</t>
-        </is>
-      </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O418" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q418" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (Trapizzino) | IG: trovato (Trapizzino)</t>
-        </is>
-      </c>
-      <c r="R418" t="inlineStr">
-        <is>
-          <t>29/06/2026</t>
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>Retrò</t>
+        </is>
+      </c>
+      <c r="B418" s="1" t="inlineStr">
+        <is>
+          <t>Via Baldo degli Ubaldi, 118</t>
+        </is>
+      </c>
+      <c r="C418" s="1" t="inlineStr">
+        <is>
+          <t>06/6636288</t>
+        </is>
+      </c>
+      <c r="D418" s="1" t="inlineStr"/>
+      <c r="E418" s="1" t="inlineStr"/>
+      <c r="F418" s="1" t="inlineStr"/>
+      <c r="G418" s="1" t="inlineStr"/>
+      <c r="H418" s="1" t="inlineStr"/>
+      <c r="I418" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J418" s="1" t="inlineStr"/>
+      <c r="K418" s="1" t="inlineStr"/>
+      <c r="L418" s="1" t="inlineStr"/>
+      <c r="M418" s="1" t="inlineStr"/>
+      <c r="N418" s="1" t="inlineStr"/>
+      <c r="O418" s="1" t="inlineStr"/>
+      <c r="P418" s="1" t="inlineStr"/>
+      <c r="Q418" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R418" s="1" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="inlineStr">
+      <c r="A419" t="inlineStr">
         <is>
           <t>Zelato</t>
         </is>
       </c>
-      <c r="B419" s="1" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>Via degli Aurunci, 40</t>
         </is>
       </c>
-      <c r="C419" s="1" t="inlineStr">
+      <c r="C419" t="inlineStr">
         <is>
           <t>375/8666287</t>
         </is>
       </c>
-      <c r="D419" s="1" t="inlineStr">
+      <c r="D419" t="inlineStr">
         <is>
           <t>www.zelato.it</t>
         </is>
       </c>
-      <c r="E419" s="1" t="inlineStr">
+      <c r="E419" t="inlineStr">
         <is>
           <t>Zelato</t>
         </is>
       </c>
-      <c r="F419" s="1" t="inlineStr">
+      <c r="F419" t="inlineStr">
         <is>
           <t>zelato_roma</t>
         </is>
       </c>
-      <c r="G419" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H419" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I419" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J419" s="1" t="inlineStr"/>
-      <c r="K419" s="1" t="inlineStr"/>
-      <c r="L419" s="1" t="inlineStr"/>
-      <c r="M419" s="1" t="inlineStr"/>
-      <c r="N419" s="1" t="inlineStr"/>
-      <c r="O419" s="1" t="inlineStr"/>
-      <c r="P419" s="1" t="inlineStr"/>
-      <c r="Q419" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R419" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '22'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (Zelato) | IG: trovato (zelato_roma)</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="inlineStr">
+      <c r="A420" t="inlineStr">
         <is>
           <t>Zia Rosetta</t>
         </is>
       </c>
-      <c r="B420" s="1" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>Via Urbana, 54</t>
         </is>
       </c>
-      <c r="C420" s="1" t="inlineStr">
+      <c r="C420" t="inlineStr">
         <is>
           <t>06/31052516</t>
         </is>
       </c>
-      <c r="D420" s="1" t="inlineStr">
+      <c r="D420" t="inlineStr">
         <is>
           <t>www.ziarosetta.com</t>
         </is>
       </c>
-      <c r="E420" s="1" t="inlineStr">
+      <c r="E420" t="inlineStr">
         <is>
           <t>ziarosettaroma</t>
         </is>
       </c>
-      <c r="F420" s="1" t="inlineStr">
+      <c r="F420" t="inlineStr">
         <is>
           <t>ziarosetta</t>
         </is>
       </c>
-      <c r="G420" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H420" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I420" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J420" s="1" t="inlineStr"/>
-      <c r="K420" s="1" t="inlineStr"/>
-      <c r="L420" s="1" t="inlineStr"/>
-      <c r="M420" s="1" t="inlineStr"/>
-      <c r="N420" s="1" t="inlineStr"/>
-      <c r="O420" s="1" t="inlineStr"/>
-      <c r="P420" s="1" t="inlineStr"/>
-      <c r="Q420" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R420" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ziarosettaroma) | IG: trovato (ziarosetta)</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25631,96 +25631,134 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B411" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C411" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D411" s="1" t="inlineStr"/>
-      <c r="E411" s="1" t="inlineStr"/>
-      <c r="F411" s="1" t="inlineStr"/>
-      <c r="G411" s="1" t="inlineStr"/>
-      <c r="H411" s="1" t="inlineStr"/>
-      <c r="I411" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J411" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K411" s="1" t="inlineStr"/>
-      <c r="L411" s="1" t="inlineStr"/>
-      <c r="M411" s="1" t="inlineStr"/>
-      <c r="N411" s="1" t="inlineStr"/>
-      <c r="O411" s="1" t="inlineStr"/>
-      <c r="P411" s="1" t="inlineStr"/>
-      <c r="Q411" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R411" s="1" t="inlineStr">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Zelato</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Via degli Aurunci, 40</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>375/8666287</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>www.zelato.it</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Zelato</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>zelato_roma</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '12', 'closes': '22'}, 'venerdì': {'opens': '12', 'closes'</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (Zelato) | IG: trovato (zelato_roma)</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="inlineStr">
-        <is>
-          <t>Mrgda Ristorante</t>
-        </is>
-      </c>
-      <c r="B412" s="1" t="inlineStr">
-        <is>
-          <t>Via Prenestina, 182</t>
-        </is>
-      </c>
-      <c r="C412" s="1" t="inlineStr">
-        <is>
-          <t>329/933355</t>
-        </is>
-      </c>
-      <c r="D412" s="1" t="inlineStr"/>
-      <c r="E412" s="1" t="inlineStr"/>
-      <c r="F412" s="1" t="inlineStr"/>
-      <c r="G412" s="1" t="inlineStr"/>
-      <c r="H412" s="1" t="inlineStr"/>
-      <c r="I412" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J412" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K412" s="1" t="inlineStr"/>
-      <c r="L412" s="1" t="inlineStr"/>
-      <c r="M412" s="1" t="inlineStr"/>
-      <c r="N412" s="1" t="inlineStr"/>
-      <c r="O412" s="1" t="inlineStr"/>
-      <c r="P412" s="1" t="inlineStr"/>
-      <c r="Q412" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R412" s="1" t="inlineStr">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Zia Rosetta</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Via Urbana, 54</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>06/31052516</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>www.ziarosetta.com</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>ziarosettaroma</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>ziarosetta</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ziarosettaroma) | IG: trovato (ziarosetta)</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
@@ -25729,17 +25767,17 @@
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
         <is>
-          <t>Clementina</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t>Via della Torre Clementina, 158</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C413" s="1" t="inlineStr">
         <is>
-          <t>328/8181651</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D413" s="1" t="inlineStr"/>
@@ -25770,24 +25808,24 @@
       </c>
       <c r="R413" s="1" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
         <is>
-          <t>Da Antonio</t>
+          <t>Mrgda Ristorante</t>
         </is>
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t>Via Mario Lizzani, 21</t>
+          <t>Via Prenestina, 182</t>
         </is>
       </c>
       <c r="C414" s="1" t="inlineStr">
         <is>
-          <t>391/7475549</t>
+          <t>329/933355</t>
         </is>
       </c>
       <c r="D414" s="1" t="inlineStr"/>
@@ -25818,24 +25856,24 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
         <is>
-          <t>Il tuo fornaio</t>
+          <t>Clementina</t>
         </is>
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>Via Francesco Sapori, 35</t>
+          <t>Via della Torre Clementina, 158</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
         <is>
-          <t>06/5017873</t>
+          <t>328/8181651</t>
         </is>
       </c>
       <c r="D415" s="1" t="inlineStr"/>
@@ -25866,22 +25904,26 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
         <is>
-          <t>Slow</t>
+          <t>Da Antonio</t>
         </is>
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t>Corso Vittorio Emanuele II, 73</t>
-        </is>
-      </c>
-      <c r="C416" s="1" t="inlineStr"/>
+          <t>Via Mario Lizzani, 21</t>
+        </is>
+      </c>
+      <c r="C416" s="1" t="inlineStr">
+        <is>
+          <t>391/7475549</t>
+        </is>
+      </c>
       <c r="D416" s="1" t="inlineStr"/>
       <c r="E416" s="1" t="inlineStr"/>
       <c r="F416" s="1" t="inlineStr"/>
@@ -25910,24 +25952,24 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
         <is>
-          <t>Giuffrè forno &amp; gelato</t>
+          <t>Il tuo fornaio</t>
         </is>
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>Via Pietro Blaserna, 11</t>
+          <t>Via Francesco Sapori, 35</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
         <is>
-          <t>06/77205274</t>
+          <t>06/5017873</t>
         </is>
       </c>
       <c r="D417" s="1" t="inlineStr"/>
@@ -25940,7 +25982,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J417" s="1" t="inlineStr"/>
+      <c r="J417" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K417" s="1" t="inlineStr"/>
       <c r="L417" s="1" t="inlineStr"/>
       <c r="M417" s="1" t="inlineStr"/>
@@ -25954,26 +26000,22 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
         <is>
-          <t>Retrò</t>
+          <t>Slow</t>
         </is>
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>Via Baldo degli Ubaldi, 118</t>
-        </is>
-      </c>
-      <c r="C418" s="1" t="inlineStr">
-        <is>
-          <t>06/6636288</t>
-        </is>
-      </c>
+          <t>Corso Vittorio Emanuele II, 73</t>
+        </is>
+      </c>
+      <c r="C418" s="1" t="inlineStr"/>
       <c r="D418" s="1" t="inlineStr"/>
       <c r="E418" s="1" t="inlineStr"/>
       <c r="F418" s="1" t="inlineStr"/>
@@ -25984,7 +26026,11 @@
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J418" s="1" t="inlineStr"/>
+      <c r="J418" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="K418" s="1" t="inlineStr"/>
       <c r="L418" s="1" t="inlineStr"/>
       <c r="M418" s="1" t="inlineStr"/>
@@ -25998,141 +26044,95 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Zelato</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Via degli Aurunci, 40</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>375/8666287</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>www.zelato.it</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>Zelato</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>zelato_roma</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J419" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M419" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '12', 'closes': '22'}, 'venerdì': {'opens': '12', 'closes'</t>
-        </is>
-      </c>
-      <c r="O419" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q419" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (Zelato) | IG: trovato (zelato_roma)</t>
-        </is>
-      </c>
-      <c r="R419" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>Giuffrè forno &amp; gelato</t>
+        </is>
+      </c>
+      <c r="B419" s="1" t="inlineStr">
+        <is>
+          <t>Via Pietro Blaserna, 11</t>
+        </is>
+      </c>
+      <c r="C419" s="1" t="inlineStr">
+        <is>
+          <t>06/77205274</t>
+        </is>
+      </c>
+      <c r="D419" s="1" t="inlineStr"/>
+      <c r="E419" s="1" t="inlineStr"/>
+      <c r="F419" s="1" t="inlineStr"/>
+      <c r="G419" s="1" t="inlineStr"/>
+      <c r="H419" s="1" t="inlineStr"/>
+      <c r="I419" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J419" s="1" t="inlineStr"/>
+      <c r="K419" s="1" t="inlineStr"/>
+      <c r="L419" s="1" t="inlineStr"/>
+      <c r="M419" s="1" t="inlineStr"/>
+      <c r="N419" s="1" t="inlineStr"/>
+      <c r="O419" s="1" t="inlineStr"/>
+      <c r="P419" s="1" t="inlineStr"/>
+      <c r="Q419" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R419" s="1" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Zia Rosetta</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Via Urbana, 54</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>06/31052516</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>www.ziarosetta.com</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>ziarosettaroma</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>ziarosetta</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="O420" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q420" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (ziarosettaroma) | IG: trovato (ziarosetta)</t>
-        </is>
-      </c>
-      <c r="R420" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>Retrò</t>
+        </is>
+      </c>
+      <c r="B420" s="1" t="inlineStr">
+        <is>
+          <t>Via Baldo degli Ubaldi, 118</t>
+        </is>
+      </c>
+      <c r="C420" s="1" t="inlineStr">
+        <is>
+          <t>06/6636288</t>
+        </is>
+      </c>
+      <c r="D420" s="1" t="inlineStr"/>
+      <c r="E420" s="1" t="inlineStr"/>
+      <c r="F420" s="1" t="inlineStr"/>
+      <c r="G420" s="1" t="inlineStr"/>
+      <c r="H420" s="1" t="inlineStr"/>
+      <c r="I420" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J420" s="1" t="inlineStr"/>
+      <c r="K420" s="1" t="inlineStr"/>
+      <c r="L420" s="1" t="inlineStr"/>
+      <c r="M420" s="1" t="inlineStr"/>
+      <c r="N420" s="1" t="inlineStr"/>
+      <c r="O420" s="1" t="inlineStr"/>
+      <c r="P420" s="1" t="inlineStr"/>
+      <c r="Q420" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R420" s="1" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25808,7 +25808,7 @@
       </c>
       <c r="R413" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -25856,7 +25856,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -25904,7 +25904,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -25947,12 +25947,12 @@
       <c r="P416" s="1" t="inlineStr"/>
       <c r="Q416" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26000,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -26088,7 +26088,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -26132,7 +26132,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25803,12 +25803,12 @@
       <c r="P413" s="1" t="inlineStr"/>
       <c r="Q413" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R413" s="1" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -25856,7 +25856,7 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -25904,7 +25904,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -25947,12 +25947,12 @@
       <c r="P416" s="1" t="inlineStr"/>
       <c r="Q416" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26000,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -26044,51 +26044,49 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="inlineStr">
+      <c r="A419" t="inlineStr">
         <is>
           <t>Giuffrè forno &amp; gelato</t>
         </is>
       </c>
-      <c r="B419" s="1" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>Via Pietro Blaserna, 11</t>
         </is>
       </c>
-      <c r="C419" s="1" t="inlineStr">
+      <c r="C419" t="inlineStr">
         <is>
           <t>06/77205274</t>
         </is>
       </c>
-      <c r="D419" s="1" t="inlineStr"/>
-      <c r="E419" s="1" t="inlineStr"/>
-      <c r="F419" s="1" t="inlineStr"/>
-      <c r="G419" s="1" t="inlineStr"/>
-      <c r="H419" s="1" t="inlineStr"/>
-      <c r="I419" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J419" s="1" t="inlineStr"/>
-      <c r="K419" s="1" t="inlineStr"/>
-      <c r="L419" s="1" t="inlineStr"/>
-      <c r="M419" s="1" t="inlineStr"/>
-      <c r="N419" s="1" t="inlineStr"/>
-      <c r="O419" s="1" t="inlineStr"/>
-      <c r="P419" s="1" t="inlineStr"/>
-      <c r="Q419" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R419" s="1" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '21:30'}, 'martedì': {'opens': '12', 'close</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -26132,7 +26130,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25765,48 +25765,42 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B413" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C413" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D413" s="1" t="inlineStr"/>
-      <c r="E413" s="1" t="inlineStr"/>
-      <c r="F413" s="1" t="inlineStr"/>
-      <c r="G413" s="1" t="inlineStr"/>
-      <c r="H413" s="1" t="inlineStr"/>
-      <c r="I413" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J413" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K413" s="1" t="inlineStr"/>
-      <c r="L413" s="1" t="inlineStr"/>
-      <c r="M413" s="1" t="inlineStr"/>
-      <c r="N413" s="1" t="inlineStr"/>
-      <c r="O413" s="1" t="inlineStr"/>
-      <c r="P413" s="1" t="inlineStr"/>
-      <c r="Q413" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R413" s="1" t="inlineStr">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Giuffrè forno &amp; gelato</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Via Pietro Blaserna, 11</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>06/77205274</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '21:30'}, 'martedì': {'opens': '12', 'close</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
@@ -25815,17 +25809,17 @@
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
         <is>
-          <t>Mrgda Ristorante</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t>Via Prenestina, 182</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C414" s="1" t="inlineStr">
         <is>
-          <t>329/933355</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D414" s="1" t="inlineStr"/>
@@ -25856,24 +25850,24 @@
       </c>
       <c r="R414" s="1" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
         <is>
-          <t>Clementina</t>
+          <t>Mrgda Ristorante</t>
         </is>
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>Via della Torre Clementina, 158</t>
+          <t>Via Prenestina, 182</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
         <is>
-          <t>328/8181651</t>
+          <t>329/933355</t>
         </is>
       </c>
       <c r="D415" s="1" t="inlineStr"/>
@@ -25904,72 +25898,66 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="inlineStr">
-        <is>
-          <t>Da Antonio</t>
-        </is>
-      </c>
-      <c r="B416" s="1" t="inlineStr">
-        <is>
-          <t>Via Mario Lizzani, 21</t>
-        </is>
-      </c>
-      <c r="C416" s="1" t="inlineStr">
-        <is>
-          <t>391/7475549</t>
-        </is>
-      </c>
-      <c r="D416" s="1" t="inlineStr"/>
-      <c r="E416" s="1" t="inlineStr"/>
-      <c r="F416" s="1" t="inlineStr"/>
-      <c r="G416" s="1" t="inlineStr"/>
-      <c r="H416" s="1" t="inlineStr"/>
-      <c r="I416" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J416" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K416" s="1" t="inlineStr"/>
-      <c r="L416" s="1" t="inlineStr"/>
-      <c r="M416" s="1" t="inlineStr"/>
-      <c r="N416" s="1" t="inlineStr"/>
-      <c r="O416" s="1" t="inlineStr"/>
-      <c r="P416" s="1" t="inlineStr"/>
-      <c r="Q416" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R416" s="1" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Clementina</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '07', 'closes': '22'}, 'venerdì': {'opens': '07', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
         <is>
-          <t>Il tuo fornaio</t>
+          <t>Da Antonio</t>
         </is>
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>Via Francesco Sapori, 35</t>
+          <t>Via Mario Lizzani, 21</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
         <is>
-          <t>06/5017873</t>
+          <t>391/7475549</t>
         </is>
       </c>
       <c r="D417" s="1" t="inlineStr"/>
@@ -26000,22 +25988,26 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
         <is>
-          <t>Slow</t>
+          <t>Il tuo fornaio</t>
         </is>
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>Corso Vittorio Emanuele II, 73</t>
-        </is>
-      </c>
-      <c r="C418" s="1" t="inlineStr"/>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C418" s="1" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
       <c r="D418" s="1" t="inlineStr"/>
       <c r="E418" s="1" t="inlineStr"/>
       <c r="F418" s="1" t="inlineStr"/>
@@ -26044,49 +26036,51 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Giuffrè forno &amp; gelato</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Via Pietro Blaserna, 11</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>06/77205274</t>
-        </is>
-      </c>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J419" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M419" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': '12', 'closes': '21:30'}, 'martedì': {'opens': '12', 'close</t>
-        </is>
-      </c>
-      <c r="Q419" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R419" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="B419" s="1" t="inlineStr">
+        <is>
+          <t>Corso Vittorio Emanuele II, 73</t>
+        </is>
+      </c>
+      <c r="C419" s="1" t="inlineStr"/>
+      <c r="D419" s="1" t="inlineStr"/>
+      <c r="E419" s="1" t="inlineStr"/>
+      <c r="F419" s="1" t="inlineStr"/>
+      <c r="G419" s="1" t="inlineStr"/>
+      <c r="H419" s="1" t="inlineStr"/>
+      <c r="I419" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J419" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K419" s="1" t="inlineStr"/>
+      <c r="L419" s="1" t="inlineStr"/>
+      <c r="M419" s="1" t="inlineStr"/>
+      <c r="N419" s="1" t="inlineStr"/>
+      <c r="O419" s="1" t="inlineStr"/>
+      <c r="P419" s="1" t="inlineStr"/>
+      <c r="Q419" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R419" s="1" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>
@@ -26130,7 +26124,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25807,48 +25807,42 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B414" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C414" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D414" s="1" t="inlineStr"/>
-      <c r="E414" s="1" t="inlineStr"/>
-      <c r="F414" s="1" t="inlineStr"/>
-      <c r="G414" s="1" t="inlineStr"/>
-      <c r="H414" s="1" t="inlineStr"/>
-      <c r="I414" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J414" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K414" s="1" t="inlineStr"/>
-      <c r="L414" s="1" t="inlineStr"/>
-      <c r="M414" s="1" t="inlineStr"/>
-      <c r="N414" s="1" t="inlineStr"/>
-      <c r="O414" s="1" t="inlineStr"/>
-      <c r="P414" s="1" t="inlineStr"/>
-      <c r="Q414" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R414" s="1" t="inlineStr">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Clementina</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Via della Torre Clementina, 158</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>328/8181651</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>{'giovedì': {'opens': '07', 'closes': '22'}, 'venerdì': {'opens': '07', 'closes'</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
@@ -25857,17 +25851,17 @@
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
         <is>
-          <t>Mrgda Ristorante</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>Via Prenestina, 182</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
         <is>
-          <t>329/933355</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="D415" s="1" t="inlineStr"/>
@@ -25898,49 +25892,55 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Clementina</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Via della Torre Clementina, 158</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>328/8181651</t>
-        </is>
-      </c>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J416" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M416" t="inlineStr">
-        <is>
-          <t>{'giovedì': {'opens': '07', 'closes': '22'}, 'venerdì': {'opens': '07', 'closes'</t>
-        </is>
-      </c>
-      <c r="Q416" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.2 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R416" t="inlineStr">
-        <is>
-          <t>16/07/2026</t>
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>Mrgda Ristorante</t>
+        </is>
+      </c>
+      <c r="B416" s="1" t="inlineStr">
+        <is>
+          <t>Via Prenestina, 182</t>
+        </is>
+      </c>
+      <c r="C416" s="1" t="inlineStr">
+        <is>
+          <t>329/933355</t>
+        </is>
+      </c>
+      <c r="D416" s="1" t="inlineStr"/>
+      <c r="E416" s="1" t="inlineStr"/>
+      <c r="F416" s="1" t="inlineStr"/>
+      <c r="G416" s="1" t="inlineStr"/>
+      <c r="H416" s="1" t="inlineStr"/>
+      <c r="I416" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J416" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K416" s="1" t="inlineStr"/>
+      <c r="L416" s="1" t="inlineStr"/>
+      <c r="M416" s="1" t="inlineStr"/>
+      <c r="N416" s="1" t="inlineStr"/>
+      <c r="O416" s="1" t="inlineStr"/>
+      <c r="P416" s="1" t="inlineStr"/>
+      <c r="Q416" s="1" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R416" s="1" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -25988,7 +25988,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -26080,7 +26080,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25892,7 +25892,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -25940,7 +25940,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -25988,7 +25988,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -26080,7 +26080,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25892,7 +25892,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -25940,7 +25940,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -25988,7 +25988,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -26080,7 +26080,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25892,7 +25892,7 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -25940,7 +25940,7 @@
       </c>
       <c r="R416" s="1" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -25988,7 +25988,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -26080,7 +26080,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25892,55 +25892,44 @@
       </c>
       <c r="R415" s="1" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="inlineStr">
+      <c r="A416" t="inlineStr">
         <is>
           <t>Mrgda Ristorante</t>
         </is>
       </c>
-      <c r="B416" s="1" t="inlineStr">
+      <c r="B416" t="inlineStr">
         <is>
           <t>Via Prenestina, 182</t>
         </is>
       </c>
-      <c r="C416" s="1" t="inlineStr">
+      <c r="C416" t="inlineStr">
         <is>
           <t>329/933355</t>
         </is>
       </c>
-      <c r="D416" s="1" t="inlineStr"/>
-      <c r="E416" s="1" t="inlineStr"/>
-      <c r="F416" s="1" t="inlineStr"/>
-      <c r="G416" s="1" t="inlineStr"/>
-      <c r="H416" s="1" t="inlineStr"/>
-      <c r="I416" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J416" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K416" s="1" t="inlineStr"/>
-      <c r="L416" s="1" t="inlineStr"/>
-      <c r="M416" s="1" t="inlineStr"/>
-      <c r="N416" s="1" t="inlineStr"/>
-      <c r="O416" s="1" t="inlineStr"/>
-      <c r="P416" s="1" t="inlineStr"/>
-      <c r="Q416" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R416" s="1" t="inlineStr">
-        <is>
-          <t>30/07/2026</t>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -25988,7 +25977,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -26036,7 +26025,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -26080,7 +26069,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -26124,7 +26113,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25849,48 +25849,37 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="inlineStr">
-        <is>
-          <t>Bless</t>
-        </is>
-      </c>
-      <c r="B415" s="1" t="inlineStr">
-        <is>
-          <t>Via dell’Indipendenza, 208</t>
-        </is>
-      </c>
-      <c r="C415" s="1" t="inlineStr">
-        <is>
-          <t>0771/030188</t>
-        </is>
-      </c>
-      <c r="D415" s="1" t="inlineStr"/>
-      <c r="E415" s="1" t="inlineStr"/>
-      <c r="F415" s="1" t="inlineStr"/>
-      <c r="G415" s="1" t="inlineStr"/>
-      <c r="H415" s="1" t="inlineStr"/>
-      <c r="I415" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J415" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K415" s="1" t="inlineStr"/>
-      <c r="L415" s="1" t="inlineStr"/>
-      <c r="M415" s="1" t="inlineStr"/>
-      <c r="N415" s="1" t="inlineStr"/>
-      <c r="O415" s="1" t="inlineStr"/>
-      <c r="P415" s="1" t="inlineStr"/>
-      <c r="Q415" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R415" s="1" t="inlineStr">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Mrgda Ristorante</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Via Prenestina, 182</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>329/933355</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
@@ -25899,17 +25888,17 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Mrgda Ristorante</t>
+          <t>Bless</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Via Prenestina, 182</t>
+          <t>Via dell’Indipendenza, 208</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>329/933355</t>
+          <t>0771/030188</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25929,7 +25918,7 @@
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -25977,7 +25966,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -26020,12 +26009,12 @@
       <c r="P418" s="1" t="inlineStr"/>
       <c r="Q418" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26058,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>
@@ -26113,7 +26102,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25966,7 +25966,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -26009,12 +26009,12 @@
       <c r="P418" s="1" t="inlineStr"/>
       <c r="Q418" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -26058,7 +26058,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25966,7 +25966,7 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -26014,7 +26014,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -26058,7 +26058,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25966,55 +25966,49 @@
       </c>
       <c r="R417" s="1" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="inlineStr">
+      <c r="A418" t="inlineStr">
         <is>
           <t>Il tuo fornaio</t>
         </is>
       </c>
-      <c r="B418" s="1" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>Via Francesco Sapori, 35</t>
         </is>
       </c>
-      <c r="C418" s="1" t="inlineStr">
+      <c r="C418" t="inlineStr">
         <is>
           <t>06/5017873</t>
         </is>
       </c>
-      <c r="D418" s="1" t="inlineStr"/>
-      <c r="E418" s="1" t="inlineStr"/>
-      <c r="F418" s="1" t="inlineStr"/>
-      <c r="G418" s="1" t="inlineStr"/>
-      <c r="H418" s="1" t="inlineStr"/>
-      <c r="I418" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J418" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K418" s="1" t="inlineStr"/>
-      <c r="L418" s="1" t="inlineStr"/>
-      <c r="M418" s="1" t="inlineStr"/>
-      <c r="N418" s="1" t="inlineStr"/>
-      <c r="O418" s="1" t="inlineStr"/>
-      <c r="P418" s="1" t="inlineStr"/>
-      <c r="Q418" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R418" s="1" t="inlineStr">
-        <is>
-          <t>13/08/2026</t>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '06:45', 'closes': '15'}, '</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -26058,7 +26052,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>
@@ -26102,7 +26096,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25923,92 +25923,92 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="inlineStr">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Il tuo fornaio</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Via Francesco Sapori, 35</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>06/5017873</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '06:45', 'closes': '15'}, '</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
         <is>
           <t>Da Antonio</t>
         </is>
       </c>
-      <c r="B417" s="1" t="inlineStr">
+      <c r="B418" s="1" t="inlineStr">
         <is>
           <t>Via Mario Lizzani, 21</t>
         </is>
       </c>
-      <c r="C417" s="1" t="inlineStr">
+      <c r="C418" s="1" t="inlineStr">
         <is>
           <t>391/7475549</t>
         </is>
       </c>
-      <c r="D417" s="1" t="inlineStr"/>
-      <c r="E417" s="1" t="inlineStr"/>
-      <c r="F417" s="1" t="inlineStr"/>
-      <c r="G417" s="1" t="inlineStr"/>
-      <c r="H417" s="1" t="inlineStr"/>
-      <c r="I417" s="1" t="inlineStr">
+      <c r="D418" s="1" t="inlineStr"/>
+      <c r="E418" s="1" t="inlineStr"/>
+      <c r="F418" s="1" t="inlineStr"/>
+      <c r="G418" s="1" t="inlineStr"/>
+      <c r="H418" s="1" t="inlineStr"/>
+      <c r="I418" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J417" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K417" s="1" t="inlineStr"/>
-      <c r="L417" s="1" t="inlineStr"/>
-      <c r="M417" s="1" t="inlineStr"/>
-      <c r="N417" s="1" t="inlineStr"/>
-      <c r="O417" s="1" t="inlineStr"/>
-      <c r="P417" s="1" t="inlineStr"/>
-      <c r="Q417" s="1" t="inlineStr">
+      <c r="J418" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K418" s="1" t="inlineStr"/>
+      <c r="L418" s="1" t="inlineStr"/>
+      <c r="M418" s="1" t="inlineStr"/>
+      <c r="N418" s="1" t="inlineStr"/>
+      <c r="O418" s="1" t="inlineStr"/>
+      <c r="P418" s="1" t="inlineStr"/>
+      <c r="Q418" s="1" t="inlineStr">
         <is>
           <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
-      <c r="R417" s="1" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Il tuo fornaio</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Via Francesco Sapori, 35</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>06/5017873</t>
-        </is>
-      </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J418" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="M418" t="inlineStr">
-        <is>
-          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '06:45', 'closes': '15'}, '</t>
-        </is>
-      </c>
-      <c r="Q418" t="inlineStr">
-        <is>
-          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R418" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
+      <c r="R418" s="1" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -26096,7 +26096,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26003,12 +26003,12 @@
       <c r="P418" s="1" t="inlineStr"/>
       <c r="Q418" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -26096,7 +26096,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26003,12 +26003,12 @@
       <c r="P418" s="1" t="inlineStr"/>
       <c r="Q418" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>
@@ -26096,7 +26096,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26008,7 +26008,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -26091,12 +26091,12 @@
       <c r="P420" s="1" t="inlineStr"/>
       <c r="Q420" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26008,7 +26008,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -26047,12 +26047,12 @@
       <c r="P419" s="1" t="inlineStr"/>
       <c r="Q419" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
@@ -26091,12 +26091,12 @@
       <c r="P420" s="1" t="inlineStr"/>
       <c r="Q420" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
     </row>
